--- a/ofsted_csc_ilacs_overview.xlsx
+++ b/ofsted_csc_ilacs_overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1429">
   <si>
     <t>80426</t>
   </si>
@@ -976,7 +976,7 @@
     <t>891, 933, 935, 926, 860, 878, 893, 929, 838, 885</t>
   </si>
   <si>
-    <t>[(891, 'good'), (933, 'good'), (935, 'requires improvement'), (926, 'outstanding'), (860, 'requires improvement'), (878, 'inadequate'), (893, 'outstanding'), (929, 'outstanding'), (838, 'outstanding'), (885, 'good')]</t>
+    <t>[(891, 'good'), (933, nan), (935, 'requires improvement'), (926, 'outstanding'), (860, 'requires improvement'), (878, 'inadequate'), (893, 'outstanding'), (929, 'outstanding'), (838, 'outstanding'), (885, 'good')]</t>
   </si>
   <si>
     <t>derbyshire</t>
@@ -1006,7 +1006,7 @@
     <t>845, 838, 926, 886, 933, 935, 938, 830, 881, 885</t>
   </si>
   <si>
-    <t>[(845, 'good'), (838, 'outstanding'), (926, 'outstanding'), (886, 'good'), (933, 'good'), (935, 'requires improvement'), (938, 'requires improvement'), (830, 'good'), (881, 'outstanding'), (885, 'good')]</t>
+    <t>[(845, 'good'), (838, 'outstanding'), (926, 'outstanding'), (886, 'good'), (933, nan), (935, 'requires improvement'), (938, 'requires improvement'), (830, 'good'), (881, 'outstanding'), (885, 'good')]</t>
   </si>
   <si>
     <t>devon</t>
@@ -1069,7 +1069,7 @@
     <t>933, 878, 893, 935, 885, 881, 830, 886, 938, 815</t>
   </si>
   <si>
-    <t>[(933, 'good'), (878, 'inadequate'), (893, 'outstanding'), (935, 'requires improvement'), (885, 'good'), (881, 'outstanding'), (830, 'good'), (886, 'good'), (938, 'requires improvement'), (815, 'outstanding')]</t>
+    <t>[(933, nan), (878, 'inadequate'), (893, 'outstanding'), (935, 'requires improvement'), (885, 'good'), (881, 'outstanding'), (830, 'good'), (886, 'good'), (938, 'requires improvement'), (815, 'outstanding')]</t>
   </si>
   <si>
     <t>dorset</t>
@@ -1153,7 +1153,7 @@
     <t>860, 893, 815, 877, 855, 933, 884, 943, 937, 830</t>
   </si>
   <si>
-    <t>[(860, 'requires improvement'), (893, 'outstanding'), (815, 'outstanding'), (877, 'good'), (855, 'outstanding'), (933, 'good'), (884, 'good'), (943, 'good'), (937, 'requires improvement'), (830, 'good')]</t>
+    <t>[(860, 'requires improvement'), (893, 'outstanding'), (815, 'outstanding'), (877, 'good'), (855, 'outstanding'), (933, nan), (884, 'good'), (943, 'good'), (937, 'requires improvement'), (830, 'good')]</t>
   </si>
   <si>
     <t>east riding of yorkshire</t>
@@ -1219,7 +1219,7 @@
     <t>886, 938, 916, 802, 935, 850, 937, 933, 303, 865</t>
   </si>
   <si>
-    <t>[(886, 'good'), (938, 'requires improvement'), (916, 'good'), (802, 'requires improvement'), (935, 'requires improvement'), (850, 'outstanding'), (937, 'requires improvement'), (933, 'good'), (303, 'outstanding'), (865, 'outstanding')]</t>
+    <t>[(886, 'good'), (938, 'requires improvement'), (916, 'good'), (802, 'requires improvement'), (935, 'requires improvement'), (850, 'outstanding'), (937, 'requires improvement'), (933, nan), (303, 'outstanding'), (865, 'outstanding')]</t>
   </si>
   <si>
     <t>essex</t>
@@ -1387,7 +1387,7 @@
     <t>943, 860, 925, 893, 933, 888, 935, 811, 815, 830</t>
   </si>
   <si>
-    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, 'good'), (888, 'good'), (935, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (830, 'good')]</t>
+    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, nan), (888, 'good'), (935, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (830, 'good')]</t>
   </si>
   <si>
     <t>herefordshire</t>
@@ -1468,7 +1468,7 @@
     <t>881, 845, 878, 303, 935, 926, 891, 938, 822, 933</t>
   </si>
   <si>
-    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, 'good')]</t>
+    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, nan)]</t>
   </si>
   <si>
     <t>kent</t>
@@ -1645,7 +1645,7 @@
     <t>821, 871, 304, 316, 333, 380, 307, 313, 330, 889</t>
   </si>
   <si>
-    <t>[(821, 'good'), (871, 'requires improvement'), (304, 'good'), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
+    <t>[(821, 'good'), (871, 'requires improvement'), (304, nan), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
   </si>
   <si>
     <t>leicester</t>
@@ -1666,7 +1666,7 @@
     <t>916, 803, 937, 802, 850, 865, 933, 938, 811, 891</t>
   </si>
   <si>
-    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, 'good'), (938, 'requires improvement'), (811, 'good'), (891, 'good')]</t>
+    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, nan), (938, 'requires improvement'), (811, 'good'), (891, 'good')]</t>
   </si>
   <si>
     <t>leicestershire</t>
@@ -1693,7 +1693,7 @@
     <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
   </si>
   <si>
-    <t>[(888, 'good'), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'requires improvement'), (940, 'requires improvement'), (830, 'good'), (933, 'good')]</t>
+    <t>[(888, 'good'), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'requires improvement'), (940, 'requires improvement'), (830, 'good'), (933, nan)]</t>
   </si>
   <si>
     <t>lincolnshire</t>
@@ -1753,7 +1753,7 @@
     <t>308, 821, 313, 333, 336, 307, 304, 312, 874, 203</t>
   </si>
   <si>
-    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, 'good'), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
+    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, nan), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
   </si>
   <si>
     <t>barking and dagenham</t>
@@ -1834,13 +1834,22 @@
     <t>brent</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50213625</t>
-  </si>
-  <si>
-    <t>24/02/2023</t>
-  </si>
-  <si>
-    <t>11/04/23</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50304386</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>monique lindsay</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>01/05/2026</t>
+  </si>
+  <si>
+    <t>17/06/26</t>
   </si>
   <si>
     <t>80490</t>
@@ -1936,7 +1945,7 @@
     <t>313, 317, 312, 320, 304, 309, 310, 871, 821, 302</t>
   </si>
   <si>
-    <t>[(313, 'good'), (317, 'outstanding'), (312, 'outstanding'), (320, 'good'), (304, 'good'), (309, 'outstanding'), (310, 'inadequate'), (871, 'requires improvement'), (821, 'good'), (302, 'good')]</t>
+    <t>[(313, 'good'), (317, 'outstanding'), (312, 'outstanding'), (320, 'good'), (304, nan), (309, 'outstanding'), (310, 'inadequate'), (871, 'requires improvement'), (821, 'good'), (302, 'good')]</t>
   </si>
   <si>
     <t>ealing</t>
@@ -2068,7 +2077,7 @@
     <t>320, 307, 209, 208, 302, 308, 210, 304, 313, 317</t>
   </si>
   <si>
-    <t>[(320, 'good'), (307, 'good'), (209, 'good'), (208, 'good'), (302, 'good'), (308, 'good'), (210, 'good'), (304, 'good'), (313, 'good'), (317, 'outstanding')]</t>
+    <t>[(320, 'good'), (307, 'good'), (209, 'good'), (208, 'good'), (302, 'good'), (308, 'good'), (210, 'good'), (304, nan), (313, 'good'), (317, 'outstanding')]</t>
   </si>
   <si>
     <t>haringey</t>
@@ -2179,7 +2188,7 @@
     <t>307, 312, 871, 317, 320, 821, 304, 310, 852, 301</t>
   </si>
   <si>
-    <t>[(307, 'good'), (312, 'outstanding'), (871, 'requires improvement'), (317, 'outstanding'), (320, 'good'), (821, 'good'), (304, 'good'), (310, 'inadequate'), (852, 'good'), (301, 'requires improvement')]</t>
+    <t>[(307, 'good'), (312, 'outstanding'), (871, 'requires improvement'), (317, 'outstanding'), (320, 'good'), (821, 'good'), (304, nan), (310, 'inadequate'), (852, 'good'), (301, 'requires improvement')]</t>
   </si>
   <si>
     <t>hounslow</t>
@@ -2308,7 +2317,7 @@
     <t>304, 301, 308, 856, 309, 821, 307, 313, 352, 871</t>
   </si>
   <si>
-    <t>[(304, 'good'), (301, 'requires improvement'), (308, 'good'), (856, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (307, 'good'), (313, 'good'), (352, 'outstanding'), (871, 'requires improvement')]</t>
+    <t>[(304, nan), (301, 'requires improvement'), (308, 'good'), (856, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (307, 'good'), (313, 'good'), (352, 'outstanding'), (871, 'requires improvement')]</t>
   </si>
   <si>
     <t>newham</t>
@@ -2422,7 +2431,7 @@
     <t>204, 206, 316, 352, 202, 309, 213, 210, 330, 304</t>
   </si>
   <si>
-    <t>[(204, 'good'), (206, 'outstanding'), (316, 'outstanding'), (352, 'outstanding'), (202, 'outstanding'), (309, 'outstanding'), (213, 'outstanding'), (210, 'good'), (330, 'good'), (304, 'good')]</t>
+    <t>[(204, 'good'), (206, 'outstanding'), (316, 'outstanding'), (352, 'outstanding'), (202, 'outstanding'), (309, 'outstanding'), (213, 'outstanding'), (210, 'good'), (330, 'good'), (304, nan)]</t>
   </si>
   <si>
     <t>tower hamlets</t>
@@ -2485,9 +2494,6 @@
     <t>https://files.ofsted.gov.uk/v1/file/50301929</t>
   </si>
   <si>
-    <t>monique lindsay</t>
-  </si>
-  <si>
     <t>06/03/2026</t>
   </si>
   <si>
@@ -2575,9 +2581,6 @@
     <t>887</t>
   </si>
   <si>
-    <t>nan</t>
-  </si>
-  <si>
     <t>E06000035</t>
   </si>
   <si>
@@ -2695,7 +2698,7 @@
     <t>935, 908, 878, 830, 929, 886, 933, 925, 891, 887</t>
   </si>
   <si>
-    <t>[(935, 'requires improvement'), (908, 'good'), (878, 'inadequate'), (830, 'good'), (929, 'outstanding'), (886, 'good'), (933, 'good'), (925, 'outstanding'), (891, 'good'), (887, 'good')]</t>
+    <t>[(935, 'requires improvement'), (908, 'good'), (878, 'inadequate'), (830, 'good'), (929, 'outstanding'), (886, 'good'), (933, nan), (925, 'outstanding'), (891, 'good'), (887, 'good')]</t>
   </si>
   <si>
     <t>norfolk</t>
@@ -2782,7 +2785,7 @@
     <t>866, 941, 935, 925, 933, 883, 891, 813, 887, 384</t>
   </si>
   <si>
-    <t>[(866, 'inadequate'), (941, 'requires improvement'), (935, 'requires improvement'), (925, 'outstanding'), (933, 'good'), (883, 'outstanding'), (891, 'good'), (813, 'outstanding'), (887, 'good'), (384, 'good')]</t>
+    <t>[(866, 'inadequate'), (941, 'requires improvement'), (935, 'requires improvement'), (925, 'outstanding'), (933, nan), (883, 'outstanding'), (891, 'good'), (813, 'outstanding'), (887, 'good'), (384, 'good')]</t>
   </si>
   <si>
     <t>north northamptonshire</t>
@@ -2857,7 +2860,7 @@
     <t>893, 895, 811, 860, 916, 877, 937, 884, 865, 933</t>
   </si>
   <si>
-    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'good'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, 'good')]</t>
+    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'good'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, nan)]</t>
   </si>
   <si>
     <t>north yorkshire</t>
@@ -2941,7 +2944,7 @@
     <t>830, 935, 933, 886, 926, 937, 855, 802, 860, 888</t>
   </si>
   <si>
-    <t>[(830, 'good'), (935, 'requires improvement'), (933, 'good'), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, 'good')]</t>
+    <t>[(830, 'good'), (935, 'requires improvement'), (933, nan), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, 'good')]</t>
   </si>
   <si>
     <t>nottinghamshire</t>
@@ -3400,7 +3403,7 @@
     <t>815, 933, 860, 811, 838, 884, 830, 885, 943, 916</t>
   </si>
   <si>
-    <t>[(815, 'outstanding'), (933, 'good'), (860, 'requires improvement'), (811, 'good'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
+    <t>[(815, 'outstanding'), (933, nan), (860, 'requires improvement'), (811, 'good'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
   </si>
   <si>
     <t>shropshire</t>
@@ -3421,7 +3424,7 @@
     <t>313, 312, 821, 307, 317, 310, 304, 874, 320, 856</t>
   </si>
   <si>
-    <t>[(313, 'good'), (312, 'outstanding'), (821, 'good'), (307, 'good'), (317, 'outstanding'), (310, 'inadequate'), (304, 'good'), (874, 'inadequate'), (320, 'good'), (856, 'requires improvement')]</t>
+    <t>[(313, 'good'), (312, 'outstanding'), (821, 'good'), (307, 'good'), (317, 'outstanding'), (310, 'inadequate'), (304, nan), (874, 'inadequate'), (320, 'good'), (856, 'requires improvement')]</t>
   </si>
   <si>
     <t>slough</t>
@@ -3472,16 +3475,7 @@
     <t>somerset</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50192873</t>
-  </si>
-  <si>
-    <t>18/07/2022</t>
-  </si>
-  <si>
-    <t>29/07/2022</t>
-  </si>
-  <si>
-    <t>21/09/22</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50304387</t>
   </si>
   <si>
     <t>80556</t>
@@ -3613,7 +3607,7 @@
     <t>811, 884, 893, 815, 933, 830, 877, 891, 943, 888</t>
   </si>
   <si>
-    <t>[(811, 'good'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, 'good'), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, 'good')]</t>
+    <t>[(811, 'good'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, nan), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, 'good')]</t>
   </si>
   <si>
     <t>staffordshire</t>
@@ -3712,7 +3706,7 @@
     <t>933, 926, 830, 891, 878, 881, 886, 838, 925, 940</t>
   </si>
   <si>
-    <t>[(933, 'good'), (926, 'outstanding'), (830, 'good'), (891, 'good'), (878, 'inadequate'), (881, 'outstanding'), (886, 'good'), (838, 'outstanding'), (925, 'outstanding'), (940, 'requires improvement')]</t>
+    <t>[(933, nan), (926, 'outstanding'), (830, 'good'), (891, 'good'), (878, 'inadequate'), (881, 'outstanding'), (886, 'good'), (838, 'outstanding'), (925, 'outstanding'), (940, 'requires improvement')]</t>
   </si>
   <si>
     <t>suffolk</t>
@@ -4036,7 +4030,7 @@
     <t>822, 940, 937, 866, 933, 935, 311, 855, 931, 303</t>
   </si>
   <si>
-    <t>[(822, 'requires improvement'), (940, 'requires improvement'), (937, 'requires improvement'), (866, 'inadequate'), (933, 'good'), (935, 'requires improvement'), (311, 'inadequate'), (855, 'outstanding'), (931, 'good'), (303, 'outstanding')]</t>
+    <t>[(822, 'requires improvement'), (940, 'requires improvement'), (937, 'requires improvement'), (866, 'inadequate'), (933, nan), (935, 'requires improvement'), (311, 'inadequate'), (855, 'outstanding'), (931, 'good'), (303, 'outstanding')]</t>
   </si>
   <si>
     <t>west northamptonshire</t>
@@ -4078,7 +4072,7 @@
     <t>884, 942, 860, 893, 811, 815, 925, 933, 935, 830</t>
   </si>
   <si>
-    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'good'), (815, 'outstanding'), (925, 'outstanding'), (933, 'good'), (935, 'requires improvement'), (830, 'good')]</t>
+    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'good'), (815, 'outstanding'), (925, 'outstanding'), (933, nan), (935, 'requires improvement'), (830, 'good')]</t>
   </si>
   <si>
     <t>westmorland and furness</t>
@@ -4213,16 +4207,13 @@
     <t>wolverhampton</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50183766</t>
-  </si>
-  <si>
-    <t>28/03/2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>18/05/22</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50304388</t>
+  </si>
+  <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
+    <t>18/06/26</t>
   </si>
   <si>
     <t>80584</t>
@@ -4237,7 +4228,7 @@
     <t>933, 916, 838, 937, 893, 938, 878, 830, 881, 815</t>
   </si>
   <si>
-    <t>[(933, 'good'), (916, 'good'), (838, 'outstanding'), (937, 'requires improvement'), (893, 'outstanding'), (938, 'requires improvement'), (878, 'inadequate'), (830, 'good'), (881, 'outstanding'), (815, 'outstanding')]</t>
+    <t>[(933, nan), (916, 'good'), (838, 'outstanding'), (937, 'requires improvement'), (893, 'outstanding'), (938, 'requires improvement'), (878, 'inadequate'), (830, 'good'), (881, 'outstanding'), (815, 'outstanding')]</t>
   </si>
   <si>
     <t>worcestershire</t>
@@ -4677,64 +4668,64 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>1430</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -5862,7 +5853,7 @@
         <v>14</v>
       </c>
       <c r="T19" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -7059,7 +7050,7 @@
         <v>105</v>
       </c>
       <c r="T38" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -7311,7 +7302,7 @@
         <v>8</v>
       </c>
       <c r="T42" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -8411,22 +8402,22 @@
         <v>606</v>
       </c>
       <c r="I60" t="s">
-        <v>8</v>
+        <v>607</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>404</v>
+        <v>608</v>
       </c>
       <c r="L60" t="s">
-        <v>50</v>
+        <v>609</v>
       </c>
       <c r="M60" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="N60" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="O60" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80489_brent", ".\export_data\inspection_reports\80489_brent")</f>
@@ -8445,33 +8436,33 @@
         <v>8</v>
       </c>
       <c r="T60" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B61" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C61" t="s">
         <v>219</v>
       </c>
       <c r="D61" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E61" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F61" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G61" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="I61" t="s">
         <v>105</v>
@@ -8480,13 +8471,13 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L61" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M61" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N61" t="s">
         <v>325</v>
@@ -8513,28 +8504,28 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B62" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C62" t="s">
         <v>219</v>
       </c>
       <c r="D62" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E62" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F62" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="G62" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="I62" t="s">
         <v>105</v>
@@ -8543,7 +8534,7 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L62" t="s">
         <v>63</v>
@@ -8576,28 +8567,28 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B63" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C63" t="s">
         <v>219</v>
       </c>
       <c r="D63" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E63" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F63" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="G63" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="I63" t="s">
         <v>8</v>
@@ -8609,13 +8600,13 @@
         <v>225</v>
       </c>
       <c r="L63" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M63" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N63" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O63" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80492_croydon", ".\export_data\inspection_reports\80492_croydon")</f>
@@ -8639,28 +8630,28 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B64" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C64" t="s">
         <v>219</v>
       </c>
       <c r="D64" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E64" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F64" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="G64" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="I64" t="s">
         <v>8</v>
@@ -8702,28 +8693,28 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B65" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C65" t="s">
         <v>219</v>
       </c>
       <c r="D65" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E65" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F65" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="G65" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I65" t="s">
         <v>8</v>
@@ -8735,13 +8726,13 @@
         <v>225</v>
       </c>
       <c r="L65" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="M65" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="N65" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="O65" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80494_enfield", ".\export_data\inspection_reports\80494_enfield")</f>
@@ -8765,28 +8756,28 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B66" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C66" t="s">
         <v>219</v>
       </c>
       <c r="D66" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E66" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F66" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G66" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="I66" t="s">
         <v>105</v>
@@ -8798,13 +8789,13 @@
         <v>393</v>
       </c>
       <c r="L66" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M66" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="N66" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="O66" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80495_greenwich", ".\export_data\inspection_reports\80495_greenwich")</f>
@@ -8828,28 +8819,28 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B67" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C67" t="s">
         <v>219</v>
       </c>
       <c r="D67" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E67" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F67" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G67" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I67" t="s">
         <v>8</v>
@@ -8864,10 +8855,10 @@
         <v>259</v>
       </c>
       <c r="M67" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="N67" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="O67" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80496_hackney", ".\export_data\inspection_reports\80496_hackney")</f>
@@ -8891,28 +8882,28 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B68" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C68" t="s">
         <v>219</v>
       </c>
       <c r="D68" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E68" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F68" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G68" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I68" t="s">
         <v>105</v>
@@ -8924,7 +8915,7 @@
         <v>225</v>
       </c>
       <c r="L68" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M68" t="s">
         <v>172</v>
@@ -8954,28 +8945,28 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B69" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C69" t="s">
         <v>219</v>
       </c>
       <c r="D69" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E69" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="F69" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="G69" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="I69" t="s">
         <v>105</v>
@@ -8990,10 +8981,10 @@
         <v>214</v>
       </c>
       <c r="M69" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="N69" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="O69" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80498_haringey", ".\export_data\inspection_reports\80498_haringey")</f>
@@ -9017,28 +9008,28 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B70" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C70" t="s">
         <v>219</v>
       </c>
       <c r="D70" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E70" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F70" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="G70" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="I70" t="s">
         <v>190</v>
@@ -9053,10 +9044,10 @@
         <v>344</v>
       </c>
       <c r="M70" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="N70" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="O70" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80499_harrow", ".\export_data\inspection_reports\80499_harrow")</f>
@@ -9080,28 +9071,28 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B71" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C71" t="s">
         <v>219</v>
       </c>
       <c r="D71" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E71" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F71" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G71" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="I71" t="s">
         <v>190</v>
@@ -9110,16 +9101,16 @@
         <v>48</v>
       </c>
       <c r="K71" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L71" t="s">
         <v>394</v>
       </c>
       <c r="M71" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="N71" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="O71" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80500_havering", ".\export_data\inspection_reports\80500_havering")</f>
@@ -9143,28 +9134,28 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B72" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C72" t="s">
         <v>219</v>
       </c>
       <c r="D72" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E72" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F72" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="G72" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="I72" t="s">
         <v>105</v>
@@ -9176,13 +9167,13 @@
         <v>225</v>
       </c>
       <c r="L72" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="M72" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="N72" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="O72" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80501_hillingdon", ".\export_data\inspection_reports\80501_hillingdon")</f>
@@ -9206,28 +9197,28 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B73" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C73" t="s">
         <v>219</v>
       </c>
       <c r="D73" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E73" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="F73" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="G73" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="I73" t="s">
         <v>8</v>
@@ -9239,13 +9230,13 @@
         <v>139</v>
       </c>
       <c r="L73" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="M73" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="N73" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="O73" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80503_hounslow", ".\export_data\inspection_reports\80503_hounslow")</f>
@@ -9269,28 +9260,28 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B74" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C74" t="s">
         <v>219</v>
       </c>
       <c r="D74" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E74" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F74" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="G74" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="I74" t="s">
         <v>105</v>
@@ -9332,28 +9323,28 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B75" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C75" t="s">
         <v>219</v>
       </c>
       <c r="D75" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E75" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F75" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G75" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="I75" t="s">
         <v>8</v>
@@ -9362,7 +9353,7 @@
         <v>48</v>
       </c>
       <c r="K75" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L75" t="s">
         <v>214</v>
@@ -9371,7 +9362,7 @@
         <v>215</v>
       </c>
       <c r="N75" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="O75" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80506_lambeth", ".\export_data\inspection_reports\80506_lambeth")</f>
@@ -9395,28 +9386,28 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B76" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C76" t="s">
         <v>219</v>
       </c>
       <c r="D76" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E76" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F76" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G76" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="I76" t="s">
         <v>8</v>
@@ -9425,16 +9416,16 @@
         <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="L76" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="M76" t="s">
         <v>395</v>
       </c>
       <c r="N76" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="O76" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80508_lewisham", ".\export_data\inspection_reports\80508_lewisham")</f>
@@ -9458,28 +9449,28 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B77" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C77" t="s">
         <v>219</v>
       </c>
       <c r="D77" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E77" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F77" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="G77" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="I77" t="s">
         <v>105</v>
@@ -9488,7 +9479,7 @@
         <v>9</v>
       </c>
       <c r="K77" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L77" t="s">
         <v>37</v>
@@ -9521,28 +9512,28 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B78" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C78" t="s">
         <v>219</v>
       </c>
       <c r="D78" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E78" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="F78" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="G78" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="I78" t="s">
         <v>105</v>
@@ -9557,7 +9548,7 @@
         <v>460</v>
       </c>
       <c r="M78" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="N78" t="s">
         <v>462</v>
@@ -9584,28 +9575,28 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B79" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C79" t="s">
         <v>219</v>
       </c>
       <c r="D79" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E79" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="F79" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="G79" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="I79" t="s">
         <v>105</v>
@@ -9614,7 +9605,7 @@
         <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="L79" t="s">
         <v>441</v>
@@ -9647,28 +9638,28 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B80" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C80" t="s">
         <v>219</v>
       </c>
       <c r="D80" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E80" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F80" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G80" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="I80" t="s">
         <v>105</v>
@@ -9710,28 +9701,28 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B81" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C81" t="s">
         <v>219</v>
       </c>
       <c r="D81" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E81" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="F81" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="G81" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="I81" t="s">
         <v>8</v>
@@ -9740,7 +9731,7 @@
         <v>9</v>
       </c>
       <c r="K81" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L81" t="s">
         <v>280</v>
@@ -9773,28 +9764,28 @@
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B82" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C82" t="s">
         <v>219</v>
       </c>
       <c r="D82" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E82" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F82" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="G82" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="I82" t="s">
         <v>8</v>
@@ -9806,7 +9797,7 @@
         <v>62</v>
       </c>
       <c r="L82" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="M82" t="s">
         <v>152</v>
@@ -9836,28 +9827,28 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B83" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C83" t="s">
         <v>219</v>
       </c>
       <c r="D83" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E83" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="F83" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="G83" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="I83" t="s">
         <v>105</v>
@@ -9869,13 +9860,13 @@
         <v>24</v>
       </c>
       <c r="L83" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M83" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="N83" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="O83" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80516_tower hamlets", ".\export_data\inspection_reports\80516_tower hamlets")</f>
@@ -9899,28 +9890,28 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B84" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C84" t="s">
         <v>219</v>
       </c>
       <c r="D84" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E84" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="F84" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G84" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="I84" t="s">
         <v>8</v>
@@ -9929,16 +9920,16 @@
         <v>9</v>
       </c>
       <c r="K84" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="L84" t="s">
         <v>507</v>
       </c>
       <c r="M84" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="N84" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="O84" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80517_waltham forest", ".\export_data\inspection_reports\80517_waltham forest")</f>
@@ -9962,28 +9953,28 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B85" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C85" t="s">
         <v>219</v>
       </c>
       <c r="D85" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E85" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="F85" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="G85" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I85" t="s">
         <v>105</v>
@@ -9992,13 +9983,13 @@
         <v>9</v>
       </c>
       <c r="K85" t="s">
-        <v>823</v>
+        <v>608</v>
       </c>
       <c r="L85" t="s">
         <v>498</v>
       </c>
       <c r="M85" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N85" t="s">
         <v>282</v>
@@ -10020,33 +10011,33 @@
         <v>105</v>
       </c>
       <c r="T85" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B86" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C86" t="s">
         <v>219</v>
       </c>
       <c r="D86" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E86" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F86" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G86" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="I86" t="s">
         <v>105</v>
@@ -10058,13 +10049,13 @@
         <v>106</v>
       </c>
       <c r="L86" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M86" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="N86" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="O86" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80519_westminster", ".\export_data\inspection_reports\80519_westminster")</f>
@@ -10088,28 +10079,28 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B87" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C87" t="s">
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E87" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F87" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="G87" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="I87" t="s">
         <v>8</v>
@@ -10121,13 +10112,13 @@
         <v>151</v>
       </c>
       <c r="L87" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M87" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N87" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="O87" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80520_luton", ".\export_data\inspection_reports\80520_luton")</f>
@@ -10151,28 +10142,28 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B88" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C88" t="s">
         <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E88" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F88" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G88" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="I88" t="s">
         <v>105</v>
@@ -10184,13 +10175,13 @@
         <v>279</v>
       </c>
       <c r="L88" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="M88" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="N88" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="O88" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80521_manchester", ".\export_data\inspection_reports\80521_manchester")</f>
@@ -10214,28 +10205,28 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B89" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C89" t="s">
-        <v>853</v>
+        <v>607</v>
       </c>
       <c r="D89" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E89" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F89" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G89" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I89" t="s">
         <v>8</v>
@@ -10247,13 +10238,13 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M89" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N89" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O89" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80522_medway", ".\export_data\inspection_reports\80522_medway")</f>
@@ -10277,28 +10268,28 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B90" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C90" t="s">
         <v>295</v>
       </c>
       <c r="D90" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E90" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F90" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G90" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="I90" t="s">
         <v>14</v>
@@ -10340,28 +10331,28 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B91" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C91" t="s">
         <v>99</v>
       </c>
       <c r="D91" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E91" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F91" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G91" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="I91" t="s">
         <v>8</v>
@@ -10370,16 +10361,16 @@
         <v>48</v>
       </c>
       <c r="K91" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="L91" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M91" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N91" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="O91" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80524_milton keynes", ".\export_data\inspection_reports\80524_milton keynes")</f>
@@ -10403,28 +10394,28 @@
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B92" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C92" t="s">
         <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E92" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F92" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G92" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="I92" t="s">
         <v>8</v>
@@ -10436,13 +10427,13 @@
         <v>247</v>
       </c>
       <c r="L92" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M92" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N92" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="O92" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80525_newcastle upon tyne", ".\export_data\inspection_reports\80525_newcastle upon tyne")</f>
@@ -10466,28 +10457,28 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B93" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E93" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F93" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G93" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I93" t="s">
         <v>105</v>
@@ -10496,13 +10487,13 @@
         <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L93" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M93" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="N93" t="s">
         <v>282</v>
@@ -10529,28 +10520,28 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B94" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E94" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F94" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G94" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="I94" t="s">
         <v>8</v>
@@ -10565,10 +10556,10 @@
         <v>37</v>
       </c>
       <c r="M94" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N94" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="O94" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80526_north east lincolnshire", ".\export_data\inspection_reports\80526_north east lincolnshire")</f>
@@ -10592,28 +10583,28 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B95" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C95" t="s">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E95" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F95" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G95" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I95" t="s">
         <v>105</v>
@@ -10625,13 +10616,13 @@
         <v>506</v>
       </c>
       <c r="L95" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M95" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="N95" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="O95" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80527_north lincolnshire", ".\export_data\inspection_reports\80527_north lincolnshire")</f>
@@ -10655,28 +10646,28 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B96" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C96" t="s">
         <v>306</v>
       </c>
       <c r="D96" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E96" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F96" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G96" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="I96" t="s">
         <v>14</v>
@@ -10688,13 +10679,13 @@
         <v>202</v>
       </c>
       <c r="L96" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M96" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N96" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="O96" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2637539_north northamptonshire", ".\export_data\inspection_reports\2637539_north northamptonshire")</f>
@@ -10713,33 +10704,33 @@
         <v>77</v>
       </c>
       <c r="T96" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B97" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E97" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F97" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G97" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="I97" t="s">
         <v>14</v>
@@ -10757,7 +10748,7 @@
         <v>573</v>
       </c>
       <c r="N97" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O97" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80528_north somerset", ".\export_data\inspection_reports\80528_north somerset")</f>
@@ -10781,28 +10772,28 @@
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B98" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C98" t="s">
         <v>295</v>
       </c>
       <c r="D98" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E98" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F98" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G98" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="I98" t="s">
         <v>105</v>
@@ -10814,13 +10805,13 @@
         <v>374</v>
       </c>
       <c r="L98" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M98" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="N98" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="O98" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80529_north tyneside", ".\export_data\inspection_reports\80529_north tyneside")</f>
@@ -10844,28 +10835,28 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B99" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C99" t="s">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E99" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F99" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G99" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I99" t="s">
         <v>105</v>
@@ -10874,16 +10865,16 @@
         <v>9</v>
       </c>
       <c r="K99" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L99" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M99" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N99" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="O99" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80530_north yorkshire", ".\export_data\inspection_reports\80530_north yorkshire")</f>
@@ -10907,28 +10898,28 @@
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B100" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C100" t="s">
         <v>295</v>
       </c>
       <c r="D100" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E100" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F100" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G100" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="I100" t="s">
         <v>105</v>
@@ -10937,10 +10928,10 @@
         <v>9</v>
       </c>
       <c r="K100" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L100" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M100" t="s">
         <v>432</v>
@@ -10965,33 +10956,33 @@
         <v>8</v>
       </c>
       <c r="T100" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B101" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C101" t="s">
         <v>306</v>
       </c>
       <c r="D101" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E101" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F101" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G101" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="I101" t="s">
         <v>190</v>
@@ -11000,10 +10991,10 @@
         <v>117</v>
       </c>
       <c r="K101" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="N101" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O101" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80533_nottingham", ".\export_data\inspection_reports\80533_nottingham")</f>
@@ -11022,33 +11013,33 @@
         <v>190</v>
       </c>
       <c r="T101" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B102" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C102" t="s">
         <v>306</v>
       </c>
       <c r="D102" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E102" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F102" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G102" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I102" t="s">
         <v>8</v>
@@ -11057,10 +11048,10 @@
         <v>9</v>
       </c>
       <c r="K102" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="L102" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M102" t="s">
         <v>432</v>
@@ -11090,28 +11081,28 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B103" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C103" t="s">
         <v>56</v>
       </c>
       <c r="D103" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E103" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F103" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G103" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I103" t="s">
         <v>8</v>
@@ -11153,28 +11144,28 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B104" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C104" t="s">
         <v>99</v>
       </c>
       <c r="D104" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E104" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F104" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G104" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="I104" t="s">
         <v>8</v>
@@ -11183,16 +11174,16 @@
         <v>48</v>
       </c>
       <c r="K104" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="L104" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M104" t="s">
         <v>162</v>
       </c>
       <c r="N104" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="O104" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80536_oxfordshire", ".\export_data\inspection_reports\80536_oxfordshire")</f>
@@ -11216,28 +11207,28 @@
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B105" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E105" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F105" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G105" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I105" t="s">
         <v>190</v>
@@ -11246,16 +11237,16 @@
         <v>48</v>
       </c>
       <c r="K105" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L105" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M105" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="N105" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="O105" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80537_peterborough", ".\export_data\inspection_reports\80537_peterborough")</f>
@@ -11279,28 +11270,28 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B106" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E106" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F106" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G106" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="I106" t="s">
         <v>14</v>
@@ -11312,13 +11303,13 @@
         <v>128</v>
       </c>
       <c r="L106" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M106" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N106" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="O106" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80538_plymouth", ".\export_data\inspection_reports\80538_plymouth")</f>
@@ -11342,28 +11333,28 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B107" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C107" t="s">
         <v>99</v>
       </c>
       <c r="D107" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F107" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G107" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="I107" t="s">
         <v>8</v>
@@ -11375,13 +11366,13 @@
         <v>225</v>
       </c>
       <c r="L107" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M107" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N107" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O107" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80539_portsmouth", ".\export_data\inspection_reports\80539_portsmouth")</f>
@@ -11405,28 +11396,28 @@
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B108" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C108" t="s">
         <v>99</v>
       </c>
       <c r="D108" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E108" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F108" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G108" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="I108" t="s">
         <v>14</v>
@@ -11468,28 +11459,28 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B109" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C109" t="s">
         <v>295</v>
       </c>
       <c r="D109" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E109" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F109" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G109" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -11501,7 +11492,7 @@
         <v>247</v>
       </c>
       <c r="L109" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M109" t="s">
         <v>108</v>
@@ -11531,28 +11522,28 @@
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B110" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C110" t="s">
         <v>56</v>
       </c>
       <c r="D110" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E110" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F110" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="I110" t="s">
         <v>14</v>
@@ -11567,10 +11558,10 @@
         <v>470</v>
       </c>
       <c r="M110" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N110" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O110" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80542_rochdale", ".\export_data\inspection_reports\80542_rochdale")</f>
@@ -11594,28 +11585,28 @@
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B111" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C111" t="s">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E111" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F111" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G111" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I111" t="s">
         <v>105</v>
@@ -11633,7 +11624,7 @@
         <v>489</v>
       </c>
       <c r="N111" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="O111" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80543_rotherham", ".\export_data\inspection_reports\80543_rotherham")</f>
@@ -11657,28 +11648,28 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B112" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C112" t="s">
         <v>219</v>
       </c>
       <c r="D112" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E112" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F112" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G112" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="I112" t="s">
         <v>105</v>
@@ -11690,13 +11681,13 @@
         <v>139</v>
       </c>
       <c r="L112" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="M112" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="N112" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="O112" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80544_kensington and chelsea", ".\export_data\inspection_reports\80544_kensington and chelsea")</f>
@@ -11720,28 +11711,28 @@
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B113" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C113" t="s">
         <v>219</v>
       </c>
       <c r="D113" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E113" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F113" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G113" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="I113" t="s">
         <v>105</v>
@@ -11750,7 +11741,7 @@
         <v>9</v>
       </c>
       <c r="K113" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="L113" t="s">
         <v>94</v>
@@ -11783,28 +11774,28 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B114" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C114" t="s">
         <v>99</v>
       </c>
       <c r="D114" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E114" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F114" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G114" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="I114" t="s">
         <v>8</v>
@@ -11813,7 +11804,7 @@
         <v>9</v>
       </c>
       <c r="K114" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L114" t="s">
         <v>290</v>
@@ -11822,7 +11813,7 @@
         <v>334</v>
       </c>
       <c r="N114" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O114" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80546_windsor &amp; maidenhead", ".\export_data\inspection_reports\80546_windsor &amp; maidenhead")</f>
@@ -11846,28 +11837,28 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B115" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C115" t="s">
         <v>306</v>
       </c>
       <c r="D115" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E115" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F115" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G115" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -11879,10 +11870,10 @@
         <v>506</v>
       </c>
       <c r="L115" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="M115" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N115" t="s">
         <v>433</v>
@@ -11909,28 +11900,28 @@
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B116" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C116" t="s">
         <v>56</v>
       </c>
       <c r="D116" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E116" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F116" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G116" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I116" t="s">
         <v>8</v>
@@ -11939,10 +11930,10 @@
         <v>9</v>
       </c>
       <c r="K116" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="L116" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="M116" t="s">
         <v>324</v>
@@ -11972,28 +11963,28 @@
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B117" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C117" t="s">
         <v>42</v>
       </c>
       <c r="D117" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E117" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F117" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G117" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="I117" t="s">
         <v>8</v>
@@ -12002,16 +11993,16 @@
         <v>48</v>
       </c>
       <c r="K117" t="s">
-        <v>823</v>
+        <v>608</v>
       </c>
       <c r="L117" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="M117" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N117" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="O117" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80549_sandwell", ".\export_data\inspection_reports\80549_sandwell")</f>
@@ -12030,33 +12021,33 @@
         <v>14</v>
       </c>
       <c r="T117" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B118" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C118" t="s">
         <v>56</v>
       </c>
       <c r="D118" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E118" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F118" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G118" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="I118" t="s">
         <v>8</v>
@@ -12068,7 +12059,7 @@
         <v>86</v>
       </c>
       <c r="L118" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M118" t="s">
         <v>537</v>
@@ -12098,28 +12089,28 @@
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B119" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C119" t="s">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E119" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F119" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G119" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="I119" t="s">
         <v>8</v>
@@ -12134,10 +12125,10 @@
         <v>11</v>
       </c>
       <c r="M119" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="N119" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="O119" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80551_sheffield", ".\export_data\inspection_reports\80551_sheffield")</f>
@@ -12161,28 +12152,28 @@
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B120" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C120" t="s">
         <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E120" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F120" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G120" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="I120" t="s">
         <v>105</v>
@@ -12191,10 +12182,10 @@
         <v>48</v>
       </c>
       <c r="K120" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L120" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M120" t="s">
         <v>537</v>
@@ -12224,28 +12215,28 @@
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B121" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C121" t="s">
         <v>99</v>
       </c>
       <c r="D121" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E121" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F121" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G121" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="I121" t="s">
         <v>14</v>
@@ -12260,10 +12251,10 @@
         <v>470</v>
       </c>
       <c r="M121" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N121" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O121" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80553_slough", ".\export_data\inspection_reports\80553_slough")</f>
@@ -12287,28 +12278,28 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B122" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C122" t="s">
         <v>42</v>
       </c>
       <c r="D122" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E122" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F122" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G122" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="I122" t="s">
         <v>8</v>
@@ -12317,13 +12308,13 @@
         <v>48</v>
       </c>
       <c r="K122" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="L122" t="s">
         <v>488</v>
       </c>
       <c r="M122" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="N122" t="s">
         <v>462</v>
@@ -12350,91 +12341,91 @@
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B123" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E123" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F123" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="G123" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I123" t="s">
-        <v>8</v>
+        <v>607</v>
       </c>
       <c r="J123" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="K123" t="s">
-        <v>404</v>
+        <v>202</v>
       </c>
       <c r="L123" t="s">
-        <v>1153</v>
+        <v>609</v>
       </c>
       <c r="M123" t="s">
-        <v>1154</v>
+        <v>610</v>
       </c>
       <c r="N123" t="s">
-        <v>1155</v>
+        <v>611</v>
       </c>
       <c r="O123" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80555_somerset", ".\export_data\inspection_reports\80555_somerset")</f>
         <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q123" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R123" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S123" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="T123" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B124" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
       </c>
       <c r="D124" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F124" t="s">
         <v>1158</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>1159</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" s="2" t="s">
         <v>1160</v>
-      </c>
-      <c r="G124" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>1162</v>
       </c>
       <c r="I124" t="s">
         <v>8</v>
@@ -12446,7 +12437,7 @@
         <v>10</v>
       </c>
       <c r="L124" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M124" t="s">
         <v>442</v>
@@ -12476,28 +12467,28 @@
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B125" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C125" t="s">
         <v>295</v>
       </c>
       <c r="D125" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F125" t="s">
         <v>1165</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>1166</v>
       </c>
-      <c r="F125" t="s">
+      <c r="H125" s="2" t="s">
         <v>1167</v>
-      </c>
-      <c r="G125" t="s">
-        <v>1168</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>1169</v>
       </c>
       <c r="I125" t="s">
         <v>190</v>
@@ -12515,7 +12506,7 @@
         <v>527</v>
       </c>
       <c r="N125" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="O125" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80557_south tyneside", ".\export_data\inspection_reports\80557_south tyneside")</f>
@@ -12539,28 +12530,28 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B126" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C126" t="s">
         <v>99</v>
       </c>
       <c r="D126" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F126" t="s">
         <v>1173</v>
       </c>
-      <c r="E126" t="s">
+      <c r="G126" t="s">
         <v>1174</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H126" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="G126" t="s">
-        <v>1176</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>1177</v>
       </c>
       <c r="I126" t="s">
         <v>8</v>
@@ -12572,13 +12563,13 @@
         <v>393</v>
       </c>
       <c r="L126" t="s">
+        <v>1176</v>
+      </c>
+      <c r="M126" t="s">
+        <v>1177</v>
+      </c>
+      <c r="N126" t="s">
         <v>1178</v>
-      </c>
-      <c r="M126" t="s">
-        <v>1179</v>
-      </c>
-      <c r="N126" t="s">
-        <v>1180</v>
       </c>
       <c r="O126" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80558_southampton", ".\export_data\inspection_reports\80558_southampton")</f>
@@ -12602,28 +12593,28 @@
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B127" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C127" t="s">
         <v>31</v>
       </c>
       <c r="D127" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F127" t="s">
         <v>1183</v>
       </c>
-      <c r="E127" t="s">
+      <c r="G127" t="s">
         <v>1184</v>
       </c>
-      <c r="F127" t="s">
+      <c r="H127" s="2" t="s">
         <v>1185</v>
-      </c>
-      <c r="G127" t="s">
-        <v>1186</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>1187</v>
       </c>
       <c r="I127" t="s">
         <v>8</v>
@@ -12635,13 +12626,13 @@
         <v>312</v>
       </c>
       <c r="L127" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M127" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N127" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O127" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80559_southend-on-sea", ".\export_data\inspection_reports\80559_southend-on-sea")</f>
@@ -12665,28 +12656,28 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B128" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C128" t="s">
         <v>56</v>
       </c>
       <c r="D128" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F128" t="s">
         <v>1190</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>1191</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="G128" t="s">
-        <v>1193</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>1194</v>
       </c>
       <c r="I128" t="s">
         <v>8</v>
@@ -12695,7 +12686,7 @@
         <v>48</v>
       </c>
       <c r="K128" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L128" t="s">
         <v>582</v>
@@ -12728,28 +12719,28 @@
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B129" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C129" t="s">
         <v>42</v>
       </c>
       <c r="D129" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F129" t="s">
         <v>1197</v>
       </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>1198</v>
       </c>
-      <c r="F129" t="s">
+      <c r="H129" s="2" t="s">
         <v>1199</v>
-      </c>
-      <c r="G129" t="s">
-        <v>1200</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="I129" t="s">
         <v>14</v>
@@ -12761,7 +12752,7 @@
         <v>202</v>
       </c>
       <c r="L129" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="M129" t="s">
         <v>324</v>
@@ -12786,33 +12777,33 @@
         <v>14</v>
       </c>
       <c r="T129" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B130" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C130" t="s">
         <v>56</v>
       </c>
       <c r="D130" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F130" t="s">
         <v>1204</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>1205</v>
       </c>
-      <c r="F130" t="s">
+      <c r="H130" s="2" t="s">
         <v>1206</v>
-      </c>
-      <c r="G130" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>1208</v>
       </c>
       <c r="I130" t="s">
         <v>14</v>
@@ -12824,13 +12815,13 @@
         <v>73</v>
       </c>
       <c r="L130" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M130" t="s">
         <v>314</v>
       </c>
       <c r="N130" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="O130" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80562_stockport", ".\export_data\inspection_reports\80562_stockport")</f>
@@ -12854,28 +12845,28 @@
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B131" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C131" t="s">
         <v>295</v>
       </c>
       <c r="D131" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F131" t="s">
         <v>1212</v>
       </c>
-      <c r="E131" t="s">
+      <c r="G131" t="s">
         <v>1213</v>
       </c>
-      <c r="F131" t="s">
+      <c r="H131" s="2" t="s">
         <v>1214</v>
-      </c>
-      <c r="G131" t="s">
-        <v>1215</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>1216</v>
       </c>
       <c r="I131" t="s">
         <v>14</v>
@@ -12884,16 +12875,16 @@
         <v>48</v>
       </c>
       <c r="K131" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M131" t="s">
         <v>1217</v>
       </c>
-      <c r="L131" t="s">
+      <c r="N131" t="s">
         <v>1218</v>
-      </c>
-      <c r="M131" t="s">
-        <v>1219</v>
-      </c>
-      <c r="N131" t="s">
-        <v>1220</v>
       </c>
       <c r="O131" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80563_stockton-on-tees", ".\export_data\inspection_reports\80563_stockton-on-tees")</f>
@@ -12917,28 +12908,28 @@
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B132" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C132" t="s">
         <v>42</v>
       </c>
       <c r="D132" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F132" t="s">
         <v>1223</v>
       </c>
-      <c r="E132" t="s">
+      <c r="G132" t="s">
         <v>1224</v>
       </c>
-      <c r="F132" t="s">
+      <c r="H132" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="G132" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>1227</v>
       </c>
       <c r="I132" t="s">
         <v>14</v>
@@ -12950,13 +12941,13 @@
         <v>49</v>
       </c>
       <c r="L132" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M132" t="s">
         <v>314</v>
       </c>
       <c r="N132" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="O132" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80564_stoke-on-trent", ".\export_data\inspection_reports\80564_stoke-on-trent")</f>
@@ -12980,28 +12971,28 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B133" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C133" t="s">
         <v>31</v>
       </c>
       <c r="D133" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F133" t="s">
         <v>1230</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
         <v>1231</v>
       </c>
-      <c r="F133" t="s">
+      <c r="H133" s="2" t="s">
         <v>1232</v>
-      </c>
-      <c r="G133" t="s">
-        <v>1233</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>1234</v>
       </c>
       <c r="I133" t="s">
         <v>14</v>
@@ -13013,13 +13004,13 @@
         <v>180</v>
       </c>
       <c r="L133" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M133" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="N133" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="O133" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80565_suffolk", ".\export_data\inspection_reports\80565_suffolk")</f>
@@ -13043,28 +13034,28 @@
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B134" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C134" t="s">
         <v>295</v>
       </c>
       <c r="D134" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F134" t="s">
         <v>1238</v>
       </c>
-      <c r="E134" t="s">
+      <c r="G134" t="s">
         <v>1239</v>
       </c>
-      <c r="F134" t="s">
+      <c r="H134" s="2" t="s">
         <v>1240</v>
-      </c>
-      <c r="G134" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>1242</v>
       </c>
       <c r="I134" t="s">
         <v>105</v>
@@ -13082,7 +13073,7 @@
         <v>345</v>
       </c>
       <c r="N134" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="O134" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80566_sunderland", ".\export_data\inspection_reports\80566_sunderland")</f>
@@ -13106,28 +13097,28 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B135" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C135" t="s">
         <v>99</v>
       </c>
       <c r="D135" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E135" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F135" t="s">
         <v>1246</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>1247</v>
       </c>
-      <c r="F135" t="s">
+      <c r="H135" s="2" t="s">
         <v>1248</v>
-      </c>
-      <c r="G135" t="s">
-        <v>1249</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>1250</v>
       </c>
       <c r="I135" t="s">
         <v>8</v>
@@ -13169,28 +13160,28 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B136" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
       </c>
       <c r="D136" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F136" t="s">
         <v>1253</v>
       </c>
-      <c r="E136" t="s">
+      <c r="G136" t="s">
         <v>1254</v>
       </c>
-      <c r="F136" t="s">
+      <c r="H136" s="2" t="s">
         <v>1255</v>
-      </c>
-      <c r="G136" t="s">
-        <v>1256</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>1257</v>
       </c>
       <c r="I136" t="s">
         <v>190</v>
@@ -13202,13 +13193,13 @@
         <v>139</v>
       </c>
       <c r="L136" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M136" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N136" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O136" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80568_swindon", ".\export_data\inspection_reports\80568_swindon")</f>
@@ -13232,28 +13223,28 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B137" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C137" t="s">
         <v>56</v>
       </c>
       <c r="D137" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E137" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F137" t="s">
         <v>1260</v>
       </c>
-      <c r="E137" t="s">
+      <c r="G137" t="s">
         <v>1261</v>
       </c>
-      <c r="F137" t="s">
+      <c r="H137" s="2" t="s">
         <v>1262</v>
-      </c>
-      <c r="G137" t="s">
-        <v>1263</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>1264</v>
       </c>
       <c r="I137" t="s">
         <v>190</v>
@@ -13265,13 +13256,13 @@
         <v>117</v>
       </c>
       <c r="L137" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="M137" t="s">
         <v>395</v>
       </c>
       <c r="N137" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="O137" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80569_tameside", ".\export_data\inspection_reports\80569_tameside")</f>
@@ -13295,28 +13286,28 @@
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B138" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C138" t="s">
         <v>42</v>
       </c>
       <c r="D138" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F138" t="s">
         <v>1268</v>
       </c>
-      <c r="E138" t="s">
+      <c r="G138" t="s">
         <v>1269</v>
       </c>
-      <c r="F138" t="s">
+      <c r="H138" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="G138" t="s">
-        <v>1271</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>1272</v>
       </c>
       <c r="I138" t="s">
         <v>105</v>
@@ -13328,7 +13319,7 @@
         <v>180</v>
       </c>
       <c r="L138" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="M138" t="s">
         <v>554</v>
@@ -13358,28 +13349,28 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B139" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
       </c>
       <c r="D139" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F139" t="s">
         <v>1276</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>1277</v>
       </c>
-      <c r="F139" t="s">
+      <c r="H139" s="2" t="s">
         <v>1278</v>
-      </c>
-      <c r="G139" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>1280</v>
       </c>
       <c r="I139" t="s">
         <v>105</v>
@@ -13391,13 +13382,13 @@
         <v>506</v>
       </c>
       <c r="L139" t="s">
+        <v>1279</v>
+      </c>
+      <c r="M139" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N139" t="s">
         <v>1281</v>
-      </c>
-      <c r="M139" t="s">
-        <v>1282</v>
-      </c>
-      <c r="N139" t="s">
-        <v>1283</v>
       </c>
       <c r="O139" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80571_thurrock", ".\export_data\inspection_reports\80571_thurrock")</f>
@@ -13421,28 +13412,28 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B140" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F140" t="s">
         <v>1286</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>1287</v>
       </c>
-      <c r="F140" t="s">
+      <c r="H140" s="2" t="s">
         <v>1288</v>
-      </c>
-      <c r="G140" t="s">
-        <v>1289</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>1290</v>
       </c>
       <c r="I140" t="s">
         <v>8</v>
@@ -13457,10 +13448,10 @@
         <v>214</v>
       </c>
       <c r="M140" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="N140" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="O140" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80572_torbay", ".\export_data\inspection_reports\80572_torbay")</f>
@@ -13484,28 +13475,28 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B141" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C141" t="s">
         <v>56</v>
       </c>
       <c r="D141" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F141" t="s">
         <v>1293</v>
       </c>
-      <c r="E141" t="s">
+      <c r="G141" t="s">
         <v>1294</v>
       </c>
-      <c r="F141" t="s">
+      <c r="H141" s="2" t="s">
         <v>1295</v>
-      </c>
-      <c r="G141" t="s">
-        <v>1296</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>1297</v>
       </c>
       <c r="I141" t="s">
         <v>14</v>
@@ -13517,13 +13508,13 @@
         <v>139</v>
       </c>
       <c r="L141" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M141" t="s">
+        <v>1297</v>
+      </c>
+      <c r="N141" t="s">
         <v>1298</v>
-      </c>
-      <c r="M141" t="s">
-        <v>1299</v>
-      </c>
-      <c r="N141" t="s">
-        <v>1300</v>
       </c>
       <c r="O141" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80573_trafford", ".\export_data\inspection_reports\80573_trafford")</f>
@@ -13547,28 +13538,28 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B142" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C142" t="s">
         <v>42</v>
       </c>
       <c r="D142" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E142" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F142" t="s">
         <v>1303</v>
       </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>1304</v>
       </c>
-      <c r="F142" t="s">
+      <c r="H142" s="2" t="s">
         <v>1305</v>
-      </c>
-      <c r="G142" t="s">
-        <v>1306</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>1307</v>
       </c>
       <c r="I142" t="s">
         <v>105</v>
@@ -13580,10 +13571,10 @@
         <v>139</v>
       </c>
       <c r="L142" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M142" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N142" t="s">
         <v>315</v>
@@ -13610,28 +13601,28 @@
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B143" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C143" t="s">
         <v>56</v>
       </c>
       <c r="D143" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E143" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F143" t="s">
         <v>1310</v>
       </c>
-      <c r="E143" t="s">
+      <c r="G143" t="s">
         <v>1311</v>
       </c>
-      <c r="F143" t="s">
+      <c r="H143" s="2" t="s">
         <v>1312</v>
-      </c>
-      <c r="G143" t="s">
-        <v>1313</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>1314</v>
       </c>
       <c r="I143" t="s">
         <v>8</v>
@@ -13649,7 +13640,7 @@
         <v>442</v>
       </c>
       <c r="N143" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="O143" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80575_warrington", ".\export_data\inspection_reports\80575_warrington")</f>
@@ -13673,28 +13664,28 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B144" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C144" t="s">
         <v>42</v>
       </c>
       <c r="D144" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E144" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F144" t="s">
         <v>1318</v>
       </c>
-      <c r="E144" t="s">
+      <c r="G144" t="s">
         <v>1319</v>
       </c>
-      <c r="F144" t="s">
+      <c r="H144" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="G144" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>1322</v>
       </c>
       <c r="I144" t="s">
         <v>14</v>
@@ -13706,13 +13697,13 @@
         <v>117</v>
       </c>
       <c r="L144" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1322</v>
+      </c>
+      <c r="N144" t="s">
         <v>1323</v>
-      </c>
-      <c r="M144" t="s">
-        <v>1324</v>
-      </c>
-      <c r="N144" t="s">
-        <v>1325</v>
       </c>
       <c r="O144" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80576_warwickshire", ".\export_data\inspection_reports\80576_warwickshire")</f>
@@ -13736,28 +13727,28 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B145" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C145" t="s">
         <v>99</v>
       </c>
       <c r="D145" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F145" t="s">
         <v>1328</v>
       </c>
-      <c r="E145" t="s">
+      <c r="G145" t="s">
         <v>1329</v>
       </c>
-      <c r="F145" t="s">
+      <c r="H145" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>1332</v>
       </c>
       <c r="I145" t="s">
         <v>8</v>
@@ -13766,16 +13757,16 @@
         <v>9</v>
       </c>
       <c r="K145" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L145" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1332</v>
+      </c>
+      <c r="N145" t="s">
         <v>1333</v>
-      </c>
-      <c r="M145" t="s">
-        <v>1334</v>
-      </c>
-      <c r="N145" t="s">
-        <v>1335</v>
       </c>
       <c r="O145" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80577_west berkshire", ".\export_data\inspection_reports\80577_west berkshire")</f>
@@ -13799,28 +13790,28 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B146" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C146" t="s">
         <v>306</v>
       </c>
       <c r="D146" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F146" t="s">
         <v>1338</v>
       </c>
-      <c r="E146" t="s">
+      <c r="G146" t="s">
         <v>1339</v>
       </c>
-      <c r="F146" t="s">
+      <c r="H146" s="2" t="s">
         <v>1340</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1341</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>1342</v>
       </c>
       <c r="I146" t="s">
         <v>14</v>
@@ -13832,13 +13823,13 @@
         <v>202</v>
       </c>
       <c r="L146" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M146" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N146" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="O146" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2637548_west northamptonshire", ".\export_data\inspection_reports\2637548_west northamptonshire")</f>
@@ -13857,33 +13848,33 @@
         <v>77</v>
       </c>
       <c r="T146" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B147" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C147" t="s">
         <v>99</v>
       </c>
       <c r="D147" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F147" t="s">
         <v>1345</v>
       </c>
-      <c r="E147" t="s">
+      <c r="G147" t="s">
         <v>1346</v>
       </c>
-      <c r="F147" t="s">
+      <c r="H147" s="2" t="s">
         <v>1347</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>1349</v>
       </c>
       <c r="I147" t="s">
         <v>14</v>
@@ -13892,7 +13883,7 @@
         <v>48</v>
       </c>
       <c r="K147" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="L147" t="s">
         <v>572</v>
@@ -13901,7 +13892,7 @@
         <v>573</v>
       </c>
       <c r="N147" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O147" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80578_west sussex", ".\export_data\inspection_reports\80578_west sussex")</f>
@@ -13925,10 +13916,10 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B148" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C148" t="s">
         <v>56</v>
@@ -13937,16 +13928,16 @@
         <v>285</v>
       </c>
       <c r="E148" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G148" t="s">
         <v>1353</v>
       </c>
-      <c r="F148" t="s">
+      <c r="H148" s="2" t="s">
         <v>1354</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1355</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>1356</v>
       </c>
       <c r="I148" t="s">
         <v>8</v>
@@ -13955,7 +13946,7 @@
         <v>48</v>
       </c>
       <c r="K148" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="L148" t="s">
         <v>553</v>
@@ -13988,28 +13979,28 @@
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B149" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C149" t="s">
         <v>56</v>
       </c>
       <c r="D149" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F149" t="s">
         <v>1359</v>
       </c>
-      <c r="E149" t="s">
+      <c r="G149" t="s">
         <v>1360</v>
       </c>
-      <c r="F149" t="s">
+      <c r="H149" s="2" t="s">
         <v>1361</v>
-      </c>
-      <c r="G149" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>1363</v>
       </c>
       <c r="I149" t="s">
         <v>8</v>
@@ -14018,16 +14009,16 @@
         <v>48</v>
       </c>
       <c r="K149" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L149" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1363</v>
+      </c>
+      <c r="N149" t="s">
         <v>1364</v>
-      </c>
-      <c r="M149" t="s">
-        <v>1365</v>
-      </c>
-      <c r="N149" t="s">
-        <v>1366</v>
       </c>
       <c r="O149" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80579_wigan", ".\export_data\inspection_reports\80579_wigan")</f>
@@ -14051,28 +14042,28 @@
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B150" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
       <c r="D150" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F150" t="s">
         <v>1369</v>
       </c>
-      <c r="E150" t="s">
+      <c r="G150" t="s">
         <v>1370</v>
       </c>
-      <c r="F150" t="s">
+      <c r="H150" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1372</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>1373</v>
       </c>
       <c r="I150" t="s">
         <v>105</v>
@@ -14084,13 +14075,13 @@
         <v>404</v>
       </c>
       <c r="L150" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1373</v>
+      </c>
+      <c r="N150" t="s">
         <v>1374</v>
-      </c>
-      <c r="M150" t="s">
-        <v>1375</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1376</v>
       </c>
       <c r="O150" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80580_wiltshire", ".\export_data\inspection_reports\80580_wiltshire")</f>
@@ -14109,33 +14100,33 @@
         <v>105</v>
       </c>
       <c r="T150" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B151" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C151" t="s">
         <v>56</v>
       </c>
       <c r="D151" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F151" t="s">
         <v>1379</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>1380</v>
       </c>
-      <c r="F151" t="s">
+      <c r="H151" s="2" t="s">
         <v>1381</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1382</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>1383</v>
       </c>
       <c r="I151" t="s">
         <v>14</v>
@@ -14147,13 +14138,13 @@
         <v>191</v>
       </c>
       <c r="L151" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="M151" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="N151" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="O151" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80581_wirral", ".\export_data\inspection_reports\80581_wirral")</f>
@@ -14177,28 +14168,28 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B152" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C152" t="s">
         <v>99</v>
       </c>
       <c r="D152" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F152" t="s">
         <v>1388</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
         <v>1389</v>
       </c>
-      <c r="F152" t="s">
+      <c r="H152" s="2" t="s">
         <v>1390</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1391</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>1392</v>
       </c>
       <c r="I152" t="s">
         <v>14</v>
@@ -14210,13 +14201,13 @@
         <v>393</v>
       </c>
       <c r="L152" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M152" t="s">
+        <v>1217</v>
+      </c>
+      <c r="N152" t="s">
         <v>1218</v>
-      </c>
-      <c r="M152" t="s">
-        <v>1219</v>
-      </c>
-      <c r="N152" t="s">
-        <v>1220</v>
       </c>
       <c r="O152" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80582_wokingham", ".\export_data\inspection_reports\80582_wokingham")</f>
@@ -14240,28 +14231,28 @@
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B153" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C153" t="s">
         <v>42</v>
       </c>
       <c r="D153" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F153" t="s">
         <v>1395</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>1396</v>
       </c>
-      <c r="F153" t="s">
+      <c r="H153" s="2" t="s">
         <v>1397</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1398</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1399</v>
       </c>
       <c r="I153" t="s">
         <v>8</v>
@@ -14270,61 +14261,61 @@
         <v>9</v>
       </c>
       <c r="K153" t="s">
-        <v>961</v>
+        <v>202</v>
       </c>
       <c r="L153" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="M153" t="s">
-        <v>1401</v>
+        <v>842</v>
       </c>
       <c r="N153" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="O153" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80583_wolverhampton", ".\export_data\inspection_reports\80583_wolverhampton")</f>
         <v>0</v>
       </c>
       <c r="P153" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="Q153" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R153" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="S153" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="T153" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B154" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="C154" t="s">
         <v>42</v>
       </c>
       <c r="D154" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G154" t="s">
         <v>1405</v>
       </c>
-      <c r="E154" t="s">
+      <c r="H154" s="2" t="s">
         <v>1406</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1407</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1408</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1409</v>
       </c>
       <c r="I154" t="s">
         <v>8</v>
@@ -14336,13 +14327,13 @@
         <v>180</v>
       </c>
       <c r="L154" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M154" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="N154" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="O154" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80584_worcestershire", ".\export_data\inspection_reports\80584_worcestershire")</f>

--- a/ofsted_csc_ilacs_overview.xlsx
+++ b/ofsted_csc_ilacs_overview.xlsx
@@ -79,7 +79,7 @@
     <t>816, 358, 919, 356, 938, 314, 825, 931, 873, 916</t>
   </si>
   <si>
-    <t>[(816, 'outstanding'), (358, 'requires improvement'), (919, 'outstanding'), (356, 'requires improvement'), (938, 'requires improvement'), (314, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (873, 'requires improvement'), (916, 'good')]</t>
+    <t>[(816, 'outstanding'), (358, nan), (919, 'outstanding'), (356, 'requires improvement'), (938, 'requires improvement'), (314, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (873, 'requires improvement'), (916, 'good')]</t>
   </si>
   <si>
     <t>bath and north east somerset</t>
@@ -214,6 +214,9 @@
     <t>23/04/25</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>80431</t>
   </si>
   <si>
@@ -226,7 +229,7 @@
     <t>805, 806, 394, 341, 393, 807, 354, 880, 355, 861</t>
   </si>
   <si>
-    <t>[(805, 'outstanding'), (806, nan), (394, 'outstanding'), (341, nan), (393, 'inadequate'), (807, 'good'), (354, 'requires improvement'), (880, 'good'), (355, 'good'), (861, 'requires improvement')]</t>
+    <t>[(805, 'outstanding'), (806, nan), (394, 'outstanding'), (341, nan), (393, nan), (807, 'good'), (354, 'requires improvement'), (880, 'good'), (355, 'good'), (861, 'requires improvement')]</t>
   </si>
   <si>
     <t>blackpool</t>
@@ -421,7 +424,7 @@
     <t>931, 919, 869, 936, 873, 867, 823, 868, 358, 850</t>
   </si>
   <si>
-    <t>[(931, 'good'), (919, 'outstanding'), (869, 'good'), (936, 'good'), (873, 'requires improvement'), (867, 'outstanding'), (823, 'good'), (868, 'good'), (358, 'requires improvement'), (850, 'outstanding')]</t>
+    <t>[(931, 'good'), (919, 'outstanding'), (869, 'good'), (936, 'good'), (873, 'requires improvement'), (867, 'outstanding'), (823, 'good'), (868, 'good'), (358, nan), (850, 'outstanding')]</t>
   </si>
   <si>
     <t>buckinghamshire</t>
@@ -442,768 +445,765 @@
     <t>14/05/25</t>
   </si>
   <si>
+    <t>80443</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>E08000002</t>
+  </si>
+  <si>
+    <t>888, 908, 392, 886, 332, 891, 808, 926, 887, 303</t>
+  </si>
+  <si>
+    <t>[(888, 'good'), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>bury</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50283347</t>
+  </si>
+  <si>
+    <t>rebecca dubbins</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>29/07/25</t>
+  </si>
+  <si>
+    <t>80444</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>E08000033</t>
+  </si>
+  <si>
+    <t>839, 845, 878, 921, 926, 882, 350, 929, 383, 356</t>
+  </si>
+  <si>
+    <t>[(839, 'good'), (845, 'good'), (878, 'inadequate'), (921, 'good'), (926, 'outstanding'), (882, 'good'), (350, 'good'), (929, 'outstanding'), (383, 'outstanding'), (356, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>calderdale</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50246982</t>
+  </si>
+  <si>
+    <t>19/02/2024</t>
+  </si>
+  <si>
+    <t>23/02/2024</t>
+  </si>
+  <si>
+    <t>15/05/24</t>
+  </si>
+  <si>
+    <t>80445</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>E10000003</t>
+  </si>
+  <si>
+    <t>931, 919, 825, 803, 937, 916, 938, 823, 850, 869</t>
+  </si>
+  <si>
+    <t>[(931, 'good'), (919, 'outstanding'), (825, 'requires improvement'), (803, 'good'), (937, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (823, 'good'), (850, 'outstanding'), (869, 'good')]</t>
+  </si>
+  <si>
+    <t>cambridgeshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50247204</t>
+  </si>
+  <si>
+    <t>04/03/2024</t>
+  </si>
+  <si>
+    <t>15/03/2024</t>
+  </si>
+  <si>
+    <t>80446</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>E06000056</t>
+  </si>
+  <si>
+    <t>825, 803, 873, 850, 865, 931, 938, 867, 869, 919</t>
+  </si>
+  <si>
+    <t>[(825, 'requires improvement'), (803, 'good'), (873, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (931, 'good'), (938, 'requires improvement'), (867, 'outstanding'), (869, 'good'), (919, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>central bedfordshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50275136</t>
+  </si>
+  <si>
+    <t>rebecca quested</t>
+  </si>
+  <si>
+    <t>10/03/2025</t>
+  </si>
+  <si>
+    <t>24/04/25</t>
+  </si>
+  <si>
+    <t>80447</t>
+  </si>
+  <si>
+    <t>895</t>
+  </si>
+  <si>
+    <t>E06000049</t>
+  </si>
+  <si>
+    <t>916, 937, 815, 877, 865, 850, 896, 931, 885, 855</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (937, 'requires improvement'), (815, 'outstanding'), (877, 'good'), (865, 'outstanding'), (850, 'outstanding'), (896, 'requires improvement'), (931, 'good'), (885, 'good'), (855, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>cheshire east</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50247203</t>
+  </si>
+  <si>
+    <t>inadequate</t>
+  </si>
+  <si>
+    <t>teresa godfrey</t>
+  </si>
+  <si>
+    <t>26/02/2024</t>
+  </si>
+  <si>
+    <t>08/03/2024</t>
+  </si>
+  <si>
+    <t>80448</t>
+  </si>
+  <si>
+    <t>896</t>
+  </si>
+  <si>
+    <t>E06000050</t>
+  </si>
+  <si>
+    <t>334, 356, 895, 937, 885, 916, 877, 878, 938, 929</t>
+  </si>
+  <si>
+    <t>[(334, 'good'), (356, 'requires improvement'), (895, 'inadequate'), (937, 'requires improvement'), (885, 'good'), (916, 'good'), (877, 'good'), (878, 'inadequate'), (938, 'requires improvement'), (929, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>cheshire west and chester</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255617</t>
+  </si>
+  <si>
+    <t>alison smale</t>
+  </si>
+  <si>
+    <t>15/07/2024</t>
+  </si>
+  <si>
+    <t>19/07/2024</t>
+  </si>
+  <si>
+    <t>28/08/24</t>
+  </si>
+  <si>
+    <t>80449</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>E08000032</t>
+  </si>
+  <si>
+    <t>889, 330, 353, 373, 831, 354, 350, 335, 333, 382</t>
+  </si>
+  <si>
+    <t>[(889, 'good'), (330, 'good'), (353, 'good'), (373, 'good'), (831, 'outstanding'), (354, 'requires improvement'), (350, 'good'), (335, 'outstanding'), (333, 'good'), (382, 'good')]</t>
+  </si>
+  <si>
+    <t>bradford</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50302265</t>
+  </si>
+  <si>
+    <t>catherine heron</t>
+  </si>
+  <si>
+    <t>12/01/2026</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
+  </si>
+  <si>
+    <t>80450</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>E09000001</t>
+  </si>
+  <si>
+    <t>202, 205, 207, 210, 208, 206, 212, 213, 209, 846</t>
+  </si>
+  <si>
+    <t>[(202, 'outstanding'), (205, 'outstanding'), (207, 'outstanding'), (210, 'good'), (208, 'good'), (206, 'outstanding'), (212, 'outstanding'), (213, 'outstanding'), (209, 'good'), (846, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>london corporation</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50260648</t>
+  </si>
+  <si>
+    <t>christine kennet</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>27/09/2024</t>
+  </si>
+  <si>
+    <t>05/11/24</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>80451</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>E08000036</t>
+  </si>
+  <si>
+    <t>332, 370, 894, 372, 925, 357, 371, 813, 841, 888</t>
+  </si>
+  <si>
+    <t>[(332, 'requires improvement'), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, 'good')]</t>
+  </si>
+  <si>
+    <t>wakefield</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50282475</t>
+  </si>
+  <si>
+    <t>24/03/2025</t>
+  </si>
+  <si>
+    <t>28/03/2025</t>
+  </si>
+  <si>
+    <t>18/07/25</t>
+  </si>
+  <si>
+    <t>80453</t>
+  </si>
+  <si>
+    <t>816</t>
+  </si>
+  <si>
+    <t>E06000014</t>
+  </si>
+  <si>
+    <t>916, 800, 802, 919, 937, 931, 938, 358, 850, 356</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (800, 'good'), (802, 'requires improvement'), (919, 'outstanding'), (937, 'requires improvement'), (931, 'good'), (938, 'requires improvement'), (358, nan), (850, 'outstanding'), (356, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>york</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50274368</t>
+  </si>
+  <si>
+    <t>rachel fairhurst</t>
+  </si>
+  <si>
+    <t>24/02/2025</t>
+  </si>
+  <si>
+    <t>07/03/2025</t>
+  </si>
+  <si>
+    <t>15/04/25</t>
+  </si>
+  <si>
+    <t>80454</t>
+  </si>
+  <si>
+    <t>908</t>
+  </si>
+  <si>
+    <t>E06000052</t>
+  </si>
+  <si>
+    <t>926, 351, 845, 830, 929, 935, 878, 891, 888, 886</t>
+  </si>
+  <si>
+    <t>[(926, 'outstanding'), (351, 'requires improvement'), (845, 'good'), (830, 'good'), (929, 'outstanding'), (935, 'requires improvement'), (878, 'inadequate'), (891, 'good'), (888, 'good'), (886, 'good')]</t>
+  </si>
+  <si>
+    <t>cornwall</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255376</t>
+  </si>
+  <si>
+    <t>sarah canto</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>05/07/2024</t>
+  </si>
+  <si>
+    <t>22/08/24</t>
+  </si>
+  <si>
+    <t>80455</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>E06000053</t>
+  </si>
+  <si>
+    <t>869, 825, 872, 931, 850, 936, 873, 802, 867, 865</t>
+  </si>
+  <si>
+    <t>[(869, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (931, 'good'), (850, 'outstanding'), (936, 'good'), (873, 'requires improvement'), (802, 'requires improvement'), (867, 'outstanding'), (865, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>isles of scilly</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50226696</t>
+  </si>
+  <si>
+    <t>11/07/2023</t>
+  </si>
+  <si>
+    <t>13/07/2023</t>
+  </si>
+  <si>
+    <t>25/08/23</t>
+  </si>
+  <si>
+    <t>80456</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>E08000026</t>
+  </si>
+  <si>
+    <t>831, 852, 874, 350, 336, 312, 354, 335, 821, 861</t>
+  </si>
+  <si>
+    <t>[(831, 'outstanding'), (852, 'good'), (874, 'inadequate'), (350, 'good'), (336, 'good'), (312, 'outstanding'), (354, 'requires improvement'), (335, 'outstanding'), (821, 'good'), (861, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>coventry</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301676</t>
+  </si>
+  <si>
+    <t>sophie wales</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>18/05/26</t>
+  </si>
+  <si>
+    <t>2733690</t>
+  </si>
+  <si>
+    <t>942</t>
+  </si>
+  <si>
+    <t>E10000006</t>
+  </si>
+  <si>
+    <t>943, 925, 884, 888, 813, 384, 860, 929, 371, 370</t>
+  </si>
+  <si>
+    <t>[(943, 'good'), (925, 'outstanding'), (884, 'good'), (888, 'good'), (813, 'outstanding'), (384, 'good'), (860, 'requires improvement'), (929, 'outstanding'), (371, 'good'), (370, 'good')]</t>
+  </si>
+  <si>
+    <t>cumberland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50262710</t>
+  </si>
+  <si>
+    <t>07/10/2024</t>
+  </si>
+  <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>26/11/24</t>
+  </si>
+  <si>
+    <t>80458</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>E06000005</t>
+  </si>
+  <si>
+    <t>390, 808, 332, 384, 888, 894, 372, 357, 840, 371</t>
+  </si>
+  <si>
+    <t>[(390, 'good'), (808, 'requires improvement'), (332, 'requires improvement'), (384, 'good'), (888, 'good'), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
+  </si>
+  <si>
+    <t>darlington</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50298056</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>24/03/26</t>
+  </si>
+  <si>
+    <t>80459</t>
+  </si>
+  <si>
+    <t>831</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>E06000015</t>
+  </si>
+  <si>
+    <t>331, 350, 335, 852, 382, 874, 354, 373, 357, 861</t>
+  </si>
+  <si>
+    <t>[(331, 'outstanding'), (350, 'good'), (335, 'outstanding'), (852, 'good'), (382, 'good'), (874, 'inadequate'), (354, 'requires improvement'), (373, 'good'), (357, 'inadequate'), (861, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>derby</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50281395</t>
+  </si>
+  <si>
+    <t>19/05/2025</t>
+  </si>
+  <si>
+    <t>23/05/2025</t>
+  </si>
+  <si>
+    <t>08/07/25</t>
+  </si>
+  <si>
+    <t>80460</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>E10000007</t>
+  </si>
+  <si>
+    <t>891, 933, 935, 926, 860, 878, 893, 929, 838, 885</t>
+  </si>
+  <si>
+    <t>[(891, 'good'), (933, nan), (935, 'requires improvement'), (926, 'outstanding'), (860, 'requires improvement'), (878, 'inadequate'), (893, 'outstanding'), (929, 'outstanding'), (838, 'outstanding'), (885, 'good')]</t>
+  </si>
+  <si>
+    <t>derbyshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50237006</t>
+  </si>
+  <si>
+    <t>30/10/2023</t>
+  </si>
+  <si>
+    <t>10/11/2023</t>
+  </si>
+  <si>
+    <t>12/01/24</t>
+  </si>
+  <si>
+    <t>80461</t>
+  </si>
+  <si>
+    <t>878</t>
+  </si>
+  <si>
+    <t>E10000008</t>
+  </si>
+  <si>
+    <t>845, 838, 926, 886, 933, 935, 938, 830, 881, 885</t>
+  </si>
+  <si>
+    <t>[(845, 'good'), (838, 'outstanding'), (926, 'outstanding'), (886, 'good'), (933, nan), (935, 'requires improvement'), (938, 'requires improvement'), (830, 'good'), (881, 'outstanding'), (885, 'good')]</t>
+  </si>
+  <si>
+    <t>devon</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50276862</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
+    <t>11/10/2024</t>
+  </si>
+  <si>
+    <t>13/05/25</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>80462</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>E08000017</t>
+  </si>
+  <si>
+    <t>372, 370, 384, 894, 357, 812, 335, 861, 354, 813</t>
+  </si>
+  <si>
+    <t>[(372, 'outstanding'), (370, 'good'), (384, 'good'), (894, 'outstanding'), (357, 'inadequate'), (812, 'good'), (335, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (813, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>doncaster</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50271937</t>
+  </si>
+  <si>
+    <t>20/01/2025</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>18/03/25</t>
+  </si>
+  <si>
+    <t>2532283</t>
+  </si>
+  <si>
+    <t>838</t>
+  </si>
+  <si>
+    <t>E10000009</t>
+  </si>
+  <si>
+    <t>933, 878, 893, 935, 885, 881, 830, 886, 938, 815</t>
+  </si>
+  <si>
+    <t>[(933, nan), (878, 'inadequate'), (893, 'outstanding'), (935, 'requires improvement'), (885, 'good'), (881, 'outstanding'), (830, 'good'), (886, 'good'), (938, 'requires improvement'), (815, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>dorset</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50276411</t>
+  </si>
+  <si>
+    <t>17/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025</t>
+  </si>
+  <si>
+    <t>09/05/25</t>
+  </si>
+  <si>
+    <t>80464</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>E08000027</t>
+  </si>
+  <si>
+    <t>384, 894, 808, 372, 370, 887, 357, 888, 841, 925</t>
+  </si>
+  <si>
+    <t>[(384, 'good'), (894, 'outstanding'), (808, 'requires improvement'), (372, 'outstanding'), (370, 'good'), (887, 'good'), (357, 'inadequate'), (888, 'good'), (841, 'outstanding'), (925, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>dudley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50204402</t>
+  </si>
+  <si>
+    <t>31/10/2022</t>
+  </si>
+  <si>
+    <t>11/11/2022</t>
+  </si>
+  <si>
+    <t>13/01/23</t>
+  </si>
+  <si>
+    <t>inspection_pre_dates_judgement</t>
+  </si>
+  <si>
+    <t>80465</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>E06000047</t>
+  </si>
+  <si>
+    <t>876, 344, 390, 807, 372, 370, 394, 393, 808, 841</t>
+  </si>
+  <si>
+    <t>[(876, 'inadequate'), (344, 'requires improvement'), (390, 'good'), (807, 'good'), (372, 'outstanding'), (370, 'good'), (394, 'outstanding'), (393, nan), (808, 'requires improvement'), (841, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>durham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50276863</t>
+  </si>
+  <si>
+    <t>ceri evans</t>
+  </si>
+  <si>
+    <t>80466</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>E06000011</t>
+  </si>
+  <si>
+    <t>860, 893, 815, 877, 855, 933, 884, 943, 937, 830</t>
+  </si>
+  <si>
+    <t>[(860, 'requires improvement'), (893, 'outstanding'), (815, 'outstanding'), (877, 'good'), (855, 'outstanding'), (933, nan), (884, 'good'), (943, 'good'), (937, 'requires improvement'), (830, 'good')]</t>
+  </si>
+  <si>
+    <t>east riding of yorkshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50212242</t>
+  </si>
+  <si>
+    <t>louise walker</t>
+  </si>
+  <si>
+    <t>30/01/2023</t>
+  </si>
+  <si>
+    <t>10/02/2023</t>
+  </si>
+  <si>
+    <t>24/03/23</t>
+  </si>
+  <si>
+    <t>80467</t>
+  </si>
+  <si>
+    <t>845</t>
+  </si>
+  <si>
+    <t>E10000011</t>
+  </si>
+  <si>
+    <t>878, 886, 908, 926, 881, 351, 838, 938, 929, 839</t>
+  </si>
+  <si>
+    <t>[(878, 'inadequate'), (886, 'good'), (908, 'good'), (926, 'outstanding'), (881, 'outstanding'), (351, 'requires improvement'), (838, 'outstanding'), (938, 'requires improvement'), (929, 'outstanding'), (839, 'good')]</t>
+  </si>
+  <si>
+    <t>east sussex</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50239111</t>
+  </si>
+  <si>
+    <t>tom anthony</t>
+  </si>
+  <si>
+    <t>11/12/2023</t>
+  </si>
+  <si>
+    <t>15/12/2023</t>
+  </si>
+  <si>
+    <t>06/02/24</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>80443</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>E08000002</t>
-  </si>
-  <si>
-    <t>888, 908, 392, 886, 332, 891, 808, 926, 887, 303</t>
-  </si>
-  <si>
-    <t>[(888, 'good'), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>bury</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50283347</t>
-  </si>
-  <si>
-    <t>rebecca dubbins</t>
-  </si>
-  <si>
-    <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>29/07/25</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>80444</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>E08000033</t>
-  </si>
-  <si>
-    <t>839, 845, 878, 921, 926, 882, 350, 929, 383, 356</t>
-  </si>
-  <si>
-    <t>[(839, 'good'), (845, 'good'), (878, 'inadequate'), (921, 'good'), (926, 'outstanding'), (882, 'good'), (350, 'good'), (929, 'outstanding'), (383, 'outstanding'), (356, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>calderdale</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50246982</t>
-  </si>
-  <si>
-    <t>19/02/2024</t>
-  </si>
-  <si>
-    <t>23/02/2024</t>
-  </si>
-  <si>
-    <t>15/05/24</t>
-  </si>
-  <si>
-    <t>80445</t>
-  </si>
-  <si>
-    <t>873</t>
-  </si>
-  <si>
-    <t>E10000003</t>
-  </si>
-  <si>
-    <t>931, 919, 825, 803, 937, 916, 938, 823, 850, 869</t>
-  </si>
-  <si>
-    <t>[(931, 'good'), (919, 'outstanding'), (825, 'requires improvement'), (803, 'good'), (937, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (823, 'good'), (850, 'outstanding'), (869, 'good')]</t>
-  </si>
-  <si>
-    <t>cambridgeshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50247204</t>
-  </si>
-  <si>
-    <t>04/03/2024</t>
-  </si>
-  <si>
-    <t>15/03/2024</t>
-  </si>
-  <si>
-    <t>80446</t>
-  </si>
-  <si>
-    <t>823</t>
-  </si>
-  <si>
-    <t>E06000056</t>
-  </si>
-  <si>
-    <t>825, 803, 873, 850, 865, 931, 938, 867, 869, 919</t>
-  </si>
-  <si>
-    <t>[(825, 'requires improvement'), (803, 'good'), (873, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (931, 'good'), (938, 'requires improvement'), (867, 'outstanding'), (869, 'good'), (919, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>central bedfordshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50275136</t>
-  </si>
-  <si>
-    <t>rebecca quested</t>
-  </si>
-  <si>
-    <t>10/03/2025</t>
-  </si>
-  <si>
-    <t>24/04/25</t>
-  </si>
-  <si>
-    <t>80447</t>
-  </si>
-  <si>
-    <t>895</t>
-  </si>
-  <si>
-    <t>E06000049</t>
-  </si>
-  <si>
-    <t>916, 937, 815, 877, 865, 850, 896, 931, 885, 855</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (937, 'requires improvement'), (815, 'outstanding'), (877, 'good'), (865, 'outstanding'), (850, 'outstanding'), (896, 'requires improvement'), (931, 'good'), (885, 'good'), (855, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>cheshire east</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50247203</t>
-  </si>
-  <si>
-    <t>inadequate</t>
-  </si>
-  <si>
-    <t>teresa godfrey</t>
-  </si>
-  <si>
-    <t>26/02/2024</t>
-  </si>
-  <si>
-    <t>08/03/2024</t>
-  </si>
-  <si>
-    <t>80448</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>E06000050</t>
-  </si>
-  <si>
-    <t>334, 356, 895, 937, 885, 916, 877, 878, 938, 929</t>
-  </si>
-  <si>
-    <t>[(334, 'good'), (356, 'requires improvement'), (895, 'inadequate'), (937, 'requires improvement'), (885, 'good'), (916, 'good'), (877, 'good'), (878, 'inadequate'), (938, 'requires improvement'), (929, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>cheshire west and chester</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255617</t>
-  </si>
-  <si>
-    <t>alison smale</t>
-  </si>
-  <si>
-    <t>15/07/2024</t>
-  </si>
-  <si>
-    <t>19/07/2024</t>
-  </si>
-  <si>
-    <t>28/08/24</t>
-  </si>
-  <si>
-    <t>80449</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>E08000032</t>
-  </si>
-  <si>
-    <t>889, 330, 353, 373, 831, 354, 350, 335, 333, 382</t>
-  </si>
-  <si>
-    <t>[(889, 'good'), (330, 'good'), (353, 'good'), (373, 'good'), (831, 'outstanding'), (354, 'requires improvement'), (350, 'good'), (335, 'outstanding'), (333, 'good'), (382, 'good')]</t>
-  </si>
-  <si>
-    <t>bradford</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50302265</t>
-  </si>
-  <si>
-    <t>catherine heron</t>
-  </si>
-  <si>
-    <t>12/01/2026</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
-  </si>
-  <si>
-    <t>80450</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>GL</t>
-  </si>
-  <si>
-    <t>E09000001</t>
-  </si>
-  <si>
-    <t>202, 205, 207, 210, 208, 206, 212, 213, 209, 846</t>
-  </si>
-  <si>
-    <t>[(202, 'outstanding'), (205, 'outstanding'), (207, 'outstanding'), (210, 'good'), (208, 'good'), (206, 'outstanding'), (212, 'outstanding'), (213, 'outstanding'), (209, 'good'), (846, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>london corporation</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50260648</t>
-  </si>
-  <si>
-    <t>christine kennet</t>
-  </si>
-  <si>
-    <t>23/09/2024</t>
-  </si>
-  <si>
-    <t>27/09/2024</t>
-  </si>
-  <si>
-    <t>05/11/24</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>80451</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>E08000036</t>
-  </si>
-  <si>
-    <t>332, 370, 894, 372, 925, 357, 371, 813, 841, 888</t>
-  </si>
-  <si>
-    <t>[(332, 'requires improvement'), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, 'good')]</t>
-  </si>
-  <si>
-    <t>wakefield</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50282475</t>
-  </si>
-  <si>
-    <t>24/03/2025</t>
-  </si>
-  <si>
-    <t>28/03/2025</t>
-  </si>
-  <si>
-    <t>18/07/25</t>
-  </si>
-  <si>
-    <t>80453</t>
-  </si>
-  <si>
-    <t>816</t>
-  </si>
-  <si>
-    <t>E06000014</t>
-  </si>
-  <si>
-    <t>916, 800, 802, 919, 937, 931, 938, 358, 850, 356</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (800, 'good'), (802, 'requires improvement'), (919, 'outstanding'), (937, 'requires improvement'), (931, 'good'), (938, 'requires improvement'), (358, 'requires improvement'), (850, 'outstanding'), (356, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>york</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50274368</t>
-  </si>
-  <si>
-    <t>rachel fairhurst</t>
-  </si>
-  <si>
-    <t>24/02/2025</t>
-  </si>
-  <si>
-    <t>07/03/2025</t>
-  </si>
-  <si>
-    <t>15/04/25</t>
-  </si>
-  <si>
-    <t>80454</t>
-  </si>
-  <si>
-    <t>908</t>
-  </si>
-  <si>
-    <t>E06000052</t>
-  </si>
-  <si>
-    <t>926, 351, 845, 830, 929, 935, 878, 891, 888, 886</t>
-  </si>
-  <si>
-    <t>[(926, 'outstanding'), (351, 'requires improvement'), (845, 'good'), (830, 'good'), (929, 'outstanding'), (935, 'requires improvement'), (878, 'inadequate'), (891, 'good'), (888, 'good'), (886, 'good')]</t>
-  </si>
-  <si>
-    <t>cornwall</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255376</t>
-  </si>
-  <si>
-    <t>sarah canto</t>
-  </si>
-  <si>
-    <t>01/07/2024</t>
-  </si>
-  <si>
-    <t>05/07/2024</t>
-  </si>
-  <si>
-    <t>22/08/24</t>
-  </si>
-  <si>
-    <t>80455</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>E06000053</t>
-  </si>
-  <si>
-    <t>869, 825, 872, 931, 850, 936, 873, 802, 867, 865</t>
-  </si>
-  <si>
-    <t>[(869, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (931, 'good'), (850, 'outstanding'), (936, 'good'), (873, 'requires improvement'), (802, 'requires improvement'), (867, 'outstanding'), (865, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>isles of scilly</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50226696</t>
-  </si>
-  <si>
-    <t>11/07/2023</t>
-  </si>
-  <si>
-    <t>13/07/2023</t>
-  </si>
-  <si>
-    <t>25/08/23</t>
-  </si>
-  <si>
-    <t>80456</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>E08000026</t>
-  </si>
-  <si>
-    <t>831, 852, 874, 350, 336, 312, 354, 335, 821, 861</t>
-  </si>
-  <si>
-    <t>[(831, 'outstanding'), (852, 'good'), (874, 'inadequate'), (350, 'good'), (336, 'good'), (312, 'outstanding'), (354, 'requires improvement'), (335, 'outstanding'), (821, 'good'), (861, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>coventry</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301676</t>
-  </si>
-  <si>
-    <t>sophie wales</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>18/05/26</t>
-  </si>
-  <si>
-    <t>2733690</t>
-  </si>
-  <si>
-    <t>942</t>
-  </si>
-  <si>
-    <t>E10000006</t>
-  </si>
-  <si>
-    <t>943, 925, 884, 888, 813, 384, 860, 929, 371, 370</t>
-  </si>
-  <si>
-    <t>[(943, 'good'), (925, 'outstanding'), (884, 'good'), (888, 'good'), (813, 'outstanding'), (384, 'good'), (860, 'requires improvement'), (929, 'outstanding'), (371, 'good'), (370, 'good')]</t>
-  </si>
-  <si>
-    <t>cumberland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50262710</t>
-  </si>
-  <si>
-    <t>07/10/2024</t>
-  </si>
-  <si>
-    <t>18/10/2024</t>
-  </si>
-  <si>
-    <t>26/11/24</t>
-  </si>
-  <si>
-    <t>80458</t>
-  </si>
-  <si>
-    <t>841</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>E06000005</t>
-  </si>
-  <si>
-    <t>390, 808, 332, 384, 888, 894, 372, 357, 840, 371</t>
-  </si>
-  <si>
-    <t>[(390, 'good'), (808, 'requires improvement'), (332, 'requires improvement'), (384, 'good'), (888, 'good'), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
-  </si>
-  <si>
-    <t>darlington</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50298056</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>13/02/2026</t>
-  </si>
-  <si>
-    <t>24/03/26</t>
-  </si>
-  <si>
-    <t>80459</t>
-  </si>
-  <si>
-    <t>831</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>E06000015</t>
-  </si>
-  <si>
-    <t>331, 350, 335, 852, 382, 874, 354, 373, 357, 861</t>
-  </si>
-  <si>
-    <t>[(331, 'outstanding'), (350, 'good'), (335, 'outstanding'), (852, 'good'), (382, 'good'), (874, 'inadequate'), (354, 'requires improvement'), (373, 'good'), (357, 'inadequate'), (861, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>derby</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50281395</t>
-  </si>
-  <si>
-    <t>19/05/2025</t>
-  </si>
-  <si>
-    <t>23/05/2025</t>
-  </si>
-  <si>
-    <t>08/07/25</t>
-  </si>
-  <si>
-    <t>80460</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
-    <t>E10000007</t>
-  </si>
-  <si>
-    <t>891, 933, 935, 926, 860, 878, 893, 929, 838, 885</t>
-  </si>
-  <si>
-    <t>[(891, 'good'), (933, nan), (935, 'requires improvement'), (926, 'outstanding'), (860, 'requires improvement'), (878, 'inadequate'), (893, 'outstanding'), (929, 'outstanding'), (838, 'outstanding'), (885, 'good')]</t>
-  </si>
-  <si>
-    <t>derbyshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50237006</t>
-  </si>
-  <si>
-    <t>30/10/2023</t>
-  </si>
-  <si>
-    <t>10/11/2023</t>
-  </si>
-  <si>
-    <t>12/01/24</t>
-  </si>
-  <si>
-    <t>80461</t>
-  </si>
-  <si>
-    <t>878</t>
-  </si>
-  <si>
-    <t>E10000008</t>
-  </si>
-  <si>
-    <t>845, 838, 926, 886, 933, 935, 938, 830, 881, 885</t>
-  </si>
-  <si>
-    <t>[(845, 'good'), (838, 'outstanding'), (926, 'outstanding'), (886, 'good'), (933, nan), (935, 'requires improvement'), (938, 'requires improvement'), (830, 'good'), (881, 'outstanding'), (885, 'good')]</t>
-  </si>
-  <si>
-    <t>devon</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50276862</t>
-  </si>
-  <si>
-    <t>30/09/2024</t>
-  </si>
-  <si>
-    <t>11/10/2024</t>
-  </si>
-  <si>
-    <t>13/05/25</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>80462</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>E08000017</t>
-  </si>
-  <si>
-    <t>372, 370, 384, 894, 357, 812, 335, 861, 354, 813</t>
-  </si>
-  <si>
-    <t>[(372, 'outstanding'), (370, 'good'), (384, 'good'), (894, 'outstanding'), (357, 'inadequate'), (812, 'good'), (335, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (813, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>doncaster</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50271937</t>
-  </si>
-  <si>
-    <t>20/01/2025</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>18/03/25</t>
-  </si>
-  <si>
-    <t>2532283</t>
-  </si>
-  <si>
-    <t>838</t>
-  </si>
-  <si>
-    <t>E10000009</t>
-  </si>
-  <si>
-    <t>933, 878, 893, 935, 885, 881, 830, 886, 938, 815</t>
-  </si>
-  <si>
-    <t>[(933, nan), (878, 'inadequate'), (893, 'outstanding'), (935, 'requires improvement'), (885, 'good'), (881, 'outstanding'), (830, 'good'), (886, 'good'), (938, 'requires improvement'), (815, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>dorset</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50276411</t>
-  </si>
-  <si>
-    <t>17/03/2025</t>
-  </si>
-  <si>
-    <t>21/03/2025</t>
-  </si>
-  <si>
-    <t>09/05/25</t>
-  </si>
-  <si>
-    <t>80464</t>
-  </si>
-  <si>
-    <t>332</t>
-  </si>
-  <si>
-    <t>E08000027</t>
-  </si>
-  <si>
-    <t>384, 894, 808, 372, 370, 887, 357, 888, 841, 925</t>
-  </si>
-  <si>
-    <t>[(384, 'good'), (894, 'outstanding'), (808, 'requires improvement'), (372, 'outstanding'), (370, 'good'), (887, 'good'), (357, 'inadequate'), (888, 'good'), (841, 'outstanding'), (925, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>dudley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50204402</t>
-  </si>
-  <si>
-    <t>31/10/2022</t>
-  </si>
-  <si>
-    <t>11/11/2022</t>
-  </si>
-  <si>
-    <t>13/01/23</t>
-  </si>
-  <si>
-    <t>inspection_pre_dates_judgement</t>
-  </si>
-  <si>
-    <t>80465</t>
-  </si>
-  <si>
-    <t>840</t>
-  </si>
-  <si>
-    <t>E06000047</t>
-  </si>
-  <si>
-    <t>876, 344, 390, 807, 372, 370, 394, 393, 808, 841</t>
-  </si>
-  <si>
-    <t>[(876, 'inadequate'), (344, 'requires improvement'), (390, 'good'), (807, 'good'), (372, 'outstanding'), (370, 'good'), (394, 'outstanding'), (393, 'inadequate'), (808, 'requires improvement'), (841, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>durham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50276863</t>
-  </si>
-  <si>
-    <t>ceri evans</t>
-  </si>
-  <si>
-    <t>80466</t>
-  </si>
-  <si>
-    <t>811</t>
-  </si>
-  <si>
-    <t>E06000011</t>
-  </si>
-  <si>
-    <t>860, 893, 815, 877, 855, 933, 884, 943, 937, 830</t>
-  </si>
-  <si>
-    <t>[(860, 'requires improvement'), (893, 'outstanding'), (815, 'outstanding'), (877, 'good'), (855, 'outstanding'), (933, nan), (884, 'good'), (943, 'good'), (937, 'requires improvement'), (830, 'good')]</t>
-  </si>
-  <si>
-    <t>east riding of yorkshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50212242</t>
-  </si>
-  <si>
-    <t>louise walker</t>
-  </si>
-  <si>
-    <t>30/01/2023</t>
-  </si>
-  <si>
-    <t>10/02/2023</t>
-  </si>
-  <si>
-    <t>24/03/23</t>
-  </si>
-  <si>
-    <t>80467</t>
-  </si>
-  <si>
-    <t>845</t>
-  </si>
-  <si>
-    <t>E10000011</t>
-  </si>
-  <si>
-    <t>878, 886, 908, 926, 881, 351, 838, 938, 929, 839</t>
-  </si>
-  <si>
-    <t>[(878, 'inadequate'), (886, 'good'), (908, 'good'), (926, 'outstanding'), (881, 'outstanding'), (351, 'requires improvement'), (838, 'outstanding'), (938, 'requires improvement'), (929, 'outstanding'), (839, 'good')]</t>
-  </si>
-  <si>
-    <t>east sussex</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50239111</t>
-  </si>
-  <si>
-    <t>tom anthony</t>
-  </si>
-  <si>
-    <t>11/12/2023</t>
-  </si>
-  <si>
-    <t>15/12/2023</t>
-  </si>
-  <si>
-    <t>06/02/24</t>
-  </si>
-  <si>
     <t>80468</t>
   </si>
   <si>
@@ -1249,7 +1249,7 @@
     <t>841, 357, 393, 372, 808, 840, 807, 394, 332, 384</t>
   </si>
   <si>
-    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, 'inadequate'), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, 'requires improvement'), (384, 'good')]</t>
+    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, nan), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, 'requires improvement'), (384, 'good')]</t>
   </si>
   <si>
     <t>gateshead</t>
@@ -1363,7 +1363,7 @@
     <t>807, 394, 393, 890, 806, 390, 840, 876, 372, 340</t>
   </si>
   <si>
-    <t>[(807, 'good'), (394, 'outstanding'), (393, 'inadequate'), (890, nan), (806, nan), (390, 'good'), (840, 'outstanding'), (876, 'inadequate'), (372, 'outstanding'), (340, 'inadequate')]</t>
+    <t>[(807, 'good'), (394, 'outstanding'), (393, nan), (890, nan), (806, nan), (390, 'good'), (840, 'outstanding'), (876, 'inadequate'), (372, 'outstanding'), (340, 'inadequate')]</t>
   </si>
   <si>
     <t>hartlepool</t>
@@ -1420,7 +1420,7 @@
     <t>931, 825, 873, 867, 938, 305, 850, 358, 916, 869</t>
   </si>
   <si>
-    <t>[(931, 'good'), (825, 'requires improvement'), (873, 'requires improvement'), (867, 'outstanding'), (938, 'requires improvement'), (305, 'outstanding'), (850, 'outstanding'), (358, 'requires improvement'), (916, 'good'), (869, 'good')]</t>
+    <t>[(931, 'good'), (825, 'requires improvement'), (873, 'requires improvement'), (867, 'outstanding'), (938, 'requires improvement'), (305, 'outstanding'), (850, 'outstanding'), (358, nan), (916, 'good'), (869, 'good')]</t>
   </si>
   <si>
     <t>hertfordshire</t>
@@ -1555,7 +1555,7 @@
     <t>342, 876, 394, 805, 807, 343, 344, 393, 840, 341</t>
   </si>
   <si>
-    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, 'inadequate'), (840, 'outstanding'), (341, nan)]</t>
+    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, nan), (840, 'outstanding'), (341, nan)]</t>
   </si>
   <si>
     <t>knowsley</t>
@@ -1726,7 +1726,7 @@
     <t>890, 805, 806, 355, 393, 340, 394, 391, 807, 354</t>
   </si>
   <si>
-    <t>[(890, nan), (805, 'outstanding'), (806, nan), (355, 'good'), (393, 'inadequate'), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
+    <t>[(890, nan), (805, 'outstanding'), (806, nan), (355, 'good'), (393, nan), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
   </si>
   <si>
     <t>liverpool</t>
@@ -1864,7 +1864,7 @@
     <t>919, 358, 825, 869, 867, 931, 850, 868, 334, 936</t>
   </si>
   <si>
-    <t>[(919, 'outstanding'), (358, 'requires improvement'), (825, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (931, 'good'), (850, 'outstanding'), (868, 'good'), (334, 'good'), (936, 'good')]</t>
+    <t>[(919, 'outstanding'), (358, nan), (825, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (931, 'good'), (850, 'outstanding'), (868, 'good'), (334, 'good'), (936, 'good')]</t>
   </si>
   <si>
     <t>bromley</t>
@@ -2365,7 +2365,7 @@
     <t>868, 314, 936, 872, 305, 358, 825, 919, 800, 869</t>
   </si>
   <si>
-    <t>[(868, 'good'), (314, 'outstanding'), (936, 'good'), (872, 'requires improvement'), (305, 'outstanding'), (358, 'requires improvement'), (825, 'requires improvement'), (919, 'outstanding'), (800, 'good'), (869, 'good')]</t>
+    <t>[(868, 'good'), (314, 'outstanding'), (936, 'good'), (872, 'requires improvement'), (305, 'outstanding'), (358, nan), (825, 'requires improvement'), (919, 'outstanding'), (800, 'good'), (869, 'good')]</t>
   </si>
   <si>
     <t>richmond upon thames</t>
@@ -2617,7 +2617,7 @@
     <t>890, 805, 861, 354, 391, 336, 335, 393, 341, 355</t>
   </si>
   <si>
-    <t>[(890, nan), (805, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (391, 'good'), (336, 'good'), (335, 'outstanding'), (393, 'inadequate'), (341, nan), (355, 'good')]</t>
+    <t>[(890, nan), (805, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (391, 'good'), (336, 'good'), (335, 'outstanding'), (393, nan), (341, nan), (355, 'good')]</t>
   </si>
   <si>
     <t>middlesbrough</t>
@@ -3130,7 +3130,7 @@
     <t>394, 393, 805, 372, 390, 840, 370, 357, 371, 880</t>
   </si>
   <si>
-    <t>[(394, 'outstanding'), (393, 'inadequate'), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
+    <t>[(394, 'outstanding'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
   </si>
   <si>
     <t>redcar and cleveland</t>
@@ -3226,7 +3226,7 @@
     <t>319, 315, 919, 305, 800, 868, 358, 318, 936, 825</t>
   </si>
   <si>
-    <t>[(319, 'good'), (315, 'outstanding'), (919, 'outstanding'), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, 'requires improvement'), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
+    <t>[(319, 'good'), (315, 'outstanding'), (919, 'outstanding'), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, nan), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
   </si>
   <si>
     <t>kingston upon thames</t>
@@ -3247,7 +3247,7 @@
     <t>936, 825, 872, 358, 919, 869, 305, 823, 931, 867</t>
   </si>
   <si>
-    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, 'requires improvement'), (919, 'outstanding'), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
+    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
   </si>
   <si>
     <t>windsor &amp; maidenhead</t>
@@ -3298,7 +3298,7 @@
     <t>373, 354, 851, 391, 390, 350, 393, 357, 852, 383</t>
   </si>
   <si>
-    <t>[(373, 'good'), (354, 'requires improvement'), (851, 'good'), (391, 'good'), (390, 'good'), (350, 'good'), (393, 'inadequate'), (357, 'inadequate'), (852, 'good'), (383, 'outstanding')]</t>
+    <t>[(373, 'good'), (354, 'requires improvement'), (851, 'good'), (391, 'good'), (390, 'good'), (350, 'good'), (393, nan), (357, 'inadequate'), (852, 'good'), (383, 'outstanding')]</t>
   </si>
   <si>
     <t>salford</t>
@@ -3520,13 +3520,16 @@
     <t>south tyneside</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50216273</t>
-  </si>
-  <si>
-    <t>05/12/2022</t>
-  </si>
-  <si>
-    <t>10/05/23</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50308876</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>04/08/26</t>
   </si>
   <si>
     <t>80558</t>
@@ -3634,7 +3637,7 @@
     <t>334, 358, 896, 916, 919, 938, 937, 802, 803, 873</t>
   </si>
   <si>
-    <t>[(334, 'good'), (358, 'requires improvement'), (896, 'requires improvement'), (916, 'good'), (919, 'outstanding'), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
+    <t>[(334, 'good'), (358, nan), (896, 'requires improvement'), (916, 'good'), (919, 'outstanding'), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
   </si>
   <si>
     <t>stockport</t>
@@ -3736,7 +3739,7 @@
     <t>807, 393, 805, 372, 357, 880, 390, 840, 370, 354</t>
   </si>
   <si>
-    <t>[(807, 'good'), (393, 'inadequate'), (805, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (880, 'good'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (354, 'requires improvement')]</t>
+    <t>[(807, 'good'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (880, 'good'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (354, 'requires improvement')]</t>
   </si>
   <si>
     <t>sunderland</t>
@@ -3760,7 +3763,7 @@
     <t>868, 825, 358, 919, 869, 823, 872, 931, 867, 873</t>
   </si>
   <si>
-    <t>[(868, 'good'), (825, 'requires improvement'), (358, 'requires improvement'), (919, 'outstanding'), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
+    <t>[(868, 'good'), (825, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
   </si>
   <si>
     <t>surrey</t>
@@ -3907,16 +3910,13 @@
     <t>trafford</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50206433</t>
-  </si>
-  <si>
-    <t>21/11/2022</t>
-  </si>
-  <si>
-    <t>02/12/2022</t>
-  </si>
-  <si>
-    <t>31/01/23</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50308602</t>
+  </si>
+  <si>
+    <t>leanne cooper</t>
+  </si>
+  <si>
+    <t>03/08/26</t>
   </si>
   <si>
     <t>80574</t>
@@ -4159,7 +4159,7 @@
     <t>840, 343, 876, 808, 394, 390, 807, 888, 351, 393</t>
   </si>
   <si>
-    <t>[(840, 'outstanding'), (343, 'good'), (876, 'inadequate'), (808, 'requires improvement'), (394, 'outstanding'), (390, 'good'), (807, 'good'), (888, 'good'), (351, 'requires improvement'), (393, 'inadequate')]</t>
+    <t>[(840, 'outstanding'), (343, 'good'), (876, 'inadequate'), (808, 'requires improvement'), (394, 'outstanding'), (390, 'good'), (807, 'good'), (888, 'good'), (351, 'requires improvement'), (393, nan)]</t>
   </si>
   <si>
     <t>wirral</t>
@@ -4186,7 +4186,7 @@
     <t>868, 936, 825, 869, 305, 358, 318, 919, 867, 823</t>
   </si>
   <si>
-    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, 'requires improvement'), (318, 'outstanding'), (919, 'outstanding'), (867, 'outstanding'), (823, 'good')]</t>
+    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, nan), (318, 'outstanding'), (919, 'outstanding'), (867, 'outstanding'), (823, 'good')]</t>
   </si>
   <si>
     <t>wokingham</t>
@@ -5046,67 +5046,67 @@
         <v>14</v>
       </c>
       <c r="T6" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" t="s">
         <v>48</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O7" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80431_blackpool", ".\export_data\inspection_reports\80431_blackpool")</f>
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="s">
         <v>8</v>
       </c>
       <c r="R7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s">
         <v>53</v>
@@ -5114,28 +5114,28 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -5144,7 +5144,7 @@
         <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s">
         <v>11</v>
@@ -5177,28 +5177,28 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I9" t="s">
         <v>8</v>
@@ -5210,13 +5210,13 @@
         <v>49</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O9" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2532287_bournemouth, christchurch &amp; poole", ".\export_data\inspection_reports\2532287_bournemouth, christchurch &amp; poole")</f>
@@ -5240,62 +5240,62 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O10" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80436_bracknell forest", ".\export_data\inspection_reports\80436_bracknell forest")</f>
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s">
         <v>53</v>
@@ -5303,85 +5303,85 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O11" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80438_brighton and hove", ".\export_data\inspection_reports\80438_brighton and hove")</f>
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="s">
         <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -5390,16 +5390,16 @@
         <v>48</v>
       </c>
       <c r="K12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O12" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80441_bristol", ".\export_data\inspection_reports\80441_bristol")</f>
@@ -5423,28 +5423,28 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -5453,16 +5453,16 @@
         <v>48</v>
       </c>
       <c r="K13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O13" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80442_buckinghamshire", ".\export_data\inspection_reports\80442_buckinghamshire")</f>
@@ -5481,7 +5481,7 @@
         <v>14</v>
       </c>
       <c r="T13" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -5544,33 +5544,33 @@
         <v>14</v>
       </c>
       <c r="T14" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="s">
         <v>154</v>
-      </c>
-      <c r="B15" t="s">
-        <v>155</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" t="s">
         <v>156</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>157</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>158</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="I15" t="s">
         <v>8</v>
@@ -5579,16 +5579,16 @@
         <v>9</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" t="s">
         <v>161</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>162</v>
-      </c>
-      <c r="N15" t="s">
-        <v>163</v>
       </c>
       <c r="O15" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80444_calderdale", ".\export_data\inspection_reports\80444_calderdale")</f>
@@ -5612,28 +5612,28 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
         <v>164</v>
-      </c>
-      <c r="B16" t="s">
-        <v>165</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
       </c>
       <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" t="s">
         <v>166</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>167</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>168</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
@@ -5642,16 +5642,16 @@
         <v>48</v>
       </c>
       <c r="K16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L16" t="s">
+        <v>170</v>
+      </c>
+      <c r="M16" t="s">
         <v>171</v>
       </c>
-      <c r="M16" t="s">
-        <v>172</v>
-      </c>
       <c r="N16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O16" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80445_cambridgeshire", ".\export_data\inspection_reports\80445_cambridgeshire")</f>
@@ -5675,28 +5675,28 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" t="s">
         <v>173</v>
-      </c>
-      <c r="B17" t="s">
-        <v>174</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" t="s">
         <v>175</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>176</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>177</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="I17" t="s">
         <v>8</v>
@@ -5705,16 +5705,16 @@
         <v>9</v>
       </c>
       <c r="K17" t="s">
+        <v>179</v>
+      </c>
+      <c r="L17" t="s">
         <v>180</v>
-      </c>
-      <c r="L17" t="s">
-        <v>181</v>
       </c>
       <c r="M17" t="s">
         <v>64</v>
       </c>
       <c r="N17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O17" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80446_central bedfordshire", ".\export_data\inspection_reports\80446_central bedfordshire")</f>
@@ -5733,51 +5733,51 @@
         <v>8</v>
       </c>
       <c r="T17" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" t="s">
         <v>183</v>
-      </c>
-      <c r="B18" t="s">
-        <v>184</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
       </c>
       <c r="D18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" t="s">
         <v>185</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>186</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>187</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" t="s">
         <v>189</v>
-      </c>
-      <c r="I18" t="s">
-        <v>190</v>
       </c>
       <c r="J18" t="s">
         <v>48</v>
       </c>
       <c r="K18" t="s">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s">
         <v>191</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>192</v>
       </c>
-      <c r="M18" t="s">
-        <v>193</v>
-      </c>
       <c r="N18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O18" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80447_cheshire east", ".\export_data\inspection_reports\80447_cheshire east")</f>
@@ -5793,7 +5793,7 @@
         <v>14</v>
       </c>
       <c r="S18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T18" t="s">
         <v>15</v>
@@ -5801,28 +5801,28 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s">
         <v>194</v>
-      </c>
-      <c r="B19" t="s">
-        <v>195</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
       </c>
       <c r="D19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" t="s">
         <v>196</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>197</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>198</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
@@ -5831,16 +5831,16 @@
         <v>9</v>
       </c>
       <c r="K19" t="s">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s">
         <v>201</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>202</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>203</v>
-      </c>
-      <c r="N19" t="s">
-        <v>204</v>
       </c>
       <c r="O19" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80448_cheshire west and chester", ".\export_data\inspection_reports\80448_cheshire west and chester")</f>
@@ -5859,33 +5859,33 @@
         <v>14</v>
       </c>
       <c r="T19" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
         <v>205</v>
-      </c>
-      <c r="B20" t="s">
-        <v>206</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
       </c>
       <c r="D20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" t="s">
         <v>207</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>208</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>209</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="I20" t="s">
         <v>14</v>
@@ -5894,16 +5894,16 @@
         <v>48</v>
       </c>
       <c r="K20" t="s">
+        <v>211</v>
+      </c>
+      <c r="L20" t="s">
         <v>212</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>213</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>214</v>
-      </c>
-      <c r="N20" t="s">
-        <v>215</v>
       </c>
       <c r="O20" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80449_bradford", ".\export_data\inspection_reports\80449_bradford")</f>
@@ -5922,96 +5922,96 @@
         <v>8</v>
       </c>
       <c r="T20" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s">
         <v>216</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>217</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>218</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>219</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>220</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>221</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s">
         <v>9</v>
       </c>
       <c r="K21" t="s">
+        <v>223</v>
+      </c>
+      <c r="L21" t="s">
         <v>224</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>225</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>226</v>
-      </c>
-      <c r="N21" t="s">
-        <v>227</v>
       </c>
       <c r="O21" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80450_london corporation", ".\export_data\inspection_reports\80450_london corporation")</f>
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q21" t="s">
         <v>8</v>
       </c>
       <c r="R21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" t="s">
         <v>229</v>
-      </c>
-      <c r="B22" t="s">
-        <v>230</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
       </c>
       <c r="D22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" t="s">
         <v>231</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>232</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>233</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="I22" t="s">
         <v>8</v>
@@ -6020,16 +6020,16 @@
         <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s">
+        <v>235</v>
+      </c>
+      <c r="M22" t="s">
         <v>236</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>237</v>
-      </c>
-      <c r="N22" t="s">
-        <v>238</v>
       </c>
       <c r="O22" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80451_wakefield", ".\export_data\inspection_reports\80451_wakefield")</f>
@@ -6042,73 +6042,73 @@
         <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s">
         <v>14</v>
       </c>
       <c r="T22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" t="s">
         <v>239</v>
-      </c>
-      <c r="B23" t="s">
-        <v>240</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
       </c>
       <c r="D23" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" t="s">
         <v>241</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>242</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s">
         <v>48</v>
       </c>
       <c r="K23" t="s">
+        <v>245</v>
+      </c>
+      <c r="L23" t="s">
         <v>246</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>247</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>248</v>
-      </c>
-      <c r="N23" t="s">
-        <v>249</v>
       </c>
       <c r="O23" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80453_york", ".\export_data\inspection_reports\80453_york")</f>
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s">
         <v>53</v>
@@ -6116,28 +6116,28 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" t="s">
         <v>250</v>
-      </c>
-      <c r="B24" t="s">
-        <v>251</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E24" t="s">
         <v>252</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>253</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>254</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="I24" t="s">
         <v>8</v>
@@ -6146,16 +6146,16 @@
         <v>9</v>
       </c>
       <c r="K24" t="s">
+        <v>256</v>
+      </c>
+      <c r="L24" t="s">
         <v>257</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>258</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>259</v>
-      </c>
-      <c r="N24" t="s">
-        <v>260</v>
       </c>
       <c r="O24" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80454_cornwall", ".\export_data\inspection_reports\80454_cornwall")</f>
@@ -6171,7 +6171,7 @@
         <v>8</v>
       </c>
       <c r="S24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s">
         <v>53</v>
@@ -6179,56 +6179,56 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" t="s">
         <v>261</v>
-      </c>
-      <c r="B25" t="s">
-        <v>262</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
+        <v>262</v>
+      </c>
+      <c r="E25" t="s">
         <v>263</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>264</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>265</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="I25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J25" t="s">
         <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
+        <v>267</v>
+      </c>
+      <c r="M25" t="s">
         <v>268</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>269</v>
-      </c>
-      <c r="N25" t="s">
-        <v>270</v>
       </c>
       <c r="O25" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80455_isles of scilly", ".\export_data\inspection_reports\80455_isles of scilly")</f>
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R25" t="s">
         <v>14</v>
@@ -6242,62 +6242,62 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" t="s">
         <v>271</v>
-      </c>
-      <c r="B26" t="s">
-        <v>272</v>
       </c>
       <c r="C26" t="s">
         <v>42</v>
       </c>
       <c r="D26" t="s">
+        <v>272</v>
+      </c>
+      <c r="E26" t="s">
         <v>273</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>274</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>275</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
       </c>
       <c r="K26" t="s">
+        <v>277</v>
+      </c>
+      <c r="L26" t="s">
         <v>278</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>279</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>280</v>
-      </c>
-      <c r="N26" t="s">
-        <v>281</v>
       </c>
       <c r="O26" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80456_coventry", ".\export_data\inspection_reports\80456_coventry")</f>
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q26" t="s">
         <v>8</v>
       </c>
       <c r="R26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s">
         <v>15</v>
@@ -6305,28 +6305,28 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" t="s">
         <v>282</v>
-      </c>
-      <c r="B27" t="s">
-        <v>283</v>
       </c>
       <c r="C27" t="s">
         <v>56</v>
       </c>
       <c r="D27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E27" t="s">
         <v>284</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>285</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>286</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="I27" t="s">
         <v>8</v>
@@ -6335,16 +6335,16 @@
         <v>48</v>
       </c>
       <c r="K27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L27" t="s">
+        <v>288</v>
+      </c>
+      <c r="M27" t="s">
         <v>289</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>290</v>
-      </c>
-      <c r="N27" t="s">
-        <v>291</v>
       </c>
       <c r="O27" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2733690_cumberland", ".\export_data\inspection_reports\2733690_cumberland")</f>
@@ -6368,31 +6368,31 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" t="s">
         <v>292</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>293</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>294</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>295</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>296</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>297</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="I28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J28" t="s">
         <v>9</v>
@@ -6401,92 +6401,92 @@
         <v>62</v>
       </c>
       <c r="L28" t="s">
+        <v>299</v>
+      </c>
+      <c r="M28" t="s">
         <v>300</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>301</v>
-      </c>
-      <c r="N28" t="s">
-        <v>302</v>
       </c>
       <c r="O28" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80458_darlington", ".\export_data\inspection_reports\80458_darlington")</f>
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q28" t="s">
         <v>8</v>
       </c>
       <c r="R28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T28" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" t="s">
         <v>303</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>304</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>305</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>306</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>307</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>308</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="I29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s">
         <v>9</v>
       </c>
       <c r="K29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L29" t="s">
+        <v>310</v>
+      </c>
+      <c r="M29" t="s">
         <v>311</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>312</v>
-      </c>
-      <c r="N29" t="s">
-        <v>313</v>
       </c>
       <c r="O29" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80459_derby", ".\export_data\inspection_reports\80459_derby")</f>
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T29" t="s">
         <v>53</v>
@@ -6494,28 +6494,28 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
         <v>314</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" t="s">
         <v>315</v>
       </c>
-      <c r="C30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>316</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>317</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>318</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="I30" t="s">
         <v>8</v>
@@ -6527,13 +6527,13 @@
         <v>49</v>
       </c>
       <c r="L30" t="s">
+        <v>320</v>
+      </c>
+      <c r="M30" t="s">
         <v>321</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>322</v>
-      </c>
-      <c r="N30" t="s">
-        <v>323</v>
       </c>
       <c r="O30" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80460_derbyshire", ".\export_data\inspection_reports\80460_derbyshire")</f>
@@ -6557,46 +6557,46 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" t="s">
         <v>324</v>
-      </c>
-      <c r="B31" t="s">
-        <v>325</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
+        <v>325</v>
+      </c>
+      <c r="E31" t="s">
         <v>326</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>327</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>328</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="I31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J31" t="s">
         <v>48</v>
       </c>
       <c r="K31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s">
+        <v>330</v>
+      </c>
+      <c r="M31" t="s">
         <v>331</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>332</v>
-      </c>
-      <c r="N31" t="s">
-        <v>333</v>
       </c>
       <c r="O31" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80461_devon", ".\export_data\inspection_reports\80461_devon")</f>
@@ -6606,42 +6606,42 @@
         <v>14</v>
       </c>
       <c r="Q31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
         <v>335</v>
-      </c>
-      <c r="B32" t="s">
-        <v>336</v>
       </c>
       <c r="C32" t="s">
         <v>2</v>
       </c>
       <c r="D32" t="s">
+        <v>336</v>
+      </c>
+      <c r="E32" t="s">
         <v>337</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>338</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>339</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="I32" t="s">
         <v>8</v>
@@ -6650,16 +6650,16 @@
         <v>48</v>
       </c>
       <c r="K32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L32" t="s">
+        <v>341</v>
+      </c>
+      <c r="M32" t="s">
         <v>342</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>343</v>
-      </c>
-      <c r="N32" t="s">
-        <v>344</v>
       </c>
       <c r="O32" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80462_doncaster", ".\export_data\inspection_reports\80462_doncaster")</f>
@@ -6678,64 +6678,64 @@
         <v>14</v>
       </c>
       <c r="T32" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" t="s">
         <v>345</v>
-      </c>
-      <c r="B33" t="s">
-        <v>346</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
       <c r="D33" t="s">
+        <v>346</v>
+      </c>
+      <c r="E33" t="s">
         <v>347</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>348</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>349</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="I33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s">
         <v>9</v>
       </c>
       <c r="K33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s">
+        <v>351</v>
+      </c>
+      <c r="M33" t="s">
         <v>352</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>353</v>
-      </c>
-      <c r="N33" t="s">
-        <v>354</v>
       </c>
       <c r="O33" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2532283_dorset", ".\export_data\inspection_reports\2532283_dorset")</f>
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s">
         <v>8</v>
@@ -6746,28 +6746,28 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
+        <v>354</v>
+      </c>
+      <c r="B34" t="s">
         <v>355</v>
-      </c>
-      <c r="B34" t="s">
-        <v>356</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
       </c>
       <c r="D34" t="s">
+        <v>356</v>
+      </c>
+      <c r="E34" t="s">
         <v>357</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>358</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>359</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -6779,13 +6779,13 @@
         <v>49</v>
       </c>
       <c r="L34" t="s">
+        <v>361</v>
+      </c>
+      <c r="M34" t="s">
         <v>362</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>363</v>
-      </c>
-      <c r="N34" t="s">
-        <v>364</v>
       </c>
       <c r="O34" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80464_dudley", ".\export_data\inspection_reports\80464_dudley")</f>
@@ -6801,7 +6801,7 @@
         <v>14</v>
       </c>
       <c r="S34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T34" t="s">
         <v>53</v>
@@ -6809,62 +6809,62 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
+        <v>365</v>
+      </c>
+      <c r="B35" t="s">
         <v>366</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>293</v>
+      </c>
+      <c r="D35" t="s">
         <v>367</v>
       </c>
-      <c r="C35" t="s">
-        <v>294</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>368</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>369</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>370</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="I35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s">
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L35" t="s">
+        <v>235</v>
+      </c>
+      <c r="M35" t="s">
         <v>236</v>
       </c>
-      <c r="M35" t="s">
-        <v>237</v>
-      </c>
       <c r="N35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O35" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80465_durham", ".\export_data\inspection_reports\80465_durham")</f>
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q35" t="s">
         <v>8</v>
       </c>
       <c r="R35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s">
         <v>53</v>
@@ -6872,28 +6872,28 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B36" t="s">
         <v>374</v>
-      </c>
-      <c r="B36" t="s">
-        <v>375</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
+        <v>375</v>
+      </c>
+      <c r="E36" t="s">
         <v>376</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>377</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>378</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="I36" t="s">
         <v>8</v>
@@ -6902,16 +6902,16 @@
         <v>48</v>
       </c>
       <c r="K36" t="s">
+        <v>380</v>
+      </c>
+      <c r="L36" t="s">
         <v>381</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>382</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>383</v>
-      </c>
-      <c r="N36" t="s">
-        <v>384</v>
       </c>
       <c r="O36" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80466_east riding of yorkshire", ".\export_data\inspection_reports\80466_east riding of yorkshire")</f>
@@ -6935,28 +6935,28 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37" t="s">
         <v>385</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
         <v>386</v>
       </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>387</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>388</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>389</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="I37" t="s">
         <v>8</v>
@@ -6965,16 +6965,16 @@
         <v>9</v>
       </c>
       <c r="K37" t="s">
+        <v>391</v>
+      </c>
+      <c r="L37" t="s">
         <v>392</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>393</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>394</v>
-      </c>
-      <c r="N37" t="s">
-        <v>395</v>
       </c>
       <c r="O37" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80467_east sussex", ".\export_data\inspection_reports\80467_east sussex")</f>
@@ -6987,13 +6987,13 @@
         <v>8</v>
       </c>
       <c r="R37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S37" t="s">
         <v>8</v>
       </c>
       <c r="T37" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -7022,7 +7022,7 @@
         <v>402</v>
       </c>
       <c r="I38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
@@ -7044,16 +7044,16 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T38" t="s">
         <v>15</v>
@@ -7067,7 +7067,7 @@
         <v>408</v>
       </c>
       <c r="C39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D39" t="s">
         <v>409</v>
@@ -7091,16 +7091,16 @@
         <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M39" t="s">
         <v>414</v>
       </c>
       <c r="N39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O39" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80469_gateshead", ".\export_data\inspection_reports\80469_gateshead")</f>
@@ -7154,7 +7154,7 @@
         <v>48</v>
       </c>
       <c r="K40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L40" t="s">
         <v>25</v>
@@ -7170,13 +7170,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q40" t="s">
         <v>8</v>
       </c>
       <c r="R40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S40" t="s">
         <v>8</v>
@@ -7211,7 +7211,7 @@
         <v>429</v>
       </c>
       <c r="I41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J41" t="s">
         <v>48</v>
@@ -7233,16 +7233,16 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T41" t="s">
         <v>434</v>
@@ -7256,7 +7256,7 @@
         <v>436</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
         <v>437</v>
@@ -7274,7 +7274,7 @@
         <v>441</v>
       </c>
       <c r="I42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -7296,13 +7296,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S42" t="s">
         <v>8</v>
@@ -7319,7 +7319,7 @@
         <v>446</v>
       </c>
       <c r="C43" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D43" t="s">
         <v>447</v>
@@ -7337,13 +7337,13 @@
         <v>451</v>
       </c>
       <c r="I43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L43" t="s">
         <v>452</v>
@@ -7352,20 +7352,20 @@
         <v>453</v>
       </c>
       <c r="N43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O43" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80473_hartlepool", ".\export_data\inspection_reports\80473_hartlepool")</f>
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S43" t="s">
         <v>8</v>
@@ -7422,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q44" t="s">
         <v>8</v>
@@ -7434,7 +7434,7 @@
         <v>8</v>
       </c>
       <c r="T44" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -7463,35 +7463,35 @@
         <v>470</v>
       </c>
       <c r="I45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s">
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L45" t="s">
         <v>471</v>
       </c>
       <c r="M45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O45" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80475_hertfordshire", ".\export_data\inspection_reports\80475_hertfordshire")</f>
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q45" t="s">
         <v>8</v>
       </c>
       <c r="R45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S45" t="s">
         <v>8</v>
@@ -7508,7 +7508,7 @@
         <v>473</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
         <v>474</v>
@@ -7535,7 +7535,7 @@
         <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s">
         <v>479</v>
@@ -7571,7 +7571,7 @@
         <v>482</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
         <v>483</v>
@@ -7617,7 +7617,7 @@
         <v>8</v>
       </c>
       <c r="R47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S47" t="s">
         <v>14</v>
@@ -7658,23 +7658,23 @@
         <v>48</v>
       </c>
       <c r="K48" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L48" t="s">
         <v>499</v>
       </c>
       <c r="M48" t="s">
+        <v>279</v>
+      </c>
+      <c r="N48" t="s">
         <v>280</v>
-      </c>
-      <c r="N48" t="s">
-        <v>281</v>
       </c>
       <c r="O48" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80477_kingston upon hull", ".\export_data\inspection_reports\80477_kingston upon hull")</f>
         <v>0</v>
       </c>
       <c r="P48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q48" t="s">
         <v>8</v>
@@ -7683,7 +7683,7 @@
         <v>8</v>
       </c>
       <c r="S48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T48" t="s">
         <v>53</v>
@@ -7727,10 +7727,10 @@
         <v>508</v>
       </c>
       <c r="M49" t="s">
+        <v>202</v>
+      </c>
+      <c r="N49" t="s">
         <v>203</v>
-      </c>
-      <c r="N49" t="s">
-        <v>204</v>
       </c>
       <c r="O49" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80478_kirklees", ".\export_data\inspection_reports\80478_kirklees")</f>
@@ -7778,7 +7778,7 @@
         <v>515</v>
       </c>
       <c r="I50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J50" t="s">
         <v>48</v>
@@ -7800,16 +7800,16 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R50" t="s">
         <v>14</v>
       </c>
       <c r="S50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T50" t="s">
         <v>15</v>
@@ -7847,7 +7847,7 @@
         <v>48</v>
       </c>
       <c r="K51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L51" t="s">
         <v>527</v>
@@ -7872,7 +7872,7 @@
         <v>8</v>
       </c>
       <c r="S51" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T51" t="s">
         <v>53</v>
@@ -7904,13 +7904,13 @@
         <v>536</v>
       </c>
       <c r="I52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
       </c>
       <c r="K52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L52" t="s">
         <v>537</v>
@@ -7926,19 +7926,19 @@
         <v>0</v>
       </c>
       <c r="P52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q52" t="s">
         <v>8</v>
       </c>
       <c r="R52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T52" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -7949,7 +7949,7 @@
         <v>541</v>
       </c>
       <c r="C53" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D53" t="s">
         <v>542</v>
@@ -7973,16 +7973,16 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s">
+        <v>224</v>
+      </c>
+      <c r="M53" t="s">
         <v>225</v>
       </c>
-      <c r="M53" t="s">
-        <v>226</v>
-      </c>
       <c r="N53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O53" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80482_leicester", ".\export_data\inspection_reports\80482_leicester")</f>
@@ -8001,7 +8001,7 @@
         <v>14</v>
       </c>
       <c r="T53" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -8012,7 +8012,7 @@
         <v>548</v>
       </c>
       <c r="C54" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D54" t="s">
         <v>549</v>
@@ -8030,13 +8030,13 @@
         <v>553</v>
       </c>
       <c r="I54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J54" t="s">
         <v>48</v>
       </c>
       <c r="K54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L54" t="s">
         <v>554</v>
@@ -8052,16 +8052,16 @@
         <v>0</v>
       </c>
       <c r="P54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q54" t="s">
         <v>8</v>
       </c>
       <c r="R54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T54" t="s">
         <v>53</v>
@@ -8075,7 +8075,7 @@
         <v>557</v>
       </c>
       <c r="C55" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D55" t="s">
         <v>558</v>
@@ -8093,13 +8093,13 @@
         <v>562</v>
       </c>
       <c r="I55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J55" t="s">
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L55" t="s">
         <v>563</v>
@@ -8115,13 +8115,13 @@
         <v>0</v>
       </c>
       <c r="P55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S55" t="s">
         <v>8</v>
@@ -8156,13 +8156,13 @@
         <v>572</v>
       </c>
       <c r="I56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J56" t="s">
         <v>48</v>
       </c>
       <c r="K56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s">
         <v>573</v>
@@ -8201,7 +8201,7 @@
         <v>577</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D57" t="s">
         <v>578</v>
@@ -8225,7 +8225,7 @@
         <v>48</v>
       </c>
       <c r="K57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s">
         <v>583</v>
@@ -8264,7 +8264,7 @@
         <v>587</v>
       </c>
       <c r="C58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D58" t="s">
         <v>588</v>
@@ -8288,7 +8288,7 @@
         <v>9</v>
       </c>
       <c r="K58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L58" t="s">
         <v>442</v>
@@ -8310,7 +8310,7 @@
         <v>8</v>
       </c>
       <c r="R58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S58" t="s">
         <v>8</v>
@@ -8327,7 +8327,7 @@
         <v>594</v>
       </c>
       <c r="C59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D59" t="s">
         <v>595</v>
@@ -8345,29 +8345,29 @@
         <v>599</v>
       </c>
       <c r="I59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J59" t="s">
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L59" t="s">
         <v>600</v>
       </c>
       <c r="M59" t="s">
+        <v>382</v>
+      </c>
+      <c r="N59" t="s">
         <v>383</v>
-      </c>
-      <c r="N59" t="s">
-        <v>384</v>
       </c>
       <c r="O59" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80488_bexley", ".\export_data\inspection_reports\80488_bexley")</f>
         <v>0</v>
       </c>
       <c r="P59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q59" t="s">
         <v>8</v>
@@ -8376,10 +8376,10 @@
         <v>8</v>
       </c>
       <c r="S59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T59" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -8390,7 +8390,7 @@
         <v>602</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
         <v>603</v>
@@ -8408,7 +8408,7 @@
         <v>607</v>
       </c>
       <c r="I60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -8453,7 +8453,7 @@
         <v>613</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D61" t="s">
         <v>614</v>
@@ -8471,7 +8471,7 @@
         <v>618</v>
       </c>
       <c r="I61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J61" t="s">
         <v>9</v>
@@ -8486,23 +8486,23 @@
         <v>621</v>
       </c>
       <c r="N61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O61" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80490_bromley", ".\export_data\inspection_reports\80490_bromley")</f>
         <v>0</v>
       </c>
       <c r="P61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T61" t="s">
         <v>53</v>
@@ -8516,7 +8516,7 @@
         <v>623</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D62" t="s">
         <v>624</v>
@@ -8534,7 +8534,7 @@
         <v>628</v>
       </c>
       <c r="I62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -8546,26 +8546,26 @@
         <v>63</v>
       </c>
       <c r="M62" t="s">
+        <v>247</v>
+      </c>
+      <c r="N62" t="s">
         <v>248</v>
-      </c>
-      <c r="N62" t="s">
-        <v>249</v>
       </c>
       <c r="O62" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80491_camden", ".\export_data\inspection_reports\80491_camden")</f>
         <v>0</v>
       </c>
       <c r="P62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T62" t="s">
         <v>53</v>
@@ -8579,7 +8579,7 @@
         <v>630</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63" t="s">
         <v>631</v>
@@ -8603,7 +8603,7 @@
         <v>48</v>
       </c>
       <c r="K63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L63" t="s">
         <v>636</v>
@@ -8631,7 +8631,7 @@
         <v>8</v>
       </c>
       <c r="T63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -8642,7 +8642,7 @@
         <v>640</v>
       </c>
       <c r="C64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D64" t="s">
         <v>641</v>
@@ -8666,7 +8666,7 @@
         <v>48</v>
       </c>
       <c r="K64" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L64" t="s">
         <v>554</v>
@@ -8694,7 +8694,7 @@
         <v>8</v>
       </c>
       <c r="T64" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -8705,7 +8705,7 @@
         <v>647</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D65" t="s">
         <v>648</v>
@@ -8729,7 +8729,7 @@
         <v>9</v>
       </c>
       <c r="K65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L65" t="s">
         <v>653</v>
@@ -8751,13 +8751,13 @@
         <v>8</v>
       </c>
       <c r="R65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S65" t="s">
         <v>8</v>
       </c>
       <c r="T65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -8768,7 +8768,7 @@
         <v>657</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D66" t="s">
         <v>658</v>
@@ -8786,13 +8786,13 @@
         <v>662</v>
       </c>
       <c r="I66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J66" t="s">
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L66" t="s">
         <v>663</v>
@@ -8808,19 +8808,19 @@
         <v>0</v>
       </c>
       <c r="P66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q66" t="s">
         <v>8</v>
       </c>
       <c r="R66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T66" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -8831,7 +8831,7 @@
         <v>667</v>
       </c>
       <c r="C67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D67" t="s">
         <v>668</v>
@@ -8855,10 +8855,10 @@
         <v>48</v>
       </c>
       <c r="K67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M67" t="s">
         <v>673</v>
@@ -8894,7 +8894,7 @@
         <v>676</v>
       </c>
       <c r="C68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D68" t="s">
         <v>677</v>
@@ -8912,41 +8912,41 @@
         <v>681</v>
       </c>
       <c r="I68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J68" t="s">
         <v>9</v>
       </c>
       <c r="K68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L68" t="s">
         <v>682</v>
       </c>
       <c r="M68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O68" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80497_hammersmith and fulham", ".\export_data\inspection_reports\80497_hammersmith and fulham")</f>
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q68" t="s">
         <v>8</v>
       </c>
       <c r="R68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -8957,7 +8957,7 @@
         <v>684</v>
       </c>
       <c r="C69" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
         <v>685</v>
@@ -8975,16 +8975,16 @@
         <v>689</v>
       </c>
       <c r="I69" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J69" t="s">
         <v>9</v>
       </c>
       <c r="K69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L69" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M69" t="s">
         <v>690</v>
@@ -8997,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q69" t="s">
         <v>8</v>
@@ -9006,10 +9006,10 @@
         <v>8</v>
       </c>
       <c r="S69" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -9020,7 +9020,7 @@
         <v>693</v>
       </c>
       <c r="C70" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D70" t="s">
         <v>694</v>
@@ -9038,7 +9038,7 @@
         <v>698</v>
       </c>
       <c r="I70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J70" t="s">
         <v>9</v>
@@ -9047,7 +9047,7 @@
         <v>516</v>
       </c>
       <c r="L70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M70" t="s">
         <v>699</v>
@@ -9069,7 +9069,7 @@
         <v>8</v>
       </c>
       <c r="S70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T70" t="s">
         <v>15</v>
@@ -9083,7 +9083,7 @@
         <v>702</v>
       </c>
       <c r="C71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D71" t="s">
         <v>703</v>
@@ -9101,7 +9101,7 @@
         <v>707</v>
       </c>
       <c r="I71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J71" t="s">
         <v>48</v>
@@ -9110,7 +9110,7 @@
         <v>619</v>
       </c>
       <c r="L71" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M71" t="s">
         <v>708</v>
@@ -9123,13 +9123,13 @@
         <v>0</v>
       </c>
       <c r="P71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S71" t="s">
         <v>14</v>
@@ -9146,7 +9146,7 @@
         <v>711</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D72" t="s">
         <v>712</v>
@@ -9164,13 +9164,13 @@
         <v>716</v>
       </c>
       <c r="I72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J72" t="s">
         <v>9</v>
       </c>
       <c r="K72" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L72" t="s">
         <v>717</v>
@@ -9186,19 +9186,19 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q72" t="s">
         <v>8</v>
       </c>
       <c r="R72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S72" t="s">
         <v>8</v>
       </c>
       <c r="T72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -9209,7 +9209,7 @@
         <v>721</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
         <v>722</v>
@@ -9233,7 +9233,7 @@
         <v>9</v>
       </c>
       <c r="K73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L73" t="s">
         <v>727</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q73" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8</v>
       </c>
       <c r="T73" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -9272,7 +9272,7 @@
         <v>731</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D74" t="s">
         <v>732</v>
@@ -9290,38 +9290,38 @@
         <v>736</v>
       </c>
       <c r="I74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J74" t="s">
         <v>9</v>
       </c>
       <c r="K74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M74" t="s">
         <v>414</v>
       </c>
       <c r="N74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O74" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80505_islington", ".\export_data\inspection_reports\80505_islington")</f>
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T74" t="s">
         <v>53</v>
@@ -9335,7 +9335,7 @@
         <v>738</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D75" t="s">
         <v>739</v>
@@ -9362,10 +9362,10 @@
         <v>744</v>
       </c>
       <c r="L75" t="s">
+        <v>212</v>
+      </c>
+      <c r="M75" t="s">
         <v>213</v>
-      </c>
-      <c r="M75" t="s">
-        <v>214</v>
       </c>
       <c r="N75" t="s">
         <v>745</v>
@@ -9384,10 +9384,10 @@
         <v>8</v>
       </c>
       <c r="S75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T75" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -9398,7 +9398,7 @@
         <v>747</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D76" t="s">
         <v>748</v>
@@ -9428,7 +9428,7 @@
         <v>754</v>
       </c>
       <c r="M76" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N76" t="s">
         <v>755</v>
@@ -9450,7 +9450,7 @@
         <v>8</v>
       </c>
       <c r="T76" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -9461,7 +9461,7 @@
         <v>757</v>
       </c>
       <c r="C77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
         <v>758</v>
@@ -9479,7 +9479,7 @@
         <v>762</v>
       </c>
       <c r="I77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J77" t="s">
         <v>9</v>
@@ -9501,16 +9501,16 @@
         <v>0</v>
       </c>
       <c r="P77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q77" t="s">
         <v>8</v>
       </c>
       <c r="R77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T77" t="s">
         <v>53</v>
@@ -9524,7 +9524,7 @@
         <v>764</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D78" t="s">
         <v>765</v>
@@ -9542,13 +9542,13 @@
         <v>769</v>
       </c>
       <c r="I78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J78" t="s">
         <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L78" t="s">
         <v>461</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="P78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T78" t="s">
         <v>53</v>
@@ -9587,7 +9587,7 @@
         <v>772</v>
       </c>
       <c r="C79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
         <v>773</v>
@@ -9605,7 +9605,7 @@
         <v>777</v>
       </c>
       <c r="I79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J79" t="s">
         <v>9</v>
@@ -9627,16 +9627,16 @@
         <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T79" t="s">
         <v>434</v>
@@ -9650,7 +9650,7 @@
         <v>780</v>
       </c>
       <c r="C80" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D80" t="s">
         <v>781</v>
@@ -9668,13 +9668,13 @@
         <v>785</v>
       </c>
       <c r="I80" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J80" t="s">
         <v>9</v>
       </c>
       <c r="K80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L80" t="s">
         <v>537</v>
@@ -9690,19 +9690,19 @@
         <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q80" t="s">
         <v>8</v>
       </c>
       <c r="R80" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S80" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T80" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -9713,7 +9713,7 @@
         <v>787</v>
       </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D81" t="s">
         <v>788</v>
@@ -9740,13 +9740,13 @@
         <v>744</v>
       </c>
       <c r="L81" t="s">
+        <v>278</v>
+      </c>
+      <c r="M81" t="s">
         <v>279</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>280</v>
-      </c>
-      <c r="N81" t="s">
-        <v>281</v>
       </c>
       <c r="O81" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80514_southwark", ".\export_data\inspection_reports\80514_southwark")</f>
@@ -9765,7 +9765,7 @@
         <v>8</v>
       </c>
       <c r="T81" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -9776,7 +9776,7 @@
         <v>794</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D82" t="s">
         <v>795</v>
@@ -9828,7 +9828,7 @@
         <v>8</v>
       </c>
       <c r="T82" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -9839,7 +9839,7 @@
         <v>802</v>
       </c>
       <c r="C83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D83" t="s">
         <v>803</v>
@@ -9857,7 +9857,7 @@
         <v>807</v>
       </c>
       <c r="I83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J83" t="s">
         <v>9</v>
@@ -9879,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q83" t="s">
         <v>8</v>
@@ -9888,7 +9888,7 @@
         <v>8</v>
       </c>
       <c r="S83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T83" t="s">
         <v>28</v>
@@ -9902,7 +9902,7 @@
         <v>812</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D84" t="s">
         <v>813</v>
@@ -9948,13 +9948,13 @@
         <v>8</v>
       </c>
       <c r="R84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S84" t="s">
         <v>8</v>
       </c>
       <c r="T84" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -9965,7 +9965,7 @@
         <v>820</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D85" t="s">
         <v>821</v>
@@ -9983,7 +9983,7 @@
         <v>825</v>
       </c>
       <c r="I85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J85" t="s">
         <v>9</v>
@@ -9998,23 +9998,23 @@
         <v>826</v>
       </c>
       <c r="N85" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O85" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80518_wandsworth", ".\export_data\inspection_reports\80518_wandsworth")</f>
         <v>0</v>
       </c>
       <c r="P85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T85" t="s">
         <v>15</v>
@@ -10028,7 +10028,7 @@
         <v>828</v>
       </c>
       <c r="C86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D86" t="s">
         <v>829</v>
@@ -10046,13 +10046,13 @@
         <v>833</v>
       </c>
       <c r="I86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J86" t="s">
         <v>9</v>
       </c>
       <c r="K86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L86" t="s">
         <v>808</v>
@@ -10068,16 +10068,16 @@
         <v>0</v>
       </c>
       <c r="P86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T86" t="s">
         <v>53</v>
@@ -10143,7 +10143,7 @@
         <v>14</v>
       </c>
       <c r="T87" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -10172,13 +10172,13 @@
         <v>849</v>
       </c>
       <c r="I88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J88" t="s">
         <v>48</v>
       </c>
       <c r="K88" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L88" t="s">
         <v>850</v>
@@ -10194,16 +10194,16 @@
         <v>0</v>
       </c>
       <c r="P88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q88" t="s">
         <v>8</v>
       </c>
       <c r="R88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T88" t="s">
         <v>15</v>
@@ -10217,7 +10217,7 @@
         <v>854</v>
       </c>
       <c r="C89" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D89" t="s">
         <v>855</v>
@@ -10280,7 +10280,7 @@
         <v>864</v>
       </c>
       <c r="C90" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D90" t="s">
         <v>865</v>
@@ -10298,7 +10298,7 @@
         <v>869</v>
       </c>
       <c r="I90" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J90" t="s">
         <v>48</v>
@@ -10307,13 +10307,13 @@
         <v>870</v>
       </c>
       <c r="L90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O90" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80523_middlesbrough", ".\export_data\inspection_reports\80523_middlesbrough")</f>
@@ -10332,7 +10332,7 @@
         <v>14</v>
       </c>
       <c r="T90" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -10343,7 +10343,7 @@
         <v>872</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
         <v>873</v>
@@ -10392,7 +10392,7 @@
         <v>8</v>
       </c>
       <c r="S91" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T91" t="s">
         <v>434</v>
@@ -10406,7 +10406,7 @@
         <v>882</v>
       </c>
       <c r="C92" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D92" t="s">
         <v>883</v>
@@ -10430,7 +10430,7 @@
         <v>9</v>
       </c>
       <c r="K92" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L92" t="s">
         <v>888</v>
@@ -10449,7 +10449,7 @@
         <v>8</v>
       </c>
       <c r="Q92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R92" t="s">
         <v>8</v>
@@ -10487,7 +10487,7 @@
         <v>897</v>
       </c>
       <c r="I93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J93" t="s">
         <v>9</v>
@@ -10502,23 +10502,23 @@
         <v>900</v>
       </c>
       <c r="N93" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O93" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80418_norfolk", ".\export_data\inspection_reports\80418_norfolk")</f>
         <v>0</v>
       </c>
       <c r="P93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T93" t="s">
         <v>434</v>
@@ -10556,7 +10556,7 @@
         <v>48</v>
       </c>
       <c r="K94" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L94" t="s">
         <v>37</v>
@@ -10572,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q94" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>916</v>
       </c>
       <c r="I95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J95" t="s">
         <v>9</v>
@@ -10635,13 +10635,13 @@
         <v>0</v>
       </c>
       <c r="P95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S95" t="s">
         <v>8</v>
@@ -10658,7 +10658,7 @@
         <v>921</v>
       </c>
       <c r="C96" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D96" t="s">
         <v>922</v>
@@ -10676,7 +10676,7 @@
         <v>926</v>
       </c>
       <c r="I96" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J96" t="s">
         <v>48</v>
@@ -10698,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q96" t="s">
         <v>8</v>
@@ -10710,7 +10710,7 @@
         <v>8</v>
       </c>
       <c r="T96" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -10784,7 +10784,7 @@
         <v>939</v>
       </c>
       <c r="C98" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D98" t="s">
         <v>940</v>
@@ -10802,13 +10802,13 @@
         <v>944</v>
       </c>
       <c r="I98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
       </c>
       <c r="K98" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L98" t="s">
         <v>808</v>
@@ -10824,16 +10824,16 @@
         <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T98" t="s">
         <v>53</v>
@@ -10865,7 +10865,7 @@
         <v>951</v>
       </c>
       <c r="I99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J99" t="s">
         <v>9</v>
@@ -10887,19 +10887,19 @@
         <v>0</v>
       </c>
       <c r="P99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -10910,7 +10910,7 @@
         <v>957</v>
       </c>
       <c r="C100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D100" t="s">
         <v>958</v>
@@ -10928,7 +10928,7 @@
         <v>962</v>
       </c>
       <c r="I100" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J100" t="s">
         <v>9</v>
@@ -10950,10 +10950,10 @@
         <v>0</v>
       </c>
       <c r="P100" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q100" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R100" t="s">
         <v>8</v>
@@ -10973,7 +10973,7 @@
         <v>966</v>
       </c>
       <c r="C101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D101" t="s">
         <v>967</v>
@@ -10991,10 +10991,10 @@
         <v>971</v>
       </c>
       <c r="I101" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K101" t="s">
         <v>963</v>
@@ -11010,13 +11010,13 @@
         <v>14</v>
       </c>
       <c r="Q101" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R101" t="s">
         <v>14</v>
       </c>
       <c r="S101" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T101" t="s">
         <v>434</v>
@@ -11030,7 +11030,7 @@
         <v>974</v>
       </c>
       <c r="C102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D102" t="s">
         <v>975</v>
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q102" t="s">
         <v>8</v>
@@ -11082,7 +11082,7 @@
         <v>8</v>
       </c>
       <c r="T102" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -11156,7 +11156,7 @@
         <v>988</v>
       </c>
       <c r="C104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D104" t="s">
         <v>989</v>
@@ -11186,7 +11186,7 @@
         <v>994</v>
       </c>
       <c r="M104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N104" t="s">
         <v>995</v>
@@ -11208,7 +11208,7 @@
         <v>8</v>
       </c>
       <c r="T104" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -11237,7 +11237,7 @@
         <v>1002</v>
       </c>
       <c r="I105" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J105" t="s">
         <v>48</v>
@@ -11268,7 +11268,7 @@
         <v>14</v>
       </c>
       <c r="S105" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T105" t="s">
         <v>434</v>
@@ -11306,7 +11306,7 @@
         <v>48</v>
       </c>
       <c r="K106" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L106" t="s">
         <v>1014</v>
@@ -11345,7 +11345,7 @@
         <v>1018</v>
       </c>
       <c r="C107" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D107" t="s">
         <v>1019</v>
@@ -11369,7 +11369,7 @@
         <v>9</v>
       </c>
       <c r="K107" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L107" t="s">
         <v>1024</v>
@@ -11388,7 +11388,7 @@
         <v>8</v>
       </c>
       <c r="Q107" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R107" t="s">
         <v>8</v>
@@ -11397,7 +11397,7 @@
         <v>14</v>
       </c>
       <c r="T107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -11408,7 +11408,7 @@
         <v>1028</v>
       </c>
       <c r="C108" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D108" t="s">
         <v>1029</v>
@@ -11432,7 +11432,7 @@
         <v>48</v>
       </c>
       <c r="K108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L108" t="s">
         <v>554</v>
@@ -11460,7 +11460,7 @@
         <v>8</v>
       </c>
       <c r="T108" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -11471,7 +11471,7 @@
         <v>1035</v>
       </c>
       <c r="C109" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D109" t="s">
         <v>1036</v>
@@ -11495,16 +11495,16 @@
         <v>48</v>
       </c>
       <c r="K109" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L109" t="s">
         <v>1041</v>
       </c>
       <c r="M109" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O109" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80541_redcar and cleveland", ".\export_data\inspection_reports\80541_redcar and cleveland")</f>
@@ -11558,7 +11558,7 @@
         <v>48</v>
       </c>
       <c r="K110" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L110" t="s">
         <v>471</v>
@@ -11615,13 +11615,13 @@
         <v>1057</v>
       </c>
       <c r="I111" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J111" t="s">
         <v>9</v>
       </c>
       <c r="K111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L111" t="s">
         <v>489</v>
@@ -11637,19 +11637,19 @@
         <v>0</v>
       </c>
       <c r="P111" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q111" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R111" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S111" t="s">
         <v>8</v>
       </c>
       <c r="T111" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112" spans="1:20">
@@ -11660,7 +11660,7 @@
         <v>1060</v>
       </c>
       <c r="C112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D112" t="s">
         <v>1061</v>
@@ -11678,13 +11678,13 @@
         <v>1065</v>
       </c>
       <c r="I112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J112" t="s">
         <v>9</v>
       </c>
       <c r="K112" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L112" t="s">
         <v>808</v>
@@ -11700,19 +11700,19 @@
         <v>0</v>
       </c>
       <c r="P112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R112" t="s">
         <v>8</v>
       </c>
       <c r="S112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T112" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:20">
@@ -11723,7 +11723,7 @@
         <v>1067</v>
       </c>
       <c r="C113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D113" t="s">
         <v>1068</v>
@@ -11741,7 +11741,7 @@
         <v>1072</v>
       </c>
       <c r="I113" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J113" t="s">
         <v>9</v>
@@ -11750,32 +11750,32 @@
         <v>753</v>
       </c>
       <c r="L113" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M113" t="s">
         <v>414</v>
       </c>
       <c r="N113" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O113" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80545_kingston upon thames", ".\export_data\inspection_reports\80545_kingston upon thames")</f>
         <v>0</v>
       </c>
       <c r="P113" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q113" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R113" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S113" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T113" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="114" spans="1:20">
@@ -11786,7 +11786,7 @@
         <v>1074</v>
       </c>
       <c r="C114" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D114" t="s">
         <v>1075</v>
@@ -11813,10 +11813,10 @@
         <v>619</v>
       </c>
       <c r="L114" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M114" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N114" t="s">
         <v>1080</v>
@@ -11835,7 +11835,7 @@
         <v>8</v>
       </c>
       <c r="S114" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T114" t="s">
         <v>53</v>
@@ -11849,7 +11849,7 @@
         <v>1082</v>
       </c>
       <c r="C115" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D115" t="s">
         <v>1083</v>
@@ -11942,17 +11942,17 @@
         <v>1098</v>
       </c>
       <c r="M116" t="s">
+        <v>321</v>
+      </c>
+      <c r="N116" t="s">
         <v>322</v>
-      </c>
-      <c r="N116" t="s">
-        <v>323</v>
       </c>
       <c r="O116" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80548_salford", ".\export_data\inspection_reports\80548_salford")</f>
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q116" t="s">
         <v>8</v>
@@ -11961,7 +11961,7 @@
         <v>8</v>
       </c>
       <c r="S116" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T116" t="s">
         <v>434</v>
@@ -12062,7 +12062,7 @@
         <v>48</v>
       </c>
       <c r="K118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L118" t="s">
         <v>1116</v>
@@ -12147,7 +12147,7 @@
         <v>8</v>
       </c>
       <c r="R119" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S119" t="s">
         <v>8</v>
@@ -12182,7 +12182,7 @@
         <v>1132</v>
       </c>
       <c r="I120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J120" t="s">
         <v>48</v>
@@ -12204,19 +12204,19 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S120" t="s">
         <v>8</v>
       </c>
       <c r="T120" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:20">
@@ -12227,7 +12227,7 @@
         <v>1134</v>
       </c>
       <c r="C121" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D121" t="s">
         <v>1135</v>
@@ -12267,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q121" t="s">
         <v>14</v>
@@ -12342,7 +12342,7 @@
         <v>8</v>
       </c>
       <c r="T122" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:20">
@@ -12371,13 +12371,13 @@
         <v>1154</v>
       </c>
       <c r="I123" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J123" t="s">
         <v>9</v>
       </c>
       <c r="K123" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L123" t="s">
         <v>609</v>
@@ -12405,7 +12405,7 @@
         <v>8</v>
       </c>
       <c r="T123" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="124" spans="1:20">
@@ -12479,7 +12479,7 @@
         <v>1163</v>
       </c>
       <c r="C125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D125" t="s">
         <v>1164</v>
@@ -12497,67 +12497,67 @@
         <v>1168</v>
       </c>
       <c r="I125" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="J125" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="K125" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="L125" t="s">
         <v>1169</v>
       </c>
       <c r="M125" t="s">
-        <v>528</v>
+        <v>1170</v>
       </c>
       <c r="N125" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O125" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80557_south tyneside", ".\export_data\inspection_reports\80557_south tyneside")</f>
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="Q125" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R125" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="S125" t="s">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="T125" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B126" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C126" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D126" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E126" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F126" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G126" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="I126" t="s">
         <v>8</v>
@@ -12566,23 +12566,23 @@
         <v>48</v>
       </c>
       <c r="K126" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L126" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="M126" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N126" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="O126" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80558_southampton", ".\export_data\inspection_reports\80558_southampton")</f>
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q126" t="s">
         <v>8</v>
@@ -12594,33 +12594,33 @@
         <v>8</v>
       </c>
       <c r="T126" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B127" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C127" t="s">
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E127" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F127" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G127" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="I127" t="s">
         <v>8</v>
@@ -12629,7 +12629,7 @@
         <v>48</v>
       </c>
       <c r="K127" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L127" t="s">
         <v>636</v>
@@ -12662,28 +12662,28 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B128" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C128" t="s">
         <v>56</v>
       </c>
       <c r="D128" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E128" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F128" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G128" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="I128" t="s">
         <v>8</v>
@@ -12725,28 +12725,28 @@
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B129" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C129" t="s">
         <v>42</v>
       </c>
       <c r="D129" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E129" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F129" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G129" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="I129" t="s">
         <v>14</v>
@@ -12755,16 +12755,16 @@
         <v>9</v>
       </c>
       <c r="K129" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L129" t="s">
         <v>1098</v>
       </c>
       <c r="M129" t="s">
+        <v>321</v>
+      </c>
+      <c r="N129" t="s">
         <v>322</v>
-      </c>
-      <c r="N129" t="s">
-        <v>323</v>
       </c>
       <c r="O129" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80561_staffordshire", ".\export_data\inspection_reports\80561_staffordshire")</f>
@@ -12783,33 +12783,33 @@
         <v>14</v>
       </c>
       <c r="T129" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B130" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C130" t="s">
         <v>56</v>
       </c>
       <c r="D130" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="E130" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F130" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G130" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="I130" t="s">
         <v>14</v>
@@ -12824,10 +12824,10 @@
         <v>888</v>
       </c>
       <c r="M130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N130" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O130" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80562_stockport", ".\export_data\inspection_reports\80562_stockport")</f>
@@ -12851,28 +12851,28 @@
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B131" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C131" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D131" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E131" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F131" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G131" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="I131" t="s">
         <v>14</v>
@@ -12881,16 +12881,16 @@
         <v>48</v>
       </c>
       <c r="K131" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="L131" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="M131" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N131" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="O131" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80563_stockton-on-tees", ".\export_data\inspection_reports\80563_stockton-on-tees")</f>
@@ -12909,33 +12909,33 @@
         <v>14</v>
       </c>
       <c r="T131" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B132" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C132" t="s">
         <v>42</v>
       </c>
       <c r="D132" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="E132" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F132" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G132" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="I132" t="s">
         <v>14</v>
@@ -12950,10 +12950,10 @@
         <v>888</v>
       </c>
       <c r="M132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N132" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O132" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80564_stoke-on-trent", ".\export_data\inspection_reports\80564_stoke-on-trent")</f>
@@ -12977,28 +12977,28 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B133" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C133" t="s">
         <v>31</v>
       </c>
       <c r="D133" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E133" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F133" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="G133" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="I133" t="s">
         <v>14</v>
@@ -13007,7 +13007,7 @@
         <v>9</v>
       </c>
       <c r="K133" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L133" t="s">
         <v>663</v>
@@ -13016,7 +13016,7 @@
         <v>664</v>
       </c>
       <c r="N133" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="O133" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80565_suffolk", ".\export_data\inspection_reports\80565_suffolk")</f>
@@ -13035,64 +13035,64 @@
         <v>14</v>
       </c>
       <c r="T133" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B134" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C134" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D134" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E134" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F134" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="G134" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="I134" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J134" t="s">
         <v>9</v>
       </c>
       <c r="K134" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M134" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N134" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="O134" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80566_sunderland", ".\export_data\inspection_reports\80566_sunderland")</f>
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q134" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R134" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S134" t="s">
         <v>8</v>
@@ -13103,28 +13103,28 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B135" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C135" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D135" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E135" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F135" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="G135" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I135" t="s">
         <v>8</v>
@@ -13136,13 +13136,13 @@
         <v>507</v>
       </c>
       <c r="L135" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M135" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N135" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O135" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80567_surrey", ".\export_data\inspection_reports\80567_surrey")</f>
@@ -13166,37 +13166,37 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B136" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E136" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F136" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="G136" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="I136" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J136" t="s">
         <v>48</v>
       </c>
       <c r="K136" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L136" t="s">
         <v>860</v>
@@ -13212,120 +13212,120 @@
         <v>0</v>
       </c>
       <c r="P136" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q136" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R136" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S136" t="s">
         <v>14</v>
       </c>
       <c r="T136" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B137" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C137" t="s">
         <v>56</v>
       </c>
       <c r="D137" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E137" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F137" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G137" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="I137" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J137" t="s">
         <v>48</v>
       </c>
       <c r="K137" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L137" t="s">
         <v>754</v>
       </c>
       <c r="M137" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N137" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="O137" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80569_tameside", ".\export_data\inspection_reports\80569_tameside")</f>
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q137" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R137" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S137" t="s">
         <v>14</v>
       </c>
       <c r="T137" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B138" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C138" t="s">
         <v>42</v>
       </c>
       <c r="D138" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E138" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="F138" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G138" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="I138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J138" t="s">
         <v>9</v>
       </c>
       <c r="K138" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L138" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="M138" t="s">
         <v>555</v>
@@ -13338,48 +13338,48 @@
         <v>0</v>
       </c>
       <c r="P138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q138" t="s">
         <v>8</v>
       </c>
       <c r="R138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S138" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T138" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B139" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
       </c>
       <c r="D139" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E139" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F139" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="G139" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="I139" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J139" t="s">
         <v>9</v>
@@ -13388,29 +13388,29 @@
         <v>507</v>
       </c>
       <c r="L139" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="M139" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N139" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O139" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80571_thurrock", ".\export_data\inspection_reports\80571_thurrock")</f>
         <v>0</v>
       </c>
       <c r="P139" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q139" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R139" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S139" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T139" t="s">
         <v>28</v>
@@ -13418,28 +13418,28 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B140" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E140" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F140" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G140" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="I140" t="s">
         <v>8</v>
@@ -13451,7 +13451,7 @@
         <v>488</v>
       </c>
       <c r="L140" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M140" t="s">
         <v>690</v>
@@ -13481,43 +13481,43 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B141" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C141" t="s">
         <v>56</v>
       </c>
       <c r="D141" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E141" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="F141" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="G141" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="I141" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J141" t="s">
         <v>48</v>
       </c>
       <c r="K141" t="s">
-        <v>138</v>
+        <v>1299</v>
       </c>
       <c r="L141" t="s">
-        <v>1298</v>
+        <v>76</v>
       </c>
       <c r="M141" t="s">
-        <v>1299</v>
+        <v>77</v>
       </c>
       <c r="N141" t="s">
         <v>1300</v>
@@ -13527,19 +13527,19 @@
         <v>0</v>
       </c>
       <c r="P141" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="Q141" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="R141" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S141" t="s">
-        <v>365</v>
+        <v>14</v>
       </c>
       <c r="T141" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142" spans="1:20">
@@ -13568,13 +13568,13 @@
         <v>1307</v>
       </c>
       <c r="I142" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J142" t="s">
         <v>9</v>
       </c>
       <c r="K142" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L142" t="s">
         <v>888</v>
@@ -13583,26 +13583,26 @@
         <v>889</v>
       </c>
       <c r="N142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O142" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80574_walsall", ".\export_data\inspection_reports\80574_walsall")</f>
         <v>0</v>
       </c>
       <c r="P142" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q142" t="s">
         <v>8</v>
       </c>
       <c r="R142" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S142" t="s">
         <v>8</v>
       </c>
       <c r="T142" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:20">
@@ -13637,7 +13637,7 @@
         <v>9</v>
       </c>
       <c r="K143" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L143" t="s">
         <v>442</v>
@@ -13653,13 +13653,13 @@
         <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q143" t="s">
         <v>8</v>
       </c>
       <c r="R143" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S143" t="s">
         <v>8</v>
@@ -13700,7 +13700,7 @@
         <v>9</v>
       </c>
       <c r="K144" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L144" t="s">
         <v>1323</v>
@@ -13728,7 +13728,7 @@
         <v>8</v>
       </c>
       <c r="T144" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:20">
@@ -13739,7 +13739,7 @@
         <v>1327</v>
       </c>
       <c r="C145" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D145" t="s">
         <v>1328</v>
@@ -13802,7 +13802,7 @@
         <v>1337</v>
       </c>
       <c r="C146" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D146" t="s">
         <v>1338</v>
@@ -13820,7 +13820,7 @@
         <v>1342</v>
       </c>
       <c r="I146" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J146" t="s">
         <v>48</v>
@@ -13842,7 +13842,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q146" t="s">
         <v>8</v>
@@ -13854,7 +13854,7 @@
         <v>8</v>
       </c>
       <c r="T146" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="147" spans="1:20">
@@ -13865,7 +13865,7 @@
         <v>1344</v>
       </c>
       <c r="C147" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D147" t="s">
         <v>1345</v>
@@ -13917,7 +13917,7 @@
         <v>14</v>
       </c>
       <c r="T147" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="148" spans="1:20">
@@ -13931,7 +13931,7 @@
         <v>56</v>
       </c>
       <c r="D148" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E148" t="s">
         <v>1353</v>
@@ -14037,13 +14037,13 @@
         <v>14</v>
       </c>
       <c r="R149" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S149" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T149" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="150" spans="1:20">
@@ -14072,7 +14072,7 @@
         <v>1373</v>
       </c>
       <c r="I150" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J150" t="s">
         <v>9</v>
@@ -14094,16 +14094,16 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q150" t="s">
         <v>8</v>
       </c>
       <c r="R150" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S150" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T150" t="s">
         <v>15</v>
@@ -14141,7 +14141,7 @@
         <v>48</v>
       </c>
       <c r="K151" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L151" t="s">
         <v>1384</v>
@@ -14180,7 +14180,7 @@
         <v>1387</v>
       </c>
       <c r="C152" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D152" t="s">
         <v>1388</v>
@@ -14204,16 +14204,16 @@
         <v>48</v>
       </c>
       <c r="K152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L152" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="M152" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N152" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="O152" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80582_wokingham", ".\export_data\inspection_reports\80582_wokingham")</f>
@@ -14232,7 +14232,7 @@
         <v>14</v>
       </c>
       <c r="T152" t="s">
-        <v>142</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:20">
@@ -14267,7 +14267,7 @@
         <v>9</v>
       </c>
       <c r="K153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L153" t="s">
         <v>1400</v>
@@ -14289,13 +14289,13 @@
         <v>14</v>
       </c>
       <c r="R153" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S153" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T153" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:20">
@@ -14330,7 +14330,7 @@
         <v>48</v>
       </c>
       <c r="K154" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L154" t="s">
         <v>1024</v>
@@ -14358,7 +14358,7 @@
         <v>8</v>
       </c>
       <c r="T154" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/ofsted_csc_ilacs_overview.xlsx
+++ b/ofsted_csc_ilacs_overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1430">
   <si>
     <t>80426</t>
   </si>
@@ -391,7 +391,7 @@
     <t>846, 383, 882, 373, 826, 851, 870, 302, 839, 382</t>
   </si>
   <si>
-    <t>[(846, 'outstanding'), (383, 'outstanding'), (882, 'good'), (373, 'good'), (826, 'good'), (851, 'good'), (870, 'requires improvement'), (302, 'good'), (839, 'good'), (382, 'good')]</t>
+    <t>[(846, 'outstanding'), (383, 'outstanding'), (882, 'good'), (373, 'good'), (826, 'good'), (851, nan), (870, 'requires improvement'), (302, 'good'), (839, 'good'), (382, 'good')]</t>
   </si>
   <si>
     <t>bristol</t>
@@ -457,7 +457,7 @@
     <t>888, 908, 392, 886, 332, 891, 808, 926, 887, 303</t>
   </si>
   <si>
-    <t>[(888, 'good'), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
+    <t>[(888, nan), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
   </si>
   <si>
     <t>bury</t>
@@ -697,7 +697,7 @@
     <t>05/11/24</t>
   </si>
   <si>
-    <t>9</t>
+    <t>8</t>
   </si>
   <si>
     <t>80451</t>
@@ -712,7 +712,7 @@
     <t>332, 370, 894, 372, 925, 357, 371, 813, 841, 888</t>
   </si>
   <si>
-    <t>[(332, 'requires improvement'), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, 'good')]</t>
+    <t>[(332, 'requires improvement'), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, nan)]</t>
   </si>
   <si>
     <t>wakefield</t>
@@ -775,7 +775,7 @@
     <t>926, 351, 845, 830, 929, 935, 878, 891, 888, 886</t>
   </si>
   <si>
-    <t>[(926, 'outstanding'), (351, 'requires improvement'), (845, 'good'), (830, 'good'), (929, 'outstanding'), (935, 'requires improvement'), (878, 'inadequate'), (891, 'good'), (888, 'good'), (886, 'good')]</t>
+    <t>[(926, 'outstanding'), (351, 'requires improvement'), (845, 'good'), (830, 'good'), (929, 'outstanding'), (935, 'requires improvement'), (878, 'inadequate'), (891, 'good'), (888, nan), (886, 'good')]</t>
   </si>
   <si>
     <t>cornwall</t>
@@ -871,7 +871,7 @@
     <t>943, 925, 884, 888, 813, 384, 860, 929, 371, 370</t>
   </si>
   <si>
-    <t>[(943, 'good'), (925, 'outstanding'), (884, 'good'), (888, 'good'), (813, 'outstanding'), (384, 'good'), (860, 'requires improvement'), (929, 'outstanding'), (371, 'good'), (370, 'good')]</t>
+    <t>[(943, 'good'), (925, 'outstanding'), (884, 'good'), (888, nan), (813, 'outstanding'), (384, 'good'), (860, 'requires improvement'), (929, 'outstanding'), (371, 'good'), (370, 'good')]</t>
   </si>
   <si>
     <t>cumberland</t>
@@ -904,7 +904,7 @@
     <t>390, 808, 332, 384, 888, 894, 372, 357, 840, 371</t>
   </si>
   <si>
-    <t>[(390, 'good'), (808, 'requires improvement'), (332, 'requires improvement'), (384, 'good'), (888, 'good'), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
+    <t>[(390, 'good'), (808, 'requires improvement'), (332, 'requires improvement'), (384, 'good'), (888, nan), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
   </si>
   <si>
     <t>darlington</t>
@@ -1090,7 +1090,7 @@
     <t>384, 894, 808, 372, 370, 887, 357, 888, 841, 925</t>
   </si>
   <si>
-    <t>[(384, 'good'), (894, 'outstanding'), (808, 'requires improvement'), (372, 'outstanding'), (370, 'good'), (887, 'good'), (357, 'inadequate'), (888, 'good'), (841, 'outstanding'), (925, 'outstanding')]</t>
+    <t>[(384, 'good'), (894, 'outstanding'), (808, 'requires improvement'), (372, 'outstanding'), (370, 'good'), (887, 'good'), (357, 'inadequate'), (888, nan), (841, 'outstanding'), (925, 'outstanding')]</t>
   </si>
   <si>
     <t>dudley</t>
@@ -1390,7 +1390,7 @@
     <t>943, 860, 925, 893, 933, 888, 935, 811, 815, 830</t>
   </si>
   <si>
-    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, nan), (888, 'good'), (935, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (830, 'good')]</t>
+    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, nan), (888, nan), (935, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (830, 'good')]</t>
   </si>
   <si>
     <t>herefordshire</t>
@@ -1528,7 +1528,7 @@
     <t>373, 357, 851, 831, 879, 354, 351, 384, 908, 390</t>
   </si>
   <si>
-    <t>[(373, 'good'), (357, 'inadequate'), (851, 'good'), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
+    <t>[(373, 'good'), (357, 'inadequate'), (851, nan), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
   </si>
   <si>
     <t>kirklees</t>
@@ -1594,16 +1594,16 @@
     <t>lancashire</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50205966</t>
-  </si>
-  <si>
-    <t>28/11/2022</t>
-  </si>
-  <si>
-    <t>09/12/2022</t>
-  </si>
-  <si>
-    <t>26/01/23</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50309857</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>22/05/2026</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
   </si>
   <si>
     <t>80481</t>
@@ -1618,7 +1618,7 @@
     <t>851, 882, 373, 826, 382, 355, 801, 852, 306, 839</t>
   </si>
   <si>
-    <t>[(851, 'good'), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
+    <t>[(851, nan), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
   </si>
   <si>
     <t>leeds</t>
@@ -1696,7 +1696,7 @@
     <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
   </si>
   <si>
-    <t>[(888, 'good'), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'requires improvement'), (940, nan), (830, 'good'), (933, nan)]</t>
+    <t>[(888, nan), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'requires improvement'), (940, nan), (830, 'good'), (933, nan)]</t>
   </si>
   <si>
     <t>lincolnshire</t>
@@ -1735,12 +1735,6 @@
     <t>https://files.ofsted.gov.uk/v1/file/50306784</t>
   </si>
   <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
     <t>07/07/26</t>
   </si>
   <si>
@@ -1996,7 +1990,7 @@
     <t>209, 208, 306, 210, 355, 320, 851, 852, 391, 870</t>
   </si>
   <si>
-    <t>[(209, 'good'), (208, 'good'), (306, 'good'), (210, 'good'), (355, 'good'), (320, 'good'), (851, 'good'), (852, 'good'), (391, 'good'), (870, 'requires improvement')]</t>
+    <t>[(209, 'good'), (208, 'good'), (306, 'good'), (210, 'good'), (355, 'good'), (320, 'good'), (851, nan), (852, 'good'), (391, 'good'), (870, 'requires improvement')]</t>
   </si>
   <si>
     <t>greenwich</t>
@@ -2671,7 +2665,7 @@
     <t>355, 373, 806, 851, 892, 383, 330, 852, 352, 890</t>
   </si>
   <si>
-    <t>[(355, 'good'), (373, 'good'), (806, nan), (851, 'good'), (892, 'inadequate'), (383, 'outstanding'), (330, 'good'), (852, 'good'), (352, 'outstanding'), (890, nan)]</t>
+    <t>[(355, 'good'), (373, 'good'), (806, nan), (851, nan), (892, 'inadequate'), (383, 'outstanding'), (330, 'good'), (852, 'good'), (352, 'outstanding'), (890, nan)]</t>
   </si>
   <si>
     <t>newcastle upon tyne</t>
@@ -2758,7 +2752,7 @@
     <t>384, 925, 371, 370, 940, 332, 942, 372, 894, 888</t>
   </si>
   <si>
-    <t>[(384, 'good'), (925, 'outstanding'), (371, 'good'), (370, 'good'), (940, nan), (332, 'requires improvement'), (942, 'good'), (372, 'outstanding'), (894, 'outstanding'), (888, 'good')]</t>
+    <t>[(384, 'good'), (925, 'outstanding'), (371, 'good'), (370, 'good'), (940, nan), (332, 'requires improvement'), (942, 'good'), (372, 'outstanding'), (894, 'outstanding'), (888, nan)]</t>
   </si>
   <si>
     <t>north lincolnshire</t>
@@ -2842,7 +2836,7 @@
     <t>351, 891, 808, 802, 841, 888, 334, 908, 390, 886</t>
   </si>
   <si>
-    <t>[(351, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (802, 'requires improvement'), (841, 'outstanding'), (888, 'good'), (334, 'good'), (908, 'good'), (390, 'good'), (886, 'good')]</t>
+    <t>[(351, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (802, 'requires improvement'), (841, 'outstanding'), (888, nan), (334, 'good'), (908, 'good'), (390, 'good'), (886, 'good')]</t>
   </si>
   <si>
     <t>north tyneside</t>
@@ -2896,7 +2890,7 @@
     <t>926, 830, 888, 908, 878, 840, 838, 886, 885, 935</t>
   </si>
   <si>
-    <t>[(926, 'outstanding'), (830, 'good'), (888, 'good'), (908, 'good'), (878, 'inadequate'), (840, 'outstanding'), (838, 'outstanding'), (886, 'good'), (885, 'good'), (935, 'requires improvement')]</t>
+    <t>[(926, 'outstanding'), (830, 'good'), (888, nan), (908, 'good'), (878, 'inadequate'), (840, 'outstanding'), (838, 'outstanding'), (886, 'good'), (885, 'good'), (935, 'requires improvement')]</t>
   </si>
   <si>
     <t>northumberland</t>
@@ -2947,7 +2941,7 @@
     <t>830, 935, 933, 886, 926, 937, 855, 802, 860, 888</t>
   </si>
   <si>
-    <t>[(830, 'good'), (935, 'requires improvement'), (933, nan), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, 'good')]</t>
+    <t>[(830, 'good'), (935, 'requires improvement'), (933, nan), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, nan)]</t>
   </si>
   <si>
     <t>nottinghamshire</t>
@@ -3085,1162 +3079,1165 @@
     <t>portsmouth</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50221956</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50309432</t>
+  </si>
+  <si>
+    <t>steve bailey</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>18/08/26</t>
+  </si>
+  <si>
+    <t>80540</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>E06000038</t>
+  </si>
+  <si>
+    <t>826, 302, 312, 315, 822, 306, 320, 383, 852, 310</t>
+  </si>
+  <si>
+    <t>[(826, 'good'), (302, 'good'), (312, 'outstanding'), (315, 'outstanding'), (822, 'requires improvement'), (306, 'good'), (320, 'good'), (383, 'outstanding'), (852, 'good'), (310, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>reading</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252257</t>
+  </si>
+  <si>
+    <t>80541</t>
+  </si>
+  <si>
+    <t>807</t>
+  </si>
+  <si>
+    <t>E06000003</t>
+  </si>
+  <si>
+    <t>394, 393, 805, 372, 390, 840, 370, 357, 371, 880</t>
+  </si>
+  <si>
+    <t>[(394, 'outstanding'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
+  </si>
+  <si>
+    <t>redcar and cleveland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50294204</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>80542</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>E08000005</t>
+  </si>
+  <si>
+    <t>335, 357, 861, 350, 394, 371, 372, 831, 353, 355</t>
+  </si>
+  <si>
+    <t>[(335, 'outstanding'), (357, 'inadequate'), (861, 'requires improvement'), (350, 'good'), (394, 'outstanding'), (371, 'good'), (372, 'outstanding'), (831, 'outstanding'), (353, 'good'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>rochdale</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50211330</t>
+  </si>
+  <si>
+    <t>03/02/2023</t>
+  </si>
+  <si>
+    <t>17/03/23</t>
+  </si>
+  <si>
+    <t>80543</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>E08000018</t>
+  </si>
+  <si>
+    <t>370, 357, 371, 384, 894, 332, 807, 394, 390, 840</t>
+  </si>
+  <si>
+    <t>[(370, 'good'), (357, 'inadequate'), (371, 'good'), (384, 'good'), (894, 'outstanding'), (332, 'requires improvement'), (807, 'good'), (394, 'outstanding'), (390, 'good'), (840, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>rotherham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50292638</t>
+  </si>
+  <si>
+    <t>16/12/25</t>
+  </si>
+  <si>
+    <t>80544</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>E09000020</t>
+  </si>
+  <si>
+    <t>205, 202, 208, 213, 210, 209, 212, 206, 302, 203</t>
+  </si>
+  <si>
+    <t>[(205, 'outstanding'), (202, 'outstanding'), (208, 'good'), (213, 'outstanding'), (210, 'good'), (209, 'good'), (212, 'outstanding'), (206, 'outstanding'), (302, 'good'), (203, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>kensington and chelsea</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50266093</t>
+  </si>
+  <si>
+    <t>80545</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>E09000021</t>
+  </si>
+  <si>
+    <t>319, 315, 919, 305, 800, 868, 358, 318, 936, 825</t>
+  </si>
+  <si>
+    <t>[(319, 'good'), (315, 'outstanding'), (919, 'outstanding'), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, nan), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>kingston upon thames</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267803</t>
+  </si>
+  <si>
+    <t>80546</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>E06000040</t>
+  </si>
+  <si>
+    <t>936, 825, 872, 358, 919, 869, 305, 823, 931, 867</t>
+  </si>
+  <si>
+    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>windsor &amp; maidenhead</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50261980</t>
+  </si>
+  <si>
+    <t>19/11/24</t>
+  </si>
+  <si>
+    <t>80547</t>
+  </si>
+  <si>
+    <t>857</t>
+  </si>
+  <si>
+    <t>E06000017</t>
+  </si>
+  <si>
+    <t>865, 815, 893, 895, 850, 823, 916, 855, 869, 811</t>
+  </si>
+  <si>
+    <t>[(865, 'outstanding'), (815, 'outstanding'), (893, 'outstanding'), (895, 'inadequate'), (850, 'outstanding'), (823, 'good'), (916, 'good'), (855, 'outstanding'), (869, 'good'), (811, 'good')]</t>
+  </si>
+  <si>
+    <t>rutland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252255</t>
+  </si>
+  <si>
+    <t>15/04/2024</t>
+  </si>
+  <si>
+    <t>26/04/2024</t>
+  </si>
+  <si>
+    <t>80548</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>E08000006</t>
+  </si>
+  <si>
+    <t>373, 354, 851, 391, 390, 350, 393, 357, 852, 383</t>
+  </si>
+  <si>
+    <t>[(373, 'good'), (354, 'requires improvement'), (851, nan), (391, 'good'), (390, 'good'), (350, 'good'), (393, nan), (357, 'inadequate'), (852, 'good'), (383, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>salford</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50237003</t>
+  </si>
+  <si>
+    <t>kathryn grindrod</t>
+  </si>
+  <si>
+    <t>06/11/2023</t>
+  </si>
+  <si>
+    <t>80549</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>E08000028</t>
+  </si>
+  <si>
+    <t>336, 810, 861, 335, 354, 380, 806, 331, 353, 821</t>
+  </si>
+  <si>
+    <t>[(336, 'good'), (810, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (354, 'requires improvement'), (380, 'requires improvement'), (806, nan), (331, 'outstanding'), (353, 'good'), (821, 'good')]</t>
+  </si>
+  <si>
+    <t>sandwell</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50291983</t>
+  </si>
+  <si>
+    <t>13/10/2025</t>
+  </si>
+  <si>
+    <t>24/10/2025</t>
+  </si>
+  <si>
+    <t>02/12/25</t>
+  </si>
+  <si>
+    <t>80550</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>E08000014</t>
+  </si>
+  <si>
+    <t>344, 342, 359, 888, 876, 840, 808, 340, 841, 351</t>
+  </si>
+  <si>
+    <t>[(344, 'requires improvement'), (342, 'good'), (359, 'good'), (888, nan), (876, 'inadequate'), (840, 'outstanding'), (808, 'requires improvement'), (340, 'inadequate'), (841, 'outstanding'), (351, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>sefton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50284335</t>
+  </si>
+  <si>
+    <t>23/06/2025</t>
+  </si>
+  <si>
+    <t>80551</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>E08000019</t>
+  </si>
+  <si>
+    <t>382, 851, 355, 383, 831, 354, 391, 852, 357, 350</t>
+  </si>
+  <si>
+    <t>[(382, 'good'), (851, nan), (355, 'good'), (383, 'outstanding'), (831, 'outstanding'), (354, 'requires improvement'), (391, 'good'), (852, 'good'), (357, 'inadequate'), (350, 'good')]</t>
+  </si>
+  <si>
+    <t>sheffield</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50231897</t>
+  </si>
+  <si>
+    <t>22/09/2023</t>
+  </si>
+  <si>
+    <t>03/11/23</t>
+  </si>
+  <si>
+    <t>80552</t>
+  </si>
+  <si>
+    <t>893</t>
+  </si>
+  <si>
+    <t>E06000051</t>
+  </si>
+  <si>
+    <t>815, 933, 860, 811, 838, 884, 830, 885, 943, 916</t>
+  </si>
+  <si>
+    <t>[(815, 'outstanding'), (933, nan), (860, 'requires improvement'), (811, 'good'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
+  </si>
+  <si>
+    <t>shropshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50284334</t>
+  </si>
+  <si>
+    <t>80553</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>E06000039</t>
+  </si>
+  <si>
+    <t>313, 312, 821, 307, 317, 310, 304, 874, 320, 856</t>
+  </si>
+  <si>
+    <t>[(313, 'good'), (312, 'outstanding'), (821, 'good'), (307, 'good'), (317, 'outstanding'), (310, 'inadequate'), (304, nan), (874, 'inadequate'), (320, 'good'), (856, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>slough</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50211331</t>
+  </si>
+  <si>
+    <t>80554</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>E08000029</t>
+  </si>
+  <si>
+    <t>356, 896, 937, 877, 886, 916, 802, 895, 881, 919</t>
+  </si>
+  <si>
+    <t>[(356, 'requires improvement'), (896, 'requires improvement'), (937, 'requires improvement'), (877, 'good'), (886, 'good'), (916, 'good'), (802, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (919, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>solihull</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50293398</t>
+  </si>
+  <si>
+    <t>80555</t>
+  </si>
+  <si>
+    <t>933</t>
+  </si>
+  <si>
+    <t>E10000027</t>
+  </si>
+  <si>
+    <t>935, 830, 838, 893, 885, 891, 878, 860, 855, 881</t>
+  </si>
+  <si>
+    <t>[(935, 'requires improvement'), (830, 'good'), (838, 'outstanding'), (893, 'outstanding'), (885, 'good'), (891, 'good'), (878, 'inadequate'), (860, 'requires improvement'), (855, 'outstanding'), (881, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>somerset</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50304387</t>
+  </si>
+  <si>
+    <t>80556</t>
+  </si>
+  <si>
+    <t>803</t>
+  </si>
+  <si>
+    <t>E06000025</t>
+  </si>
+  <si>
+    <t>855, 850, 938, 873, 823, 802, 916, 881, 931, 865</t>
+  </si>
+  <si>
+    <t>[(855, 'outstanding'), (850, 'outstanding'), (938, 'requires improvement'), (873, 'requires improvement'), (823, 'good'), (802, 'requires improvement'), (916, 'good'), (881, 'outstanding'), (931, 'good'), (865, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>south gloucestershire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253185</t>
+  </si>
+  <si>
+    <t>80557</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>E08000023</t>
+  </si>
+  <si>
+    <t>394, 807, 390, 805, 840, 357, 372, 354, 890, 841</t>
+  </si>
+  <si>
+    <t>[(394, 'outstanding'), (807, 'good'), (390, 'good'), (805, 'outstanding'), (840, 'outstanding'), (357, 'inadequate'), (372, 'outstanding'), (354, 'requires improvement'), (890, nan), (841, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>south tyneside</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50308876</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>04/08/26</t>
+  </si>
+  <si>
+    <t>80558</t>
+  </si>
+  <si>
+    <t>852</t>
+  </si>
+  <si>
+    <t>E06000045</t>
+  </si>
+  <si>
+    <t>331, 831, 851, 373, 312, 355, 874, 383, 350, 320</t>
+  </si>
+  <si>
+    <t>[(331, 'outstanding'), (831, 'outstanding'), (851, nan), (373, 'good'), (312, 'outstanding'), (355, 'good'), (874, 'inadequate'), (383, 'outstanding'), (350, 'good'), (320, 'good')]</t>
+  </si>
+  <si>
+    <t>southampton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50224705</t>
+  </si>
+  <si>
+    <t>05/06/2023</t>
+  </si>
+  <si>
+    <t>16/06/2023</t>
+  </si>
+  <si>
+    <t>28/07/23</t>
+  </si>
+  <si>
+    <t>80559</t>
+  </si>
+  <si>
+    <t>882</t>
+  </si>
+  <si>
+    <t>E06000033</t>
+  </si>
+  <si>
+    <t>839, 383, 826, 351, 845, 851, 886, 303, 392, 822</t>
+  </si>
+  <si>
+    <t>[(839, 'good'), (383, 'outstanding'), (826, 'good'), (351, 'requires improvement'), (845, 'good'), (851, nan), (886, 'good'), (303, 'outstanding'), (392, 'outstanding'), (822, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>southend-on-sea</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50263392</t>
+  </si>
+  <si>
+    <t>80560</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>E08000013</t>
+  </si>
+  <si>
+    <t>876, 343, 340, 840, 807, 370, 394, 344, 808, 894</t>
+  </si>
+  <si>
+    <t>[(876, 'inadequate'), (343, 'good'), (340, 'inadequate'), (840, 'outstanding'), (807, 'good'), (370, 'good'), (394, 'outstanding'), (344, 'requires improvement'), (808, 'requires improvement'), (894, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>st helens</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50227184</t>
+  </si>
+  <si>
+    <t>80561</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>E10000028</t>
+  </si>
+  <si>
+    <t>811, 884, 893, 815, 933, 830, 877, 891, 943, 888</t>
+  </si>
+  <si>
+    <t>[(811, 'good'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, nan), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, nan)]</t>
+  </si>
+  <si>
+    <t>staffordshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50237007</t>
+  </si>
+  <si>
+    <t>80562</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>E08000007</t>
+  </si>
+  <si>
+    <t>334, 358, 896, 916, 919, 938, 937, 802, 803, 873</t>
+  </si>
+  <si>
+    <t>[(334, 'good'), (358, nan), (896, 'requires improvement'), (916, 'good'), (919, 'outstanding'), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>stockport</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50282103</t>
+  </si>
+  <si>
+    <t>15/07/25</t>
+  </si>
+  <si>
+    <t>80563</t>
+  </si>
+  <si>
+    <t>808</t>
+  </si>
+  <si>
+    <t>E06000004</t>
+  </si>
+  <si>
+    <t>841, 332, 888, 390, 384, 351, 840, 372, 894, 344</t>
+  </si>
+  <si>
+    <t>[(841, 'outstanding'), (332, 'requires improvement'), (888, nan), (390, 'good'), (384, 'good'), (351, 'requires improvement'), (840, 'outstanding'), (372, 'outstanding'), (894, 'outstanding'), (344, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>stockton-on-tees</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50215915</t>
+  </si>
+  <si>
+    <t>joanna warburton</t>
+  </si>
+  <si>
+    <t>06/03/2023</t>
+  </si>
+  <si>
+    <t>17/03/2023</t>
+  </si>
+  <si>
+    <t>09/05/23</t>
+  </si>
+  <si>
+    <t>80564</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>E06000021</t>
+  </si>
+  <si>
+    <t>335, 354, 336, 371, 812, 810, 333, 357, 831, 372</t>
+  </si>
+  <si>
+    <t>[(335, 'outstanding'), (354, 'requires improvement'), (336, 'good'), (371, 'good'), (812, 'good'), (810, 'good'), (333, 'good'), (357, 'inadequate'), (831, 'outstanding'), (372, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>stoke-on-trent</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50282104</t>
+  </si>
+  <si>
+    <t>80565</t>
+  </si>
+  <si>
+    <t>935</t>
+  </si>
+  <si>
+    <t>E10000029</t>
+  </si>
+  <si>
+    <t>933, 926, 830, 891, 878, 881, 886, 838, 925, 940</t>
+  </si>
+  <si>
+    <t>[(933, nan), (926, 'outstanding'), (830, 'good'), (891, 'good'), (878, 'inadequate'), (881, 'outstanding'), (886, 'good'), (838, 'outstanding'), (925, 'outstanding'), (940, nan)]</t>
+  </si>
+  <si>
+    <t>suffolk</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255285</t>
+  </si>
+  <si>
+    <t>21/08/24</t>
+  </si>
+  <si>
+    <t>80566</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>E08000024</t>
+  </si>
+  <si>
+    <t>807, 393, 805, 372, 357, 880, 390, 840, 370, 354</t>
+  </si>
+  <si>
+    <t>[(807, 'good'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (880, 'good'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (354, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>sunderland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50271150</t>
+  </si>
+  <si>
+    <t>11/03/25</t>
+  </si>
+  <si>
+    <t>80567</t>
+  </si>
+  <si>
+    <t>936</t>
+  </si>
+  <si>
+    <t>E10000030</t>
+  </si>
+  <si>
+    <t>868, 825, 358, 919, 869, 823, 872, 931, 867, 873</t>
+  </si>
+  <si>
+    <t>[(868, 'good'), (825, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>surrey</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50276410</t>
+  </si>
+  <si>
+    <t>80568</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>E06000030</t>
+  </si>
+  <si>
+    <t>887, 940, 883, 303, 822, 941, 935, 311, 891, 886</t>
+  </si>
+  <si>
+    <t>[(887, 'good'), (940, nan), (883, 'outstanding'), (303, 'outstanding'), (822, 'requires improvement'), (941, nan), (935, 'requires improvement'), (311, 'inadequate'), (891, 'good'), (886, 'good')]</t>
+  </si>
+  <si>
+    <t>swindon</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50227724</t>
+  </si>
+  <si>
+    <t>80569</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>E08000008</t>
+  </si>
+  <si>
+    <t>372, 390, 354, 370, 384, 332, 894, 879, 394, 880</t>
+  </si>
+  <si>
+    <t>[(372, 'outstanding'), (390, 'good'), (354, 'requires improvement'), (370, 'good'), (384, 'good'), (332, 'requires improvement'), (894, 'outstanding'), (879, 'requires improvement'), (394, 'outstanding'), (880, 'good')]</t>
+  </si>
+  <si>
+    <t>tameside</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50239562</t>
+  </si>
+  <si>
+    <t>13/02/24</t>
+  </si>
+  <si>
+    <t>80570</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>E06000020</t>
+  </si>
+  <si>
+    <t>384, 372, 332, 370, 357, 371, 841, 390, 879, 808</t>
+  </si>
+  <si>
+    <t>[(384, 'good'), (372, 'outstanding'), (332, 'requires improvement'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (841, 'outstanding'), (390, 'good'), (879, 'requires improvement'), (808, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>telford &amp; wrekin</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252260</t>
+  </si>
+  <si>
+    <t>29/04/2024</t>
+  </si>
+  <si>
+    <t>80571</t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>E06000034</t>
+  </si>
+  <si>
+    <t>866, 303, 311, 887, 940, 822, 941, 332, 925, 935</t>
+  </si>
+  <si>
+    <t>[(866, 'inadequate'), (303, 'outstanding'), (311, 'inadequate'), (887, 'good'), (940, nan), (822, 'requires improvement'), (941, nan), (332, 'requires improvement'), (925, 'outstanding'), (935, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>thurrock</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50260250</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>20/09/2024</t>
+  </si>
+  <si>
+    <t>29/10/24</t>
+  </si>
+  <si>
+    <t>80572</t>
+  </si>
+  <si>
+    <t>880</t>
+  </si>
+  <si>
+    <t>E06000027</t>
+  </si>
+  <si>
+    <t>357, 394, 879, 372, 807, 921, 370, 390, 354, 894</t>
+  </si>
+  <si>
+    <t>[(357, 'inadequate'), (394, 'outstanding'), (879, 'requires improvement'), (372, 'outstanding'), (807, 'good'), (921, 'good'), (370, 'good'), (390, 'good'), (354, 'requires improvement'), (894, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>torbay</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50295967</t>
+  </si>
+  <si>
+    <t>80573</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>E08000009</t>
+  </si>
+  <si>
+    <t>919, 356, 825, 931, 936, 305, 895, 873, 916, 334</t>
+  </si>
+  <si>
+    <t>[(919, 'outstanding'), (356, 'requires improvement'), (825, 'requires improvement'), (931, 'good'), (936, 'good'), (305, 'outstanding'), (895, 'inadequate'), (873, 'requires improvement'), (916, 'good'), (334, 'good')]</t>
+  </si>
+  <si>
+    <t>trafford</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50308602</t>
+  </si>
+  <si>
+    <t>leanne cooper</t>
+  </si>
+  <si>
+    <t>03/08/26</t>
+  </si>
+  <si>
+    <t>80574</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>E08000030</t>
+  </si>
+  <si>
+    <t>354, 861, 357, 336, 371, 831, 350, 372, 812, 333</t>
+  </si>
+  <si>
+    <t>[(354, 'requires improvement'), (861, 'requires improvement'), (357, 'inadequate'), (336, 'good'), (371, 'good'), (831, 'outstanding'), (350, 'good'), (372, 'outstanding'), (812, 'good'), (333, 'good')]</t>
+  </si>
+  <si>
+    <t>walsall</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50281396</t>
+  </si>
+  <si>
+    <t>80575</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>E06000007</t>
+  </si>
+  <si>
+    <t>895, 937, 860, 811, 815, 916, 334, 893, 885, 865</t>
+  </si>
+  <si>
+    <t>[(895, 'inadequate'), (937, 'requires improvement'), (860, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (916, 'good'), (334, 'good'), (893, 'outstanding'), (885, 'good'), (865, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>warrington</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253719</t>
+  </si>
+  <si>
+    <t>30/07/24</t>
+  </si>
+  <si>
+    <t>80576</t>
+  </si>
+  <si>
+    <t>937</t>
+  </si>
+  <si>
+    <t>E10000031</t>
+  </si>
+  <si>
+    <t>916, 895, 931, 802, 855, 938, 850, 877, 865, 881</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (895, 'inadequate'), (931, 'good'), (802, 'requires improvement'), (855, 'outstanding'), (938, 'requires improvement'), (850, 'outstanding'), (877, 'good'), (865, 'outstanding'), (881, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>warwickshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50289041</t>
+  </si>
+  <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>14/10/25</t>
+  </si>
+  <si>
+    <t>80577</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>E06000037</t>
+  </si>
+  <si>
+    <t>825, 850, 931, 867, 919, 873, 823, 865, 916, 305</t>
+  </si>
+  <si>
+    <t>[(825, 'requires improvement'), (850, 'outstanding'), (931, 'good'), (867, 'outstanding'), (919, 'outstanding'), (873, 'requires improvement'), (823, 'good'), (865, 'outstanding'), (916, 'good'), (305, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>west berkshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50290038</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>28/10/25</t>
+  </si>
+  <si>
+    <t>2637548</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>E06000062</t>
+  </si>
+  <si>
+    <t>822, 940, 937, 866, 933, 935, 311, 855, 931, 303</t>
+  </si>
+  <si>
+    <t>[(822, 'requires improvement'), (940, nan), (937, 'requires improvement'), (866, 'inadequate'), (933, nan), (935, 'requires improvement'), (311, 'inadequate'), (855, 'outstanding'), (931, 'good'), (303, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>west northamptonshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50306547</t>
+  </si>
+  <si>
+    <t>80578</t>
+  </si>
+  <si>
+    <t>938</t>
+  </si>
+  <si>
+    <t>E10000032</t>
+  </si>
+  <si>
+    <t>916, 881, 850, 919, 937, 865, 802, 931, 803, 878</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (881, 'outstanding'), (850, 'outstanding'), (919, 'outstanding'), (937, 'requires improvement'), (865, 'outstanding'), (802, 'requires improvement'), (931, 'good'), (803, 'good'), (878, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>west sussex</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50216276</t>
+  </si>
+  <si>
+    <t>maire atherton</t>
+  </si>
+  <si>
+    <t>2733698</t>
+  </si>
+  <si>
+    <t>943</t>
+  </si>
+  <si>
+    <t>884, 942, 860, 893, 811, 815, 925, 933, 935, 830</t>
+  </si>
+  <si>
+    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'good'), (815, 'outstanding'), (925, 'outstanding'), (933, nan), (935, 'requires improvement'), (830, 'good')]</t>
+  </si>
+  <si>
+    <t>westmorland and furness</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252261</t>
+  </si>
+  <si>
+    <t>80579</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>E08000010</t>
+  </si>
+  <si>
+    <t>888, 925, 343, 877, 860, 332, 929, 884, 808, 893</t>
+  </si>
+  <si>
+    <t>[(888, nan), (925, 'outstanding'), (343, 'good'), (877, 'good'), (860, 'requires improvement'), (332, 'requires improvement'), (929, 'outstanding'), (884, 'good'), (808, 'requires improvement'), (893, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>wigan</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50291724</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>26/11/25</t>
+  </si>
+  <si>
+    <t>80580</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>E06000054</t>
+  </si>
+  <si>
+    <t>850, 916, 802, 938, 855, 937, 895, 881, 815, 803</t>
+  </si>
+  <si>
+    <t>[(850, 'outstanding'), (916, 'good'), (802, 'requires improvement'), (938, 'requires improvement'), (855, 'outstanding'), (937, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (815, 'outstanding'), (803, 'good')]</t>
+  </si>
+  <si>
+    <t>wiltshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50235241</t>
+  </si>
+  <si>
+    <t>25/09/2023</t>
+  </si>
+  <si>
+    <t>29/09/2023</t>
+  </si>
+  <si>
+    <t>12/12/23</t>
+  </si>
+  <si>
+    <t>80581</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>E08000015</t>
+  </si>
+  <si>
+    <t>840, 343, 876, 808, 394, 390, 807, 888, 351, 393</t>
+  </si>
+  <si>
+    <t>[(840, 'outstanding'), (343, 'good'), (876, 'inadequate'), (808, 'requires improvement'), (394, 'outstanding'), (390, 'good'), (807, 'good'), (888, nan), (351, 'requires improvement'), (393, nan)]</t>
+  </si>
+  <si>
+    <t>wirral</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50238913</t>
+  </si>
+  <si>
+    <t>18/09/2023</t>
+  </si>
+  <si>
+    <t>02/02/24</t>
+  </si>
+  <si>
+    <t>80582</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>E06000041</t>
+  </si>
+  <si>
+    <t>868, 936, 825, 869, 305, 358, 318, 919, 867, 823</t>
+  </si>
+  <si>
+    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, nan), (318, 'outstanding'), (919, 'outstanding'), (867, 'outstanding'), (823, 'good')]</t>
+  </si>
+  <si>
+    <t>wokingham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50215917</t>
+  </si>
+  <si>
+    <t>80583</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>E08000031</t>
+  </si>
+  <si>
+    <t>333, 861, 335, 810, 354, 331, 371, 831, 806, 812</t>
+  </si>
+  <si>
+    <t>[(333, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (810, 'good'), (354, 'requires improvement'), (331, 'outstanding'), (371, 'good'), (831, 'outstanding'), (806, nan), (812, 'good')]</t>
+  </si>
+  <si>
+    <t>wolverhampton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50304388</t>
+  </si>
+  <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
+    <t>18/06/26</t>
+  </si>
+  <si>
+    <t>80584</t>
+  </si>
+  <si>
+    <t>885</t>
+  </si>
+  <si>
+    <t>E10000034</t>
+  </si>
+  <si>
+    <t>933, 916, 838, 937, 893, 938, 878, 830, 881, 815</t>
+  </si>
+  <si>
+    <t>[(933, nan), (916, 'good'), (838, 'outstanding'), (937, 'requires improvement'), (893, 'outstanding'), (938, 'requires improvement'), (878, 'inadequate'), (830, 'good'), (881, 'outstanding'), (815, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>worcestershire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50223271</t>
   </si>
   <si>
     <t>15/05/2023</t>
-  </si>
-  <si>
-    <t>19/05/2023</t>
-  </si>
-  <si>
-    <t>03/07/23</t>
-  </si>
-  <si>
-    <t>80540</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>E06000038</t>
-  </si>
-  <si>
-    <t>826, 302, 312, 315, 822, 306, 320, 383, 852, 310</t>
-  </si>
-  <si>
-    <t>[(826, 'good'), (302, 'good'), (312, 'outstanding'), (315, 'outstanding'), (822, 'requires improvement'), (306, 'good'), (320, 'good'), (383, 'outstanding'), (852, 'good'), (310, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>reading</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252257</t>
-  </si>
-  <si>
-    <t>80541</t>
-  </si>
-  <si>
-    <t>807</t>
-  </si>
-  <si>
-    <t>E06000003</t>
-  </si>
-  <si>
-    <t>394, 393, 805, 372, 390, 840, 370, 357, 371, 880</t>
-  </si>
-  <si>
-    <t>[(394, 'outstanding'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
-  </si>
-  <si>
-    <t>redcar and cleveland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50294204</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>80542</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>E08000005</t>
-  </si>
-  <si>
-    <t>335, 357, 861, 350, 394, 371, 372, 831, 353, 355</t>
-  </si>
-  <si>
-    <t>[(335, 'outstanding'), (357, 'inadequate'), (861, 'requires improvement'), (350, 'good'), (394, 'outstanding'), (371, 'good'), (372, 'outstanding'), (831, 'outstanding'), (353, 'good'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>rochdale</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50211330</t>
-  </si>
-  <si>
-    <t>03/02/2023</t>
-  </si>
-  <si>
-    <t>17/03/23</t>
-  </si>
-  <si>
-    <t>80543</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>E08000018</t>
-  </si>
-  <si>
-    <t>370, 357, 371, 384, 894, 332, 807, 394, 390, 840</t>
-  </si>
-  <si>
-    <t>[(370, 'good'), (357, 'inadequate'), (371, 'good'), (384, 'good'), (894, 'outstanding'), (332, 'requires improvement'), (807, 'good'), (394, 'outstanding'), (390, 'good'), (840, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>rotherham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50292638</t>
-  </si>
-  <si>
-    <t>16/12/25</t>
-  </si>
-  <si>
-    <t>80544</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>E09000020</t>
-  </si>
-  <si>
-    <t>205, 202, 208, 213, 210, 209, 212, 206, 302, 203</t>
-  </si>
-  <si>
-    <t>[(205, 'outstanding'), (202, 'outstanding'), (208, 'good'), (213, 'outstanding'), (210, 'good'), (209, 'good'), (212, 'outstanding'), (206, 'outstanding'), (302, 'good'), (203, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>kensington and chelsea</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50266093</t>
-  </si>
-  <si>
-    <t>80545</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>E09000021</t>
-  </si>
-  <si>
-    <t>319, 315, 919, 305, 800, 868, 358, 318, 936, 825</t>
-  </si>
-  <si>
-    <t>[(319, 'good'), (315, 'outstanding'), (919, 'outstanding'), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, nan), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>kingston upon thames</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267803</t>
-  </si>
-  <si>
-    <t>80546</t>
-  </si>
-  <si>
-    <t>868</t>
-  </si>
-  <si>
-    <t>E06000040</t>
-  </si>
-  <si>
-    <t>936, 825, 872, 358, 919, 869, 305, 823, 931, 867</t>
-  </si>
-  <si>
-    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>windsor &amp; maidenhead</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50261980</t>
-  </si>
-  <si>
-    <t>19/11/24</t>
-  </si>
-  <si>
-    <t>80547</t>
-  </si>
-  <si>
-    <t>857</t>
-  </si>
-  <si>
-    <t>E06000017</t>
-  </si>
-  <si>
-    <t>865, 815, 893, 895, 850, 823, 916, 855, 869, 811</t>
-  </si>
-  <si>
-    <t>[(865, 'outstanding'), (815, 'outstanding'), (893, 'outstanding'), (895, 'inadequate'), (850, 'outstanding'), (823, 'good'), (916, 'good'), (855, 'outstanding'), (869, 'good'), (811, 'good')]</t>
-  </si>
-  <si>
-    <t>rutland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252255</t>
-  </si>
-  <si>
-    <t>15/04/2024</t>
-  </si>
-  <si>
-    <t>26/04/2024</t>
-  </si>
-  <si>
-    <t>80548</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>E08000006</t>
-  </si>
-  <si>
-    <t>373, 354, 851, 391, 390, 350, 393, 357, 852, 383</t>
-  </si>
-  <si>
-    <t>[(373, 'good'), (354, 'requires improvement'), (851, 'good'), (391, 'good'), (390, 'good'), (350, 'good'), (393, nan), (357, 'inadequate'), (852, 'good'), (383, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>salford</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50237003</t>
-  </si>
-  <si>
-    <t>kathryn grindrod</t>
-  </si>
-  <si>
-    <t>06/11/2023</t>
-  </si>
-  <si>
-    <t>80549</t>
-  </si>
-  <si>
-    <t>333</t>
-  </si>
-  <si>
-    <t>E08000028</t>
-  </si>
-  <si>
-    <t>336, 810, 861, 335, 354, 380, 806, 331, 353, 821</t>
-  </si>
-  <si>
-    <t>[(336, 'good'), (810, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (354, 'requires improvement'), (380, 'requires improvement'), (806, nan), (331, 'outstanding'), (353, 'good'), (821, 'good')]</t>
-  </si>
-  <si>
-    <t>sandwell</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50291983</t>
-  </si>
-  <si>
-    <t>13/10/2025</t>
-  </si>
-  <si>
-    <t>24/10/2025</t>
-  </si>
-  <si>
-    <t>02/12/25</t>
-  </si>
-  <si>
-    <t>80550</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>E08000014</t>
-  </si>
-  <si>
-    <t>344, 342, 359, 888, 876, 840, 808, 340, 841, 351</t>
-  </si>
-  <si>
-    <t>[(344, 'requires improvement'), (342, 'good'), (359, 'good'), (888, 'good'), (876, 'inadequate'), (840, 'outstanding'), (808, 'requires improvement'), (340, 'inadequate'), (841, 'outstanding'), (351, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>sefton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50284335</t>
-  </si>
-  <si>
-    <t>23/06/2025</t>
-  </si>
-  <si>
-    <t>80551</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>E08000019</t>
-  </si>
-  <si>
-    <t>382, 851, 355, 383, 831, 354, 391, 852, 357, 350</t>
-  </si>
-  <si>
-    <t>[(382, 'good'), (851, 'good'), (355, 'good'), (383, 'outstanding'), (831, 'outstanding'), (354, 'requires improvement'), (391, 'good'), (852, 'good'), (357, 'inadequate'), (350, 'good')]</t>
-  </si>
-  <si>
-    <t>sheffield</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50231897</t>
-  </si>
-  <si>
-    <t>22/09/2023</t>
-  </si>
-  <si>
-    <t>03/11/23</t>
-  </si>
-  <si>
-    <t>80552</t>
-  </si>
-  <si>
-    <t>893</t>
-  </si>
-  <si>
-    <t>E06000051</t>
-  </si>
-  <si>
-    <t>815, 933, 860, 811, 838, 884, 830, 885, 943, 916</t>
-  </si>
-  <si>
-    <t>[(815, 'outstanding'), (933, nan), (860, 'requires improvement'), (811, 'good'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
-  </si>
-  <si>
-    <t>shropshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50284334</t>
-  </si>
-  <si>
-    <t>80553</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>E06000039</t>
-  </si>
-  <si>
-    <t>313, 312, 821, 307, 317, 310, 304, 874, 320, 856</t>
-  </si>
-  <si>
-    <t>[(313, 'good'), (312, 'outstanding'), (821, 'good'), (307, 'good'), (317, 'outstanding'), (310, 'inadequate'), (304, nan), (874, 'inadequate'), (320, 'good'), (856, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>slough</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50211331</t>
-  </si>
-  <si>
-    <t>80554</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>E08000029</t>
-  </si>
-  <si>
-    <t>356, 896, 937, 877, 886, 916, 802, 895, 881, 919</t>
-  </si>
-  <si>
-    <t>[(356, 'requires improvement'), (896, 'requires improvement'), (937, 'requires improvement'), (877, 'good'), (886, 'good'), (916, 'good'), (802, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (919, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>solihull</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50293398</t>
-  </si>
-  <si>
-    <t>steve bailey</t>
-  </si>
-  <si>
-    <t>80555</t>
-  </si>
-  <si>
-    <t>933</t>
-  </si>
-  <si>
-    <t>E10000027</t>
-  </si>
-  <si>
-    <t>935, 830, 838, 893, 885, 891, 878, 860, 855, 881</t>
-  </si>
-  <si>
-    <t>[(935, 'requires improvement'), (830, 'good'), (838, 'outstanding'), (893, 'outstanding'), (885, 'good'), (891, 'good'), (878, 'inadequate'), (860, 'requires improvement'), (855, 'outstanding'), (881, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>somerset</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50304387</t>
-  </si>
-  <si>
-    <t>80556</t>
-  </si>
-  <si>
-    <t>803</t>
-  </si>
-  <si>
-    <t>E06000025</t>
-  </si>
-  <si>
-    <t>855, 850, 938, 873, 823, 802, 916, 881, 931, 865</t>
-  </si>
-  <si>
-    <t>[(855, 'outstanding'), (850, 'outstanding'), (938, 'requires improvement'), (873, 'requires improvement'), (823, 'good'), (802, 'requires improvement'), (916, 'good'), (881, 'outstanding'), (931, 'good'), (865, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>south gloucestershire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253185</t>
-  </si>
-  <si>
-    <t>80557</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>E08000023</t>
-  </si>
-  <si>
-    <t>394, 807, 390, 805, 840, 357, 372, 354, 890, 841</t>
-  </si>
-  <si>
-    <t>[(394, 'outstanding'), (807, 'good'), (390, 'good'), (805, 'outstanding'), (840, 'outstanding'), (357, 'inadequate'), (372, 'outstanding'), (354, 'requires improvement'), (890, nan), (841, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>south tyneside</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50308876</t>
-  </si>
-  <si>
-    <t>15/06/2026</t>
-  </si>
-  <si>
-    <t>26/06/2026</t>
-  </si>
-  <si>
-    <t>04/08/26</t>
-  </si>
-  <si>
-    <t>80558</t>
-  </si>
-  <si>
-    <t>852</t>
-  </si>
-  <si>
-    <t>E06000045</t>
-  </si>
-  <si>
-    <t>331, 831, 851, 373, 312, 355, 874, 383, 350, 320</t>
-  </si>
-  <si>
-    <t>[(331, 'outstanding'), (831, 'outstanding'), (851, 'good'), (373, 'good'), (312, 'outstanding'), (355, 'good'), (874, 'inadequate'), (383, 'outstanding'), (350, 'good'), (320, 'good')]</t>
-  </si>
-  <si>
-    <t>southampton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50224705</t>
-  </si>
-  <si>
-    <t>05/06/2023</t>
-  </si>
-  <si>
-    <t>16/06/2023</t>
-  </si>
-  <si>
-    <t>28/07/23</t>
-  </si>
-  <si>
-    <t>80559</t>
-  </si>
-  <si>
-    <t>882</t>
-  </si>
-  <si>
-    <t>E06000033</t>
-  </si>
-  <si>
-    <t>839, 383, 826, 351, 845, 851, 886, 303, 392, 822</t>
-  </si>
-  <si>
-    <t>[(839, 'good'), (383, 'outstanding'), (826, 'good'), (351, 'requires improvement'), (845, 'good'), (851, 'good'), (886, 'good'), (303, 'outstanding'), (392, 'outstanding'), (822, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>southend-on-sea</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50263392</t>
-  </si>
-  <si>
-    <t>80560</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>E08000013</t>
-  </si>
-  <si>
-    <t>876, 343, 340, 840, 807, 370, 394, 344, 808, 894</t>
-  </si>
-  <si>
-    <t>[(876, 'inadequate'), (343, 'good'), (340, 'inadequate'), (840, 'outstanding'), (807, 'good'), (370, 'good'), (394, 'outstanding'), (344, 'requires improvement'), (808, 'requires improvement'), (894, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>st helens</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50227184</t>
-  </si>
-  <si>
-    <t>80561</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>E10000028</t>
-  </si>
-  <si>
-    <t>811, 884, 893, 815, 933, 830, 877, 891, 943, 888</t>
-  </si>
-  <si>
-    <t>[(811, 'good'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, nan), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, 'good')]</t>
-  </si>
-  <si>
-    <t>staffordshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50237007</t>
-  </si>
-  <si>
-    <t>80562</t>
-  </si>
-  <si>
-    <t>356</t>
-  </si>
-  <si>
-    <t>E08000007</t>
-  </si>
-  <si>
-    <t>334, 358, 896, 916, 919, 938, 937, 802, 803, 873</t>
-  </si>
-  <si>
-    <t>[(334, 'good'), (358, nan), (896, 'requires improvement'), (916, 'good'), (919, 'outstanding'), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>stockport</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50282103</t>
-  </si>
-  <si>
-    <t>15/07/25</t>
-  </si>
-  <si>
-    <t>80563</t>
-  </si>
-  <si>
-    <t>808</t>
-  </si>
-  <si>
-    <t>E06000004</t>
-  </si>
-  <si>
-    <t>841, 332, 888, 390, 384, 351, 840, 372, 894, 344</t>
-  </si>
-  <si>
-    <t>[(841, 'outstanding'), (332, 'requires improvement'), (888, 'good'), (390, 'good'), (384, 'good'), (351, 'requires improvement'), (840, 'outstanding'), (372, 'outstanding'), (894, 'outstanding'), (344, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>stockton-on-tees</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50215915</t>
-  </si>
-  <si>
-    <t>joanna warburton</t>
-  </si>
-  <si>
-    <t>06/03/2023</t>
-  </si>
-  <si>
-    <t>17/03/2023</t>
-  </si>
-  <si>
-    <t>09/05/23</t>
-  </si>
-  <si>
-    <t>80564</t>
-  </si>
-  <si>
-    <t>861</t>
-  </si>
-  <si>
-    <t>E06000021</t>
-  </si>
-  <si>
-    <t>335, 354, 336, 371, 812, 810, 333, 357, 831, 372</t>
-  </si>
-  <si>
-    <t>[(335, 'outstanding'), (354, 'requires improvement'), (336, 'good'), (371, 'good'), (812, 'good'), (810, 'good'), (333, 'good'), (357, 'inadequate'), (831, 'outstanding'), (372, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>stoke-on-trent</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50282104</t>
-  </si>
-  <si>
-    <t>80565</t>
-  </si>
-  <si>
-    <t>935</t>
-  </si>
-  <si>
-    <t>E10000029</t>
-  </si>
-  <si>
-    <t>933, 926, 830, 891, 878, 881, 886, 838, 925, 940</t>
-  </si>
-  <si>
-    <t>[(933, nan), (926, 'outstanding'), (830, 'good'), (891, 'good'), (878, 'inadequate'), (881, 'outstanding'), (886, 'good'), (838, 'outstanding'), (925, 'outstanding'), (940, nan)]</t>
-  </si>
-  <si>
-    <t>suffolk</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255285</t>
-  </si>
-  <si>
-    <t>21/08/24</t>
-  </si>
-  <si>
-    <t>80566</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>E08000024</t>
-  </si>
-  <si>
-    <t>807, 393, 805, 372, 357, 880, 390, 840, 370, 354</t>
-  </si>
-  <si>
-    <t>[(807, 'good'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (880, 'good'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (354, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>sunderland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50271150</t>
-  </si>
-  <si>
-    <t>11/03/25</t>
-  </si>
-  <si>
-    <t>80567</t>
-  </si>
-  <si>
-    <t>936</t>
-  </si>
-  <si>
-    <t>E10000030</t>
-  </si>
-  <si>
-    <t>868, 825, 358, 919, 869, 823, 872, 931, 867, 873</t>
-  </si>
-  <si>
-    <t>[(868, 'good'), (825, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>surrey</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50276410</t>
-  </si>
-  <si>
-    <t>80568</t>
-  </si>
-  <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>E06000030</t>
-  </si>
-  <si>
-    <t>887, 940, 883, 303, 822, 941, 935, 311, 891, 886</t>
-  </si>
-  <si>
-    <t>[(887, 'good'), (940, nan), (883, 'outstanding'), (303, 'outstanding'), (822, 'requires improvement'), (941, nan), (935, 'requires improvement'), (311, 'inadequate'), (891, 'good'), (886, 'good')]</t>
-  </si>
-  <si>
-    <t>swindon</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50227724</t>
-  </si>
-  <si>
-    <t>80569</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>E08000008</t>
-  </si>
-  <si>
-    <t>372, 390, 354, 370, 384, 332, 894, 879, 394, 880</t>
-  </si>
-  <si>
-    <t>[(372, 'outstanding'), (390, 'good'), (354, 'requires improvement'), (370, 'good'), (384, 'good'), (332, 'requires improvement'), (894, 'outstanding'), (879, 'requires improvement'), (394, 'outstanding'), (880, 'good')]</t>
-  </si>
-  <si>
-    <t>tameside</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50239562</t>
-  </si>
-  <si>
-    <t>13/02/24</t>
-  </si>
-  <si>
-    <t>80570</t>
-  </si>
-  <si>
-    <t>894</t>
-  </si>
-  <si>
-    <t>E06000020</t>
-  </si>
-  <si>
-    <t>384, 372, 332, 370, 357, 371, 841, 390, 879, 808</t>
-  </si>
-  <si>
-    <t>[(384, 'good'), (372, 'outstanding'), (332, 'requires improvement'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (841, 'outstanding'), (390, 'good'), (879, 'requires improvement'), (808, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>telford &amp; wrekin</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252260</t>
-  </si>
-  <si>
-    <t>29/04/2024</t>
-  </si>
-  <si>
-    <t>80571</t>
-  </si>
-  <si>
-    <t>883</t>
-  </si>
-  <si>
-    <t>E06000034</t>
-  </si>
-  <si>
-    <t>866, 303, 311, 887, 940, 822, 941, 332, 925, 935</t>
-  </si>
-  <si>
-    <t>[(866, 'inadequate'), (303, 'outstanding'), (311, 'inadequate'), (887, 'good'), (940, nan), (822, 'requires improvement'), (941, nan), (332, 'requires improvement'), (925, 'outstanding'), (935, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>thurrock</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50260250</t>
-  </si>
-  <si>
-    <t>16/09/2024</t>
-  </si>
-  <si>
-    <t>20/09/2024</t>
-  </si>
-  <si>
-    <t>29/10/24</t>
-  </si>
-  <si>
-    <t>80572</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>E06000027</t>
-  </si>
-  <si>
-    <t>357, 394, 879, 372, 807, 921, 370, 390, 354, 894</t>
-  </si>
-  <si>
-    <t>[(357, 'inadequate'), (394, 'outstanding'), (879, 'requires improvement'), (372, 'outstanding'), (807, 'good'), (921, 'good'), (370, 'good'), (390, 'good'), (354, 'requires improvement'), (894, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>torbay</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50295967</t>
-  </si>
-  <si>
-    <t>80573</t>
-  </si>
-  <si>
-    <t>358</t>
-  </si>
-  <si>
-    <t>E08000009</t>
-  </si>
-  <si>
-    <t>919, 356, 825, 931, 936, 305, 895, 873, 916, 334</t>
-  </si>
-  <si>
-    <t>[(919, 'outstanding'), (356, 'requires improvement'), (825, 'requires improvement'), (931, 'good'), (936, 'good'), (305, 'outstanding'), (895, 'inadequate'), (873, 'requires improvement'), (916, 'good'), (334, 'good')]</t>
-  </si>
-  <si>
-    <t>trafford</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50308602</t>
-  </si>
-  <si>
-    <t>leanne cooper</t>
-  </si>
-  <si>
-    <t>03/08/26</t>
-  </si>
-  <si>
-    <t>80574</t>
-  </si>
-  <si>
-    <t>335</t>
-  </si>
-  <si>
-    <t>E08000030</t>
-  </si>
-  <si>
-    <t>354, 861, 357, 336, 371, 831, 350, 372, 812, 333</t>
-  </si>
-  <si>
-    <t>[(354, 'requires improvement'), (861, 'requires improvement'), (357, 'inadequate'), (336, 'good'), (371, 'good'), (831, 'outstanding'), (350, 'good'), (372, 'outstanding'), (812, 'good'), (333, 'good')]</t>
-  </si>
-  <si>
-    <t>walsall</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50281396</t>
-  </si>
-  <si>
-    <t>80575</t>
-  </si>
-  <si>
-    <t>877</t>
-  </si>
-  <si>
-    <t>E06000007</t>
-  </si>
-  <si>
-    <t>895, 937, 860, 811, 815, 916, 334, 893, 885, 865</t>
-  </si>
-  <si>
-    <t>[(895, 'inadequate'), (937, 'requires improvement'), (860, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (916, 'good'), (334, 'good'), (893, 'outstanding'), (885, 'good'), (865, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>warrington</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253719</t>
-  </si>
-  <si>
-    <t>30/07/24</t>
-  </si>
-  <si>
-    <t>80576</t>
-  </si>
-  <si>
-    <t>937</t>
-  </si>
-  <si>
-    <t>E10000031</t>
-  </si>
-  <si>
-    <t>916, 895, 931, 802, 855, 938, 850, 877, 865, 881</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (895, 'inadequate'), (931, 'good'), (802, 'requires improvement'), (855, 'outstanding'), (938, 'requires improvement'), (850, 'outstanding'), (877, 'good'), (865, 'outstanding'), (881, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>warwickshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50289041</t>
-  </si>
-  <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>14/10/25</t>
-  </si>
-  <si>
-    <t>80577</t>
-  </si>
-  <si>
-    <t>869</t>
-  </si>
-  <si>
-    <t>E06000037</t>
-  </si>
-  <si>
-    <t>825, 850, 931, 867, 919, 873, 823, 865, 916, 305</t>
-  </si>
-  <si>
-    <t>[(825, 'requires improvement'), (850, 'outstanding'), (931, 'good'), (867, 'outstanding'), (919, 'outstanding'), (873, 'requires improvement'), (823, 'good'), (865, 'outstanding'), (916, 'good'), (305, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>west berkshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50290038</t>
-  </si>
-  <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>28/10/25</t>
-  </si>
-  <si>
-    <t>2637548</t>
-  </si>
-  <si>
-    <t>941</t>
-  </si>
-  <si>
-    <t>E06000062</t>
-  </si>
-  <si>
-    <t>822, 940, 937, 866, 933, 935, 311, 855, 931, 303</t>
-  </si>
-  <si>
-    <t>[(822, 'requires improvement'), (940, nan), (937, 'requires improvement'), (866, 'inadequate'), (933, nan), (935, 'requires improvement'), (311, 'inadequate'), (855, 'outstanding'), (931, 'good'), (303, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>west northamptonshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50306547</t>
-  </si>
-  <si>
-    <t>80578</t>
-  </si>
-  <si>
-    <t>938</t>
-  </si>
-  <si>
-    <t>E10000032</t>
-  </si>
-  <si>
-    <t>916, 881, 850, 919, 937, 865, 802, 931, 803, 878</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (881, 'outstanding'), (850, 'outstanding'), (919, 'outstanding'), (937, 'requires improvement'), (865, 'outstanding'), (802, 'requires improvement'), (931, 'good'), (803, 'good'), (878, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>west sussex</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50216276</t>
-  </si>
-  <si>
-    <t>maire atherton</t>
-  </si>
-  <si>
-    <t>2733698</t>
-  </si>
-  <si>
-    <t>943</t>
-  </si>
-  <si>
-    <t>884, 942, 860, 893, 811, 815, 925, 933, 935, 830</t>
-  </si>
-  <si>
-    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'good'), (815, 'outstanding'), (925, 'outstanding'), (933, nan), (935, 'requires improvement'), (830, 'good')]</t>
-  </si>
-  <si>
-    <t>westmorland and furness</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252261</t>
-  </si>
-  <si>
-    <t>80579</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>E08000010</t>
-  </si>
-  <si>
-    <t>888, 925, 343, 877, 860, 332, 929, 884, 808, 893</t>
-  </si>
-  <si>
-    <t>[(888, 'good'), (925, 'outstanding'), (343, 'good'), (877, 'good'), (860, 'requires improvement'), (332, 'requires improvement'), (929, 'outstanding'), (884, 'good'), (808, 'requires improvement'), (893, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>wigan</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50291724</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>26/11/25</t>
-  </si>
-  <si>
-    <t>80580</t>
-  </si>
-  <si>
-    <t>865</t>
-  </si>
-  <si>
-    <t>E06000054</t>
-  </si>
-  <si>
-    <t>850, 916, 802, 938, 855, 937, 895, 881, 815, 803</t>
-  </si>
-  <si>
-    <t>[(850, 'outstanding'), (916, 'good'), (802, 'requires improvement'), (938, 'requires improvement'), (855, 'outstanding'), (937, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (815, 'outstanding'), (803, 'good')]</t>
-  </si>
-  <si>
-    <t>wiltshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50235241</t>
-  </si>
-  <si>
-    <t>25/09/2023</t>
-  </si>
-  <si>
-    <t>29/09/2023</t>
-  </si>
-  <si>
-    <t>12/12/23</t>
-  </si>
-  <si>
-    <t>80581</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>E08000015</t>
-  </si>
-  <si>
-    <t>840, 343, 876, 808, 394, 390, 807, 888, 351, 393</t>
-  </si>
-  <si>
-    <t>[(840, 'outstanding'), (343, 'good'), (876, 'inadequate'), (808, 'requires improvement'), (394, 'outstanding'), (390, 'good'), (807, 'good'), (888, 'good'), (351, 'requires improvement'), (393, nan)]</t>
-  </si>
-  <si>
-    <t>wirral</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50238913</t>
-  </si>
-  <si>
-    <t>18/09/2023</t>
-  </si>
-  <si>
-    <t>02/02/24</t>
-  </si>
-  <si>
-    <t>80582</t>
-  </si>
-  <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>E06000041</t>
-  </si>
-  <si>
-    <t>868, 936, 825, 869, 305, 358, 318, 919, 867, 823</t>
-  </si>
-  <si>
-    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, nan), (318, 'outstanding'), (919, 'outstanding'), (867, 'outstanding'), (823, 'good')]</t>
-  </si>
-  <si>
-    <t>wokingham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50215917</t>
-  </si>
-  <si>
-    <t>80583</t>
-  </si>
-  <si>
-    <t>336</t>
-  </si>
-  <si>
-    <t>E08000031</t>
-  </si>
-  <si>
-    <t>333, 861, 335, 810, 354, 331, 371, 831, 806, 812</t>
-  </si>
-  <si>
-    <t>[(333, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (810, 'good'), (354, 'requires improvement'), (331, 'outstanding'), (371, 'good'), (831, 'outstanding'), (806, nan), (812, 'good')]</t>
-  </si>
-  <si>
-    <t>wolverhampton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50304388</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>18/06/26</t>
-  </si>
-  <si>
-    <t>80584</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>E10000034</t>
-  </si>
-  <si>
-    <t>933, 916, 838, 937, 893, 938, 878, 830, 881, 815</t>
-  </si>
-  <si>
-    <t>[(933, nan), (916, 'good'), (838, 'outstanding'), (937, 'requires improvement'), (893, 'outstanding'), (938, 'requires improvement'), (878, 'inadequate'), (830, 'good'), (881, 'outstanding'), (815, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>worcestershire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50223271</t>
   </si>
   <si>
     <t>26/05/2023</t>
@@ -4674,64 +4671,64 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>1429</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6111,7 +6108,7 @@
         <v>79</v>
       </c>
       <c r="T23" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -6174,7 +6171,7 @@
         <v>79</v>
       </c>
       <c r="T24" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -6741,7 +6738,7 @@
         <v>8</v>
       </c>
       <c r="T33" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -7119,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="T39" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -7497,7 +7494,7 @@
         <v>8</v>
       </c>
       <c r="T45" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -7686,7 +7683,7 @@
         <v>79</v>
       </c>
       <c r="T48" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -7841,13 +7838,13 @@
         <v>526</v>
       </c>
       <c r="I51" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="J51" t="s">
         <v>48</v>
       </c>
       <c r="K51" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="L51" t="s">
         <v>527</v>
@@ -7863,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="Q51" t="s">
         <v>8</v>
@@ -7872,10 +7869,10 @@
         <v>8</v>
       </c>
       <c r="S51" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="T51" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -8165,13 +8162,13 @@
         <v>190</v>
       </c>
       <c r="L56" t="s">
+        <v>527</v>
+      </c>
+      <c r="M56" t="s">
+        <v>528</v>
+      </c>
+      <c r="N56" t="s">
         <v>573</v>
-      </c>
-      <c r="M56" t="s">
-        <v>574</v>
-      </c>
-      <c r="N56" t="s">
-        <v>575</v>
       </c>
       <c r="O56" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80485_liverpool", ".\export_data\inspection_reports\80485_liverpool")</f>
@@ -8195,28 +8192,28 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B57" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C57" t="s">
         <v>217</v>
       </c>
       <c r="D57" t="s">
+        <v>576</v>
+      </c>
+      <c r="E57" t="s">
+        <v>577</v>
+      </c>
+      <c r="F57" t="s">
         <v>578</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>579</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="G57" t="s">
-        <v>581</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="I57" t="s">
         <v>14</v>
@@ -8228,13 +8225,13 @@
         <v>106</v>
       </c>
       <c r="L57" t="s">
+        <v>581</v>
+      </c>
+      <c r="M57" t="s">
+        <v>582</v>
+      </c>
+      <c r="N57" t="s">
         <v>583</v>
-      </c>
-      <c r="M57" t="s">
-        <v>584</v>
-      </c>
-      <c r="N57" t="s">
-        <v>585</v>
       </c>
       <c r="O57" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80486_barking and dagenham", ".\export_data\inspection_reports\80486_barking and dagenham")</f>
@@ -8258,28 +8255,28 @@
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B58" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C58" t="s">
         <v>217</v>
       </c>
       <c r="D58" t="s">
+        <v>586</v>
+      </c>
+      <c r="E58" t="s">
+        <v>587</v>
+      </c>
+      <c r="F58" t="s">
         <v>588</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>589</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="G58" t="s">
-        <v>591</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="I58" t="s">
         <v>8</v>
@@ -8321,28 +8318,28 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B59" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C59" t="s">
         <v>217</v>
       </c>
       <c r="D59" t="s">
+        <v>593</v>
+      </c>
+      <c r="E59" t="s">
+        <v>594</v>
+      </c>
+      <c r="F59" t="s">
         <v>595</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>596</v>
       </c>
-      <c r="F59" t="s">
+      <c r="H59" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="G59" t="s">
-        <v>598</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="I59" t="s">
         <v>79</v>
@@ -8354,7 +8351,7 @@
         <v>391</v>
       </c>
       <c r="L59" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="M59" t="s">
         <v>382</v>
@@ -8384,28 +8381,28 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B60" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C60" t="s">
         <v>217</v>
       </c>
       <c r="D60" t="s">
+        <v>601</v>
+      </c>
+      <c r="E60" t="s">
+        <v>602</v>
+      </c>
+      <c r="F60" t="s">
         <v>603</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>604</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="G60" t="s">
-        <v>606</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="I60" t="s">
         <v>74</v>
@@ -8414,16 +8411,16 @@
         <v>9</v>
       </c>
       <c r="K60" t="s">
+        <v>606</v>
+      </c>
+      <c r="L60" t="s">
+        <v>607</v>
+      </c>
+      <c r="M60" t="s">
         <v>608</v>
       </c>
-      <c r="L60" t="s">
+      <c r="N60" t="s">
         <v>609</v>
-      </c>
-      <c r="M60" t="s">
-        <v>610</v>
-      </c>
-      <c r="N60" t="s">
-        <v>611</v>
       </c>
       <c r="O60" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80489_brent", ".\export_data\inspection_reports\80489_brent")</f>
@@ -8447,28 +8444,28 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B61" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C61" t="s">
         <v>217</v>
       </c>
       <c r="D61" t="s">
+        <v>612</v>
+      </c>
+      <c r="E61" t="s">
+        <v>613</v>
+      </c>
+      <c r="F61" t="s">
         <v>614</v>
       </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>615</v>
       </c>
-      <c r="F61" t="s">
+      <c r="H61" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="G61" t="s">
-        <v>617</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="I61" t="s">
         <v>79</v>
@@ -8477,13 +8474,13 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
+        <v>617</v>
+      </c>
+      <c r="L61" t="s">
+        <v>618</v>
+      </c>
+      <c r="M61" t="s">
         <v>619</v>
-      </c>
-      <c r="L61" t="s">
-        <v>620</v>
-      </c>
-      <c r="M61" t="s">
-        <v>621</v>
       </c>
       <c r="N61" t="s">
         <v>322</v>
@@ -8510,28 +8507,28 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B62" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C62" t="s">
         <v>217</v>
       </c>
       <c r="D62" t="s">
+        <v>622</v>
+      </c>
+      <c r="E62" t="s">
+        <v>623</v>
+      </c>
+      <c r="F62" t="s">
         <v>624</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>625</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="G62" t="s">
-        <v>627</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="I62" t="s">
         <v>79</v>
@@ -8540,7 +8537,7 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L62" t="s">
         <v>63</v>
@@ -8573,28 +8570,28 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B63" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C63" t="s">
         <v>217</v>
       </c>
       <c r="D63" t="s">
+        <v>629</v>
+      </c>
+      <c r="E63" t="s">
+        <v>630</v>
+      </c>
+      <c r="F63" t="s">
         <v>631</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>632</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="G63" t="s">
-        <v>634</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="I63" t="s">
         <v>8</v>
@@ -8606,13 +8603,13 @@
         <v>223</v>
       </c>
       <c r="L63" t="s">
+        <v>634</v>
+      </c>
+      <c r="M63" t="s">
+        <v>635</v>
+      </c>
+      <c r="N63" t="s">
         <v>636</v>
-      </c>
-      <c r="M63" t="s">
-        <v>637</v>
-      </c>
-      <c r="N63" t="s">
-        <v>638</v>
       </c>
       <c r="O63" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80492_croydon", ".\export_data\inspection_reports\80492_croydon")</f>
@@ -8636,28 +8633,28 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B64" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C64" t="s">
         <v>217</v>
       </c>
       <c r="D64" t="s">
+        <v>639</v>
+      </c>
+      <c r="E64" t="s">
+        <v>640</v>
+      </c>
+      <c r="F64" t="s">
         <v>641</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>642</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="G64" t="s">
-        <v>644</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="I64" t="s">
         <v>8</v>
@@ -8699,28 +8696,28 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B65" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C65" t="s">
         <v>217</v>
       </c>
       <c r="D65" t="s">
+        <v>646</v>
+      </c>
+      <c r="E65" t="s">
+        <v>647</v>
+      </c>
+      <c r="F65" t="s">
         <v>648</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>649</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="G65" t="s">
-        <v>651</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="I65" t="s">
         <v>8</v>
@@ -8732,13 +8729,13 @@
         <v>223</v>
       </c>
       <c r="L65" t="s">
+        <v>651</v>
+      </c>
+      <c r="M65" t="s">
+        <v>652</v>
+      </c>
+      <c r="N65" t="s">
         <v>653</v>
-      </c>
-      <c r="M65" t="s">
-        <v>654</v>
-      </c>
-      <c r="N65" t="s">
-        <v>655</v>
       </c>
       <c r="O65" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80494_enfield", ".\export_data\inspection_reports\80494_enfield")</f>
@@ -8762,28 +8759,28 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B66" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C66" t="s">
         <v>217</v>
       </c>
       <c r="D66" t="s">
+        <v>656</v>
+      </c>
+      <c r="E66" t="s">
+        <v>657</v>
+      </c>
+      <c r="F66" t="s">
         <v>658</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>659</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="G66" t="s">
-        <v>661</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="I66" t="s">
         <v>79</v>
@@ -8795,13 +8792,13 @@
         <v>391</v>
       </c>
       <c r="L66" t="s">
+        <v>661</v>
+      </c>
+      <c r="M66" t="s">
+        <v>662</v>
+      </c>
+      <c r="N66" t="s">
         <v>663</v>
-      </c>
-      <c r="M66" t="s">
-        <v>664</v>
-      </c>
-      <c r="N66" t="s">
-        <v>665</v>
       </c>
       <c r="O66" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80495_greenwich", ".\export_data\inspection_reports\80495_greenwich")</f>
@@ -8825,28 +8822,28 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B67" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C67" t="s">
         <v>217</v>
       </c>
       <c r="D67" t="s">
+        <v>666</v>
+      </c>
+      <c r="E67" t="s">
+        <v>667</v>
+      </c>
+      <c r="F67" t="s">
         <v>668</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>669</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="G67" t="s">
-        <v>671</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="I67" t="s">
         <v>8</v>
@@ -8861,10 +8858,10 @@
         <v>257</v>
       </c>
       <c r="M67" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="N67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="O67" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80496_hackney", ".\export_data\inspection_reports\80496_hackney")</f>
@@ -8888,28 +8885,28 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B68" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C68" t="s">
         <v>217</v>
       </c>
       <c r="D68" t="s">
+        <v>675</v>
+      </c>
+      <c r="E68" t="s">
+        <v>676</v>
+      </c>
+      <c r="F68" t="s">
         <v>677</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>678</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="G68" t="s">
-        <v>680</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="I68" t="s">
         <v>79</v>
@@ -8921,7 +8918,7 @@
         <v>223</v>
       </c>
       <c r="L68" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="M68" t="s">
         <v>171</v>
@@ -8951,28 +8948,28 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B69" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C69" t="s">
         <v>217</v>
       </c>
       <c r="D69" t="s">
+        <v>683</v>
+      </c>
+      <c r="E69" t="s">
+        <v>684</v>
+      </c>
+      <c r="F69" t="s">
         <v>685</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>686</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="G69" t="s">
-        <v>688</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="I69" t="s">
         <v>79</v>
@@ -8987,10 +8984,10 @@
         <v>212</v>
       </c>
       <c r="M69" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="N69" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="O69" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80498_haringey", ".\export_data\inspection_reports\80498_haringey")</f>
@@ -9014,28 +9011,28 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B70" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C70" t="s">
         <v>217</v>
       </c>
       <c r="D70" t="s">
+        <v>692</v>
+      </c>
+      <c r="E70" t="s">
+        <v>693</v>
+      </c>
+      <c r="F70" t="s">
         <v>694</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>695</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="G70" t="s">
-        <v>697</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="I70" t="s">
         <v>189</v>
@@ -9050,10 +9047,10 @@
         <v>341</v>
       </c>
       <c r="M70" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="N70" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="O70" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80499_harrow", ".\export_data\inspection_reports\80499_harrow")</f>
@@ -9077,28 +9074,28 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B71" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C71" t="s">
         <v>217</v>
       </c>
       <c r="D71" t="s">
+        <v>701</v>
+      </c>
+      <c r="E71" t="s">
+        <v>702</v>
+      </c>
+      <c r="F71" t="s">
         <v>703</v>
       </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>704</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="G71" t="s">
-        <v>706</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="I71" t="s">
         <v>189</v>
@@ -9107,16 +9104,16 @@
         <v>48</v>
       </c>
       <c r="K71" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L71" t="s">
         <v>392</v>
       </c>
       <c r="M71" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="N71" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="O71" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80500_havering", ".\export_data\inspection_reports\80500_havering")</f>
@@ -9140,28 +9137,28 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B72" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C72" t="s">
         <v>217</v>
       </c>
       <c r="D72" t="s">
+        <v>710</v>
+      </c>
+      <c r="E72" t="s">
+        <v>711</v>
+      </c>
+      <c r="F72" t="s">
         <v>712</v>
       </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>713</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="G72" t="s">
-        <v>715</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="I72" t="s">
         <v>79</v>
@@ -9173,13 +9170,13 @@
         <v>223</v>
       </c>
       <c r="L72" t="s">
+        <v>715</v>
+      </c>
+      <c r="M72" t="s">
+        <v>716</v>
+      </c>
+      <c r="N72" t="s">
         <v>717</v>
-      </c>
-      <c r="M72" t="s">
-        <v>718</v>
-      </c>
-      <c r="N72" t="s">
-        <v>719</v>
       </c>
       <c r="O72" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80501_hillingdon", ".\export_data\inspection_reports\80501_hillingdon")</f>
@@ -9203,28 +9200,28 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B73" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C73" t="s">
         <v>217</v>
       </c>
       <c r="D73" t="s">
+        <v>720</v>
+      </c>
+      <c r="E73" t="s">
+        <v>721</v>
+      </c>
+      <c r="F73" t="s">
         <v>722</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>723</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="G73" t="s">
-        <v>725</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="I73" t="s">
         <v>8</v>
@@ -9236,13 +9233,13 @@
         <v>139</v>
       </c>
       <c r="L73" t="s">
+        <v>725</v>
+      </c>
+      <c r="M73" t="s">
+        <v>726</v>
+      </c>
+      <c r="N73" t="s">
         <v>727</v>
-      </c>
-      <c r="M73" t="s">
-        <v>728</v>
-      </c>
-      <c r="N73" t="s">
-        <v>729</v>
       </c>
       <c r="O73" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80503_hounslow", ".\export_data\inspection_reports\80503_hounslow")</f>
@@ -9266,28 +9263,28 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B74" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C74" t="s">
         <v>217</v>
       </c>
       <c r="D74" t="s">
+        <v>730</v>
+      </c>
+      <c r="E74" t="s">
+        <v>731</v>
+      </c>
+      <c r="F74" t="s">
         <v>732</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>733</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="G74" t="s">
-        <v>735</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="I74" t="s">
         <v>79</v>
@@ -9324,33 +9321,33 @@
         <v>79</v>
       </c>
       <c r="T74" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B75" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C75" t="s">
         <v>217</v>
       </c>
       <c r="D75" t="s">
+        <v>737</v>
+      </c>
+      <c r="E75" t="s">
+        <v>738</v>
+      </c>
+      <c r="F75" t="s">
         <v>739</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>740</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="G75" t="s">
-        <v>742</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="I75" t="s">
         <v>8</v>
@@ -9359,7 +9356,7 @@
         <v>48</v>
       </c>
       <c r="K75" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L75" t="s">
         <v>212</v>
@@ -9368,7 +9365,7 @@
         <v>213</v>
       </c>
       <c r="N75" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O75" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80506_lambeth", ".\export_data\inspection_reports\80506_lambeth")</f>
@@ -9392,28 +9389,28 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B76" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C76" t="s">
         <v>217</v>
       </c>
       <c r="D76" t="s">
+        <v>746</v>
+      </c>
+      <c r="E76" t="s">
+        <v>747</v>
+      </c>
+      <c r="F76" t="s">
         <v>748</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>749</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="G76" t="s">
-        <v>751</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="I76" t="s">
         <v>8</v>
@@ -9422,16 +9419,16 @@
         <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L76" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="M76" t="s">
         <v>393</v>
       </c>
       <c r="N76" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="O76" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80508_lewisham", ".\export_data\inspection_reports\80508_lewisham")</f>
@@ -9455,28 +9452,28 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B77" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C77" t="s">
         <v>217</v>
       </c>
       <c r="D77" t="s">
+        <v>756</v>
+      </c>
+      <c r="E77" t="s">
+        <v>757</v>
+      </c>
+      <c r="F77" t="s">
         <v>758</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>759</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="G77" t="s">
-        <v>761</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="I77" t="s">
         <v>79</v>
@@ -9485,7 +9482,7 @@
         <v>9</v>
       </c>
       <c r="K77" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L77" t="s">
         <v>37</v>
@@ -9518,28 +9515,28 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B78" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C78" t="s">
         <v>217</v>
       </c>
       <c r="D78" t="s">
+        <v>763</v>
+      </c>
+      <c r="E78" t="s">
+        <v>764</v>
+      </c>
+      <c r="F78" t="s">
         <v>765</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>766</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="G78" t="s">
-        <v>768</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="I78" t="s">
         <v>79</v>
@@ -9554,7 +9551,7 @@
         <v>461</v>
       </c>
       <c r="M78" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="N78" t="s">
         <v>463</v>
@@ -9581,28 +9578,28 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B79" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C79" t="s">
         <v>217</v>
       </c>
       <c r="D79" t="s">
+        <v>771</v>
+      </c>
+      <c r="E79" t="s">
+        <v>772</v>
+      </c>
+      <c r="F79" t="s">
         <v>773</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>774</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="G79" t="s">
-        <v>776</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="I79" t="s">
         <v>79</v>
@@ -9611,7 +9608,7 @@
         <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L79" t="s">
         <v>442</v>
@@ -9644,28 +9641,28 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B80" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C80" t="s">
         <v>217</v>
       </c>
       <c r="D80" t="s">
+        <v>779</v>
+      </c>
+      <c r="E80" t="s">
+        <v>780</v>
+      </c>
+      <c r="F80" t="s">
         <v>781</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>782</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="G80" t="s">
-        <v>784</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="I80" t="s">
         <v>79</v>
@@ -9707,28 +9704,28 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B81" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C81" t="s">
         <v>217</v>
       </c>
       <c r="D81" t="s">
+        <v>786</v>
+      </c>
+      <c r="E81" t="s">
+        <v>787</v>
+      </c>
+      <c r="F81" t="s">
         <v>788</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>789</v>
       </c>
-      <c r="F81" t="s">
+      <c r="H81" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="G81" t="s">
-        <v>791</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="I81" t="s">
         <v>8</v>
@@ -9737,7 +9734,7 @@
         <v>9</v>
       </c>
       <c r="K81" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L81" t="s">
         <v>278</v>
@@ -9770,28 +9767,28 @@
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B82" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C82" t="s">
         <v>217</v>
       </c>
       <c r="D82" t="s">
+        <v>793</v>
+      </c>
+      <c r="E82" t="s">
+        <v>794</v>
+      </c>
+      <c r="F82" t="s">
         <v>795</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>796</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H82" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="G82" t="s">
-        <v>798</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="I82" t="s">
         <v>8</v>
@@ -9803,7 +9800,7 @@
         <v>62</v>
       </c>
       <c r="L82" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="M82" t="s">
         <v>151</v>
@@ -9833,28 +9830,28 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B83" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C83" t="s">
         <v>217</v>
       </c>
       <c r="D83" t="s">
+        <v>801</v>
+      </c>
+      <c r="E83" t="s">
+        <v>802</v>
+      </c>
+      <c r="F83" t="s">
         <v>803</v>
       </c>
-      <c r="E83" t="s">
+      <c r="G83" t="s">
         <v>804</v>
       </c>
-      <c r="F83" t="s">
+      <c r="H83" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="G83" t="s">
-        <v>806</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="I83" t="s">
         <v>79</v>
@@ -9866,13 +9863,13 @@
         <v>24</v>
       </c>
       <c r="L83" t="s">
+        <v>806</v>
+      </c>
+      <c r="M83" t="s">
+        <v>807</v>
+      </c>
+      <c r="N83" t="s">
         <v>808</v>
-      </c>
-      <c r="M83" t="s">
-        <v>809</v>
-      </c>
-      <c r="N83" t="s">
-        <v>810</v>
       </c>
       <c r="O83" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80516_tower hamlets", ".\export_data\inspection_reports\80516_tower hamlets")</f>
@@ -9896,28 +9893,28 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B84" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C84" t="s">
         <v>217</v>
       </c>
       <c r="D84" t="s">
+        <v>811</v>
+      </c>
+      <c r="E84" t="s">
+        <v>812</v>
+      </c>
+      <c r="F84" t="s">
         <v>813</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>814</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="G84" t="s">
-        <v>816</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>817</v>
       </c>
       <c r="I84" t="s">
         <v>8</v>
@@ -9926,16 +9923,16 @@
         <v>9</v>
       </c>
       <c r="K84" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="L84" t="s">
         <v>508</v>
       </c>
       <c r="M84" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="N84" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="O84" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80517_waltham forest", ".\export_data\inspection_reports\80517_waltham forest")</f>
@@ -9959,28 +9956,28 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B85" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C85" t="s">
         <v>217</v>
       </c>
       <c r="D85" t="s">
+        <v>819</v>
+      </c>
+      <c r="E85" t="s">
+        <v>820</v>
+      </c>
+      <c r="F85" t="s">
         <v>821</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>822</v>
       </c>
-      <c r="F85" t="s">
+      <c r="H85" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="G85" t="s">
-        <v>824</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="I85" t="s">
         <v>79</v>
@@ -9989,13 +9986,13 @@
         <v>9</v>
       </c>
       <c r="K85" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L85" t="s">
         <v>499</v>
       </c>
       <c r="M85" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="N85" t="s">
         <v>280</v>
@@ -10022,28 +10019,28 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C86" t="s">
         <v>217</v>
       </c>
       <c r="D86" t="s">
+        <v>827</v>
+      </c>
+      <c r="E86" t="s">
+        <v>828</v>
+      </c>
+      <c r="F86" t="s">
         <v>829</v>
       </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>830</v>
       </c>
-      <c r="F86" t="s">
+      <c r="H86" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="G86" t="s">
-        <v>832</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>833</v>
       </c>
       <c r="I86" t="s">
         <v>79</v>
@@ -10055,13 +10052,13 @@
         <v>106</v>
       </c>
       <c r="L86" t="s">
+        <v>806</v>
+      </c>
+      <c r="M86" t="s">
+        <v>807</v>
+      </c>
+      <c r="N86" t="s">
         <v>808</v>
-      </c>
-      <c r="M86" t="s">
-        <v>809</v>
-      </c>
-      <c r="N86" t="s">
-        <v>810</v>
       </c>
       <c r="O86" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80519_westminster", ".\export_data\inspection_reports\80519_westminster")</f>
@@ -10085,28 +10082,28 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B87" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C87" t="s">
         <v>31</v>
       </c>
       <c r="D87" t="s">
+        <v>834</v>
+      </c>
+      <c r="E87" t="s">
+        <v>835</v>
+      </c>
+      <c r="F87" t="s">
         <v>836</v>
       </c>
-      <c r="E87" t="s">
+      <c r="G87" t="s">
         <v>837</v>
       </c>
-      <c r="F87" t="s">
+      <c r="H87" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="G87" t="s">
-        <v>839</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="I87" t="s">
         <v>8</v>
@@ -10118,13 +10115,13 @@
         <v>150</v>
       </c>
       <c r="L87" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M87" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="N87" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O87" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80520_luton", ".\export_data\inspection_reports\80520_luton")</f>
@@ -10148,28 +10145,28 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B88" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C88" t="s">
         <v>56</v>
       </c>
       <c r="D88" t="s">
+        <v>843</v>
+      </c>
+      <c r="E88" t="s">
+        <v>844</v>
+      </c>
+      <c r="F88" t="s">
         <v>845</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>846</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="G88" t="s">
-        <v>848</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>849</v>
       </c>
       <c r="I88" t="s">
         <v>79</v>
@@ -10181,13 +10178,13 @@
         <v>277</v>
       </c>
       <c r="L88" t="s">
+        <v>848</v>
+      </c>
+      <c r="M88" t="s">
+        <v>849</v>
+      </c>
+      <c r="N88" t="s">
         <v>850</v>
-      </c>
-      <c r="M88" t="s">
-        <v>851</v>
-      </c>
-      <c r="N88" t="s">
-        <v>852</v>
       </c>
       <c r="O88" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80521_manchester", ".\export_data\inspection_reports\80521_manchester")</f>
@@ -10211,28 +10208,28 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B89" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C89" t="s">
         <v>74</v>
       </c>
       <c r="D89" t="s">
+        <v>853</v>
+      </c>
+      <c r="E89" t="s">
+        <v>854</v>
+      </c>
+      <c r="F89" t="s">
         <v>855</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>856</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="G89" t="s">
-        <v>858</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>859</v>
       </c>
       <c r="I89" t="s">
         <v>8</v>
@@ -10244,13 +10241,13 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
+        <v>858</v>
+      </c>
+      <c r="M89" t="s">
+        <v>859</v>
+      </c>
+      <c r="N89" t="s">
         <v>860</v>
-      </c>
-      <c r="M89" t="s">
-        <v>861</v>
-      </c>
-      <c r="N89" t="s">
-        <v>862</v>
       </c>
       <c r="O89" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80522_medway", ".\export_data\inspection_reports\80522_medway")</f>
@@ -10274,28 +10271,28 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B90" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C90" t="s">
         <v>293</v>
       </c>
       <c r="D90" t="s">
+        <v>863</v>
+      </c>
+      <c r="E90" t="s">
+        <v>864</v>
+      </c>
+      <c r="F90" t="s">
         <v>865</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>866</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" s="2" t="s">
         <v>867</v>
-      </c>
-      <c r="G90" t="s">
-        <v>868</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>869</v>
       </c>
       <c r="I90" t="s">
         <v>74</v>
@@ -10304,7 +10301,7 @@
         <v>48</v>
       </c>
       <c r="K90" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="L90" t="s">
         <v>76</v>
@@ -10337,28 +10334,28 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B91" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C91" t="s">
         <v>100</v>
       </c>
       <c r="D91" t="s">
+        <v>871</v>
+      </c>
+      <c r="E91" t="s">
+        <v>872</v>
+      </c>
+      <c r="F91" t="s">
         <v>873</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>874</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="G91" t="s">
-        <v>876</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>877</v>
       </c>
       <c r="I91" t="s">
         <v>8</v>
@@ -10367,16 +10364,16 @@
         <v>48</v>
       </c>
       <c r="K91" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L91" t="s">
+        <v>876</v>
+      </c>
+      <c r="M91" t="s">
+        <v>877</v>
+      </c>
+      <c r="N91" t="s">
         <v>878</v>
-      </c>
-      <c r="M91" t="s">
-        <v>879</v>
-      </c>
-      <c r="N91" t="s">
-        <v>880</v>
       </c>
       <c r="O91" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80524_milton keynes", ".\export_data\inspection_reports\80524_milton keynes")</f>
@@ -10400,28 +10397,28 @@
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B92" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C92" t="s">
         <v>293</v>
       </c>
       <c r="D92" t="s">
+        <v>881</v>
+      </c>
+      <c r="E92" t="s">
+        <v>882</v>
+      </c>
+      <c r="F92" t="s">
         <v>883</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>884</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" s="2" t="s">
         <v>885</v>
-      </c>
-      <c r="G92" t="s">
-        <v>886</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>887</v>
       </c>
       <c r="I92" t="s">
         <v>8</v>
@@ -10433,13 +10430,13 @@
         <v>245</v>
       </c>
       <c r="L92" t="s">
+        <v>886</v>
+      </c>
+      <c r="M92" t="s">
+        <v>887</v>
+      </c>
+      <c r="N92" t="s">
         <v>888</v>
-      </c>
-      <c r="M92" t="s">
-        <v>889</v>
-      </c>
-      <c r="N92" t="s">
-        <v>890</v>
       </c>
       <c r="O92" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80525_newcastle upon tyne", ".\export_data\inspection_reports\80525_newcastle upon tyne")</f>
@@ -10458,33 +10455,33 @@
         <v>14</v>
       </c>
       <c r="T92" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B93" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93" t="s">
+        <v>891</v>
+      </c>
+      <c r="E93" t="s">
+        <v>892</v>
+      </c>
+      <c r="F93" t="s">
         <v>893</v>
       </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>894</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="G93" t="s">
-        <v>896</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="I93" t="s">
         <v>79</v>
@@ -10493,13 +10490,13 @@
         <v>9</v>
       </c>
       <c r="K93" t="s">
+        <v>896</v>
+      </c>
+      <c r="L93" t="s">
+        <v>897</v>
+      </c>
+      <c r="M93" t="s">
         <v>898</v>
-      </c>
-      <c r="L93" t="s">
-        <v>899</v>
-      </c>
-      <c r="M93" t="s">
-        <v>900</v>
       </c>
       <c r="N93" t="s">
         <v>280</v>
@@ -10526,28 +10523,28 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B94" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
       </c>
       <c r="D94" t="s">
+        <v>901</v>
+      </c>
+      <c r="E94" t="s">
+        <v>902</v>
+      </c>
+      <c r="F94" t="s">
         <v>903</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>904</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="G94" t="s">
-        <v>906</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>907</v>
       </c>
       <c r="I94" t="s">
         <v>8</v>
@@ -10562,10 +10559,10 @@
         <v>37</v>
       </c>
       <c r="M94" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="N94" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="O94" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80526_north east lincolnshire", ".\export_data\inspection_reports\80526_north east lincolnshire")</f>
@@ -10589,28 +10586,28 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B95" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C95" t="s">
         <v>2</v>
       </c>
       <c r="D95" t="s">
+        <v>910</v>
+      </c>
+      <c r="E95" t="s">
+        <v>911</v>
+      </c>
+      <c r="F95" t="s">
         <v>912</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>913</v>
       </c>
-      <c r="F95" t="s">
+      <c r="H95" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="G95" t="s">
-        <v>915</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="I95" t="s">
         <v>79</v>
@@ -10622,13 +10619,13 @@
         <v>507</v>
       </c>
       <c r="L95" t="s">
+        <v>915</v>
+      </c>
+      <c r="M95" t="s">
+        <v>916</v>
+      </c>
+      <c r="N95" t="s">
         <v>917</v>
-      </c>
-      <c r="M95" t="s">
-        <v>918</v>
-      </c>
-      <c r="N95" t="s">
-        <v>919</v>
       </c>
       <c r="O95" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80527_north lincolnshire", ".\export_data\inspection_reports\80527_north lincolnshire")</f>
@@ -10652,28 +10649,28 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B96" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C96" t="s">
         <v>304</v>
       </c>
       <c r="D96" t="s">
+        <v>920</v>
+      </c>
+      <c r="E96" t="s">
+        <v>921</v>
+      </c>
+      <c r="F96" t="s">
         <v>922</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>923</v>
       </c>
-      <c r="F96" t="s">
+      <c r="H96" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="G96" t="s">
-        <v>925</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>926</v>
       </c>
       <c r="I96" t="s">
         <v>74</v>
@@ -10682,16 +10679,16 @@
         <v>48</v>
       </c>
       <c r="K96" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="L96" t="s">
+        <v>527</v>
+      </c>
+      <c r="M96" t="s">
+        <v>528</v>
+      </c>
+      <c r="N96" t="s">
         <v>573</v>
-      </c>
-      <c r="M96" t="s">
-        <v>574</v>
-      </c>
-      <c r="N96" t="s">
-        <v>575</v>
       </c>
       <c r="O96" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2637539_north northamptonshire", ".\export_data\inspection_reports\2637539_north northamptonshire")</f>
@@ -10715,28 +10712,28 @@
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B97" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="s">
+        <v>928</v>
+      </c>
+      <c r="E97" t="s">
+        <v>929</v>
+      </c>
+      <c r="F97" t="s">
         <v>930</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>931</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="G97" t="s">
-        <v>933</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>934</v>
       </c>
       <c r="I97" t="s">
         <v>14</v>
@@ -10748,13 +10745,13 @@
         <v>10</v>
       </c>
       <c r="L97" t="s">
+        <v>933</v>
+      </c>
+      <c r="M97" t="s">
+        <v>934</v>
+      </c>
+      <c r="N97" t="s">
         <v>935</v>
-      </c>
-      <c r="M97" t="s">
-        <v>936</v>
-      </c>
-      <c r="N97" t="s">
-        <v>937</v>
       </c>
       <c r="O97" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80528_north somerset", ".\export_data\inspection_reports\80528_north somerset")</f>
@@ -10778,28 +10775,28 @@
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B98" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C98" t="s">
         <v>293</v>
       </c>
       <c r="D98" t="s">
+        <v>938</v>
+      </c>
+      <c r="E98" t="s">
+        <v>939</v>
+      </c>
+      <c r="F98" t="s">
         <v>940</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>941</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="G98" t="s">
-        <v>943</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="I98" t="s">
         <v>79</v>
@@ -10811,13 +10808,13 @@
         <v>372</v>
       </c>
       <c r="L98" t="s">
+        <v>806</v>
+      </c>
+      <c r="M98" t="s">
+        <v>807</v>
+      </c>
+      <c r="N98" t="s">
         <v>808</v>
-      </c>
-      <c r="M98" t="s">
-        <v>809</v>
-      </c>
-      <c r="N98" t="s">
-        <v>810</v>
       </c>
       <c r="O98" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80529_north tyneside", ".\export_data\inspection_reports\80529_north tyneside")</f>
@@ -10841,28 +10838,28 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B99" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C99" t="s">
         <v>2</v>
       </c>
       <c r="D99" t="s">
+        <v>945</v>
+      </c>
+      <c r="E99" t="s">
+        <v>946</v>
+      </c>
+      <c r="F99" t="s">
         <v>947</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>948</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" s="2" t="s">
         <v>949</v>
-      </c>
-      <c r="G99" t="s">
-        <v>950</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>951</v>
       </c>
       <c r="I99" t="s">
         <v>79</v>
@@ -10871,16 +10868,16 @@
         <v>9</v>
       </c>
       <c r="K99" t="s">
+        <v>950</v>
+      </c>
+      <c r="L99" t="s">
+        <v>951</v>
+      </c>
+      <c r="M99" t="s">
         <v>952</v>
       </c>
-      <c r="L99" t="s">
+      <c r="N99" t="s">
         <v>953</v>
-      </c>
-      <c r="M99" t="s">
-        <v>954</v>
-      </c>
-      <c r="N99" t="s">
-        <v>955</v>
       </c>
       <c r="O99" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80530_north yorkshire", ".\export_data\inspection_reports\80530_north yorkshire")</f>
@@ -10904,28 +10901,28 @@
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B100" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C100" t="s">
         <v>293</v>
       </c>
       <c r="D100" t="s">
+        <v>956</v>
+      </c>
+      <c r="E100" t="s">
+        <v>957</v>
+      </c>
+      <c r="F100" t="s">
         <v>958</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>959</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="G100" t="s">
-        <v>961</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>962</v>
       </c>
       <c r="I100" t="s">
         <v>79</v>
@@ -10934,10 +10931,10 @@
         <v>9</v>
       </c>
       <c r="K100" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="L100" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="M100" t="s">
         <v>432</v>
@@ -10967,28 +10964,28 @@
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B101" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C101" t="s">
         <v>304</v>
       </c>
       <c r="D101" t="s">
+        <v>965</v>
+      </c>
+      <c r="E101" t="s">
+        <v>966</v>
+      </c>
+      <c r="F101" t="s">
         <v>967</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>968</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="G101" t="s">
-        <v>970</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="I101" t="s">
         <v>189</v>
@@ -10997,10 +10994,10 @@
         <v>117</v>
       </c>
       <c r="K101" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="N101" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="O101" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80533_nottingham", ".\export_data\inspection_reports\80533_nottingham")</f>
@@ -11024,28 +11021,28 @@
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B102" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C102" t="s">
         <v>304</v>
       </c>
       <c r="D102" t="s">
+        <v>973</v>
+      </c>
+      <c r="E102" t="s">
+        <v>974</v>
+      </c>
+      <c r="F102" t="s">
         <v>975</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>976</v>
       </c>
-      <c r="F102" t="s">
+      <c r="H102" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="G102" t="s">
-        <v>978</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>979</v>
       </c>
       <c r="I102" t="s">
         <v>8</v>
@@ -11054,10 +11051,10 @@
         <v>9</v>
       </c>
       <c r="K102" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L102" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="M102" t="s">
         <v>432</v>
@@ -11087,28 +11084,28 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B103" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C103" t="s">
         <v>56</v>
       </c>
       <c r="D103" t="s">
+        <v>980</v>
+      </c>
+      <c r="E103" t="s">
+        <v>981</v>
+      </c>
+      <c r="F103" t="s">
         <v>982</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>983</v>
       </c>
-      <c r="F103" t="s">
+      <c r="H103" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="G103" t="s">
-        <v>985</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="I103" t="s">
         <v>8</v>
@@ -11150,28 +11147,28 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B104" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C104" t="s">
         <v>100</v>
       </c>
       <c r="D104" t="s">
+        <v>987</v>
+      </c>
+      <c r="E104" t="s">
+        <v>988</v>
+      </c>
+      <c r="F104" t="s">
         <v>989</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>990</v>
       </c>
-      <c r="F104" t="s">
+      <c r="H104" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="G104" t="s">
-        <v>992</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>993</v>
       </c>
       <c r="I104" t="s">
         <v>8</v>
@@ -11180,16 +11177,16 @@
         <v>48</v>
       </c>
       <c r="K104" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L104" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M104" t="s">
         <v>161</v>
       </c>
       <c r="N104" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="O104" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80536_oxfordshire", ".\export_data\inspection_reports\80536_oxfordshire")</f>
@@ -11213,28 +11210,28 @@
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B105" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
       </c>
       <c r="D105" t="s">
+        <v>996</v>
+      </c>
+      <c r="E105" t="s">
+        <v>997</v>
+      </c>
+      <c r="F105" t="s">
         <v>998</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>999</v>
       </c>
-      <c r="F105" t="s">
+      <c r="H105" s="2" t="s">
         <v>1000</v>
-      </c>
-      <c r="G105" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>1002</v>
       </c>
       <c r="I105" t="s">
         <v>189</v>
@@ -11243,16 +11240,16 @@
         <v>48</v>
       </c>
       <c r="K105" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M105" t="s">
         <v>1003</v>
       </c>
-      <c r="L105" t="s">
+      <c r="N105" t="s">
         <v>1004</v>
-      </c>
-      <c r="M105" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N105" t="s">
-        <v>1006</v>
       </c>
       <c r="O105" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80537_peterborough", ".\export_data\inspection_reports\80537_peterborough")</f>
@@ -11276,28 +11273,28 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B106" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F106" t="s">
         <v>1009</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>1010</v>
       </c>
-      <c r="F106" t="s">
+      <c r="H106" s="2" t="s">
         <v>1011</v>
-      </c>
-      <c r="G106" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>1013</v>
       </c>
       <c r="I106" t="s">
         <v>14</v>
@@ -11309,13 +11306,13 @@
         <v>128</v>
       </c>
       <c r="L106" t="s">
+        <v>1012</v>
+      </c>
+      <c r="M106" t="s">
+        <v>1013</v>
+      </c>
+      <c r="N106" t="s">
         <v>1014</v>
-      </c>
-      <c r="M106" t="s">
-        <v>1015</v>
-      </c>
-      <c r="N106" t="s">
-        <v>1016</v>
       </c>
       <c r="O106" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80538_plymouth", ".\export_data\inspection_reports\80538_plymouth")</f>
@@ -11339,91 +11336,91 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B107" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C107" t="s">
         <v>100</v>
       </c>
       <c r="D107" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F107" t="s">
         <v>1019</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>1020</v>
       </c>
-      <c r="F107" t="s">
+      <c r="H107" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="G107" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>1023</v>
-      </c>
       <c r="I107" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="J107" t="s">
         <v>9</v>
       </c>
       <c r="K107" t="s">
-        <v>223</v>
+        <v>1022</v>
       </c>
       <c r="L107" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M107" t="s">
         <v>1024</v>
       </c>
-      <c r="M107" t="s">
+      <c r="N107" t="s">
         <v>1025</v>
-      </c>
-      <c r="N107" t="s">
-        <v>1026</v>
       </c>
       <c r="O107" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80539_portsmouth", ".\export_data\inspection_reports\80539_portsmouth")</f>
         <v>0</v>
       </c>
       <c r="P107" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="Q107" t="s">
         <v>79</v>
       </c>
       <c r="R107" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="S107" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="T107" t="s">
-        <v>227</v>
+        <v>434</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B108" t="s">
         <v>1027</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1028</v>
       </c>
       <c r="C108" t="s">
         <v>100</v>
       </c>
       <c r="D108" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E108" t="s">
         <v>1029</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>1030</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>1031</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>1033</v>
       </c>
       <c r="I108" t="s">
         <v>14</v>
@@ -11465,28 +11462,28 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B109" t="s">
         <v>1034</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1035</v>
       </c>
       <c r="C109" t="s">
         <v>293</v>
       </c>
       <c r="D109" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E109" t="s">
         <v>1036</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>1037</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>1038</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>1040</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -11498,7 +11495,7 @@
         <v>245</v>
       </c>
       <c r="L109" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="M109" t="s">
         <v>108</v>
@@ -11523,33 +11520,33 @@
         <v>8</v>
       </c>
       <c r="T109" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B110" t="s">
         <v>1042</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1043</v>
       </c>
       <c r="C110" t="s">
         <v>56</v>
       </c>
       <c r="D110" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E110" t="s">
         <v>1044</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>1045</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>1046</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" s="2" t="s">
         <v>1047</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>1048</v>
       </c>
       <c r="I110" t="s">
         <v>14</v>
@@ -11564,10 +11561,10 @@
         <v>471</v>
       </c>
       <c r="M110" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N110" t="s">
         <v>1049</v>
-      </c>
-      <c r="N110" t="s">
-        <v>1050</v>
       </c>
       <c r="O110" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80542_rochdale", ".\export_data\inspection_reports\80542_rochdale")</f>
@@ -11591,28 +11588,28 @@
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B111" t="s">
         <v>1051</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1052</v>
       </c>
       <c r="C111" t="s">
         <v>2</v>
       </c>
       <c r="D111" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E111" t="s">
         <v>1053</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>1054</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>1055</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>1057</v>
       </c>
       <c r="I111" t="s">
         <v>79</v>
@@ -11630,7 +11627,7 @@
         <v>490</v>
       </c>
       <c r="N111" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="O111" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80543_rotherham", ".\export_data\inspection_reports\80543_rotherham")</f>
@@ -11654,28 +11651,28 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B112" t="s">
         <v>1059</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1060</v>
       </c>
       <c r="C112" t="s">
         <v>217</v>
       </c>
       <c r="D112" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E112" t="s">
         <v>1061</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>1062</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>1063</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>1065</v>
       </c>
       <c r="I112" t="s">
         <v>79</v>
@@ -11687,13 +11684,13 @@
         <v>139</v>
       </c>
       <c r="L112" t="s">
+        <v>806</v>
+      </c>
+      <c r="M112" t="s">
+        <v>807</v>
+      </c>
+      <c r="N112" t="s">
         <v>808</v>
-      </c>
-      <c r="M112" t="s">
-        <v>809</v>
-      </c>
-      <c r="N112" t="s">
-        <v>810</v>
       </c>
       <c r="O112" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80544_kensington and chelsea", ".\export_data\inspection_reports\80544_kensington and chelsea")</f>
@@ -11717,28 +11714,28 @@
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B113" t="s">
         <v>1066</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1067</v>
       </c>
       <c r="C113" t="s">
         <v>217</v>
       </c>
       <c r="D113" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E113" t="s">
         <v>1068</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>1069</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>1070</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>1072</v>
       </c>
       <c r="I113" t="s">
         <v>79</v>
@@ -11747,7 +11744,7 @@
         <v>9</v>
       </c>
       <c r="K113" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L113" t="s">
         <v>95</v>
@@ -11780,28 +11777,28 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B114" t="s">
         <v>1073</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1074</v>
       </c>
       <c r="C114" t="s">
         <v>100</v>
       </c>
       <c r="D114" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E114" t="s">
         <v>1075</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>1076</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>1077</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="I114" t="s">
         <v>8</v>
@@ -11810,7 +11807,7 @@
         <v>9</v>
       </c>
       <c r="K114" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L114" t="s">
         <v>288</v>
@@ -11819,7 +11816,7 @@
         <v>331</v>
       </c>
       <c r="N114" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="O114" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80546_windsor &amp; maidenhead", ".\export_data\inspection_reports\80546_windsor &amp; maidenhead")</f>
@@ -11843,28 +11840,28 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B115" t="s">
         <v>1081</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1082</v>
       </c>
       <c r="C115" t="s">
         <v>304</v>
       </c>
       <c r="D115" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E115" t="s">
         <v>1083</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>1084</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>1085</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -11876,10 +11873,10 @@
         <v>507</v>
       </c>
       <c r="L115" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M115" t="s">
         <v>1088</v>
-      </c>
-      <c r="M115" t="s">
-        <v>1089</v>
       </c>
       <c r="N115" t="s">
         <v>433</v>
@@ -11906,28 +11903,28 @@
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B116" t="s">
         <v>1090</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1091</v>
       </c>
       <c r="C116" t="s">
         <v>56</v>
       </c>
       <c r="D116" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E116" t="s">
         <v>1092</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>1093</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>1094</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" s="2" t="s">
         <v>1095</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>1096</v>
       </c>
       <c r="I116" t="s">
         <v>8</v>
@@ -11936,10 +11933,10 @@
         <v>9</v>
       </c>
       <c r="K116" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L116" t="s">
         <v>1097</v>
-      </c>
-      <c r="L116" t="s">
-        <v>1098</v>
       </c>
       <c r="M116" t="s">
         <v>321</v>
@@ -11969,28 +11966,28 @@
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B117" t="s">
         <v>1099</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1100</v>
       </c>
       <c r="C117" t="s">
         <v>42</v>
       </c>
       <c r="D117" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E117" t="s">
         <v>1101</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>1102</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>1103</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>1105</v>
       </c>
       <c r="I117" t="s">
         <v>8</v>
@@ -11999,16 +11996,16 @@
         <v>48</v>
       </c>
       <c r="K117" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L117" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M117" t="s">
         <v>1106</v>
       </c>
-      <c r="M117" t="s">
+      <c r="N117" t="s">
         <v>1107</v>
-      </c>
-      <c r="N117" t="s">
-        <v>1108</v>
       </c>
       <c r="O117" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80549_sandwell", ".\export_data\inspection_reports\80549_sandwell")</f>
@@ -12032,28 +12029,28 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B118" t="s">
         <v>1109</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1110</v>
       </c>
       <c r="C118" t="s">
         <v>56</v>
       </c>
       <c r="D118" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E118" t="s">
         <v>1111</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>1112</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>1113</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" s="2" t="s">
         <v>1114</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>1115</v>
       </c>
       <c r="I118" t="s">
         <v>8</v>
@@ -12065,7 +12062,7 @@
         <v>87</v>
       </c>
       <c r="L118" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="M118" t="s">
         <v>538</v>
@@ -12095,28 +12092,28 @@
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B119" t="s">
         <v>1117</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1118</v>
       </c>
       <c r="C119" t="s">
         <v>2</v>
       </c>
       <c r="D119" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E119" t="s">
         <v>1119</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>1120</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>1121</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>1123</v>
       </c>
       <c r="I119" t="s">
         <v>8</v>
@@ -12131,10 +12128,10 @@
         <v>11</v>
       </c>
       <c r="M119" t="s">
+        <v>1123</v>
+      </c>
+      <c r="N119" t="s">
         <v>1124</v>
-      </c>
-      <c r="N119" t="s">
-        <v>1125</v>
       </c>
       <c r="O119" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80551_sheffield", ".\export_data\inspection_reports\80551_sheffield")</f>
@@ -12158,28 +12155,28 @@
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B120" t="s">
         <v>1126</v>
-      </c>
-      <c r="B120" t="s">
-        <v>1127</v>
       </c>
       <c r="C120" t="s">
         <v>42</v>
       </c>
       <c r="D120" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E120" t="s">
         <v>1128</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>1129</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>1130</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" s="2" t="s">
         <v>1131</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>1132</v>
       </c>
       <c r="I120" t="s">
         <v>79</v>
@@ -12188,10 +12185,10 @@
         <v>48</v>
       </c>
       <c r="K120" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L120" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="M120" t="s">
         <v>538</v>
@@ -12221,28 +12218,28 @@
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B121" t="s">
         <v>1133</v>
-      </c>
-      <c r="B121" t="s">
-        <v>1134</v>
       </c>
       <c r="C121" t="s">
         <v>100</v>
       </c>
       <c r="D121" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E121" t="s">
         <v>1135</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>1136</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>1137</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>1139</v>
       </c>
       <c r="I121" t="s">
         <v>14</v>
@@ -12257,10 +12254,10 @@
         <v>471</v>
       </c>
       <c r="M121" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N121" t="s">
         <v>1049</v>
-      </c>
-      <c r="N121" t="s">
-        <v>1050</v>
       </c>
       <c r="O121" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80553_slough", ".\export_data\inspection_reports\80553_slough")</f>
@@ -12284,28 +12281,28 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B122" t="s">
         <v>1140</v>
-      </c>
-      <c r="B122" t="s">
-        <v>1141</v>
       </c>
       <c r="C122" t="s">
         <v>42</v>
       </c>
       <c r="D122" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E122" t="s">
         <v>1142</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>1143</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>1144</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" s="2" t="s">
         <v>1145</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>1146</v>
       </c>
       <c r="I122" t="s">
         <v>8</v>
@@ -12314,13 +12311,13 @@
         <v>48</v>
       </c>
       <c r="K122" t="s">
-        <v>1147</v>
+        <v>1022</v>
       </c>
       <c r="L122" t="s">
         <v>489</v>
       </c>
       <c r="M122" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="N122" t="s">
         <v>463</v>
@@ -12342,33 +12339,33 @@
         <v>8</v>
       </c>
       <c r="T122" t="s">
-        <v>120</v>
+        <v>434</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B123" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F123" t="s">
         <v>1150</v>
       </c>
-      <c r="E123" t="s">
+      <c r="G123" t="s">
         <v>1151</v>
       </c>
-      <c r="F123" t="s">
+      <c r="H123" s="2" t="s">
         <v>1152</v>
-      </c>
-      <c r="G123" t="s">
-        <v>1153</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="I123" t="s">
         <v>74</v>
@@ -12380,13 +12377,13 @@
         <v>200</v>
       </c>
       <c r="L123" t="s">
+        <v>607</v>
+      </c>
+      <c r="M123" t="s">
+        <v>608</v>
+      </c>
+      <c r="N123" t="s">
         <v>609</v>
-      </c>
-      <c r="M123" t="s">
-        <v>610</v>
-      </c>
-      <c r="N123" t="s">
-        <v>611</v>
       </c>
       <c r="O123" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80555_somerset", ".\export_data\inspection_reports\80555_somerset")</f>
@@ -12410,28 +12407,28 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B124" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
       </c>
       <c r="D124" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F124" t="s">
         <v>1157</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>1158</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="G124" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>1161</v>
       </c>
       <c r="I124" t="s">
         <v>8</v>
@@ -12443,7 +12440,7 @@
         <v>10</v>
       </c>
       <c r="L124" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M124" t="s">
         <v>443</v>
@@ -12473,28 +12470,28 @@
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B125" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C125" t="s">
         <v>293</v>
       </c>
       <c r="D125" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F125" t="s">
         <v>1164</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>1165</v>
       </c>
-      <c r="F125" t="s">
+      <c r="H125" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="G125" t="s">
-        <v>1167</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>1168</v>
       </c>
       <c r="I125" t="s">
         <v>74</v>
@@ -12506,13 +12503,13 @@
         <v>62</v>
       </c>
       <c r="L125" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M125" t="s">
+        <v>1168</v>
+      </c>
+      <c r="N125" t="s">
         <v>1169</v>
-      </c>
-      <c r="M125" t="s">
-        <v>1170</v>
-      </c>
-      <c r="N125" t="s">
-        <v>1171</v>
       </c>
       <c r="O125" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80557_south tyneside", ".\export_data\inspection_reports\80557_south tyneside")</f>
@@ -12536,28 +12533,28 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B126" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C126" t="s">
         <v>100</v>
       </c>
       <c r="D126" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F126" t="s">
         <v>1174</v>
       </c>
-      <c r="E126" t="s">
+      <c r="G126" t="s">
         <v>1175</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H126" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="G126" t="s">
-        <v>1177</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>1178</v>
       </c>
       <c r="I126" t="s">
         <v>8</v>
@@ -12569,13 +12566,13 @@
         <v>391</v>
       </c>
       <c r="L126" t="s">
+        <v>1177</v>
+      </c>
+      <c r="M126" t="s">
+        <v>1178</v>
+      </c>
+      <c r="N126" t="s">
         <v>1179</v>
-      </c>
-      <c r="M126" t="s">
-        <v>1180</v>
-      </c>
-      <c r="N126" t="s">
-        <v>1181</v>
       </c>
       <c r="O126" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80558_southampton", ".\export_data\inspection_reports\80558_southampton")</f>
@@ -12599,28 +12596,28 @@
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B127" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C127" t="s">
         <v>31</v>
       </c>
       <c r="D127" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F127" t="s">
         <v>1184</v>
       </c>
-      <c r="E127" t="s">
+      <c r="G127" t="s">
         <v>1185</v>
       </c>
-      <c r="F127" t="s">
+      <c r="H127" s="2" t="s">
         <v>1186</v>
-      </c>
-      <c r="G127" t="s">
-        <v>1187</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>1188</v>
       </c>
       <c r="I127" t="s">
         <v>8</v>
@@ -12632,13 +12629,13 @@
         <v>75</v>
       </c>
       <c r="L127" t="s">
+        <v>634</v>
+      </c>
+      <c r="M127" t="s">
+        <v>635</v>
+      </c>
+      <c r="N127" t="s">
         <v>636</v>
-      </c>
-      <c r="M127" t="s">
-        <v>637</v>
-      </c>
-      <c r="N127" t="s">
-        <v>638</v>
       </c>
       <c r="O127" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80559_southend-on-sea", ".\export_data\inspection_reports\80559_southend-on-sea")</f>
@@ -12662,28 +12659,28 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B128" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C128" t="s">
         <v>56</v>
       </c>
       <c r="D128" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F128" t="s">
         <v>1191</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>1192</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="G128" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>1195</v>
       </c>
       <c r="I128" t="s">
         <v>8</v>
@@ -12692,16 +12689,16 @@
         <v>48</v>
       </c>
       <c r="K128" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="L128" t="s">
+        <v>581</v>
+      </c>
+      <c r="M128" t="s">
+        <v>582</v>
+      </c>
+      <c r="N128" t="s">
         <v>583</v>
-      </c>
-      <c r="M128" t="s">
-        <v>584</v>
-      </c>
-      <c r="N128" t="s">
-        <v>585</v>
       </c>
       <c r="O128" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80560_st helens", ".\export_data\inspection_reports\80560_st helens")</f>
@@ -12725,28 +12722,28 @@
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B129" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C129" t="s">
         <v>42</v>
       </c>
       <c r="D129" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F129" t="s">
         <v>1198</v>
       </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>1199</v>
       </c>
-      <c r="F129" t="s">
+      <c r="H129" s="2" t="s">
         <v>1200</v>
-      </c>
-      <c r="G129" t="s">
-        <v>1201</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>1202</v>
       </c>
       <c r="I129" t="s">
         <v>14</v>
@@ -12758,7 +12755,7 @@
         <v>200</v>
       </c>
       <c r="L129" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="M129" t="s">
         <v>321</v>
@@ -12788,28 +12785,28 @@
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B130" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C130" t="s">
         <v>56</v>
       </c>
       <c r="D130" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F130" t="s">
         <v>1205</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>1206</v>
       </c>
-      <c r="F130" t="s">
+      <c r="H130" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="G130" t="s">
-        <v>1208</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>1209</v>
       </c>
       <c r="I130" t="s">
         <v>14</v>
@@ -12821,13 +12818,13 @@
         <v>430</v>
       </c>
       <c r="L130" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="M130" t="s">
         <v>311</v>
       </c>
       <c r="N130" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="O130" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80562_stockport", ".\export_data\inspection_reports\80562_stockport")</f>
@@ -12851,28 +12848,28 @@
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B131" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C131" t="s">
         <v>293</v>
       </c>
       <c r="D131" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F131" t="s">
         <v>1213</v>
       </c>
-      <c r="E131" t="s">
+      <c r="G131" t="s">
         <v>1214</v>
       </c>
-      <c r="F131" t="s">
+      <c r="H131" s="2" t="s">
         <v>1215</v>
-      </c>
-      <c r="G131" t="s">
-        <v>1216</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>1217</v>
       </c>
       <c r="I131" t="s">
         <v>14</v>
@@ -12881,16 +12878,16 @@
         <v>48</v>
       </c>
       <c r="K131" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M131" t="s">
         <v>1218</v>
       </c>
-      <c r="L131" t="s">
+      <c r="N131" t="s">
         <v>1219</v>
-      </c>
-      <c r="M131" t="s">
-        <v>1220</v>
-      </c>
-      <c r="N131" t="s">
-        <v>1221</v>
       </c>
       <c r="O131" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80563_stockton-on-tees", ".\export_data\inspection_reports\80563_stockton-on-tees")</f>
@@ -12914,28 +12911,28 @@
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B132" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C132" t="s">
         <v>42</v>
       </c>
       <c r="D132" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F132" t="s">
         <v>1224</v>
       </c>
-      <c r="E132" t="s">
+      <c r="G132" t="s">
         <v>1225</v>
       </c>
-      <c r="F132" t="s">
+      <c r="H132" s="2" t="s">
         <v>1226</v>
-      </c>
-      <c r="G132" t="s">
-        <v>1227</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>1228</v>
       </c>
       <c r="I132" t="s">
         <v>14</v>
@@ -12947,13 +12944,13 @@
         <v>49</v>
       </c>
       <c r="L132" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="M132" t="s">
         <v>311</v>
       </c>
       <c r="N132" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="O132" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80564_stoke-on-trent", ".\export_data\inspection_reports\80564_stoke-on-trent")</f>
@@ -12977,28 +12974,28 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B133" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C133" t="s">
         <v>31</v>
       </c>
       <c r="D133" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F133" t="s">
         <v>1231</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
         <v>1232</v>
       </c>
-      <c r="F133" t="s">
+      <c r="H133" s="2" t="s">
         <v>1233</v>
-      </c>
-      <c r="G133" t="s">
-        <v>1234</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>1235</v>
       </c>
       <c r="I133" t="s">
         <v>14</v>
@@ -13010,13 +13007,13 @@
         <v>179</v>
       </c>
       <c r="L133" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M133" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="N133" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="O133" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80565_suffolk", ".\export_data\inspection_reports\80565_suffolk")</f>
@@ -13040,28 +13037,28 @@
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B134" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C134" t="s">
         <v>293</v>
       </c>
       <c r="D134" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F134" t="s">
         <v>1239</v>
       </c>
-      <c r="E134" t="s">
+      <c r="G134" t="s">
         <v>1240</v>
       </c>
-      <c r="F134" t="s">
+      <c r="H134" s="2" t="s">
         <v>1241</v>
-      </c>
-      <c r="G134" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>1243</v>
       </c>
       <c r="I134" t="s">
         <v>79</v>
@@ -13079,7 +13076,7 @@
         <v>342</v>
       </c>
       <c r="N134" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="O134" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80566_sunderland", ".\export_data\inspection_reports\80566_sunderland")</f>
@@ -13103,28 +13100,28 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B135" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C135" t="s">
         <v>100</v>
       </c>
       <c r="D135" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E135" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F135" t="s">
         <v>1247</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>1248</v>
       </c>
-      <c r="F135" t="s">
+      <c r="H135" s="2" t="s">
         <v>1249</v>
-      </c>
-      <c r="G135" t="s">
-        <v>1250</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>1251</v>
       </c>
       <c r="I135" t="s">
         <v>8</v>
@@ -13166,28 +13163,28 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B136" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
       </c>
       <c r="D136" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F136" t="s">
         <v>1254</v>
       </c>
-      <c r="E136" t="s">
+      <c r="G136" t="s">
         <v>1255</v>
       </c>
-      <c r="F136" t="s">
+      <c r="H136" s="2" t="s">
         <v>1256</v>
-      </c>
-      <c r="G136" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>1258</v>
       </c>
       <c r="I136" t="s">
         <v>189</v>
@@ -13199,13 +13196,13 @@
         <v>139</v>
       </c>
       <c r="L136" t="s">
+        <v>858</v>
+      </c>
+      <c r="M136" t="s">
+        <v>859</v>
+      </c>
+      <c r="N136" t="s">
         <v>860</v>
-      </c>
-      <c r="M136" t="s">
-        <v>861</v>
-      </c>
-      <c r="N136" t="s">
-        <v>862</v>
       </c>
       <c r="O136" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80568_swindon", ".\export_data\inspection_reports\80568_swindon")</f>
@@ -13229,28 +13226,28 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B137" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C137" t="s">
         <v>56</v>
       </c>
       <c r="D137" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E137" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F137" t="s">
         <v>1261</v>
       </c>
-      <c r="E137" t="s">
+      <c r="G137" t="s">
         <v>1262</v>
       </c>
-      <c r="F137" t="s">
+      <c r="H137" s="2" t="s">
         <v>1263</v>
-      </c>
-      <c r="G137" t="s">
-        <v>1264</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>1265</v>
       </c>
       <c r="I137" t="s">
         <v>189</v>
@@ -13262,13 +13259,13 @@
         <v>117</v>
       </c>
       <c r="L137" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="M137" t="s">
         <v>393</v>
       </c>
       <c r="N137" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="O137" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80569_tameside", ".\export_data\inspection_reports\80569_tameside")</f>
@@ -13292,28 +13289,28 @@
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B138" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C138" t="s">
         <v>42</v>
       </c>
       <c r="D138" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F138" t="s">
         <v>1269</v>
       </c>
-      <c r="E138" t="s">
+      <c r="G138" t="s">
         <v>1270</v>
       </c>
-      <c r="F138" t="s">
+      <c r="H138" s="2" t="s">
         <v>1271</v>
-      </c>
-      <c r="G138" t="s">
-        <v>1272</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>1273</v>
       </c>
       <c r="I138" t="s">
         <v>79</v>
@@ -13325,7 +13322,7 @@
         <v>179</v>
       </c>
       <c r="L138" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="M138" t="s">
         <v>555</v>
@@ -13355,28 +13352,28 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B139" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
       </c>
       <c r="D139" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F139" t="s">
         <v>1277</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>1278</v>
       </c>
-      <c r="F139" t="s">
+      <c r="H139" s="2" t="s">
         <v>1279</v>
-      </c>
-      <c r="G139" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>1281</v>
       </c>
       <c r="I139" t="s">
         <v>79</v>
@@ -13388,13 +13385,13 @@
         <v>507</v>
       </c>
       <c r="L139" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M139" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N139" t="s">
         <v>1282</v>
-      </c>
-      <c r="M139" t="s">
-        <v>1283</v>
-      </c>
-      <c r="N139" t="s">
-        <v>1284</v>
       </c>
       <c r="O139" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80571_thurrock", ".\export_data\inspection_reports\80571_thurrock")</f>
@@ -13418,28 +13415,28 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B140" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F140" t="s">
         <v>1287</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>1288</v>
       </c>
-      <c r="F140" t="s">
+      <c r="H140" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="G140" t="s">
-        <v>1290</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>1291</v>
       </c>
       <c r="I140" t="s">
         <v>8</v>
@@ -13454,10 +13451,10 @@
         <v>212</v>
       </c>
       <c r="M140" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="N140" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="O140" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80572_torbay", ".\export_data\inspection_reports\80572_torbay")</f>
@@ -13481,28 +13478,28 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B141" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C141" t="s">
         <v>56</v>
       </c>
       <c r="D141" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F141" t="s">
         <v>1294</v>
       </c>
-      <c r="E141" t="s">
+      <c r="G141" t="s">
         <v>1295</v>
       </c>
-      <c r="F141" t="s">
+      <c r="H141" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="G141" t="s">
-        <v>1297</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>1298</v>
       </c>
       <c r="I141" t="s">
         <v>74</v>
@@ -13511,7 +13508,7 @@
         <v>48</v>
       </c>
       <c r="K141" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="L141" t="s">
         <v>76</v>
@@ -13520,7 +13517,7 @@
         <v>77</v>
       </c>
       <c r="N141" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="O141" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80573_trafford", ".\export_data\inspection_reports\80573_trafford")</f>
@@ -13544,28 +13541,28 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B142" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C142" t="s">
         <v>42</v>
       </c>
       <c r="D142" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E142" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F142" t="s">
         <v>1303</v>
       </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>1304</v>
       </c>
-      <c r="F142" t="s">
+      <c r="H142" s="2" t="s">
         <v>1305</v>
-      </c>
-      <c r="G142" t="s">
-        <v>1306</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>1307</v>
       </c>
       <c r="I142" t="s">
         <v>79</v>
@@ -13577,10 +13574,10 @@
         <v>139</v>
       </c>
       <c r="L142" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="M142" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="N142" t="s">
         <v>312</v>
@@ -13607,28 +13604,28 @@
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B143" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C143" t="s">
         <v>56</v>
       </c>
       <c r="D143" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E143" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F143" t="s">
         <v>1310</v>
       </c>
-      <c r="E143" t="s">
+      <c r="G143" t="s">
         <v>1311</v>
       </c>
-      <c r="F143" t="s">
+      <c r="H143" s="2" t="s">
         <v>1312</v>
-      </c>
-      <c r="G143" t="s">
-        <v>1313</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>1314</v>
       </c>
       <c r="I143" t="s">
         <v>8</v>
@@ -13646,7 +13643,7 @@
         <v>443</v>
       </c>
       <c r="N143" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="O143" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80575_warrington", ".\export_data\inspection_reports\80575_warrington")</f>
@@ -13670,28 +13667,28 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B144" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C144" t="s">
         <v>42</v>
       </c>
       <c r="D144" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E144" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F144" t="s">
         <v>1318</v>
       </c>
-      <c r="E144" t="s">
+      <c r="G144" t="s">
         <v>1319</v>
       </c>
-      <c r="F144" t="s">
+      <c r="H144" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="G144" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>1322</v>
       </c>
       <c r="I144" t="s">
         <v>14</v>
@@ -13703,13 +13700,13 @@
         <v>117</v>
       </c>
       <c r="L144" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1322</v>
+      </c>
+      <c r="N144" t="s">
         <v>1323</v>
-      </c>
-      <c r="M144" t="s">
-        <v>1324</v>
-      </c>
-      <c r="N144" t="s">
-        <v>1325</v>
       </c>
       <c r="O144" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80576_warwickshire", ".\export_data\inspection_reports\80576_warwickshire")</f>
@@ -13733,28 +13730,28 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B145" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C145" t="s">
         <v>100</v>
       </c>
       <c r="D145" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F145" t="s">
         <v>1328</v>
       </c>
-      <c r="E145" t="s">
+      <c r="G145" t="s">
         <v>1329</v>
       </c>
-      <c r="F145" t="s">
+      <c r="H145" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>1332</v>
       </c>
       <c r="I145" t="s">
         <v>8</v>
@@ -13763,16 +13760,16 @@
         <v>9</v>
       </c>
       <c r="K145" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="L145" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1332</v>
+      </c>
+      <c r="N145" t="s">
         <v>1333</v>
-      </c>
-      <c r="M145" t="s">
-        <v>1334</v>
-      </c>
-      <c r="N145" t="s">
-        <v>1335</v>
       </c>
       <c r="O145" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80577_west berkshire", ".\export_data\inspection_reports\80577_west berkshire")</f>
@@ -13796,28 +13793,28 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B146" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C146" t="s">
         <v>304</v>
       </c>
       <c r="D146" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F146" t="s">
         <v>1338</v>
       </c>
-      <c r="E146" t="s">
+      <c r="G146" t="s">
         <v>1339</v>
       </c>
-      <c r="F146" t="s">
+      <c r="H146" s="2" t="s">
         <v>1340</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1341</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>1342</v>
       </c>
       <c r="I146" t="s">
         <v>74</v>
@@ -13829,13 +13826,13 @@
         <v>150</v>
       </c>
       <c r="L146" t="s">
+        <v>527</v>
+      </c>
+      <c r="M146" t="s">
+        <v>528</v>
+      </c>
+      <c r="N146" t="s">
         <v>573</v>
-      </c>
-      <c r="M146" t="s">
-        <v>574</v>
-      </c>
-      <c r="N146" t="s">
-        <v>575</v>
       </c>
       <c r="O146" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2637548_west northamptonshire", ".\export_data\inspection_reports\2637548_west northamptonshire")</f>
@@ -13859,28 +13856,28 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B147" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C147" t="s">
         <v>100</v>
       </c>
       <c r="D147" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F147" t="s">
         <v>1345</v>
       </c>
-      <c r="E147" t="s">
+      <c r="G147" t="s">
         <v>1346</v>
       </c>
-      <c r="F147" t="s">
+      <c r="H147" s="2" t="s">
         <v>1347</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>1349</v>
       </c>
       <c r="I147" t="s">
         <v>14</v>
@@ -13889,16 +13886,16 @@
         <v>48</v>
       </c>
       <c r="K147" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="L147" t="s">
+        <v>933</v>
+      </c>
+      <c r="M147" t="s">
+        <v>934</v>
+      </c>
+      <c r="N147" t="s">
         <v>935</v>
-      </c>
-      <c r="M147" t="s">
-        <v>936</v>
-      </c>
-      <c r="N147" t="s">
-        <v>937</v>
       </c>
       <c r="O147" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80578_west sussex", ".\export_data\inspection_reports\80578_west sussex")</f>
@@ -13922,10 +13919,10 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B148" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C148" t="s">
         <v>56</v>
@@ -13934,16 +13931,16 @@
         <v>283</v>
       </c>
       <c r="E148" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G148" t="s">
         <v>1353</v>
       </c>
-      <c r="F148" t="s">
+      <c r="H148" s="2" t="s">
         <v>1354</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1355</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>1356</v>
       </c>
       <c r="I148" t="s">
         <v>8</v>
@@ -13952,7 +13949,7 @@
         <v>48</v>
       </c>
       <c r="K148" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="L148" t="s">
         <v>554</v>
@@ -13985,28 +13982,28 @@
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B149" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C149" t="s">
         <v>56</v>
       </c>
       <c r="D149" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F149" t="s">
         <v>1359</v>
       </c>
-      <c r="E149" t="s">
+      <c r="G149" t="s">
         <v>1360</v>
       </c>
-      <c r="F149" t="s">
+      <c r="H149" s="2" t="s">
         <v>1361</v>
-      </c>
-      <c r="G149" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>1363</v>
       </c>
       <c r="I149" t="s">
         <v>8</v>
@@ -14015,16 +14012,16 @@
         <v>48</v>
       </c>
       <c r="K149" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L149" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1363</v>
+      </c>
+      <c r="N149" t="s">
         <v>1364</v>
-      </c>
-      <c r="M149" t="s">
-        <v>1365</v>
-      </c>
-      <c r="N149" t="s">
-        <v>1366</v>
       </c>
       <c r="O149" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80579_wigan", ".\export_data\inspection_reports\80579_wigan")</f>
@@ -14048,28 +14045,28 @@
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B150" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
       <c r="D150" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F150" t="s">
         <v>1369</v>
       </c>
-      <c r="E150" t="s">
+      <c r="G150" t="s">
         <v>1370</v>
       </c>
-      <c r="F150" t="s">
+      <c r="H150" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1372</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>1373</v>
       </c>
       <c r="I150" t="s">
         <v>79</v>
@@ -14081,13 +14078,13 @@
         <v>403</v>
       </c>
       <c r="L150" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1373</v>
+      </c>
+      <c r="N150" t="s">
         <v>1374</v>
-      </c>
-      <c r="M150" t="s">
-        <v>1375</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1376</v>
       </c>
       <c r="O150" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80580_wiltshire", ".\export_data\inspection_reports\80580_wiltshire")</f>
@@ -14111,28 +14108,28 @@
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B151" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C151" t="s">
         <v>56</v>
       </c>
       <c r="D151" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F151" t="s">
         <v>1379</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>1380</v>
       </c>
-      <c r="F151" t="s">
+      <c r="H151" s="2" t="s">
         <v>1381</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1382</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>1383</v>
       </c>
       <c r="I151" t="s">
         <v>14</v>
@@ -14144,13 +14141,13 @@
         <v>190</v>
       </c>
       <c r="L151" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="M151" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="N151" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="O151" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80581_wirral", ".\export_data\inspection_reports\80581_wirral")</f>
@@ -14174,28 +14171,28 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B152" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C152" t="s">
         <v>100</v>
       </c>
       <c r="D152" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F152" t="s">
         <v>1388</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
         <v>1389</v>
       </c>
-      <c r="F152" t="s">
+      <c r="H152" s="2" t="s">
         <v>1390</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1391</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>1392</v>
       </c>
       <c r="I152" t="s">
         <v>14</v>
@@ -14207,13 +14204,13 @@
         <v>391</v>
       </c>
       <c r="L152" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M152" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N152" t="s">
         <v>1219</v>
-      </c>
-      <c r="M152" t="s">
-        <v>1220</v>
-      </c>
-      <c r="N152" t="s">
-        <v>1221</v>
       </c>
       <c r="O152" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80582_wokingham", ".\export_data\inspection_reports\80582_wokingham")</f>
@@ -14237,28 +14234,28 @@
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B153" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C153" t="s">
         <v>42</v>
       </c>
       <c r="D153" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F153" t="s">
         <v>1395</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>1396</v>
       </c>
-      <c r="F153" t="s">
+      <c r="H153" s="2" t="s">
         <v>1397</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1398</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1399</v>
       </c>
       <c r="I153" t="s">
         <v>8</v>
@@ -14270,13 +14267,13 @@
         <v>200</v>
       </c>
       <c r="L153" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="M153" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="N153" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="O153" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80583_wolverhampton", ".\export_data\inspection_reports\80583_wolverhampton")</f>
@@ -14300,28 +14297,28 @@
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B154" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C154" t="s">
         <v>42</v>
       </c>
       <c r="D154" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F154" t="s">
         <v>1404</v>
       </c>
-      <c r="E154" t="s">
+      <c r="G154" t="s">
         <v>1405</v>
       </c>
-      <c r="F154" t="s">
+      <c r="H154" s="2" t="s">
         <v>1406</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1408</v>
       </c>
       <c r="I154" t="s">
         <v>8</v>
@@ -14333,13 +14330,13 @@
         <v>179</v>
       </c>
       <c r="L154" t="s">
-        <v>1024</v>
+        <v>1407</v>
       </c>
       <c r="M154" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N154" t="s">
         <v>1409</v>
-      </c>
-      <c r="N154" t="s">
-        <v>1410</v>
       </c>
       <c r="O154" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80584_worcestershire", ".\export_data\inspection_reports\80584_worcestershire")</f>

--- a/ofsted_csc_ilacs_overview.xlsx
+++ b/ofsted_csc_ilacs_overview.xlsx
@@ -31,7 +31,7 @@
     <t>372, 384, 357, 371, 332, 894, 840, 390, 807, 394</t>
   </si>
   <si>
-    <t>[(372, 'outstanding'), (384, 'good'), (357, 'inadequate'), (371, 'good'), (332, 'requires improvement'), (894, 'outstanding'), (840, 'outstanding'), (390, 'good'), (807, 'good'), (394, 'outstanding')]</t>
+    <t>[(372, 'outstanding'), (384, 'good'), (357, 'inadequate'), (371, 'good'), (332, nan), (894, 'outstanding'), (840, 'outstanding'), (390, 'good'), (807, 'good'), (394, 'outstanding')]</t>
   </si>
   <si>
     <t>barnsley</t>
@@ -79,7 +79,7 @@
     <t>816, 358, 919, 356, 938, 314, 825, 931, 873, 916</t>
   </si>
   <si>
-    <t>[(816, 'outstanding'), (358, nan), (919, 'outstanding'), (356, 'requires improvement'), (938, 'requires improvement'), (314, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (873, 'requires improvement'), (916, 'good')]</t>
+    <t>[(816, 'outstanding'), (358, nan), (919, nan), (356, 'requires improvement'), (938, 'requires improvement'), (314, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (873, 'requires improvement'), (916, 'good')]</t>
   </si>
   <si>
     <t>bath and north east somerset</t>
@@ -100,186 +100,186 @@
     <t>05/08/25</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>80428</t>
+  </si>
+  <si>
+    <t>822</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>E06000055</t>
+  </si>
+  <si>
+    <t>303, 826, 941, 311, 937, 839, 886, 935, 881, 866</t>
+  </si>
+  <si>
+    <t>[(303, 'outstanding'), (826, 'good'), (941, nan), (311, 'inadequate'), (937, 'requires improvement'), (839, 'good'), (886, 'good'), (935, 'requires improvement'), (881, 'outstanding'), (866, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>bedford</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50285308</t>
+  </si>
+  <si>
+    <t>14/07/2025</t>
+  </si>
+  <si>
+    <t>18/07/2025</t>
+  </si>
+  <si>
+    <t>27/08/25</t>
+  </si>
+  <si>
+    <t>80429</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t>E08000025</t>
+  </si>
+  <si>
+    <t>892, 352, 380, 391, 353, 889, 373, 806, 852, 355</t>
+  </si>
+  <si>
+    <t>[(892, 'inadequate'), (352, 'outstanding'), (380, 'requires improvement'), (391, 'good'), (353, 'good'), (889, 'good'), (373, 'good'), (806, nan), (852, 'good'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>birmingham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50214110</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>john roughton</t>
+  </si>
+  <si>
+    <t>20/02/2023</t>
+  </si>
+  <si>
+    <t>03/03/2023</t>
+  </si>
+  <si>
+    <t>18/04/23</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>80430</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>NW</t>
+  </si>
+  <si>
+    <t>E06000008</t>
+  </si>
+  <si>
+    <t>380, 353, 350, 831, 354, 335, 373, 861, 330, 382</t>
+  </si>
+  <si>
+    <t>[(380, 'requires improvement'), (353, 'good'), (350, 'good'), (831, 'outstanding'), (354, 'requires improvement'), (335, 'outstanding'), (373, 'good'), (861, 'requires improvement'), (330, 'good'), (382, 'good')]</t>
+  </si>
+  <si>
+    <t>blackburn with darwen</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50275023</t>
+  </si>
+  <si>
+    <t>gareth dakin</t>
+  </si>
+  <si>
+    <t>03/03/2025</t>
+  </si>
+  <si>
+    <t>14/03/2025</t>
+  </si>
+  <si>
+    <t>23/04/25</t>
+  </si>
+  <si>
+    <t>80431</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>E06000009</t>
+  </si>
+  <si>
+    <t>805, 806, 394, 341, 393, 807, 354, 880, 355, 861</t>
+  </si>
+  <si>
+    <t>[(805, 'outstanding'), (806, nan), (394, 'outstanding'), (341, nan), (393, nan), (807, 'good'), (354, 'requires improvement'), (880, 'good'), (355, 'good'), (861, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>blackpool</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50308110</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>margaret burke</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>28/07/26</t>
+  </si>
+  <si>
+    <t>outstanding</t>
+  </si>
+  <si>
+    <t>80432</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>E08000001</t>
+  </si>
+  <si>
+    <t>354, 831, 353, 357, 335, 355, 889, 331, 373, 874</t>
+  </si>
+  <si>
+    <t>[(354, 'requires improvement'), (831, 'outstanding'), (353, 'good'), (357, 'inadequate'), (335, 'outstanding'), (355, 'good'), (889, 'good'), (331, 'outstanding'), (373, 'good'), (874, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>bolton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50231519</t>
+  </si>
+  <si>
+    <t>lisa walsh</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>80428</t>
-  </si>
-  <si>
-    <t>822</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>E06000055</t>
-  </si>
-  <si>
-    <t>303, 826, 941, 311, 937, 839, 886, 935, 881, 866</t>
-  </si>
-  <si>
-    <t>[(303, 'outstanding'), (826, 'good'), (941, nan), (311, 'inadequate'), (937, 'requires improvement'), (839, 'good'), (886, 'good'), (935, 'requires improvement'), (881, 'outstanding'), (866, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>bedford</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50285308</t>
-  </si>
-  <si>
-    <t>14/07/2025</t>
-  </si>
-  <si>
-    <t>18/07/2025</t>
-  </si>
-  <si>
-    <t>27/08/25</t>
-  </si>
-  <si>
-    <t>80429</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>WM</t>
-  </si>
-  <si>
-    <t>E08000025</t>
-  </si>
-  <si>
-    <t>892, 352, 380, 391, 353, 889, 373, 806, 852, 355</t>
-  </si>
-  <si>
-    <t>[(892, 'inadequate'), (352, 'outstanding'), (380, 'requires improvement'), (391, 'good'), (353, 'good'), (889, 'good'), (373, 'good'), (806, nan), (852, 'good'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>birmingham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50214110</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>john roughton</t>
-  </si>
-  <si>
-    <t>20/02/2023</t>
-  </si>
-  <si>
-    <t>03/03/2023</t>
-  </si>
-  <si>
-    <t>18/04/23</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>80430</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
-    <t>NW</t>
-  </si>
-  <si>
-    <t>E06000008</t>
-  </si>
-  <si>
-    <t>380, 353, 350, 831, 354, 335, 373, 861, 330, 382</t>
-  </si>
-  <si>
-    <t>[(380, 'requires improvement'), (353, 'good'), (350, 'good'), (831, 'outstanding'), (354, 'requires improvement'), (335, 'outstanding'), (373, 'good'), (861, 'requires improvement'), (330, 'good'), (382, 'good')]</t>
-  </si>
-  <si>
-    <t>blackburn with darwen</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50275023</t>
-  </si>
-  <si>
-    <t>gareth dakin</t>
-  </si>
-  <si>
-    <t>03/03/2025</t>
-  </si>
-  <si>
-    <t>14/03/2025</t>
-  </si>
-  <si>
-    <t>23/04/25</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>80431</t>
-  </si>
-  <si>
-    <t>890</t>
-  </si>
-  <si>
-    <t>E06000009</t>
-  </si>
-  <si>
-    <t>805, 806, 394, 341, 393, 807, 354, 880, 355, 861</t>
-  </si>
-  <si>
-    <t>[(805, 'outstanding'), (806, nan), (394, 'outstanding'), (341, nan), (393, nan), (807, 'good'), (354, 'requires improvement'), (880, 'good'), (355, 'good'), (861, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>blackpool</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50308110</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>margaret burke</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>19/06/2026</t>
-  </si>
-  <si>
-    <t>28/07/26</t>
-  </si>
-  <si>
-    <t>outstanding</t>
-  </si>
-  <si>
-    <t>80432</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>E08000001</t>
-  </si>
-  <si>
-    <t>354, 831, 353, 357, 335, 355, 889, 331, 373, 874</t>
-  </si>
-  <si>
-    <t>[(354, 'requires improvement'), (831, 'outstanding'), (353, 'good'), (357, 'inadequate'), (335, 'outstanding'), (355, 'good'), (889, 'good'), (331, 'outstanding'), (373, 'good'), (874, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>bolton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50231519</t>
-  </si>
-  <si>
-    <t>lisa walsh</t>
-  </si>
-  <si>
     <t>2532287</t>
   </si>
   <si>
@@ -325,7 +325,7 @@
     <t>919, 850, 825, 931, 869, 938, 803, 823, 916, 865</t>
   </si>
   <si>
-    <t>[(919, 'outstanding'), (850, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (869, 'good'), (938, 'requires improvement'), (803, 'good'), (823, 'good'), (916, 'good'), (865, 'outstanding')]</t>
+    <t>[(919, nan), (850, 'outstanding'), (825, 'requires improvement'), (931, 'good'), (869, 'good'), (938, 'requires improvement'), (803, 'good'), (823, 'good'), (916, 'good'), (865, 'outstanding')]</t>
   </si>
   <si>
     <t>bracknell forest</t>
@@ -424,7 +424,7 @@
     <t>931, 919, 869, 936, 873, 867, 823, 868, 358, 850</t>
   </si>
   <si>
-    <t>[(931, 'good'), (919, 'outstanding'), (869, 'good'), (936, 'good'), (873, 'requires improvement'), (867, 'outstanding'), (823, 'good'), (868, 'good'), (358, nan), (850, 'outstanding')]</t>
+    <t>[(931, 'good'), (919, nan), (869, 'good'), (936, 'good'), (873, 'requires improvement'), (867, 'outstanding'), (823, 'good'), (868, 'good'), (358, nan), (850, 'outstanding')]</t>
   </si>
   <si>
     <t>buckinghamshire</t>
@@ -457,7 +457,7 @@
     <t>888, 908, 392, 886, 332, 891, 808, 926, 887, 303</t>
   </si>
   <si>
-    <t>[(888, nan), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
+    <t>[(888, nan), (908, 'good'), (392, 'outstanding'), (886, 'good'), (332, nan), (891, 'good'), (808, 'requires improvement'), (926, 'outstanding'), (887, 'good'), (303, 'outstanding')]</t>
   </si>
   <si>
     <t>bury</t>
@@ -517,7 +517,7 @@
     <t>931, 919, 825, 803, 937, 916, 938, 823, 850, 869</t>
   </si>
   <si>
-    <t>[(931, 'good'), (919, 'outstanding'), (825, 'requires improvement'), (803, 'good'), (937, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (823, 'good'), (850, 'outstanding'), (869, 'good')]</t>
+    <t>[(931, 'good'), (919, nan), (825, 'requires improvement'), (803, 'good'), (937, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (823, 'good'), (850, 'outstanding'), (869, 'good')]</t>
   </si>
   <si>
     <t>cambridgeshire</t>
@@ -544,7 +544,7 @@
     <t>825, 803, 873, 850, 865, 931, 938, 867, 869, 919</t>
   </si>
   <si>
-    <t>[(825, 'requires improvement'), (803, 'good'), (873, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (931, 'good'), (938, 'requires improvement'), (867, 'outstanding'), (869, 'good'), (919, 'outstanding')]</t>
+    <t>[(825, 'requires improvement'), (803, 'good'), (873, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (931, 'good'), (938, 'requires improvement'), (867, 'outstanding'), (869, 'good'), (919, nan)]</t>
   </si>
   <si>
     <t>central bedfordshire</t>
@@ -712,7 +712,7 @@
     <t>332, 370, 894, 372, 925, 357, 371, 813, 841, 888</t>
   </si>
   <si>
-    <t>[(332, 'requires improvement'), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, nan)]</t>
+    <t>[(332, nan), (370, 'good'), (894, 'outstanding'), (372, 'outstanding'), (925, 'outstanding'), (357, 'inadequate'), (371, 'good'), (813, 'outstanding'), (841, 'outstanding'), (888, nan)]</t>
   </si>
   <si>
     <t>wakefield</t>
@@ -742,7 +742,7 @@
     <t>916, 800, 802, 919, 937, 931, 938, 358, 850, 356</t>
   </si>
   <si>
-    <t>[(916, 'good'), (800, 'good'), (802, 'requires improvement'), (919, 'outstanding'), (937, 'requires improvement'), (931, 'good'), (938, 'requires improvement'), (358, nan), (850, 'outstanding'), (356, 'requires improvement')]</t>
+    <t>[(916, 'good'), (800, 'good'), (802, 'requires improvement'), (919, nan), (937, 'requires improvement'), (931, 'good'), (938, 'requires improvement'), (358, nan), (850, 'outstanding'), (356, 'requires improvement')]</t>
   </si>
   <si>
     <t>york</t>
@@ -904,7 +904,7 @@
     <t>390, 808, 332, 384, 888, 894, 372, 357, 840, 371</t>
   </si>
   <si>
-    <t>[(390, 'good'), (808, 'requires improvement'), (332, 'requires improvement'), (384, 'good'), (888, nan), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
+    <t>[(390, 'good'), (808, 'requires improvement'), (332, nan), (384, 'good'), (888, nan), (894, 'outstanding'), (372, 'outstanding'), (357, 'inadequate'), (840, 'outstanding'), (371, 'good')]</t>
   </si>
   <si>
     <t>darlington</t>
@@ -1096,19 +1096,16 @@
     <t>dudley</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50204402</t>
-  </si>
-  <si>
-    <t>31/10/2022</t>
-  </si>
-  <si>
-    <t>11/11/2022</t>
-  </si>
-  <si>
-    <t>13/01/23</t>
-  </si>
-  <si>
-    <t>inspection_pre_dates_judgement</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50309682</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>25/08/26</t>
   </si>
   <si>
     <t>80465</t>
@@ -1249,7 +1246,7 @@
     <t>841, 357, 393, 372, 808, 840, 807, 394, 332, 384</t>
   </si>
   <si>
-    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, nan), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, 'requires improvement'), (384, 'good')]</t>
+    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, nan), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, nan), (384, 'good')]</t>
   </si>
   <si>
     <t>gateshead</t>
@@ -1426,1740 +1423,1743 @@
     <t>hertfordshire</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50210577</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50309681</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>data_unreadable</t>
+  </si>
+  <si>
+    <t>80419</t>
+  </si>
+  <si>
+    <t>921</t>
+  </si>
+  <si>
+    <t>E06000046</t>
+  </si>
+  <si>
+    <t>357, 908, 926, 880, 879, 350, 929, 372, 354, 351</t>
+  </si>
+  <si>
+    <t>[(357, 'inadequate'), (908, 'good'), (926, 'outstanding'), (880, 'good'), (879, 'requires improvement'), (350, 'good'), (929, 'outstanding'), (372, 'outstanding'), (354, 'requires improvement'), (351, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>isle of wight</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50235617</t>
+  </si>
+  <si>
+    <t>03/11/2023</t>
+  </si>
+  <si>
+    <t>15/12/23</t>
+  </si>
+  <si>
+    <t>80476</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>E10000016</t>
+  </si>
+  <si>
+    <t>881, 845, 878, 303, 935, 926, 891, 938, 822, 933</t>
+  </si>
+  <si>
+    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, nan)]</t>
+  </si>
+  <si>
+    <t>kent</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50294428</t>
+  </si>
+  <si>
+    <t>steve lowe</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>02/02/26</t>
+  </si>
+  <si>
+    <t>80477</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>E06000010</t>
+  </si>
+  <si>
+    <t>333, 336, 861, 335, 812, 354, 806, 371, 831, 372</t>
+  </si>
+  <si>
+    <t>[(333, 'good'), (336, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (812, 'good'), (354, 'requires improvement'), (806, nan), (371, 'good'), (831, 'outstanding'), (372, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>kingston upon hull</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301678</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>80478</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>E08000034</t>
+  </si>
+  <si>
+    <t>373, 357, 851, 831, 879, 354, 351, 384, 908, 390</t>
+  </si>
+  <si>
+    <t>[(373, 'good'), (357, 'inadequate'), (851, nan), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
+  </si>
+  <si>
+    <t>kirklees</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255618</t>
+  </si>
+  <si>
+    <t>rachel griffiths</t>
+  </si>
+  <si>
+    <t>08/07/2024</t>
+  </si>
+  <si>
+    <t>80479</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>E08000011</t>
+  </si>
+  <si>
+    <t>342, 876, 394, 805, 807, 343, 344, 393, 840, 341</t>
+  </si>
+  <si>
+    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, nan), (840, 'outstanding'), (341, nan)]</t>
+  </si>
+  <si>
+    <t>knowsley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267008</t>
+  </si>
+  <si>
+    <t>rebekah tucker</t>
+  </si>
+  <si>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>20/01/25</t>
+  </si>
+  <si>
+    <t>80480</t>
+  </si>
+  <si>
+    <t>888</t>
+  </si>
+  <si>
+    <t>E10000017</t>
+  </si>
+  <si>
+    <t>925, 351, 332, 884, 841, 808, 384, 891, 929, 359</t>
+  </si>
+  <si>
+    <t>[(925, 'outstanding'), (351, 'requires improvement'), (332, nan), (884, 'good'), (841, 'outstanding'), (808, 'requires improvement'), (384, 'good'), (891, 'good'), (929, 'outstanding'), (359, 'good')]</t>
+  </si>
+  <si>
+    <t>lancashire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50309857</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>22/05/2026</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
+  </si>
+  <si>
+    <t>80481</t>
+  </si>
+  <si>
+    <t>383</t>
+  </si>
+  <si>
+    <t>E08000035</t>
+  </si>
+  <si>
+    <t>851, 882, 373, 826, 382, 355, 801, 852, 306, 839</t>
+  </si>
+  <si>
+    <t>[(851, nan), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
+  </si>
+  <si>
+    <t>leeds</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50284438</t>
+  </si>
+  <si>
+    <t>30/06/2025</t>
+  </si>
+  <si>
+    <t>04/07/2025</t>
+  </si>
+  <si>
+    <t>12/08/25</t>
+  </si>
+  <si>
+    <t>80482</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>E06000016</t>
+  </si>
+  <si>
+    <t>821, 871, 304, 316, 333, 380, 307, 313, 330, 889</t>
+  </si>
+  <si>
+    <t>[(821, 'good'), (871, nan), (304, nan), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
+  </si>
+  <si>
+    <t>leicester</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267800</t>
+  </si>
+  <si>
+    <t>80483</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>E10000018</t>
+  </si>
+  <si>
+    <t>916, 803, 937, 802, 850, 865, 933, 938, 811, 891</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, nan), (938, 'requires improvement'), (811, 'good'), (891, 'good')]</t>
+  </si>
+  <si>
+    <t>leicestershire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252253</t>
+  </si>
+  <si>
+    <t>22/04/2024</t>
+  </si>
+  <si>
+    <t>03/05/2024</t>
+  </si>
+  <si>
+    <t>80484</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
+    <t>E10000019</t>
+  </si>
+  <si>
+    <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
+  </si>
+  <si>
+    <t>[(888, nan), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, nan), (940, nan), (830, 'good'), (933, nan)]</t>
+  </si>
+  <si>
+    <t>lincolnshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50219720</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>28/04/2023</t>
+  </si>
+  <si>
+    <t>14/06/23</t>
+  </si>
+  <si>
+    <t>80485</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>E08000012</t>
+  </si>
+  <si>
+    <t>890, 805, 806, 355, 393, 340, 394, 391, 807, 354</t>
+  </si>
+  <si>
+    <t>[(890, nan), (805, 'outstanding'), (806, nan), (355, 'good'), (393, nan), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>liverpool</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50306784</t>
+  </si>
+  <si>
+    <t>07/07/26</t>
+  </si>
+  <si>
+    <t>80486</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>E09000002</t>
+  </si>
+  <si>
+    <t>308, 821, 313, 333, 336, 307, 304, 312, 874, 203</t>
+  </si>
+  <si>
+    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, nan), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>barking and dagenham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50227183</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
+    <t>04/09/23</t>
+  </si>
+  <si>
+    <t>80487</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>E09000003</t>
+  </si>
+  <si>
+    <t>320, 870, 310, 317, 315, 306, 209, 312, 309, 307</t>
+  </si>
+  <si>
+    <t>[(320, 'good'), (870, 'requires improvement'), (310, 'inadequate'), (317, 'outstanding'), (315, 'outstanding'), (306, 'good'), (209, 'good'), (312, 'outstanding'), (309, 'outstanding'), (307, 'good')]</t>
+  </si>
+  <si>
+    <t>barnet</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253182</t>
+  </si>
+  <si>
+    <t>80488</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>E09000004</t>
+  </si>
+  <si>
+    <t>311, 822, 886, 881, 883, 887, 826, 866, 839, 351</t>
+  </si>
+  <si>
+    <t>[(311, 'inadequate'), (822, 'requires improvement'), (886, 'good'), (881, 'outstanding'), (883, 'outstanding'), (887, 'good'), (826, 'good'), (866, 'inadequate'), (839, 'good'), (351, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>bexley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50212243</t>
+  </si>
+  <si>
+    <t>06/02/2023</t>
+  </si>
+  <si>
+    <t>80489</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>E09000005</t>
+  </si>
+  <si>
+    <t>307, 316, 313, 309, 821, 871, 301, 308, 320, 317</t>
+  </si>
+  <si>
+    <t>[(307, 'good'), (316, 'outstanding'), (313, 'good'), (309, 'outstanding'), (821, 'good'), (871, nan), (301, 'requires improvement'), (308, 'good'), (320, 'good'), (317, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>brent</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50304386</t>
+  </si>
+  <si>
+    <t>monique lindsay</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>01/05/2026</t>
+  </si>
+  <si>
+    <t>17/06/26</t>
+  </si>
+  <si>
+    <t>80490</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>E09000006</t>
+  </si>
+  <si>
+    <t>919, 358, 825, 869, 867, 931, 850, 868, 334, 936</t>
+  </si>
+  <si>
+    <t>[(919, nan), (358, nan), (825, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (931, 'good'), (850, 'outstanding'), (868, 'good'), (334, 'good'), (936, 'good')]</t>
+  </si>
+  <si>
+    <t>bromley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50237004</t>
+  </si>
+  <si>
+    <t>claire beckingham</t>
+  </si>
+  <si>
+    <t>13/11/2023</t>
+  </si>
+  <si>
+    <t>17/11/2023</t>
+  </si>
+  <si>
+    <t>80491</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>E09000007</t>
+  </si>
+  <si>
+    <t>206, 213, 205, 210, 208, 207, 209, 309, 204, 302</t>
+  </si>
+  <si>
+    <t>[(206, 'outstanding'), (213, 'outstanding'), (205, 'outstanding'), (210, 'good'), (208, 'good'), (207, 'outstanding'), (209, 'good'), (309, 'outstanding'), (204, 'good'), (302, 'good')]</t>
+  </si>
+  <si>
+    <t>camden</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50274369</t>
+  </si>
+  <si>
+    <t>80492</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>E09000008</t>
+  </si>
+  <si>
+    <t>209, 320, 383, 870, 826, 882, 302, 852, 355, 203</t>
+  </si>
+  <si>
+    <t>[(209, 'good'), (320, 'good'), (383, 'outstanding'), (870, 'requires improvement'), (826, 'good'), (882, 'good'), (302, 'good'), (852, 'good'), (355, 'good'), (203, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>croydon</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50263391</t>
+  </si>
+  <si>
+    <t>14/10/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>03/12/24</t>
+  </si>
+  <si>
+    <t>80493</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>E09000009</t>
+  </si>
+  <si>
+    <t>313, 317, 312, 320, 304, 309, 310, 871, 821, 302</t>
+  </si>
+  <si>
+    <t>[(313, 'good'), (317, 'outstanding'), (312, 'outstanding'), (320, 'good'), (304, nan), (309, 'outstanding'), (310, 'inadequate'), (871, nan), (821, 'good'), (302, 'good')]</t>
+  </si>
+  <si>
+    <t>ealing</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252258</t>
+  </si>
+  <si>
+    <t>80494</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>E09000010</t>
+  </si>
+  <si>
+    <t>301, 309, 821, 330, 352, 307, 320, 203, 306, 355</t>
+  </si>
+  <si>
+    <t>[(301, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (330, 'good'), (352, 'outstanding'), (307, 'good'), (320, 'good'), (203, 'outstanding'), (306, 'good'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>enfield</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50256007</t>
+  </si>
+  <si>
+    <t>22/07/2024</t>
+  </si>
+  <si>
+    <t>26/07/2024</t>
+  </si>
+  <si>
+    <t>04/09/24</t>
+  </si>
+  <si>
+    <t>80495</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>E09000011</t>
+  </si>
+  <si>
+    <t>209, 208, 306, 210, 355, 320, 851, 852, 391, 870</t>
+  </si>
+  <si>
+    <t>[(209, 'good'), (208, 'good'), (306, 'good'), (210, 'good'), (355, 'good'), (320, 'good'), (851, nan), (852, 'good'), (391, 'good'), (870, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>greenwich</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252576</t>
+  </si>
+  <si>
+    <t>03/06/2024</t>
+  </si>
+  <si>
+    <t>07/06/2024</t>
+  </si>
+  <si>
+    <t>16/07/24</t>
+  </si>
+  <si>
+    <t>80496</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>E09000012</t>
+  </si>
+  <si>
+    <t>210, 206, 309, 208, 211, 209, 202, 352, 320, 213</t>
+  </si>
+  <si>
+    <t>[(210, 'good'), (206, 'outstanding'), (309, 'outstanding'), (208, 'good'), (211, 'outstanding'), (209, 'good'), (202, 'outstanding'), (352, 'outstanding'), (320, 'good'), (213, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>hackney</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255165</t>
+  </si>
+  <si>
+    <t>12/07/2024</t>
+  </si>
+  <si>
+    <t>20/08/24</t>
+  </si>
+  <si>
+    <t>80497</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>E09000013</t>
+  </si>
+  <si>
+    <t>208, 207, 209, 210, 212, 202, 302, 309, 306, 206</t>
+  </si>
+  <si>
+    <t>[(208, 'good'), (207, 'outstanding'), (209, 'good'), (210, 'good'), (212, 'outstanding'), (202, 'outstanding'), (302, 'good'), (309, 'outstanding'), (306, 'good'), (206, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>hammersmith and fulham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50247205</t>
+  </si>
+  <si>
+    <t>11/03/2024</t>
+  </si>
+  <si>
+    <t>80498</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>E09000014</t>
+  </si>
+  <si>
+    <t>320, 307, 209, 208, 302, 308, 210, 304, 313, 317</t>
+  </si>
+  <si>
+    <t>[(320, 'good'), (307, 'good'), (209, 'good'), (208, 'good'), (302, 'good'), (308, 'good'), (210, 'good'), (304, nan), (313, 'good'), (317, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>haringey</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50295650</t>
+  </si>
+  <si>
+    <t>16/01/2026</t>
+  </si>
+  <si>
+    <t>24/02/26</t>
+  </si>
+  <si>
+    <t>80499</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>E09000015</t>
+  </si>
+  <si>
+    <t>317, 312, 302, 307, 320, 870, 313, 315, 871, 826</t>
+  </si>
+  <si>
+    <t>[(317, 'outstanding'), (312, 'outstanding'), (302, 'good'), (307, 'good'), (320, 'good'), (870, 'requires improvement'), (313, 'good'), (315, 'outstanding'), (871, nan), (826, 'good')]</t>
+  </si>
+  <si>
+    <t>harrow</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50270419</t>
+  </si>
+  <si>
+    <t>24/01/2025</t>
+  </si>
+  <si>
+    <t>04/03/25</t>
+  </si>
+  <si>
+    <t>80500</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>E09000016</t>
+  </si>
+  <si>
+    <t>303, 822, 883, 881, 886, 866, 941, 826, 887, 938</t>
+  </si>
+  <si>
+    <t>[(303, 'outstanding'), (822, 'requires improvement'), (883, 'outstanding'), (881, 'outstanding'), (886, 'good'), (866, 'inadequate'), (941, nan), (826, 'good'), (887, 'good'), (938, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>havering</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50239788</t>
+  </si>
+  <si>
+    <t>22/12/2023</t>
+  </si>
+  <si>
+    <t>16/02/24</t>
+  </si>
+  <si>
+    <t>80501</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>E09000017</t>
+  </si>
+  <si>
+    <t>313, 317, 320, 874, 307, 852, 310, 870, 871, 331</t>
+  </si>
+  <si>
+    <t>[(313, 'good'), (317, 'outstanding'), (320, 'good'), (874, 'inadequate'), (307, 'good'), (852, 'good'), (310, 'inadequate'), (870, 'requires improvement'), (871, nan), (331, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>hillingdon</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50233295</t>
+  </si>
+  <si>
+    <t>02/10/2023</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t>20/11/23</t>
+  </si>
+  <si>
+    <t>80503</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>E09000018</t>
+  </si>
+  <si>
+    <t>307, 312, 871, 317, 320, 821, 304, 310, 852, 301</t>
+  </si>
+  <si>
+    <t>[(307, 'good'), (312, 'outstanding'), (871, nan), (317, 'outstanding'), (320, 'good'), (821, 'good'), (304, nan), (310, 'inadequate'), (852, 'good'), (301, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>hounslow</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50234334</t>
+  </si>
+  <si>
+    <t>16/10/2023</t>
+  </si>
+  <si>
+    <t>20/10/2023</t>
+  </si>
+  <si>
+    <t>01/12/23</t>
+  </si>
+  <si>
+    <t>80505</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>E09000019</t>
+  </si>
+  <si>
+    <t>202, 210, 208, 213, 204, 205, 209, 309, 203, 352</t>
+  </si>
+  <si>
+    <t>[(202, 'outstanding'), (210, 'good'), (208, 'good'), (213, 'outstanding'), (204, 'good'), (205, 'outstanding'), (209, 'good'), (309, 'outstanding'), (203, 'outstanding'), (352, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>islington</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267801</t>
+  </si>
+  <si>
+    <t>80506</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>E09000022</t>
+  </si>
+  <si>
+    <t>210, 209, 205, 203, 309, 206, 306, 320, 202, 212</t>
+  </si>
+  <si>
+    <t>[(210, 'good'), (209, 'good'), (205, 'outstanding'), (203, 'outstanding'), (309, 'outstanding'), (206, 'outstanding'), (306, 'good'), (320, 'good'), (202, 'outstanding'), (212, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>lambeth</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50296623</t>
+  </si>
+  <si>
+    <t>jenny -ellen scotland</t>
+  </si>
+  <si>
+    <t>10/03/26</t>
+  </si>
+  <si>
+    <t>80508</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>E09000023</t>
+  </si>
+  <si>
+    <t>208, 210, 306, 205, 203, 320, 309, 302, 383, 355</t>
+  </si>
+  <si>
+    <t>[(208, 'good'), (210, 'good'), (306, 'good'), (205, 'outstanding'), (203, 'outstanding'), (320, 'good'), (309, 'outstanding'), (302, 'good'), (383, 'outstanding'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>lewisham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50238709</t>
+  </si>
+  <si>
+    <t>nicki shaw</t>
+  </si>
+  <si>
+    <t>04/12/2023</t>
+  </si>
+  <si>
+    <t>31/01/24</t>
+  </si>
+  <si>
+    <t>80510</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>E09000024</t>
+  </si>
+  <si>
+    <t>319, 314, 870, 302, 826, 822, 306, 919, 310, 873</t>
+  </si>
+  <si>
+    <t>[(319, 'good'), (314, 'outstanding'), (870, 'requires improvement'), (302, 'good'), (826, 'good'), (822, 'requires improvement'), (306, 'good'), (919, nan), (310, 'inadequate'), (873, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>merton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50285309</t>
+  </si>
+  <si>
+    <t>80511</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>E09000025</t>
+  </si>
+  <si>
+    <t>304, 301, 308, 856, 309, 821, 307, 313, 352, 871</t>
+  </si>
+  <si>
+    <t>[(304, nan), (301, 'requires improvement'), (308, 'good'), (856, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (307, 'good'), (313, 'good'), (352, 'outstanding'), (871, nan)]</t>
+  </si>
+  <si>
+    <t>newham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50293404</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>80512</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>E09000026</t>
+  </si>
+  <si>
+    <t>310, 312, 320, 307, 313, 302, 871, 870, 852, 821</t>
+  </si>
+  <si>
+    <t>[(310, 'inadequate'), (312, 'outstanding'), (320, 'good'), (307, 'good'), (313, 'good'), (302, 'good'), (871, nan), (870, 'requires improvement'), (852, 'good'), (821, 'good')]</t>
+  </si>
+  <si>
+    <t>redbridge</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253184</t>
+  </si>
+  <si>
+    <t>brenda mclaughlin</t>
+  </si>
+  <si>
+    <t>80513</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>E09000027</t>
+  </si>
+  <si>
+    <t>868, 314, 936, 872, 305, 358, 825, 919, 800, 869</t>
+  </si>
+  <si>
+    <t>[(868, 'good'), (314, 'outstanding'), (936, 'good'), (872, 'requires improvement'), (305, 'outstanding'), (358, nan), (825, 'requires improvement'), (919, nan), (800, 'good'), (869, 'good')]</t>
+  </si>
+  <si>
+    <t>richmond upon thames</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50284336</t>
+  </si>
+  <si>
+    <t>80514</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>E09000028</t>
+  </si>
+  <si>
+    <t>208, 209, 205, 206, 203, 309, 202, 204, 306, 320</t>
+  </si>
+  <si>
+    <t>[(208, 'good'), (209, 'good'), (205, 'outstanding'), (206, 'outstanding'), (203, 'outstanding'), (309, 'outstanding'), (202, 'outstanding'), (204, 'good'), (306, 'good'), (320, 'good')]</t>
+  </si>
+  <si>
+    <t>southwark</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301679</t>
+  </si>
+  <si>
+    <t>80515</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>E09000029</t>
+  </si>
+  <si>
+    <t>315, 919, 826, 873, 931, 314, 822, 938, 839, 825</t>
+  </si>
+  <si>
+    <t>[(315, 'outstanding'), (919, nan), (826, 'good'), (873, 'requires improvement'), (931, 'good'), (314, 'outstanding'), (822, 'requires improvement'), (938, 'requires improvement'), (839, 'good'), (825, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>sutton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50283346</t>
+  </si>
+  <si>
+    <t>16/06/2025</t>
+  </si>
+  <si>
+    <t>80516</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>E09000030</t>
+  </si>
+  <si>
+    <t>204, 206, 316, 352, 202, 309, 213, 210, 330, 304</t>
+  </si>
+  <si>
+    <t>[(204, 'good'), (206, 'outstanding'), (316, 'outstanding'), (352, 'outstanding'), (202, 'outstanding'), (309, 'outstanding'), (213, 'outstanding'), (210, 'good'), (330, 'good'), (304, nan)]</t>
+  </si>
+  <si>
+    <t>tower hamlets</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50266090</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
+  </si>
+  <si>
+    <t>15/11/2024</t>
+  </si>
+  <si>
+    <t>13/01/25</t>
+  </si>
+  <si>
+    <t>80517</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>E09000031</t>
+  </si>
+  <si>
+    <t>317, 302, 312, 306, 307, 309, 313, 310, 209, 852</t>
+  </si>
+  <si>
+    <t>[(317, 'outstanding'), (302, 'good'), (312, 'outstanding'), (306, 'good'), (307, 'good'), (309, 'outstanding'), (313, 'good'), (310, 'inadequate'), (209, 'good'), (852, 'good')]</t>
+  </si>
+  <si>
+    <t>waltham forest</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255164</t>
+  </si>
+  <si>
+    <t>jo warburton</t>
+  </si>
+  <si>
+    <t>80518</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>E09000032</t>
+  </si>
+  <si>
+    <t>205, 314, 315, 208, 209, 302, 870, 801, 846, 305</t>
+  </si>
+  <si>
+    <t>[(205, 'outstanding'), (314, 'outstanding'), (315, 'outstanding'), (208, 'good'), (209, 'good'), (302, 'good'), (870, 'requires improvement'), (801, 'requires improvement'), (846, 'outstanding'), (305, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>wandsworth</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301929</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>80519</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>E09000033</t>
+  </si>
+  <si>
+    <t>202, 206, 210, 207, 205, 208, 203, 352, 204, 309</t>
+  </si>
+  <si>
+    <t>[(202, 'outstanding'), (206, 'outstanding'), (210, 'good'), (207, 'outstanding'), (205, 'outstanding'), (208, 'good'), (203, 'outstanding'), (352, 'outstanding'), (204, 'good'), (309, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>westminster</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50266091</t>
+  </si>
+  <si>
+    <t>80520</t>
+  </si>
+  <si>
+    <t>821</t>
+  </si>
+  <si>
+    <t>E06000032</t>
+  </si>
+  <si>
+    <t>871, 874, 331, 313, 312, 856, 307, 333, 852, 301</t>
+  </si>
+  <si>
+    <t>[(871, nan), (874, 'inadequate'), (331, 'outstanding'), (313, 'good'), (312, 'outstanding'), (856, 'requires improvement'), (307, 'good'), (333, 'good'), (852, 'good'), (301, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>luton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50296961</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>80521</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>E08000003</t>
+  </si>
+  <si>
+    <t>892, 330, 391, 308, 380, 355, 806, 852, 309, 353</t>
+  </si>
+  <si>
+    <t>[(892, 'inadequate'), (330, 'good'), (391, 'good'), (308, 'good'), (380, 'requires improvement'), (355, 'good'), (806, nan), (852, 'good'), (309, 'outstanding'), (353, 'good')]</t>
+  </si>
+  <si>
+    <t>manchester</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50290914</t>
+  </si>
+  <si>
+    <t>22/09/2025</t>
+  </si>
+  <si>
+    <t>03/10/2025</t>
+  </si>
+  <si>
+    <t>11/11/25</t>
+  </si>
+  <si>
+    <t>80522</t>
+  </si>
+  <si>
+    <t>887</t>
+  </si>
+  <si>
+    <t>E06000035</t>
+  </si>
+  <si>
+    <t>866, 332, 886, 303, 926, 935, 883, 891, 351, 384</t>
+  </si>
+  <si>
+    <t>[(866, 'inadequate'), (332, nan), (886, 'good'), (303, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (883, 'outstanding'), (891, 'good'), (351, 'requires improvement'), (384, 'good')]</t>
+  </si>
+  <si>
+    <t>medway</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50227723</t>
+  </si>
+  <si>
+    <t>17/07/2023</t>
+  </si>
+  <si>
+    <t>28/07/2023</t>
+  </si>
+  <si>
+    <t>11/09/23</t>
+  </si>
+  <si>
+    <t>80523</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>E06000002</t>
+  </si>
+  <si>
+    <t>890, 805, 861, 354, 391, 336, 335, 393, 341, 355</t>
+  </si>
+  <si>
+    <t>[(890, nan), (805, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (391, 'good'), (336, 'good'), (335, 'outstanding'), (393, nan), (341, nan), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>middlesbrough</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50308109</t>
+  </si>
+  <si>
+    <t>nabeel hussain</t>
+  </si>
+  <si>
+    <t>80524</t>
+  </si>
+  <si>
+    <t>826</t>
+  </si>
+  <si>
+    <t>E06000042</t>
+  </si>
+  <si>
+    <t>822, 303, 882, 870, 839, 311, 919, 886, 319, 383</t>
+  </si>
+  <si>
+    <t>[(822, 'requires improvement'), (303, 'outstanding'), (882, 'good'), (870, 'requires improvement'), (839, 'good'), (311, 'inadequate'), (919, nan), (886, 'good'), (319, 'good'), (383, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>milton keynes</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50264642</t>
+  </si>
+  <si>
+    <t>28/10/2024</t>
+  </si>
+  <si>
+    <t>08/11/2024</t>
+  </si>
+  <si>
+    <t>17/12/24</t>
+  </si>
+  <si>
+    <t>80525</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>E08000021</t>
+  </si>
+  <si>
+    <t>355, 373, 806, 851, 892, 383, 330, 852, 352, 890</t>
+  </si>
+  <si>
+    <t>[(355, 'good'), (373, 'good'), (806, nan), (851, nan), (892, 'inadequate'), (383, 'outstanding'), (330, 'good'), (852, 'good'), (352, 'outstanding'), (890, nan)]</t>
+  </si>
+  <si>
+    <t>newcastle upon tyne</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50280258</t>
+  </si>
+  <si>
+    <t>12/05/2025</t>
+  </si>
+  <si>
+    <t>16/05/2025</t>
+  </si>
+  <si>
+    <t>25/06/25</t>
+  </si>
+  <si>
+    <t>80418</t>
+  </si>
+  <si>
+    <t>926</t>
+  </si>
+  <si>
+    <t>E10000020</t>
+  </si>
+  <si>
+    <t>935, 908, 878, 830, 929, 886, 933, 925, 891, 887</t>
+  </si>
+  <si>
+    <t>[(935, 'requires improvement'), (908, 'good'), (878, 'inadequate'), (830, 'good'), (929, 'outstanding'), (886, 'good'), (933, nan), (925, 'outstanding'), (891, 'good'), (887, 'good')]</t>
+  </si>
+  <si>
+    <t>norfolk</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301680</t>
+  </si>
+  <si>
+    <t>rodica cobarzan</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>80526</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>E06000012</t>
+  </si>
+  <si>
+    <t>371, 861, 372, 894, 335, 384, 841, 370, 807, 357</t>
+  </si>
+  <si>
+    <t>[(371, 'good'), (861, 'requires improvement'), (372, 'outstanding'), (894, 'outstanding'), (335, 'outstanding'), (384, 'good'), (841, 'outstanding'), (370, 'good'), (807, 'good'), (357, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>north east lincolnshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50285393</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>03/09/25</t>
+  </si>
+  <si>
+    <t>80527</t>
+  </si>
+  <si>
+    <t>813</t>
+  </si>
+  <si>
+    <t>E06000013</t>
+  </si>
+  <si>
+    <t>384, 925, 371, 370, 940, 332, 942, 372, 894, 888</t>
+  </si>
+  <si>
+    <t>[(384, 'good'), (925, 'outstanding'), (371, 'good'), (370, 'good'), (940, nan), (332, nan), (942, 'good'), (372, 'outstanding'), (894, 'outstanding'), (888, nan)]</t>
+  </si>
+  <si>
+    <t>north lincolnshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50300420</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>30/04/26</t>
+  </si>
+  <si>
+    <t>2637539</t>
+  </si>
+  <si>
+    <t>940</t>
+  </si>
+  <si>
+    <t>E06000061</t>
+  </si>
+  <si>
+    <t>866, 941, 935, 925, 933, 883, 891, 813, 887, 384</t>
+  </si>
+  <si>
+    <t>[(866, 'inadequate'), (941, nan), (935, 'requires improvement'), (925, 'outstanding'), (933, nan), (883, 'outstanding'), (891, 'good'), (813, 'outstanding'), (887, 'good'), (384, 'good')]</t>
+  </si>
+  <si>
+    <t>north northamptonshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50306548</t>
+  </si>
+  <si>
+    <t>david cohen</t>
+  </si>
+  <si>
+    <t>80528</t>
+  </si>
+  <si>
+    <t>802</t>
+  </si>
+  <si>
+    <t>E06000024</t>
+  </si>
+  <si>
+    <t>850, 916, 865, 937, 855, 881, 938, 803, 891, 886</t>
+  </si>
+  <si>
+    <t>[(850, 'outstanding'), (916, 'good'), (865, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (881, 'outstanding'), (938, 'requires improvement'), (803, 'good'), (891, 'good'), (886, 'good')]</t>
+  </si>
+  <si>
+    <t>north somerset</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50216275</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>11/05/23</t>
+  </si>
+  <si>
+    <t>80529</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>E08000022</t>
+  </si>
+  <si>
+    <t>351, 891, 808, 802, 841, 888, 334, 908, 390, 886</t>
+  </si>
+  <si>
+    <t>[(351, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (802, 'requires improvement'), (841, 'outstanding'), (888, nan), (334, 'good'), (908, 'good'), (390, 'good'), (886, 'good')]</t>
+  </si>
+  <si>
+    <t>north tyneside</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50266092</t>
+  </si>
+  <si>
+    <t>80530</t>
+  </si>
+  <si>
+    <t>815</t>
+  </si>
+  <si>
+    <t>E10000023</t>
+  </si>
+  <si>
+    <t>893, 895, 811, 860, 916, 877, 937, 884, 865, 933</t>
+  </si>
+  <si>
+    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'good'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, nan)]</t>
+  </si>
+  <si>
+    <t>north yorkshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50226213</t>
+  </si>
+  <si>
+    <t>jan edwards</t>
+  </si>
+  <si>
+    <t>03/07/2023</t>
+  </si>
+  <si>
+    <t>07/07/2023</t>
+  </si>
+  <si>
+    <t>18/08/23</t>
+  </si>
+  <si>
+    <t>80532</t>
+  </si>
+  <si>
+    <t>929</t>
+  </si>
+  <si>
+    <t>E06000057</t>
+  </si>
+  <si>
+    <t>926, 830, 888, 908, 878, 840, 838, 886, 885, 935</t>
+  </si>
+  <si>
+    <t>[(926, 'outstanding'), (830, 'good'), (888, nan), (908, 'good'), (878, 'inadequate'), (840, 'outstanding'), (838, 'outstanding'), (886, 'good'), (885, 'good'), (935, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>northumberland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252256</t>
+  </si>
+  <si>
+    <t>andy waugh</t>
+  </si>
+  <si>
+    <t>20/05/2024</t>
+  </si>
+  <si>
+    <t>80533</t>
+  </si>
+  <si>
+    <t>892</t>
+  </si>
+  <si>
+    <t>E06000018</t>
+  </si>
+  <si>
+    <t>330, 352, 391, 806, 380, 333, 852, 353, 373, 355</t>
+  </si>
+  <si>
+    <t>[(330, 'good'), (352, 'outstanding'), (391, 'good'), (806, nan), (380, 'requires improvement'), (333, 'good'), (852, 'good'), (353, 'good'), (373, 'good'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>nottingham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50192198</t>
+  </si>
+  <si>
+    <t>05/09/22</t>
+  </si>
+  <si>
+    <t>80534</t>
+  </si>
+  <si>
+    <t>891</t>
+  </si>
+  <si>
+    <t>E10000024</t>
+  </si>
+  <si>
+    <t>830, 935, 933, 886, 926, 937, 855, 802, 860, 888</t>
+  </si>
+  <si>
+    <t>[(830, 'good'), (935, 'requires improvement'), (933, nan), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, nan)]</t>
+  </si>
+  <si>
+    <t>nottinghamshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252254</t>
+  </si>
+  <si>
+    <t>80535</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>E08000004</t>
+  </si>
+  <si>
+    <t>889, 350, 354, 380, 335, 831, 861, 331, 330, 333</t>
+  </si>
+  <si>
+    <t>[(889, 'good'), (350, 'good'), (354, 'requires improvement'), (380, 'requires improvement'), (335, 'outstanding'), (831, 'outstanding'), (861, 'requires improvement'), (331, 'outstanding'), (330, 'good'), (333, 'good')]</t>
+  </si>
+  <si>
+    <t>oldham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252252</t>
+  </si>
+  <si>
+    <t>80536</t>
+  </si>
+  <si>
+    <t>931</t>
+  </si>
+  <si>
+    <t>E10000025</t>
+  </si>
+  <si>
+    <t>873, 919, 825, 937, 916, 850, 867, 938, 869, 803</t>
+  </si>
+  <si>
+    <t>[(873, 'requires improvement'), (919, nan), (825, 'requires improvement'), (937, 'requires improvement'), (916, 'good'), (850, 'outstanding'), (867, 'outstanding'), (938, 'requires improvement'), (869, 'good'), (803, 'good')]</t>
+  </si>
+  <si>
+    <t>oxfordshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50243682</t>
+  </si>
+  <si>
+    <t>12/02/2024</t>
+  </si>
+  <si>
+    <t>09/04/24</t>
+  </si>
+  <si>
+    <t>80537</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>E06000031</t>
+  </si>
+  <si>
+    <t>331, 831, 312, 350, 852, 335, 821, 354, 336, 883</t>
+  </si>
+  <si>
+    <t>[(331, 'outstanding'), (831, 'outstanding'), (312, 'outstanding'), (350, 'good'), (852, 'good'), (335, 'outstanding'), (821, 'good'), (354, 'requires improvement'), (336, 'good'), (883, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>peterborough</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50238583</t>
+  </si>
+  <si>
+    <t>russel breyer</t>
+  </si>
+  <si>
+    <t>27/11/2023</t>
+  </si>
+  <si>
+    <t>08/12/2023</t>
+  </si>
+  <si>
+    <t>30/01/24</t>
+  </si>
+  <si>
+    <t>80538</t>
+  </si>
+  <si>
+    <t>879</t>
+  </si>
+  <si>
+    <t>E06000026</t>
+  </si>
+  <si>
+    <t>357, 880, 894, 332, 372, 384, 382, 390, 887, 908</t>
+  </si>
+  <si>
+    <t>[(357, 'inadequate'), (880, 'good'), (894, 'outstanding'), (332, nan), (372, 'outstanding'), (384, 'good'), (382, 'good'), (390, 'good'), (887, 'good'), (908, 'good')]</t>
+  </si>
+  <si>
+    <t>plymouth</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50241802</t>
+  </si>
+  <si>
+    <t>22/01/2024</t>
+  </si>
+  <si>
+    <t>02/02/2024</t>
+  </si>
+  <si>
+    <t>15/03/24</t>
+  </si>
+  <si>
+    <t>80539</t>
+  </si>
+  <si>
+    <t>851</t>
+  </si>
+  <si>
+    <t>E06000044</t>
+  </si>
+  <si>
+    <t>373, 383, 382, 355, 852, 882, 879, 831, 390, 357</t>
+  </si>
+  <si>
+    <t>[(373, 'good'), (383, 'outstanding'), (382, 'good'), (355, 'good'), (852, 'good'), (882, 'good'), (879, 'requires improvement'), (831, 'outstanding'), (390, 'good'), (357, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>portsmouth</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50309432</t>
+  </si>
+  <si>
+    <t>steve bailey</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>18/08/26</t>
+  </si>
+  <si>
+    <t>80540</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>E06000038</t>
+  </si>
+  <si>
+    <t>826, 302, 312, 315, 822, 306, 320, 383, 852, 310</t>
+  </si>
+  <si>
+    <t>[(826, 'good'), (302, 'good'), (312, 'outstanding'), (315, 'outstanding'), (822, 'requires improvement'), (306, 'good'), (320, 'good'), (383, 'outstanding'), (852, 'good'), (310, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>reading</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252257</t>
+  </si>
+  <si>
+    <t>80541</t>
+  </si>
+  <si>
+    <t>807</t>
+  </si>
+  <si>
+    <t>E06000003</t>
+  </si>
+  <si>
+    <t>394, 393, 805, 372, 390, 840, 370, 357, 371, 880</t>
+  </si>
+  <si>
+    <t>[(394, 'outstanding'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
+  </si>
+  <si>
+    <t>redcar and cleveland</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50294204</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>80542</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>E08000005</t>
+  </si>
+  <si>
+    <t>335, 357, 861, 350, 394, 371, 372, 831, 353, 355</t>
+  </si>
+  <si>
+    <t>[(335, 'outstanding'), (357, 'inadequate'), (861, 'requires improvement'), (350, 'good'), (394, 'outstanding'), (371, 'good'), (372, 'outstanding'), (831, 'outstanding'), (353, 'good'), (355, 'good')]</t>
+  </si>
+  <si>
+    <t>rochdale</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50211330</t>
   </si>
   <si>
     <t>23/01/2023</t>
   </si>
   <si>
-    <t>80419</t>
-  </si>
-  <si>
-    <t>921</t>
-  </si>
-  <si>
-    <t>E06000046</t>
-  </si>
-  <si>
-    <t>357, 908, 926, 880, 879, 350, 929, 372, 354, 351</t>
-  </si>
-  <si>
-    <t>[(357, 'inadequate'), (908, 'good'), (926, 'outstanding'), (880, 'good'), (879, 'requires improvement'), (350, 'good'), (929, 'outstanding'), (372, 'outstanding'), (354, 'requires improvement'), (351, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>isle of wight</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50235617</t>
-  </si>
-  <si>
-    <t>03/11/2023</t>
-  </si>
-  <si>
-    <t>15/12/23</t>
-  </si>
-  <si>
-    <t>80476</t>
-  </si>
-  <si>
-    <t>886</t>
-  </si>
-  <si>
-    <t>E10000016</t>
-  </si>
-  <si>
-    <t>881, 845, 878, 303, 935, 926, 891, 938, 822, 933</t>
-  </si>
-  <si>
-    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, nan)]</t>
-  </si>
-  <si>
-    <t>kent</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50294428</t>
-  </si>
-  <si>
-    <t>steve lowe</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
-    <t>02/02/26</t>
-  </si>
-  <si>
-    <t>80477</t>
-  </si>
-  <si>
-    <t>810</t>
-  </si>
-  <si>
-    <t>E06000010</t>
-  </si>
-  <si>
-    <t>333, 336, 861, 335, 812, 354, 806, 371, 831, 372</t>
-  </si>
-  <si>
-    <t>[(333, 'good'), (336, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (812, 'good'), (354, 'requires improvement'), (806, nan), (371, 'good'), (831, 'outstanding'), (372, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>kingston upon hull</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301678</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>80478</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>E08000034</t>
-  </si>
-  <si>
-    <t>373, 357, 851, 831, 879, 354, 351, 384, 908, 390</t>
-  </si>
-  <si>
-    <t>[(373, 'good'), (357, 'inadequate'), (851, nan), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
-  </si>
-  <si>
-    <t>kirklees</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255618</t>
-  </si>
-  <si>
-    <t>rachel griffiths</t>
-  </si>
-  <si>
-    <t>08/07/2024</t>
-  </si>
-  <si>
-    <t>80479</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>E08000011</t>
-  </si>
-  <si>
-    <t>342, 876, 394, 805, 807, 343, 344, 393, 840, 341</t>
-  </si>
-  <si>
-    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, nan), (840, 'outstanding'), (341, nan)]</t>
-  </si>
-  <si>
-    <t>knowsley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267008</t>
-  </si>
-  <si>
-    <t>rebekah tucker</t>
-  </si>
-  <si>
-    <t>18/11/2024</t>
-  </si>
-  <si>
-    <t>29/11/2024</t>
-  </si>
-  <si>
-    <t>20/01/25</t>
-  </si>
-  <si>
-    <t>80480</t>
-  </si>
-  <si>
-    <t>888</t>
-  </si>
-  <si>
-    <t>E10000017</t>
-  </si>
-  <si>
-    <t>925, 351, 332, 884, 841, 808, 384, 891, 929, 359</t>
-  </si>
-  <si>
-    <t>[(925, 'outstanding'), (351, 'requires improvement'), (332, 'requires improvement'), (884, 'good'), (841, 'outstanding'), (808, 'requires improvement'), (384, 'good'), (891, 'good'), (929, 'outstanding'), (359, 'good')]</t>
-  </si>
-  <si>
-    <t>lancashire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50309857</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
-    <t>20/08/26</t>
-  </si>
-  <si>
-    <t>80481</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>E08000035</t>
-  </si>
-  <si>
-    <t>851, 882, 373, 826, 382, 355, 801, 852, 306, 839</t>
-  </si>
-  <si>
-    <t>[(851, nan), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
-  </si>
-  <si>
-    <t>leeds</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50284438</t>
-  </si>
-  <si>
-    <t>30/06/2025</t>
-  </si>
-  <si>
-    <t>04/07/2025</t>
-  </si>
-  <si>
-    <t>12/08/25</t>
-  </si>
-  <si>
-    <t>80482</t>
-  </si>
-  <si>
-    <t>856</t>
-  </si>
-  <si>
-    <t>E06000016</t>
-  </si>
-  <si>
-    <t>821, 871, 304, 316, 333, 380, 307, 313, 330, 889</t>
-  </si>
-  <si>
-    <t>[(821, 'good'), (871, 'requires improvement'), (304, nan), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
-  </si>
-  <si>
-    <t>leicester</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267800</t>
-  </si>
-  <si>
-    <t>80483</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>E10000018</t>
-  </si>
-  <si>
-    <t>916, 803, 937, 802, 850, 865, 933, 938, 811, 891</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, nan), (938, 'requires improvement'), (811, 'good'), (891, 'good')]</t>
-  </si>
-  <si>
-    <t>leicestershire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252253</t>
-  </si>
-  <si>
-    <t>22/04/2024</t>
-  </si>
-  <si>
-    <t>03/05/2024</t>
-  </si>
-  <si>
-    <t>80484</t>
-  </si>
-  <si>
-    <t>925</t>
-  </si>
-  <si>
-    <t>E10000019</t>
-  </si>
-  <si>
-    <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
-  </si>
-  <si>
-    <t>[(888, nan), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'requires improvement'), (940, nan), (830, 'good'), (933, nan)]</t>
-  </si>
-  <si>
-    <t>lincolnshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50219720</t>
-  </si>
-  <si>
-    <t>24/04/2023</t>
-  </si>
-  <si>
-    <t>28/04/2023</t>
-  </si>
-  <si>
-    <t>14/06/23</t>
-  </si>
-  <si>
-    <t>80485</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>E08000012</t>
-  </si>
-  <si>
-    <t>890, 805, 806, 355, 393, 340, 394, 391, 807, 354</t>
-  </si>
-  <si>
-    <t>[(890, nan), (805, 'outstanding'), (806, nan), (355, 'good'), (393, nan), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>liverpool</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50306784</t>
-  </si>
-  <si>
-    <t>07/07/26</t>
-  </si>
-  <si>
-    <t>80486</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>E09000002</t>
-  </si>
-  <si>
-    <t>308, 821, 313, 333, 336, 307, 304, 312, 874, 203</t>
-  </si>
-  <si>
-    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, nan), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>barking and dagenham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50227183</t>
-  </si>
-  <si>
-    <t>10/07/2023</t>
-  </si>
-  <si>
-    <t>21/07/2023</t>
-  </si>
-  <si>
-    <t>04/09/23</t>
-  </si>
-  <si>
-    <t>80487</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>E09000003</t>
-  </si>
-  <si>
-    <t>320, 870, 310, 317, 315, 306, 209, 312, 309, 307</t>
-  </si>
-  <si>
-    <t>[(320, 'good'), (870, 'requires improvement'), (310, 'inadequate'), (317, 'outstanding'), (315, 'outstanding'), (306, 'good'), (209, 'good'), (312, 'outstanding'), (309, 'outstanding'), (307, 'good')]</t>
-  </si>
-  <si>
-    <t>barnet</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253182</t>
-  </si>
-  <si>
-    <t>80488</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>E09000004</t>
-  </si>
-  <si>
-    <t>311, 822, 886, 881, 883, 887, 826, 866, 839, 351</t>
-  </si>
-  <si>
-    <t>[(311, 'inadequate'), (822, 'requires improvement'), (886, 'good'), (881, 'outstanding'), (883, 'outstanding'), (887, 'good'), (826, 'good'), (866, 'inadequate'), (839, 'good'), (351, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>bexley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50212243</t>
-  </si>
-  <si>
-    <t>06/02/2023</t>
-  </si>
-  <si>
-    <t>80489</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>E09000005</t>
-  </si>
-  <si>
-    <t>307, 316, 313, 309, 821, 871, 301, 308, 320, 317</t>
-  </si>
-  <si>
-    <t>[(307, 'good'), (316, 'outstanding'), (313, 'good'), (309, 'outstanding'), (821, 'good'), (871, 'requires improvement'), (301, 'requires improvement'), (308, 'good'), (320, 'good'), (317, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>brent</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50304386</t>
-  </si>
-  <si>
-    <t>monique lindsay</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>01/05/2026</t>
-  </si>
-  <si>
-    <t>17/06/26</t>
-  </si>
-  <si>
-    <t>80490</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>E09000006</t>
-  </si>
-  <si>
-    <t>919, 358, 825, 869, 867, 931, 850, 868, 334, 936</t>
-  </si>
-  <si>
-    <t>[(919, 'outstanding'), (358, nan), (825, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (931, 'good'), (850, 'outstanding'), (868, 'good'), (334, 'good'), (936, 'good')]</t>
-  </si>
-  <si>
-    <t>bromley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50237004</t>
-  </si>
-  <si>
-    <t>claire beckingham</t>
-  </si>
-  <si>
-    <t>13/11/2023</t>
-  </si>
-  <si>
-    <t>17/11/2023</t>
-  </si>
-  <si>
-    <t>80491</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>E09000007</t>
-  </si>
-  <si>
-    <t>206, 213, 205, 210, 208, 207, 209, 309, 204, 302</t>
-  </si>
-  <si>
-    <t>[(206, 'outstanding'), (213, 'outstanding'), (205, 'outstanding'), (210, 'good'), (208, 'good'), (207, 'outstanding'), (209, 'good'), (309, 'outstanding'), (204, 'good'), (302, 'good')]</t>
-  </si>
-  <si>
-    <t>camden</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50274369</t>
-  </si>
-  <si>
-    <t>80492</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>E09000008</t>
-  </si>
-  <si>
-    <t>209, 320, 383, 870, 826, 882, 302, 852, 355, 203</t>
-  </si>
-  <si>
-    <t>[(209, 'good'), (320, 'good'), (383, 'outstanding'), (870, 'requires improvement'), (826, 'good'), (882, 'good'), (302, 'good'), (852, 'good'), (355, 'good'), (203, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>croydon</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50263391</t>
-  </si>
-  <si>
-    <t>14/10/2024</t>
-  </si>
-  <si>
-    <t>25/10/2024</t>
-  </si>
-  <si>
-    <t>03/12/24</t>
-  </si>
-  <si>
-    <t>80493</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>E09000009</t>
-  </si>
-  <si>
-    <t>313, 317, 312, 320, 304, 309, 310, 871, 821, 302</t>
-  </si>
-  <si>
-    <t>[(313, 'good'), (317, 'outstanding'), (312, 'outstanding'), (320, 'good'), (304, nan), (309, 'outstanding'), (310, 'inadequate'), (871, 'requires improvement'), (821, 'good'), (302, 'good')]</t>
-  </si>
-  <si>
-    <t>ealing</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252258</t>
-  </si>
-  <si>
-    <t>80494</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>E09000010</t>
-  </si>
-  <si>
-    <t>301, 309, 821, 330, 352, 307, 320, 203, 306, 355</t>
-  </si>
-  <si>
-    <t>[(301, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (330, 'good'), (352, 'outstanding'), (307, 'good'), (320, 'good'), (203, 'outstanding'), (306, 'good'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>enfield</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50256007</t>
-  </si>
-  <si>
-    <t>22/07/2024</t>
-  </si>
-  <si>
-    <t>26/07/2024</t>
-  </si>
-  <si>
-    <t>04/09/24</t>
-  </si>
-  <si>
-    <t>80495</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>E09000011</t>
-  </si>
-  <si>
-    <t>209, 208, 306, 210, 355, 320, 851, 852, 391, 870</t>
-  </si>
-  <si>
-    <t>[(209, 'good'), (208, 'good'), (306, 'good'), (210, 'good'), (355, 'good'), (320, 'good'), (851, nan), (852, 'good'), (391, 'good'), (870, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>greenwich</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252576</t>
-  </si>
-  <si>
-    <t>03/06/2024</t>
-  </si>
-  <si>
-    <t>07/06/2024</t>
-  </si>
-  <si>
-    <t>16/07/24</t>
-  </si>
-  <si>
-    <t>80496</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>E09000012</t>
-  </si>
-  <si>
-    <t>210, 206, 309, 208, 211, 209, 202, 352, 320, 213</t>
-  </si>
-  <si>
-    <t>[(210, 'good'), (206, 'outstanding'), (309, 'outstanding'), (208, 'good'), (211, 'outstanding'), (209, 'good'), (202, 'outstanding'), (352, 'outstanding'), (320, 'good'), (213, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>hackney</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255165</t>
-  </si>
-  <si>
-    <t>12/07/2024</t>
-  </si>
-  <si>
-    <t>20/08/24</t>
-  </si>
-  <si>
-    <t>80497</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>E09000013</t>
-  </si>
-  <si>
-    <t>208, 207, 209, 210, 212, 202, 302, 309, 306, 206</t>
-  </si>
-  <si>
-    <t>[(208, 'good'), (207, 'outstanding'), (209, 'good'), (210, 'good'), (212, 'outstanding'), (202, 'outstanding'), (302, 'good'), (309, 'outstanding'), (306, 'good'), (206, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>hammersmith and fulham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50247205</t>
-  </si>
-  <si>
-    <t>11/03/2024</t>
-  </si>
-  <si>
-    <t>80498</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>E09000014</t>
-  </si>
-  <si>
-    <t>320, 307, 209, 208, 302, 308, 210, 304, 313, 317</t>
-  </si>
-  <si>
-    <t>[(320, 'good'), (307, 'good'), (209, 'good'), (208, 'good'), (302, 'good'), (308, 'good'), (210, 'good'), (304, nan), (313, 'good'), (317, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>haringey</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50295650</t>
-  </si>
-  <si>
-    <t>16/01/2026</t>
-  </si>
-  <si>
-    <t>24/02/26</t>
-  </si>
-  <si>
-    <t>80499</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>E09000015</t>
-  </si>
-  <si>
-    <t>317, 312, 302, 307, 320, 870, 313, 315, 871, 826</t>
-  </si>
-  <si>
-    <t>[(317, 'outstanding'), (312, 'outstanding'), (302, 'good'), (307, 'good'), (320, 'good'), (870, 'requires improvement'), (313, 'good'), (315, 'outstanding'), (871, 'requires improvement'), (826, 'good')]</t>
-  </si>
-  <si>
-    <t>harrow</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50270419</t>
-  </si>
-  <si>
-    <t>24/01/2025</t>
-  </si>
-  <si>
-    <t>04/03/25</t>
-  </si>
-  <si>
-    <t>80500</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>E09000016</t>
-  </si>
-  <si>
-    <t>303, 822, 883, 881, 886, 866, 941, 826, 887, 938</t>
-  </si>
-  <si>
-    <t>[(303, 'outstanding'), (822, 'requires improvement'), (883, 'outstanding'), (881, 'outstanding'), (886, 'good'), (866, 'inadequate'), (941, nan), (826, 'good'), (887, 'good'), (938, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>havering</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50239788</t>
-  </si>
-  <si>
-    <t>22/12/2023</t>
-  </si>
-  <si>
-    <t>16/02/24</t>
-  </si>
-  <si>
-    <t>80501</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>E09000017</t>
-  </si>
-  <si>
-    <t>313, 317, 320, 874, 307, 852, 310, 870, 871, 331</t>
-  </si>
-  <si>
-    <t>[(313, 'good'), (317, 'outstanding'), (320, 'good'), (874, 'inadequate'), (307, 'good'), (852, 'good'), (310, 'inadequate'), (870, 'requires improvement'), (871, 'requires improvement'), (331, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>hillingdon</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50233295</t>
-  </si>
-  <si>
-    <t>02/10/2023</t>
-  </si>
-  <si>
-    <t>06/10/2023</t>
-  </si>
-  <si>
-    <t>20/11/23</t>
-  </si>
-  <si>
-    <t>80503</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>E09000018</t>
-  </si>
-  <si>
-    <t>307, 312, 871, 317, 320, 821, 304, 310, 852, 301</t>
-  </si>
-  <si>
-    <t>[(307, 'good'), (312, 'outstanding'), (871, 'requires improvement'), (317, 'outstanding'), (320, 'good'), (821, 'good'), (304, nan), (310, 'inadequate'), (852, 'good'), (301, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>hounslow</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50234334</t>
-  </si>
-  <si>
-    <t>16/10/2023</t>
-  </si>
-  <si>
-    <t>20/10/2023</t>
-  </si>
-  <si>
-    <t>01/12/23</t>
-  </si>
-  <si>
-    <t>80505</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>E09000019</t>
-  </si>
-  <si>
-    <t>202, 210, 208, 213, 204, 205, 209, 309, 203, 352</t>
-  </si>
-  <si>
-    <t>[(202, 'outstanding'), (210, 'good'), (208, 'good'), (213, 'outstanding'), (204, 'good'), (205, 'outstanding'), (209, 'good'), (309, 'outstanding'), (203, 'outstanding'), (352, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>islington</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267801</t>
-  </si>
-  <si>
-    <t>80506</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>E09000022</t>
-  </si>
-  <si>
-    <t>210, 209, 205, 203, 309, 206, 306, 320, 202, 212</t>
-  </si>
-  <si>
-    <t>[(210, 'good'), (209, 'good'), (205, 'outstanding'), (203, 'outstanding'), (309, 'outstanding'), (206, 'outstanding'), (306, 'good'), (320, 'good'), (202, 'outstanding'), (212, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>lambeth</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50296623</t>
-  </si>
-  <si>
-    <t>jenny -ellen scotland</t>
-  </si>
-  <si>
-    <t>10/03/26</t>
-  </si>
-  <si>
-    <t>80508</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>E09000023</t>
-  </si>
-  <si>
-    <t>208, 210, 306, 205, 203, 320, 309, 302, 383, 355</t>
-  </si>
-  <si>
-    <t>[(208, 'good'), (210, 'good'), (306, 'good'), (205, 'outstanding'), (203, 'outstanding'), (320, 'good'), (309, 'outstanding'), (302, 'good'), (383, 'outstanding'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>lewisham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50238709</t>
-  </si>
-  <si>
-    <t>nicki shaw</t>
-  </si>
-  <si>
-    <t>04/12/2023</t>
-  </si>
-  <si>
-    <t>31/01/24</t>
-  </si>
-  <si>
-    <t>80510</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>E09000024</t>
-  </si>
-  <si>
-    <t>319, 314, 870, 302, 826, 822, 306, 919, 310, 873</t>
-  </si>
-  <si>
-    <t>[(319, 'good'), (314, 'outstanding'), (870, 'requires improvement'), (302, 'good'), (826, 'good'), (822, 'requires improvement'), (306, 'good'), (919, 'outstanding'), (310, 'inadequate'), (873, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>merton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50285309</t>
-  </si>
-  <si>
-    <t>80511</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>E09000025</t>
-  </si>
-  <si>
-    <t>304, 301, 308, 856, 309, 821, 307, 313, 352, 871</t>
-  </si>
-  <si>
-    <t>[(304, nan), (301, 'requires improvement'), (308, 'good'), (856, 'requires improvement'), (309, 'outstanding'), (821, 'good'), (307, 'good'), (313, 'good'), (352, 'outstanding'), (871, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>newham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50293404</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>80512</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>E09000026</t>
-  </si>
-  <si>
-    <t>310, 312, 320, 307, 313, 302, 871, 870, 852, 821</t>
-  </si>
-  <si>
-    <t>[(310, 'inadequate'), (312, 'outstanding'), (320, 'good'), (307, 'good'), (313, 'good'), (302, 'good'), (871, 'requires improvement'), (870, 'requires improvement'), (852, 'good'), (821, 'good')]</t>
-  </si>
-  <si>
-    <t>redbridge</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253184</t>
-  </si>
-  <si>
-    <t>brenda mclaughlin</t>
-  </si>
-  <si>
-    <t>80513</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>E09000027</t>
-  </si>
-  <si>
-    <t>868, 314, 936, 872, 305, 358, 825, 919, 800, 869</t>
-  </si>
-  <si>
-    <t>[(868, 'good'), (314, 'outstanding'), (936, 'good'), (872, 'requires improvement'), (305, 'outstanding'), (358, nan), (825, 'requires improvement'), (919, 'outstanding'), (800, 'good'), (869, 'good')]</t>
-  </si>
-  <si>
-    <t>richmond upon thames</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50284336</t>
-  </si>
-  <si>
-    <t>80514</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>E09000028</t>
-  </si>
-  <si>
-    <t>208, 209, 205, 206, 203, 309, 202, 204, 306, 320</t>
-  </si>
-  <si>
-    <t>[(208, 'good'), (209, 'good'), (205, 'outstanding'), (206, 'outstanding'), (203, 'outstanding'), (309, 'outstanding'), (202, 'outstanding'), (204, 'good'), (306, 'good'), (320, 'good')]</t>
-  </si>
-  <si>
-    <t>southwark</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301679</t>
-  </si>
-  <si>
-    <t>80515</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>E09000029</t>
-  </si>
-  <si>
-    <t>315, 919, 826, 873, 931, 314, 822, 938, 839, 825</t>
-  </si>
-  <si>
-    <t>[(315, 'outstanding'), (919, 'outstanding'), (826, 'good'), (873, 'requires improvement'), (931, 'good'), (314, 'outstanding'), (822, 'requires improvement'), (938, 'requires improvement'), (839, 'good'), (825, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>sutton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50283346</t>
-  </si>
-  <si>
-    <t>16/06/2025</t>
-  </si>
-  <si>
-    <t>80516</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>E09000030</t>
-  </si>
-  <si>
-    <t>204, 206, 316, 352, 202, 309, 213, 210, 330, 304</t>
-  </si>
-  <si>
-    <t>[(204, 'good'), (206, 'outstanding'), (316, 'outstanding'), (352, 'outstanding'), (202, 'outstanding'), (309, 'outstanding'), (213, 'outstanding'), (210, 'good'), (330, 'good'), (304, nan)]</t>
-  </si>
-  <si>
-    <t>tower hamlets</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50266090</t>
-  </si>
-  <si>
-    <t>11/11/2024</t>
-  </si>
-  <si>
-    <t>15/11/2024</t>
-  </si>
-  <si>
-    <t>13/01/25</t>
-  </si>
-  <si>
-    <t>80517</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>E09000031</t>
-  </si>
-  <si>
-    <t>317, 302, 312, 306, 307, 309, 313, 310, 209, 852</t>
-  </si>
-  <si>
-    <t>[(317, 'outstanding'), (302, 'good'), (312, 'outstanding'), (306, 'good'), (307, 'good'), (309, 'outstanding'), (313, 'good'), (310, 'inadequate'), (209, 'good'), (852, 'good')]</t>
-  </si>
-  <si>
-    <t>waltham forest</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255164</t>
-  </si>
-  <si>
-    <t>jo warburton</t>
-  </si>
-  <si>
-    <t>80518</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>E09000032</t>
-  </si>
-  <si>
-    <t>205, 314, 315, 208, 209, 302, 870, 801, 846, 305</t>
-  </si>
-  <si>
-    <t>[(205, 'outstanding'), (314, 'outstanding'), (315, 'outstanding'), (208, 'good'), (209, 'good'), (302, 'good'), (870, 'requires improvement'), (801, 'requires improvement'), (846, 'outstanding'), (305, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>wandsworth</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301929</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>80519</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>E09000033</t>
-  </si>
-  <si>
-    <t>202, 206, 210, 207, 205, 208, 203, 352, 204, 309</t>
-  </si>
-  <si>
-    <t>[(202, 'outstanding'), (206, 'outstanding'), (210, 'good'), (207, 'outstanding'), (205, 'outstanding'), (208, 'good'), (203, 'outstanding'), (352, 'outstanding'), (204, 'good'), (309, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>westminster</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50266091</t>
-  </si>
-  <si>
-    <t>80520</t>
-  </si>
-  <si>
-    <t>821</t>
-  </si>
-  <si>
-    <t>E06000032</t>
-  </si>
-  <si>
-    <t>871, 874, 331, 313, 312, 856, 307, 333, 852, 301</t>
-  </si>
-  <si>
-    <t>[(871, 'requires improvement'), (874, 'inadequate'), (331, 'outstanding'), (313, 'good'), (312, 'outstanding'), (856, 'requires improvement'), (307, 'good'), (333, 'good'), (852, 'good'), (301, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>luton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50296961</t>
-  </si>
-  <si>
-    <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>80521</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>E08000003</t>
-  </si>
-  <si>
-    <t>892, 330, 391, 308, 380, 355, 806, 852, 309, 353</t>
-  </si>
-  <si>
-    <t>[(892, 'inadequate'), (330, 'good'), (391, 'good'), (308, 'good'), (380, 'requires improvement'), (355, 'good'), (806, nan), (852, 'good'), (309, 'outstanding'), (353, 'good')]</t>
-  </si>
-  <si>
-    <t>manchester</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50290914</t>
-  </si>
-  <si>
-    <t>22/09/2025</t>
-  </si>
-  <si>
-    <t>03/10/2025</t>
-  </si>
-  <si>
-    <t>11/11/25</t>
-  </si>
-  <si>
-    <t>80522</t>
-  </si>
-  <si>
-    <t>887</t>
-  </si>
-  <si>
-    <t>E06000035</t>
-  </si>
-  <si>
-    <t>866, 332, 886, 303, 926, 935, 883, 891, 351, 384</t>
-  </si>
-  <si>
-    <t>[(866, 'inadequate'), (332, 'requires improvement'), (886, 'good'), (303, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (883, 'outstanding'), (891, 'good'), (351, 'requires improvement'), (384, 'good')]</t>
-  </si>
-  <si>
-    <t>medway</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50227723</t>
-  </si>
-  <si>
-    <t>17/07/2023</t>
-  </si>
-  <si>
-    <t>28/07/2023</t>
-  </si>
-  <si>
-    <t>11/09/23</t>
-  </si>
-  <si>
-    <t>80523</t>
-  </si>
-  <si>
-    <t>806</t>
-  </si>
-  <si>
-    <t>E06000002</t>
-  </si>
-  <si>
-    <t>890, 805, 861, 354, 391, 336, 335, 393, 341, 355</t>
-  </si>
-  <si>
-    <t>[(890, nan), (805, 'outstanding'), (861, 'requires improvement'), (354, 'requires improvement'), (391, 'good'), (336, 'good'), (335, 'outstanding'), (393, nan), (341, nan), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>middlesbrough</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50308109</t>
-  </si>
-  <si>
-    <t>nabeel hussain</t>
-  </si>
-  <si>
-    <t>80524</t>
-  </si>
-  <si>
-    <t>826</t>
-  </si>
-  <si>
-    <t>E06000042</t>
-  </si>
-  <si>
-    <t>822, 303, 882, 870, 839, 311, 919, 886, 319, 383</t>
-  </si>
-  <si>
-    <t>[(822, 'requires improvement'), (303, 'outstanding'), (882, 'good'), (870, 'requires improvement'), (839, 'good'), (311, 'inadequate'), (919, 'outstanding'), (886, 'good'), (319, 'good'), (383, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>milton keynes</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50264642</t>
-  </si>
-  <si>
-    <t>28/10/2024</t>
-  </si>
-  <si>
-    <t>08/11/2024</t>
-  </si>
-  <si>
-    <t>17/12/24</t>
-  </si>
-  <si>
-    <t>80525</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>E08000021</t>
-  </si>
-  <si>
-    <t>355, 373, 806, 851, 892, 383, 330, 852, 352, 890</t>
-  </si>
-  <si>
-    <t>[(355, 'good'), (373, 'good'), (806, nan), (851, nan), (892, 'inadequate'), (383, 'outstanding'), (330, 'good'), (852, 'good'), (352, 'outstanding'), (890, nan)]</t>
-  </si>
-  <si>
-    <t>newcastle upon tyne</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50280258</t>
-  </si>
-  <si>
-    <t>12/05/2025</t>
-  </si>
-  <si>
-    <t>16/05/2025</t>
-  </si>
-  <si>
-    <t>25/06/25</t>
-  </si>
-  <si>
-    <t>80418</t>
-  </si>
-  <si>
-    <t>926</t>
-  </si>
-  <si>
-    <t>E10000020</t>
-  </si>
-  <si>
-    <t>935, 908, 878, 830, 929, 886, 933, 925, 891, 887</t>
-  </si>
-  <si>
-    <t>[(935, 'requires improvement'), (908, 'good'), (878, 'inadequate'), (830, 'good'), (929, 'outstanding'), (886, 'good'), (933, nan), (925, 'outstanding'), (891, 'good'), (887, 'good')]</t>
-  </si>
-  <si>
-    <t>norfolk</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301680</t>
-  </si>
-  <si>
-    <t>rodica cobarzan</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>27/02/2026</t>
-  </si>
-  <si>
-    <t>80526</t>
-  </si>
-  <si>
-    <t>812</t>
-  </si>
-  <si>
-    <t>E06000012</t>
-  </si>
-  <si>
-    <t>371, 861, 372, 894, 335, 384, 841, 370, 807, 357</t>
-  </si>
-  <si>
-    <t>[(371, 'good'), (861, 'requires improvement'), (372, 'outstanding'), (894, 'outstanding'), (335, 'outstanding'), (384, 'good'), (841, 'outstanding'), (370, 'good'), (807, 'good'), (357, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>north east lincolnshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50285393</t>
-  </si>
-  <si>
-    <t>25/07/2025</t>
-  </si>
-  <si>
-    <t>03/09/25</t>
-  </si>
-  <si>
-    <t>80527</t>
-  </si>
-  <si>
-    <t>813</t>
-  </si>
-  <si>
-    <t>E06000013</t>
-  </si>
-  <si>
-    <t>384, 925, 371, 370, 940, 332, 942, 372, 894, 888</t>
-  </si>
-  <si>
-    <t>[(384, 'good'), (925, 'outstanding'), (371, 'good'), (370, 'good'), (940, nan), (332, 'requires improvement'), (942, 'good'), (372, 'outstanding'), (894, 'outstanding'), (888, nan)]</t>
-  </si>
-  <si>
-    <t>north lincolnshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50300420</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>30/04/26</t>
-  </si>
-  <si>
-    <t>2637539</t>
-  </si>
-  <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>E06000061</t>
-  </si>
-  <si>
-    <t>866, 941, 935, 925, 933, 883, 891, 813, 887, 384</t>
-  </si>
-  <si>
-    <t>[(866, 'inadequate'), (941, nan), (935, 'requires improvement'), (925, 'outstanding'), (933, nan), (883, 'outstanding'), (891, 'good'), (813, 'outstanding'), (887, 'good'), (384, 'good')]</t>
-  </si>
-  <si>
-    <t>north northamptonshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50306548</t>
-  </si>
-  <si>
-    <t>david cohen</t>
-  </si>
-  <si>
-    <t>80528</t>
-  </si>
-  <si>
-    <t>802</t>
-  </si>
-  <si>
-    <t>E06000024</t>
-  </si>
-  <si>
-    <t>850, 916, 865, 937, 855, 881, 938, 803, 891, 886</t>
-  </si>
-  <si>
-    <t>[(850, 'outstanding'), (916, 'good'), (865, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (881, 'outstanding'), (938, 'requires improvement'), (803, 'good'), (891, 'good'), (886, 'good')]</t>
-  </si>
-  <si>
-    <t>north somerset</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50216275</t>
-  </si>
-  <si>
-    <t>13/03/2023</t>
-  </si>
-  <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
-    <t>11/05/23</t>
-  </si>
-  <si>
-    <t>80529</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>E08000022</t>
-  </si>
-  <si>
-    <t>351, 891, 808, 802, 841, 888, 334, 908, 390, 886</t>
-  </si>
-  <si>
-    <t>[(351, 'requires improvement'), (891, 'good'), (808, 'requires improvement'), (802, 'requires improvement'), (841, 'outstanding'), (888, nan), (334, 'good'), (908, 'good'), (390, 'good'), (886, 'good')]</t>
-  </si>
-  <si>
-    <t>north tyneside</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50266092</t>
-  </si>
-  <si>
-    <t>80530</t>
-  </si>
-  <si>
-    <t>815</t>
-  </si>
-  <si>
-    <t>E10000023</t>
-  </si>
-  <si>
-    <t>893, 895, 811, 860, 916, 877, 937, 884, 865, 933</t>
-  </si>
-  <si>
-    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'good'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, nan)]</t>
-  </si>
-  <si>
-    <t>north yorkshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50226213</t>
-  </si>
-  <si>
-    <t>jan edwards</t>
-  </si>
-  <si>
-    <t>03/07/2023</t>
-  </si>
-  <si>
-    <t>07/07/2023</t>
-  </si>
-  <si>
-    <t>18/08/23</t>
-  </si>
-  <si>
-    <t>80532</t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>E06000057</t>
-  </si>
-  <si>
-    <t>926, 830, 888, 908, 878, 840, 838, 886, 885, 935</t>
-  </si>
-  <si>
-    <t>[(926, 'outstanding'), (830, 'good'), (888, nan), (908, 'good'), (878, 'inadequate'), (840, 'outstanding'), (838, 'outstanding'), (886, 'good'), (885, 'good'), (935, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>northumberland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252256</t>
-  </si>
-  <si>
-    <t>andy waugh</t>
-  </si>
-  <si>
-    <t>20/05/2024</t>
-  </si>
-  <si>
-    <t>80533</t>
-  </si>
-  <si>
-    <t>892</t>
-  </si>
-  <si>
-    <t>E06000018</t>
-  </si>
-  <si>
-    <t>330, 352, 391, 806, 380, 333, 852, 353, 373, 355</t>
-  </si>
-  <si>
-    <t>[(330, 'good'), (352, 'outstanding'), (391, 'good'), (806, nan), (380, 'requires improvement'), (333, 'good'), (852, 'good'), (353, 'good'), (373, 'good'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>nottingham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50192198</t>
-  </si>
-  <si>
-    <t>05/09/22</t>
-  </si>
-  <si>
-    <t>80534</t>
-  </si>
-  <si>
-    <t>891</t>
-  </si>
-  <si>
-    <t>E10000024</t>
-  </si>
-  <si>
-    <t>830, 935, 933, 886, 926, 937, 855, 802, 860, 888</t>
-  </si>
-  <si>
-    <t>[(830, 'good'), (935, 'requires improvement'), (933, nan), (886, 'good'), (926, 'outstanding'), (937, 'requires improvement'), (855, 'outstanding'), (802, 'requires improvement'), (860, 'requires improvement'), (888, nan)]</t>
-  </si>
-  <si>
-    <t>nottinghamshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252254</t>
-  </si>
-  <si>
-    <t>80535</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>E08000004</t>
-  </si>
-  <si>
-    <t>889, 350, 354, 380, 335, 831, 861, 331, 330, 333</t>
-  </si>
-  <si>
-    <t>[(889, 'good'), (350, 'good'), (354, 'requires improvement'), (380, 'requires improvement'), (335, 'outstanding'), (831, 'outstanding'), (861, 'requires improvement'), (331, 'outstanding'), (330, 'good'), (333, 'good')]</t>
-  </si>
-  <si>
-    <t>oldham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252252</t>
-  </si>
-  <si>
-    <t>80536</t>
-  </si>
-  <si>
-    <t>931</t>
-  </si>
-  <si>
-    <t>E10000025</t>
-  </si>
-  <si>
-    <t>873, 919, 825, 937, 916, 850, 867, 938, 869, 803</t>
-  </si>
-  <si>
-    <t>[(873, 'requires improvement'), (919, 'outstanding'), (825, 'requires improvement'), (937, 'requires improvement'), (916, 'good'), (850, 'outstanding'), (867, 'outstanding'), (938, 'requires improvement'), (869, 'good'), (803, 'good')]</t>
-  </si>
-  <si>
-    <t>oxfordshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50243682</t>
-  </si>
-  <si>
-    <t>12/02/2024</t>
-  </si>
-  <si>
-    <t>09/04/24</t>
-  </si>
-  <si>
-    <t>80537</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>E06000031</t>
-  </si>
-  <si>
-    <t>331, 831, 312, 350, 852, 335, 821, 354, 336, 883</t>
-  </si>
-  <si>
-    <t>[(331, 'outstanding'), (831, 'outstanding'), (312, 'outstanding'), (350, 'good'), (852, 'good'), (335, 'outstanding'), (821, 'good'), (354, 'requires improvement'), (336, 'good'), (883, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>peterborough</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50238583</t>
-  </si>
-  <si>
-    <t>russel breyer</t>
-  </si>
-  <si>
-    <t>27/11/2023</t>
-  </si>
-  <si>
-    <t>08/12/2023</t>
-  </si>
-  <si>
-    <t>30/01/24</t>
-  </si>
-  <si>
-    <t>80538</t>
-  </si>
-  <si>
-    <t>879</t>
-  </si>
-  <si>
-    <t>E06000026</t>
-  </si>
-  <si>
-    <t>357, 880, 894, 332, 372, 384, 382, 390, 887, 908</t>
-  </si>
-  <si>
-    <t>[(357, 'inadequate'), (880, 'good'), (894, 'outstanding'), (332, 'requires improvement'), (372, 'outstanding'), (384, 'good'), (382, 'good'), (390, 'good'), (887, 'good'), (908, 'good')]</t>
-  </si>
-  <si>
-    <t>plymouth</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50241802</t>
-  </si>
-  <si>
-    <t>22/01/2024</t>
-  </si>
-  <si>
-    <t>02/02/2024</t>
-  </si>
-  <si>
-    <t>15/03/24</t>
-  </si>
-  <si>
-    <t>80539</t>
-  </si>
-  <si>
-    <t>851</t>
-  </si>
-  <si>
-    <t>E06000044</t>
-  </si>
-  <si>
-    <t>373, 383, 382, 355, 852, 882, 879, 831, 390, 357</t>
-  </si>
-  <si>
-    <t>[(373, 'good'), (383, 'outstanding'), (382, 'good'), (355, 'good'), (852, 'good'), (882, 'good'), (879, 'requires improvement'), (831, 'outstanding'), (390, 'good'), (357, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>portsmouth</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50309432</t>
-  </si>
-  <si>
-    <t>steve bailey</t>
-  </si>
-  <si>
-    <t>06/07/2026</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>18/08/26</t>
-  </si>
-  <si>
-    <t>80540</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>E06000038</t>
-  </si>
-  <si>
-    <t>826, 302, 312, 315, 822, 306, 320, 383, 852, 310</t>
-  </si>
-  <si>
-    <t>[(826, 'good'), (302, 'good'), (312, 'outstanding'), (315, 'outstanding'), (822, 'requires improvement'), (306, 'good'), (320, 'good'), (383, 'outstanding'), (852, 'good'), (310, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>reading</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252257</t>
-  </si>
-  <si>
-    <t>80541</t>
-  </si>
-  <si>
-    <t>807</t>
-  </si>
-  <si>
-    <t>E06000003</t>
-  </si>
-  <si>
-    <t>394, 393, 805, 372, 390, 840, 370, 357, 371, 880</t>
-  </si>
-  <si>
-    <t>[(394, 'outstanding'), (393, nan), (805, 'outstanding'), (372, 'outstanding'), (390, 'good'), (840, 'outstanding'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (880, 'good')]</t>
-  </si>
-  <si>
-    <t>redcar and cleveland</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50294204</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>80542</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>E08000005</t>
-  </si>
-  <si>
-    <t>335, 357, 861, 350, 394, 371, 372, 831, 353, 355</t>
-  </si>
-  <si>
-    <t>[(335, 'outstanding'), (357, 'inadequate'), (861, 'requires improvement'), (350, 'good'), (394, 'outstanding'), (371, 'good'), (372, 'outstanding'), (831, 'outstanding'), (353, 'good'), (355, 'good')]</t>
-  </si>
-  <si>
-    <t>rochdale</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50211330</t>
-  </si>
-  <si>
     <t>03/02/2023</t>
   </si>
   <si>
@@ -3178,7 +3178,7 @@
     <t>370, 357, 371, 384, 894, 332, 807, 394, 390, 840</t>
   </si>
   <si>
-    <t>[(370, 'good'), (357, 'inadequate'), (371, 'good'), (384, 'good'), (894, 'outstanding'), (332, 'requires improvement'), (807, 'good'), (394, 'outstanding'), (390, 'good'), (840, 'outstanding')]</t>
+    <t>[(370, 'good'), (357, 'inadequate'), (371, 'good'), (384, 'good'), (894, 'outstanding'), (332, nan), (807, 'good'), (394, 'outstanding'), (390, 'good'), (840, 'outstanding')]</t>
   </si>
   <si>
     <t>rotherham</t>
@@ -3223,7 +3223,7 @@
     <t>319, 315, 919, 305, 800, 868, 358, 318, 936, 825</t>
   </si>
   <si>
-    <t>[(319, 'good'), (315, 'outstanding'), (919, 'outstanding'), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, nan), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
+    <t>[(319, 'good'), (315, 'outstanding'), (919, nan), (305, 'outstanding'), (800, 'good'), (868, 'good'), (358, nan), (318, 'outstanding'), (936, 'good'), (825, 'requires improvement')]</t>
   </si>
   <si>
     <t>kingston upon thames</t>
@@ -3244,7 +3244,7 @@
     <t>936, 825, 872, 358, 919, 869, 305, 823, 931, 867</t>
   </si>
   <si>
-    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
+    <t>[(936, 'good'), (825, 'requires improvement'), (872, 'requires improvement'), (358, nan), (919, nan), (869, 'good'), (305, 'outstanding'), (823, 'good'), (931, 'good'), (867, 'outstanding')]</t>
   </si>
   <si>
     <t>windsor &amp; maidenhead</t>
@@ -3430,7 +3430,7 @@
     <t>slough</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50211331</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50309683</t>
   </si>
   <si>
     <t>80554</t>
@@ -3445,7 +3445,7 @@
     <t>356, 896, 937, 877, 886, 916, 802, 895, 881, 919</t>
   </si>
   <si>
-    <t>[(356, 'requires improvement'), (896, 'requires improvement'), (937, 'requires improvement'), (877, 'good'), (886, 'good'), (916, 'good'), (802, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (919, 'outstanding')]</t>
+    <t>[(356, 'requires improvement'), (896, 'requires improvement'), (937, 'requires improvement'), (877, 'good'), (886, 'good'), (916, 'good'), (802, 'requires improvement'), (895, 'inadequate'), (881, 'outstanding'), (919, nan)]</t>
   </si>
   <si>
     <t>solihull</t>
@@ -3631,7 +3631,7 @@
     <t>334, 358, 896, 916, 919, 938, 937, 802, 803, 873</t>
   </si>
   <si>
-    <t>[(334, 'good'), (358, nan), (896, 'requires improvement'), (916, 'good'), (919, 'outstanding'), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
+    <t>[(334, 'good'), (358, nan), (896, 'requires improvement'), (916, 'good'), (919, nan), (938, 'requires improvement'), (937, 'requires improvement'), (802, 'requires improvement'), (803, 'good'), (873, 'requires improvement')]</t>
   </si>
   <si>
     <t>stockport</t>
@@ -3655,7 +3655,7 @@
     <t>841, 332, 888, 390, 384, 351, 840, 372, 894, 344</t>
   </si>
   <si>
-    <t>[(841, 'outstanding'), (332, 'requires improvement'), (888, nan), (390, 'good'), (384, 'good'), (351, 'requires improvement'), (840, 'outstanding'), (372, 'outstanding'), (894, 'outstanding'), (344, 'requires improvement')]</t>
+    <t>[(841, 'outstanding'), (332, nan), (888, nan), (390, 'good'), (384, 'good'), (351, 'requires improvement'), (840, 'outstanding'), (372, 'outstanding'), (894, 'outstanding'), (344, 'requires improvement')]</t>
   </si>
   <si>
     <t>stockton-on-tees</t>
@@ -3757,7 +3757,7 @@
     <t>868, 825, 358, 919, 869, 823, 872, 931, 867, 873</t>
   </si>
   <si>
-    <t>[(868, 'good'), (825, 'requires improvement'), (358, nan), (919, 'outstanding'), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
+    <t>[(868, 'good'), (825, 'requires improvement'), (358, nan), (919, nan), (869, 'good'), (823, 'good'), (872, 'requires improvement'), (931, 'good'), (867, 'outstanding'), (873, 'requires improvement')]</t>
   </si>
   <si>
     <t>surrey</t>
@@ -3799,7 +3799,7 @@
     <t>372, 390, 354, 370, 384, 332, 894, 879, 394, 880</t>
   </si>
   <si>
-    <t>[(372, 'outstanding'), (390, 'good'), (354, 'requires improvement'), (370, 'good'), (384, 'good'), (332, 'requires improvement'), (894, 'outstanding'), (879, 'requires improvement'), (394, 'outstanding'), (880, 'good')]</t>
+    <t>[(372, 'outstanding'), (390, 'good'), (354, 'requires improvement'), (370, 'good'), (384, 'good'), (332, nan), (894, 'outstanding'), (879, 'requires improvement'), (394, 'outstanding'), (880, 'good')]</t>
   </si>
   <si>
     <t>tameside</t>
@@ -3823,7 +3823,7 @@
     <t>384, 372, 332, 370, 357, 371, 841, 390, 879, 808</t>
   </si>
   <si>
-    <t>[(384, 'good'), (372, 'outstanding'), (332, 'requires improvement'), (370, 'good'), (357, 'inadequate'), (371, 'good'), (841, 'outstanding'), (390, 'good'), (879, 'requires improvement'), (808, 'requires improvement')]</t>
+    <t>[(384, 'good'), (372, 'outstanding'), (332, nan), (370, 'good'), (357, 'inadequate'), (371, 'good'), (841, 'outstanding'), (390, 'good'), (879, 'requires improvement'), (808, 'requires improvement')]</t>
   </si>
   <si>
     <t>telford &amp; wrekin</t>
@@ -3847,7 +3847,7 @@
     <t>866, 303, 311, 887, 940, 822, 941, 332, 925, 935</t>
   </si>
   <si>
-    <t>[(866, 'inadequate'), (303, 'outstanding'), (311, 'inadequate'), (887, 'good'), (940, nan), (822, 'requires improvement'), (941, nan), (332, 'requires improvement'), (925, 'outstanding'), (935, 'requires improvement')]</t>
+    <t>[(866, 'inadequate'), (303, 'outstanding'), (311, 'inadequate'), (887, 'good'), (940, nan), (822, 'requires improvement'), (941, nan), (332, nan), (925, 'outstanding'), (935, 'requires improvement')]</t>
   </si>
   <si>
     <t>thurrock</t>
@@ -3898,7 +3898,7 @@
     <t>919, 356, 825, 931, 936, 305, 895, 873, 916, 334</t>
   </si>
   <si>
-    <t>[(919, 'outstanding'), (356, 'requires improvement'), (825, 'requires improvement'), (931, 'good'), (936, 'good'), (305, 'outstanding'), (895, 'inadequate'), (873, 'requires improvement'), (916, 'good'), (334, 'good')]</t>
+    <t>[(919, nan), (356, 'requires improvement'), (825, 'requires improvement'), (931, 'good'), (936, 'good'), (305, 'outstanding'), (895, 'inadequate'), (873, 'requires improvement'), (916, 'good'), (334, 'good')]</t>
   </si>
   <si>
     <t>trafford</t>
@@ -4000,7 +4000,7 @@
     <t>825, 850, 931, 867, 919, 873, 823, 865, 916, 305</t>
   </si>
   <si>
-    <t>[(825, 'requires improvement'), (850, 'outstanding'), (931, 'good'), (867, 'outstanding'), (919, 'outstanding'), (873, 'requires improvement'), (823, 'good'), (865, 'outstanding'), (916, 'good'), (305, 'outstanding')]</t>
+    <t>[(825, 'requires improvement'), (850, 'outstanding'), (931, 'good'), (867, 'outstanding'), (919, nan), (873, 'requires improvement'), (823, 'good'), (865, 'outstanding'), (916, 'good'), (305, 'outstanding')]</t>
   </si>
   <si>
     <t>west berkshire</t>
@@ -4051,7 +4051,7 @@
     <t>916, 881, 850, 919, 937, 865, 802, 931, 803, 878</t>
   </si>
   <si>
-    <t>[(916, 'good'), (881, 'outstanding'), (850, 'outstanding'), (919, 'outstanding'), (937, 'requires improvement'), (865, 'outstanding'), (802, 'requires improvement'), (931, 'good'), (803, 'good'), (878, 'inadequate')]</t>
+    <t>[(916, 'good'), (881, 'outstanding'), (850, 'outstanding'), (919, nan), (937, 'requires improvement'), (865, 'outstanding'), (802, 'requires improvement'), (931, 'good'), (803, 'good'), (878, 'inadequate')]</t>
   </si>
   <si>
     <t>west sussex</t>
@@ -4093,7 +4093,7 @@
     <t>888, 925, 343, 877, 860, 332, 929, 884, 808, 893</t>
   </si>
   <si>
-    <t>[(888, nan), (925, 'outstanding'), (343, 'good'), (877, 'good'), (860, 'requires improvement'), (332, 'requires improvement'), (929, 'outstanding'), (884, 'good'), (808, 'requires improvement'), (893, 'outstanding')]</t>
+    <t>[(888, nan), (925, 'outstanding'), (343, 'good'), (877, 'good'), (860, 'requires improvement'), (332, nan), (929, 'outstanding'), (884, 'good'), (808, 'requires improvement'), (893, 'outstanding')]</t>
   </si>
   <si>
     <t>wigan</t>
@@ -4180,7 +4180,7 @@
     <t>868, 936, 825, 869, 305, 358, 318, 919, 867, 823</t>
   </si>
   <si>
-    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, nan), (318, 'outstanding'), (919, 'outstanding'), (867, 'outstanding'), (823, 'good')]</t>
+    <t>[(868, 'good'), (936, 'good'), (825, 'requires improvement'), (869, 'good'), (305, 'outstanding'), (358, nan), (318, 'outstanding'), (919, nan), (867, 'outstanding'), (823, 'good')]</t>
   </si>
   <si>
     <t>wokingham</t>
@@ -5043,96 +5043,96 @@
         <v>14</v>
       </c>
       <c r="T6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>56</v>
       </c>
       <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
         <v>69</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>70</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" t="s">
         <v>73</v>
-      </c>
-      <c r="I7" t="s">
-        <v>74</v>
       </c>
       <c r="J7" t="s">
         <v>48</v>
       </c>
       <c r="K7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
         <v>75</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>76</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>77</v>
-      </c>
-      <c r="N7" t="s">
-        <v>78</v>
       </c>
       <c r="O7" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80431_blackpool", ".\export_data\inspection_reports\80431_blackpool")</f>
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="s">
         <v>8</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
       </c>
       <c r="C8" t="s">
         <v>56</v>
       </c>
       <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
         <v>82</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>83</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -5141,7 +5141,7 @@
         <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L8" t="s">
         <v>11</v>
@@ -5169,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="T8" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -5261,7 +5261,7 @@
         <v>105</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
@@ -5283,19 +5283,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T10" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -5324,7 +5324,7 @@
         <v>116</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J11" t="s">
         <v>117</v>
@@ -5340,16 +5340,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q11" t="s">
         <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s">
         <v>120</v>
@@ -5478,7 +5478,7 @@
         <v>14</v>
       </c>
       <c r="T13" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -5541,7 +5541,7 @@
         <v>14</v>
       </c>
       <c r="T14" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -5604,7 +5604,7 @@
         <v>8</v>
       </c>
       <c r="T15" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -5639,7 +5639,7 @@
         <v>48</v>
       </c>
       <c r="K16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L16" t="s">
         <v>170</v>
@@ -5667,7 +5667,7 @@
         <v>14</v>
       </c>
       <c r="T16" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -5730,7 +5730,7 @@
         <v>8</v>
       </c>
       <c r="T17" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -5793,7 +5793,7 @@
         <v>189</v>
       </c>
       <c r="T18" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -5856,7 +5856,7 @@
         <v>14</v>
       </c>
       <c r="T19" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -5919,7 +5919,7 @@
         <v>8</v>
       </c>
       <c r="T20" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -5948,7 +5948,7 @@
         <v>222</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s">
         <v>9</v>
@@ -5970,16 +5970,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q21" t="s">
         <v>8</v>
       </c>
       <c r="R21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T21" t="s">
         <v>227</v>
@@ -6039,7 +6039,7 @@
         <v>8</v>
       </c>
       <c r="R22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S22" t="s">
         <v>14</v>
@@ -6074,7 +6074,7 @@
         <v>244</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s">
         <v>48</v>
@@ -6096,19 +6096,19 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T23" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -6168,10 +6168,10 @@
         <v>8</v>
       </c>
       <c r="S24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T24" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -6263,7 +6263,7 @@
         <v>276</v>
       </c>
       <c r="I26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -6285,19 +6285,19 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q26" t="s">
         <v>8</v>
       </c>
       <c r="R26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T26" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -6332,7 +6332,7 @@
         <v>48</v>
       </c>
       <c r="K27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s">
         <v>288</v>
@@ -6360,7 +6360,7 @@
         <v>8</v>
       </c>
       <c r="T27" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -6389,7 +6389,7 @@
         <v>298</v>
       </c>
       <c r="I28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s">
         <v>9</v>
@@ -6411,19 +6411,19 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q28" t="s">
         <v>8</v>
       </c>
       <c r="R28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T28" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -6452,13 +6452,13 @@
         <v>309</v>
       </c>
       <c r="I29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s">
         <v>9</v>
       </c>
       <c r="K29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L29" t="s">
         <v>310</v>
@@ -6474,19 +6474,19 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T29" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -6675,7 +6675,7 @@
         <v>14</v>
       </c>
       <c r="T32" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -6704,7 +6704,7 @@
         <v>350</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s">
         <v>9</v>
@@ -6726,19 +6726,19 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s">
         <v>8</v>
       </c>
       <c r="T33" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -6767,13 +6767,13 @@
         <v>360</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s">
         <v>48</v>
       </c>
       <c r="K34" t="s">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s">
         <v>361</v>
@@ -6789,16 +6789,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="Q34" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="R34" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="S34" t="s">
-        <v>364</v>
+        <v>189</v>
       </c>
       <c r="T34" t="s">
         <v>53</v>
@@ -6806,37 +6806,37 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
+        <v>364</v>
+      </c>
+      <c r="B35" t="s">
         <v>365</v>
-      </c>
-      <c r="B35" t="s">
-        <v>366</v>
       </c>
       <c r="C35" t="s">
         <v>293</v>
       </c>
       <c r="D35" t="s">
+        <v>366</v>
+      </c>
+      <c r="E35" t="s">
         <v>367</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>368</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>369</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="I35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s">
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s">
         <v>235</v>
@@ -6852,45 +6852,45 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q35" t="s">
         <v>8</v>
       </c>
       <c r="R35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T35" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
+        <v>372</v>
+      </c>
+      <c r="B36" t="s">
         <v>373</v>
-      </c>
-      <c r="B36" t="s">
-        <v>374</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
+        <v>374</v>
+      </c>
+      <c r="E36" t="s">
         <v>375</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>376</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>377</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="I36" t="s">
         <v>8</v>
@@ -6899,16 +6899,16 @@
         <v>48</v>
       </c>
       <c r="K36" t="s">
+        <v>379</v>
+      </c>
+      <c r="L36" t="s">
         <v>380</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>381</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>382</v>
-      </c>
-      <c r="N36" t="s">
-        <v>383</v>
       </c>
       <c r="O36" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80466_east riding of yorkshire", ".\export_data\inspection_reports\80466_east riding of yorkshire")</f>
@@ -6932,28 +6932,28 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
+        <v>383</v>
+      </c>
+      <c r="B37" t="s">
         <v>384</v>
-      </c>
-      <c r="B37" t="s">
-        <v>385</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
       </c>
       <c r="D37" t="s">
+        <v>385</v>
+      </c>
+      <c r="E37" t="s">
         <v>386</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>387</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>388</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="I37" t="s">
         <v>8</v>
@@ -6962,16 +6962,16 @@
         <v>9</v>
       </c>
       <c r="K37" t="s">
+        <v>390</v>
+      </c>
+      <c r="L37" t="s">
         <v>391</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>392</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>393</v>
-      </c>
-      <c r="N37" t="s">
-        <v>394</v>
       </c>
       <c r="O37" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80467_east sussex", ".\export_data\inspection_reports\80467_east sussex")</f>
@@ -6984,73 +6984,73 @@
         <v>8</v>
       </c>
       <c r="R37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s">
         <v>8</v>
       </c>
       <c r="T37" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B38" t="s">
         <v>396</v>
-      </c>
-      <c r="B38" t="s">
-        <v>397</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>397</v>
+      </c>
+      <c r="E38" t="s">
         <v>398</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>399</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>400</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
       </c>
       <c r="K38" t="s">
+        <v>402</v>
+      </c>
+      <c r="L38" t="s">
         <v>403</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>404</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>405</v>
-      </c>
-      <c r="N38" t="s">
-        <v>406</v>
       </c>
       <c r="O38" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80468_essex", ".\export_data\inspection_reports\80468_essex")</f>
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T38" t="s">
         <v>15</v>
@@ -7058,28 +7058,28 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
+        <v>406</v>
+      </c>
+      <c r="B39" t="s">
         <v>407</v>
-      </c>
-      <c r="B39" t="s">
-        <v>408</v>
       </c>
       <c r="C39" t="s">
         <v>293</v>
       </c>
       <c r="D39" t="s">
+        <v>408</v>
+      </c>
+      <c r="E39" t="s">
         <v>409</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>410</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>411</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="I39" t="s">
         <v>8</v>
@@ -7094,7 +7094,7 @@
         <v>95</v>
       </c>
       <c r="M39" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N39" t="s">
         <v>97</v>
@@ -7116,33 +7116,33 @@
         <v>8</v>
       </c>
       <c r="T39" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" t="s">
         <v>415</v>
-      </c>
-      <c r="B40" t="s">
-        <v>416</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
+        <v>416</v>
+      </c>
+      <c r="E40" t="s">
         <v>417</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>418</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>419</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="I40" t="s">
         <v>8</v>
@@ -7160,52 +7160,52 @@
         <v>151</v>
       </c>
       <c r="N40" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O40" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80470_gloucestershire", ".\export_data\inspection_reports\80470_gloucestershire")</f>
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q40" t="s">
         <v>8</v>
       </c>
       <c r="R40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S40" t="s">
         <v>8</v>
       </c>
       <c r="T40" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
+        <v>422</v>
+      </c>
+      <c r="B41" t="s">
         <v>423</v>
-      </c>
-      <c r="B41" t="s">
-        <v>424</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
       </c>
       <c r="D41" t="s">
+        <v>424</v>
+      </c>
+      <c r="E41" t="s">
         <v>425</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>426</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>427</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="I41" t="s">
         <v>189</v>
@@ -7214,16 +7214,16 @@
         <v>48</v>
       </c>
       <c r="K41" t="s">
+        <v>429</v>
+      </c>
+      <c r="L41" t="s">
         <v>430</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>431</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>432</v>
-      </c>
-      <c r="N41" t="s">
-        <v>433</v>
       </c>
       <c r="O41" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80471_halton", ".\export_data\inspection_reports\80471_halton")</f>
@@ -7242,64 +7242,64 @@
         <v>189</v>
       </c>
       <c r="T41" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
+        <v>434</v>
+      </c>
+      <c r="B42" t="s">
         <v>435</v>
-      </c>
-      <c r="B42" t="s">
-        <v>436</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
       </c>
       <c r="D42" t="s">
+        <v>436</v>
+      </c>
+      <c r="E42" t="s">
         <v>437</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>438</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>439</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="I42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L42" t="s">
+        <v>441</v>
+      </c>
+      <c r="M42" t="s">
         <v>442</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>443</v>
-      </c>
-      <c r="N42" t="s">
-        <v>444</v>
       </c>
       <c r="O42" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80472_hampshire", ".\export_data\inspection_reports\80472_hampshire")</f>
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S42" t="s">
         <v>8</v>
@@ -7310,43 +7310,43 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
+        <v>444</v>
+      </c>
+      <c r="B43" t="s">
         <v>445</v>
-      </c>
-      <c r="B43" t="s">
-        <v>446</v>
       </c>
       <c r="C43" t="s">
         <v>293</v>
       </c>
       <c r="D43" t="s">
+        <v>446</v>
+      </c>
+      <c r="E43" t="s">
         <v>447</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>448</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>449</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>451</v>
-      </c>
       <c r="I43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L43" t="s">
+        <v>451</v>
+      </c>
+      <c r="M43" t="s">
         <v>452</v>
-      </c>
-      <c r="M43" t="s">
-        <v>453</v>
       </c>
       <c r="N43" t="s">
         <v>119</v>
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S43" t="s">
         <v>8</v>
@@ -7373,28 +7373,28 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
+        <v>453</v>
+      </c>
+      <c r="B44" t="s">
         <v>454</v>
-      </c>
-      <c r="B44" t="s">
-        <v>455</v>
       </c>
       <c r="C44" t="s">
         <v>42</v>
       </c>
       <c r="D44" t="s">
+        <v>455</v>
+      </c>
+      <c r="E44" t="s">
         <v>456</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>457</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>458</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="I44" t="s">
         <v>8</v>
@@ -7406,20 +7406,20 @@
         <v>150</v>
       </c>
       <c r="L44" t="s">
+        <v>460</v>
+      </c>
+      <c r="M44" t="s">
         <v>461</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>462</v>
-      </c>
-      <c r="N44" t="s">
-        <v>463</v>
       </c>
       <c r="O44" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80474_herefordshire", ".\export_data\inspection_reports\80474_herefordshire")</f>
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q44" t="s">
         <v>8</v>
@@ -7431,70 +7431,70 @@
         <v>8</v>
       </c>
       <c r="T44" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
+        <v>463</v>
+      </c>
+      <c r="B45" t="s">
         <v>464</v>
-      </c>
-      <c r="B45" t="s">
-        <v>465</v>
       </c>
       <c r="C45" t="s">
         <v>31</v>
       </c>
       <c r="D45" t="s">
+        <v>465</v>
+      </c>
+      <c r="E45" t="s">
         <v>466</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>467</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>468</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>470</v>
-      </c>
       <c r="I45" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J45" t="s">
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="L45" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M45" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="N45" t="s">
-        <v>131</v>
+        <v>363</v>
       </c>
       <c r="O45" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80475_hertfordshire", ".\export_data\inspection_reports\80475_hertfordshire")</f>
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="Q45" t="s">
-        <v>8</v>
+        <v>471</v>
       </c>
       <c r="R45" t="s">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="S45" t="s">
-        <v>8</v>
+        <v>471</v>
       </c>
       <c r="T45" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -7614,13 +7614,13 @@
         <v>8</v>
       </c>
       <c r="R47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S47" t="s">
         <v>14</v>
       </c>
       <c r="T47" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -7671,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q48" t="s">
         <v>8</v>
@@ -7680,10 +7680,10 @@
         <v>8</v>
       </c>
       <c r="S48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T48" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -7746,7 +7746,7 @@
         <v>14</v>
       </c>
       <c r="T49" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -7838,7 +7838,7 @@
         <v>526</v>
       </c>
       <c r="I51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J51" t="s">
         <v>48</v>
@@ -7860,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q51" t="s">
         <v>8</v>
@@ -7869,10 +7869,10 @@
         <v>8</v>
       </c>
       <c r="S51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T51" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -7901,7 +7901,7 @@
         <v>536</v>
       </c>
       <c r="I52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -7923,19 +7923,19 @@
         <v>0</v>
       </c>
       <c r="P52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q52" t="s">
         <v>8</v>
       </c>
       <c r="R52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T52" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -7970,7 +7970,7 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s">
         <v>224</v>
@@ -7998,7 +7998,7 @@
         <v>14</v>
       </c>
       <c r="T53" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -8027,13 +8027,13 @@
         <v>553</v>
       </c>
       <c r="I54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J54" t="s">
         <v>48</v>
       </c>
       <c r="K54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L54" t="s">
         <v>554</v>
@@ -8042,26 +8042,26 @@
         <v>555</v>
       </c>
       <c r="N54" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O54" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80483_leicestershire", ".\export_data\inspection_reports\80483_leicestershire")</f>
         <v>0</v>
       </c>
       <c r="P54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q54" t="s">
         <v>8</v>
       </c>
       <c r="R54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T54" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -8090,13 +8090,13 @@
         <v>562</v>
       </c>
       <c r="I55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s">
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L55" t="s">
         <v>563</v>
@@ -8112,19 +8112,19 @@
         <v>0</v>
       </c>
       <c r="P55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S55" t="s">
         <v>8</v>
       </c>
       <c r="T55" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -8153,7 +8153,7 @@
         <v>572</v>
       </c>
       <c r="I56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J56" t="s">
         <v>48</v>
@@ -8187,7 +8187,7 @@
         <v>14</v>
       </c>
       <c r="T56" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -8250,7 +8250,7 @@
         <v>8</v>
       </c>
       <c r="T57" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -8288,13 +8288,13 @@
         <v>106</v>
       </c>
       <c r="L58" t="s">
+        <v>441</v>
+      </c>
+      <c r="M58" t="s">
         <v>442</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" t="s">
         <v>443</v>
-      </c>
-      <c r="N58" t="s">
-        <v>444</v>
       </c>
       <c r="O58" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80487_barnet", ".\export_data\inspection_reports\80487_barnet")</f>
@@ -8307,13 +8307,13 @@
         <v>8</v>
       </c>
       <c r="R58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S58" t="s">
         <v>8</v>
       </c>
       <c r="T58" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -8342,29 +8342,29 @@
         <v>597</v>
       </c>
       <c r="I59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J59" t="s">
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L59" t="s">
         <v>598</v>
       </c>
       <c r="M59" t="s">
+        <v>381</v>
+      </c>
+      <c r="N59" t="s">
         <v>382</v>
-      </c>
-      <c r="N59" t="s">
-        <v>383</v>
       </c>
       <c r="O59" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80488_bexley", ".\export_data\inspection_reports\80488_bexley")</f>
         <v>0</v>
       </c>
       <c r="P59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q59" t="s">
         <v>8</v>
@@ -8373,10 +8373,10 @@
         <v>8</v>
       </c>
       <c r="S59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -8405,7 +8405,7 @@
         <v>605</v>
       </c>
       <c r="I60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -8468,7 +8468,7 @@
         <v>616</v>
       </c>
       <c r="I61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J61" t="s">
         <v>9</v>
@@ -8490,19 +8490,19 @@
         <v>0</v>
       </c>
       <c r="P61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T61" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -8531,7 +8531,7 @@
         <v>626</v>
       </c>
       <c r="I62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -8553,19 +8553,19 @@
         <v>0</v>
       </c>
       <c r="P62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T62" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -8663,7 +8663,7 @@
         <v>48</v>
       </c>
       <c r="K64" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L64" t="s">
         <v>554</v>
@@ -8672,7 +8672,7 @@
         <v>555</v>
       </c>
       <c r="N64" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O64" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80493_ealing", ".\export_data\inspection_reports\80493_ealing")</f>
@@ -8691,7 +8691,7 @@
         <v>8</v>
       </c>
       <c r="T64" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -8748,7 +8748,7 @@
         <v>8</v>
       </c>
       <c r="R65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S65" t="s">
         <v>8</v>
@@ -8783,13 +8783,13 @@
         <v>660</v>
       </c>
       <c r="I66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s">
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L66" t="s">
         <v>661</v>
@@ -8805,19 +8805,19 @@
         <v>0</v>
       </c>
       <c r="P66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q66" t="s">
         <v>8</v>
       </c>
       <c r="R66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T66" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -8852,7 +8852,7 @@
         <v>48</v>
       </c>
       <c r="K67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L67" t="s">
         <v>257</v>
@@ -8880,7 +8880,7 @@
         <v>14</v>
       </c>
       <c r="T67" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -8909,7 +8909,7 @@
         <v>679</v>
       </c>
       <c r="I68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J68" t="s">
         <v>9</v>
@@ -8931,16 +8931,16 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q68" t="s">
         <v>8</v>
       </c>
       <c r="R68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T68" t="s">
         <v>227</v>
@@ -8972,7 +8972,7 @@
         <v>687</v>
       </c>
       <c r="I69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q69" t="s">
         <v>8</v>
@@ -9003,7 +9003,7 @@
         <v>8</v>
       </c>
       <c r="S69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T69" t="s">
         <v>227</v>
@@ -9107,7 +9107,7 @@
         <v>617</v>
       </c>
       <c r="L71" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M71" t="s">
         <v>706</v>
@@ -9132,7 +9132,7 @@
         <v>14</v>
       </c>
       <c r="T71" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -9161,7 +9161,7 @@
         <v>714</v>
       </c>
       <c r="I72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J72" t="s">
         <v>9</v>
@@ -9183,13 +9183,13 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q72" t="s">
         <v>8</v>
       </c>
       <c r="R72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S72" t="s">
         <v>8</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q73" t="s">
         <v>8</v>
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="T73" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -9287,7 +9287,7 @@
         <v>734</v>
       </c>
       <c r="I74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J74" t="s">
         <v>9</v>
@@ -9299,7 +9299,7 @@
         <v>95</v>
       </c>
       <c r="M74" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N74" t="s">
         <v>97</v>
@@ -9309,19 +9309,19 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T74" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -9381,10 +9381,10 @@
         <v>8</v>
       </c>
       <c r="S75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T75" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -9425,7 +9425,7 @@
         <v>752</v>
       </c>
       <c r="M76" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N76" t="s">
         <v>753</v>
@@ -9447,7 +9447,7 @@
         <v>8</v>
       </c>
       <c r="T76" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -9476,7 +9476,7 @@
         <v>760</v>
       </c>
       <c r="I77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J77" t="s">
         <v>9</v>
@@ -9498,19 +9498,19 @@
         <v>0</v>
       </c>
       <c r="P77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q77" t="s">
         <v>8</v>
       </c>
       <c r="R77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T77" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -9539,41 +9539,41 @@
         <v>767</v>
       </c>
       <c r="I78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J78" t="s">
         <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L78" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M78" t="s">
         <v>768</v>
       </c>
       <c r="N78" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="O78" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80511_newham", ".\export_data\inspection_reports\80511_newham")</f>
         <v>0</v>
       </c>
       <c r="P78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T78" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -9602,7 +9602,7 @@
         <v>775</v>
       </c>
       <c r="I79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J79" t="s">
         <v>9</v>
@@ -9611,32 +9611,32 @@
         <v>776</v>
       </c>
       <c r="L79" t="s">
+        <v>441</v>
+      </c>
+      <c r="M79" t="s">
         <v>442</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>443</v>
-      </c>
-      <c r="N79" t="s">
-        <v>444</v>
       </c>
       <c r="O79" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80512_redbridge", ".\export_data\inspection_reports\80512_redbridge")</f>
         <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T79" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -9665,7 +9665,7 @@
         <v>783</v>
       </c>
       <c r="I80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J80" t="s">
         <v>9</v>
@@ -9687,19 +9687,19 @@
         <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q80" t="s">
         <v>8</v>
       </c>
       <c r="R80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T80" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -9762,7 +9762,7 @@
         <v>8</v>
       </c>
       <c r="T81" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -9825,7 +9825,7 @@
         <v>8</v>
       </c>
       <c r="T82" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -9854,7 +9854,7 @@
         <v>805</v>
       </c>
       <c r="I83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J83" t="s">
         <v>9</v>
@@ -9876,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q83" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>8</v>
       </c>
       <c r="S83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T83" t="s">
         <v>28</v>
@@ -9945,7 +9945,7 @@
         <v>8</v>
       </c>
       <c r="R84" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S84" t="s">
         <v>8</v>
@@ -9980,7 +9980,7 @@
         <v>823</v>
       </c>
       <c r="I85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J85" t="s">
         <v>9</v>
@@ -10002,16 +10002,16 @@
         <v>0</v>
       </c>
       <c r="P85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T85" t="s">
         <v>15</v>
@@ -10043,7 +10043,7 @@
         <v>831</v>
       </c>
       <c r="I86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J86" t="s">
         <v>9</v>
@@ -10065,19 +10065,19 @@
         <v>0</v>
       </c>
       <c r="P86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T86" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -10140,7 +10140,7 @@
         <v>14</v>
       </c>
       <c r="T87" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -10169,7 +10169,7 @@
         <v>847</v>
       </c>
       <c r="I88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s">
         <v>48</v>
@@ -10191,19 +10191,19 @@
         <v>0</v>
       </c>
       <c r="P88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q88" t="s">
         <v>8</v>
       </c>
       <c r="R88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T88" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -10214,7 +10214,7 @@
         <v>852</v>
       </c>
       <c r="C89" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
         <v>853</v>
@@ -10295,7 +10295,7 @@
         <v>867</v>
       </c>
       <c r="I90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J90" t="s">
         <v>48</v>
@@ -10304,13 +10304,13 @@
         <v>868</v>
       </c>
       <c r="L90" t="s">
+        <v>75</v>
+      </c>
+      <c r="M90" t="s">
         <v>76</v>
       </c>
-      <c r="M90" t="s">
+      <c r="N90" t="s">
         <v>77</v>
-      </c>
-      <c r="N90" t="s">
-        <v>78</v>
       </c>
       <c r="O90" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80523_middlesbrough", ".\export_data\inspection_reports\80523_middlesbrough")</f>
@@ -10389,10 +10389,10 @@
         <v>8</v>
       </c>
       <c r="S91" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T91" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -10446,7 +10446,7 @@
         <v>8</v>
       </c>
       <c r="Q92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R92" t="s">
         <v>8</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="T92" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -10484,7 +10484,7 @@
         <v>895</v>
       </c>
       <c r="I93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J93" t="s">
         <v>9</v>
@@ -10506,19 +10506,19 @@
         <v>0</v>
       </c>
       <c r="P93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T93" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -10553,7 +10553,7 @@
         <v>48</v>
       </c>
       <c r="K94" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L94" t="s">
         <v>37</v>
@@ -10569,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q94" t="s">
         <v>8</v>
@@ -10581,7 +10581,7 @@
         <v>8</v>
       </c>
       <c r="T94" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -10610,7 +10610,7 @@
         <v>914</v>
       </c>
       <c r="I95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J95" t="s">
         <v>9</v>
@@ -10632,19 +10632,19 @@
         <v>0</v>
       </c>
       <c r="P95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S95" t="s">
         <v>8</v>
       </c>
       <c r="T95" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -10673,7 +10673,7 @@
         <v>924</v>
       </c>
       <c r="I96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J96" t="s">
         <v>48</v>
@@ -10695,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q96" t="s">
         <v>8</v>
@@ -10799,13 +10799,13 @@
         <v>942</v>
       </c>
       <c r="I98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
       </c>
       <c r="K98" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L98" t="s">
         <v>806</v>
@@ -10821,19 +10821,19 @@
         <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T98" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -10862,7 +10862,7 @@
         <v>949</v>
       </c>
       <c r="I99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J99" t="s">
         <v>9</v>
@@ -10884,16 +10884,16 @@
         <v>0</v>
       </c>
       <c r="P99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T99" t="s">
         <v>120</v>
@@ -10925,7 +10925,7 @@
         <v>960</v>
       </c>
       <c r="I100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s">
         <v>9</v>
@@ -10937,20 +10937,20 @@
         <v>962</v>
       </c>
       <c r="M100" t="s">
+        <v>431</v>
+      </c>
+      <c r="N100" t="s">
         <v>432</v>
-      </c>
-      <c r="N100" t="s">
-        <v>433</v>
       </c>
       <c r="O100" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80532_northumberland", ".\export_data\inspection_reports\80532_northumberland")</f>
         <v>0</v>
       </c>
       <c r="P100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R100" t="s">
         <v>8</v>
@@ -10959,7 +10959,7 @@
         <v>8</v>
       </c>
       <c r="T100" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -11016,7 +11016,7 @@
         <v>189</v>
       </c>
       <c r="T101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -11057,17 +11057,17 @@
         <v>962</v>
       </c>
       <c r="M102" t="s">
+        <v>431</v>
+      </c>
+      <c r="N102" t="s">
         <v>432</v>
-      </c>
-      <c r="N102" t="s">
-        <v>433</v>
       </c>
       <c r="O102" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80534_nottinghamshire", ".\export_data\inspection_reports\80534_nottinghamshire")</f>
         <v>0</v>
       </c>
       <c r="P102" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q102" t="s">
         <v>8</v>
@@ -11079,7 +11079,7 @@
         <v>8</v>
       </c>
       <c r="T102" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -11117,13 +11117,13 @@
         <v>516</v>
       </c>
       <c r="L103" t="s">
+        <v>430</v>
+      </c>
+      <c r="M103" t="s">
         <v>431</v>
       </c>
-      <c r="M103" t="s">
+      <c r="N103" t="s">
         <v>432</v>
-      </c>
-      <c r="N103" t="s">
-        <v>433</v>
       </c>
       <c r="O103" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80535_oldham", ".\export_data\inspection_reports\80535_oldham")</f>
@@ -11205,7 +11205,7 @@
         <v>8</v>
       </c>
       <c r="T104" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -11268,7 +11268,7 @@
         <v>189</v>
       </c>
       <c r="T105" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -11360,7 +11360,7 @@
         <v>1021</v>
       </c>
       <c r="I107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J107" t="s">
         <v>9</v>
@@ -11369,58 +11369,58 @@
         <v>1022</v>
       </c>
       <c r="L107" t="s">
+        <v>361</v>
+      </c>
+      <c r="M107" t="s">
         <v>1023</v>
       </c>
-      <c r="M107" t="s">
+      <c r="N107" t="s">
         <v>1024</v>
-      </c>
-      <c r="N107" t="s">
-        <v>1025</v>
       </c>
       <c r="O107" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80539_portsmouth", ".\export_data\inspection_reports\80539_portsmouth")</f>
         <v>0</v>
       </c>
       <c r="P107" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q107" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R107" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S107" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T107" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B108" t="s">
         <v>1026</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1027</v>
       </c>
       <c r="C108" t="s">
         <v>100</v>
       </c>
       <c r="D108" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E108" t="s">
         <v>1028</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>1029</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>1030</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" s="2" t="s">
         <v>1031</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>1032</v>
       </c>
       <c r="I108" t="s">
         <v>14</v>
@@ -11438,7 +11438,7 @@
         <v>555</v>
       </c>
       <c r="N108" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O108" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80540_reading", ".\export_data\inspection_reports\80540_reading")</f>
@@ -11462,28 +11462,28 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B109" t="s">
         <v>1033</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1034</v>
       </c>
       <c r="C109" t="s">
         <v>293</v>
       </c>
       <c r="D109" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E109" t="s">
         <v>1035</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>1036</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>1037</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>1039</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -11495,7 +11495,7 @@
         <v>245</v>
       </c>
       <c r="L109" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="M109" t="s">
         <v>108</v>
@@ -11520,33 +11520,33 @@
         <v>8</v>
       </c>
       <c r="T109" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B110" t="s">
         <v>1041</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1042</v>
       </c>
       <c r="C110" t="s">
         <v>56</v>
       </c>
       <c r="D110" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E110" t="s">
         <v>1043</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>1044</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>1045</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="I110" t="s">
         <v>14</v>
@@ -11555,10 +11555,10 @@
         <v>48</v>
       </c>
       <c r="K110" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L110" t="s">
-        <v>471</v>
+        <v>1047</v>
       </c>
       <c r="M110" t="s">
         <v>1048</v>
@@ -11583,7 +11583,7 @@
         <v>14</v>
       </c>
       <c r="T110" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:20">
@@ -11612,7 +11612,7 @@
         <v>1056</v>
       </c>
       <c r="I111" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J111" t="s">
         <v>9</v>
@@ -11634,19 +11634,19 @@
         <v>0</v>
       </c>
       <c r="P111" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q111" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R111" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S111" t="s">
         <v>8</v>
       </c>
       <c r="T111" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:20">
@@ -11675,7 +11675,7 @@
         <v>1064</v>
       </c>
       <c r="I112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J112" t="s">
         <v>9</v>
@@ -11697,19 +11697,19 @@
         <v>0</v>
       </c>
       <c r="P112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R112" t="s">
         <v>8</v>
       </c>
       <c r="S112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T112" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:20">
@@ -11738,7 +11738,7 @@
         <v>1071</v>
       </c>
       <c r="I113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J113" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>95</v>
       </c>
       <c r="M113" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N113" t="s">
         <v>97</v>
@@ -11760,19 +11760,19 @@
         <v>0</v>
       </c>
       <c r="P113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T113" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" spans="1:20">
@@ -11832,10 +11832,10 @@
         <v>8</v>
       </c>
       <c r="S114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T114" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:20">
@@ -11879,7 +11879,7 @@
         <v>1088</v>
       </c>
       <c r="N115" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O115" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80547_rutland", ".\export_data\inspection_reports\80547_rutland")</f>
@@ -11898,7 +11898,7 @@
         <v>8</v>
       </c>
       <c r="T115" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="1:20">
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q116" t="s">
         <v>8</v>
@@ -11958,10 +11958,10 @@
         <v>8</v>
       </c>
       <c r="S116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T116" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="117" spans="1:20">
@@ -12059,7 +12059,7 @@
         <v>48</v>
       </c>
       <c r="K118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L118" t="s">
         <v>1115</v>
@@ -12087,7 +12087,7 @@
         <v>8</v>
       </c>
       <c r="T118" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:20">
@@ -12144,13 +12144,13 @@
         <v>8</v>
       </c>
       <c r="R119" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S119" t="s">
         <v>8</v>
       </c>
       <c r="T119" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="1:20">
@@ -12179,7 +12179,7 @@
         <v>1131</v>
       </c>
       <c r="I120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J120" t="s">
         <v>48</v>
@@ -12201,19 +12201,19 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S120" t="s">
         <v>8</v>
       </c>
       <c r="T120" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" spans="1:20">
@@ -12242,22 +12242,22 @@
         <v>1138</v>
       </c>
       <c r="I121" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="J121" t="s">
         <v>48</v>
       </c>
       <c r="K121" t="s">
-        <v>24</v>
+        <v>617</v>
       </c>
       <c r="L121" t="s">
-        <v>471</v>
+        <v>361</v>
       </c>
       <c r="M121" t="s">
-        <v>1048</v>
+        <v>362</v>
       </c>
       <c r="N121" t="s">
-        <v>1049</v>
+        <v>363</v>
       </c>
       <c r="O121" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80553_slough", ".\export_data\inspection_reports\80553_slough")</f>
@@ -12267,16 +12267,16 @@
         <v>189</v>
       </c>
       <c r="Q121" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="R121" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="S121" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="T121" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:20">
@@ -12320,7 +12320,7 @@
         <v>768</v>
       </c>
       <c r="N122" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="O122" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80554_solihull", ".\export_data\inspection_reports\80554_solihull")</f>
@@ -12339,7 +12339,7 @@
         <v>8</v>
       </c>
       <c r="T122" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="123" spans="1:20">
@@ -12368,7 +12368,7 @@
         <v>1152</v>
       </c>
       <c r="I123" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J123" t="s">
         <v>9</v>
@@ -12402,7 +12402,7 @@
         <v>8</v>
       </c>
       <c r="T123" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:20">
@@ -12443,10 +12443,10 @@
         <v>661</v>
       </c>
       <c r="M124" t="s">
+        <v>442</v>
+      </c>
+      <c r="N124" t="s">
         <v>443</v>
-      </c>
-      <c r="N124" t="s">
-        <v>444</v>
       </c>
       <c r="O124" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80556_south gloucestershire", ".\export_data\inspection_reports\80556_south gloucestershire")</f>
@@ -12494,7 +12494,7 @@
         <v>1166</v>
       </c>
       <c r="I125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J125" t="s">
         <v>48</v>
@@ -12525,10 +12525,10 @@
         <v>8</v>
       </c>
       <c r="S125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T125" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126" spans="1:20">
@@ -12563,7 +12563,7 @@
         <v>48</v>
       </c>
       <c r="K126" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L126" t="s">
         <v>1177</v>
@@ -12579,7 +12579,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q126" t="s">
         <v>8</v>
@@ -12591,7 +12591,7 @@
         <v>8</v>
       </c>
       <c r="T126" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:20">
@@ -12626,7 +12626,7 @@
         <v>48</v>
       </c>
       <c r="K127" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L127" t="s">
         <v>634</v>
@@ -12654,7 +12654,7 @@
         <v>8</v>
       </c>
       <c r="T127" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:20">
@@ -12717,7 +12717,7 @@
         <v>8</v>
       </c>
       <c r="T128" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="129" spans="1:20">
@@ -12780,7 +12780,7 @@
         <v>14</v>
       </c>
       <c r="T129" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130" spans="1:20">
@@ -12815,7 +12815,7 @@
         <v>48</v>
       </c>
       <c r="K130" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L130" t="s">
         <v>886</v>
@@ -12843,7 +12843,7 @@
         <v>8</v>
       </c>
       <c r="T130" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="131" spans="1:20">
@@ -13032,7 +13032,7 @@
         <v>14</v>
       </c>
       <c r="T133" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="134" spans="1:20">
@@ -13061,13 +13061,13 @@
         <v>1241</v>
       </c>
       <c r="I134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J134" t="s">
         <v>9</v>
       </c>
       <c r="K134" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L134" t="s">
         <v>140</v>
@@ -13083,13 +13083,13 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S134" t="s">
         <v>8</v>
@@ -13158,7 +13158,7 @@
         <v>8</v>
       </c>
       <c r="T135" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="136" spans="1:20">
@@ -13221,7 +13221,7 @@
         <v>14</v>
       </c>
       <c r="T136" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" spans="1:20">
@@ -13262,7 +13262,7 @@
         <v>752</v>
       </c>
       <c r="M137" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N137" t="s">
         <v>1264</v>
@@ -13313,7 +13313,7 @@
         <v>1271</v>
       </c>
       <c r="I138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J138" t="s">
         <v>9</v>
@@ -13328,26 +13328,26 @@
         <v>555</v>
       </c>
       <c r="N138" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O138" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80570_telford &amp; wrekin", ".\export_data\inspection_reports\80570_telford &amp; wrekin")</f>
         <v>0</v>
       </c>
       <c r="P138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q138" t="s">
         <v>8</v>
       </c>
       <c r="R138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T138" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="139" spans="1:20">
@@ -13376,7 +13376,7 @@
         <v>1279</v>
       </c>
       <c r="I139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J139" t="s">
         <v>9</v>
@@ -13398,19 +13398,19 @@
         <v>0</v>
       </c>
       <c r="P139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T139" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="140" spans="1:20">
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="T140" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" spans="1:20">
@@ -13502,7 +13502,7 @@
         <v>1296</v>
       </c>
       <c r="I141" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J141" t="s">
         <v>48</v>
@@ -13511,10 +13511,10 @@
         <v>1297</v>
       </c>
       <c r="L141" t="s">
+        <v>75</v>
+      </c>
+      <c r="M141" t="s">
         <v>76</v>
-      </c>
-      <c r="M141" t="s">
-        <v>77</v>
       </c>
       <c r="N141" t="s">
         <v>1298</v>
@@ -13565,7 +13565,7 @@
         <v>1305</v>
       </c>
       <c r="I142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J142" t="s">
         <v>9</v>
@@ -13587,19 +13587,19 @@
         <v>0</v>
       </c>
       <c r="P142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q142" t="s">
         <v>8</v>
       </c>
       <c r="R142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S142" t="s">
         <v>8</v>
       </c>
       <c r="T142" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="143" spans="1:20">
@@ -13634,13 +13634,13 @@
         <v>9</v>
       </c>
       <c r="K143" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L143" t="s">
+        <v>441</v>
+      </c>
+      <c r="M143" t="s">
         <v>442</v>
-      </c>
-      <c r="M143" t="s">
-        <v>443</v>
       </c>
       <c r="N143" t="s">
         <v>1313</v>
@@ -13650,19 +13650,19 @@
         <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q143" t="s">
         <v>8</v>
       </c>
       <c r="R143" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S143" t="s">
         <v>8</v>
       </c>
       <c r="T143" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="144" spans="1:20">
@@ -13788,7 +13788,7 @@
         <v>8</v>
       </c>
       <c r="T145" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="146" spans="1:20">
@@ -13817,7 +13817,7 @@
         <v>1340</v>
       </c>
       <c r="I146" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J146" t="s">
         <v>48</v>
@@ -13839,7 +13839,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q146" t="s">
         <v>8</v>
@@ -13851,7 +13851,7 @@
         <v>8</v>
       </c>
       <c r="T146" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" spans="1:20">
@@ -13958,7 +13958,7 @@
         <v>555</v>
       </c>
       <c r="N148" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O148" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2733698_westmorland and furness", ".\export_data\inspection_reports\2733698_westmorland and furness")</f>
@@ -13977,7 +13977,7 @@
         <v>14</v>
       </c>
       <c r="T148" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="149" spans="1:20">
@@ -14034,13 +14034,13 @@
         <v>14</v>
       </c>
       <c r="R149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T149" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="150" spans="1:20">
@@ -14069,13 +14069,13 @@
         <v>1371</v>
       </c>
       <c r="I150" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J150" t="s">
         <v>9</v>
       </c>
       <c r="K150" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L150" t="s">
         <v>1372</v>
@@ -14091,16 +14091,16 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q150" t="s">
         <v>8</v>
       </c>
       <c r="R150" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S150" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T150" t="s">
         <v>15</v>
@@ -14166,7 +14166,7 @@
         <v>14</v>
       </c>
       <c r="T151" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="152" spans="1:20">
@@ -14201,7 +14201,7 @@
         <v>48</v>
       </c>
       <c r="K152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L152" t="s">
         <v>1217</v>
@@ -14229,7 +14229,7 @@
         <v>14</v>
       </c>
       <c r="T152" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="1:20">
@@ -14286,13 +14286,13 @@
         <v>14</v>
       </c>
       <c r="R153" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S153" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T153" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="154" spans="1:20">
@@ -14355,7 +14355,7 @@
         <v>8</v>
       </c>
       <c r="T154" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
